--- a/coverage.xlsx
+++ b/coverage.xlsx
@@ -583,12 +583,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>86.9%</t>
+          <t>87.8%</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>83.6%</t>
         </is>
       </c>
     </row>
@@ -639,12 +639,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -680,14 +680,14 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>数据范围: 20261001 ~ 20261014</t>
+          <t>数据范围: 20261001 ~ 20261015</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>工作日: 10天, 周末: 4天</t>
+          <t>工作日: 11天, 周末: 4天</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U37"/>
+  <dimension ref="A1:V37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -754,6 +754,7 @@
     <col width="11" customWidth="1" min="19" max="19"/>
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -869,6 +870,11 @@
           <t>10-14(三)</t>
         </is>
       </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>10-15(四)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -895,25 +901,25 @@
         <v>10</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="L3" s="7" t="n">
@@ -946,6 +952,9 @@
       <c r="U3" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="V3" s="8" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -972,25 +981,25 @@
         <v>20</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>3</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="L4" s="8" t="n">
@@ -1023,6 +1032,9 @@
       <c r="U4" s="8" t="n">
         <v>25</v>
       </c>
+      <c r="V4" s="9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -1049,25 +1061,25 @@
         <v>19</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H5" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="I5" s="3" t="n">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="L5" s="8" t="n">
@@ -1100,6 +1112,9 @@
       <c r="U5" s="8" t="n">
         <v>40</v>
       </c>
+      <c r="V5" s="8" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1126,25 +1141,25 @@
         <v>15</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>217</v>
+        <v>260</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="L6" s="8" t="n">
@@ -1177,6 +1192,9 @@
       <c r="U6" s="8" t="n">
         <v>22</v>
       </c>
+      <c r="V6" s="8" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -1203,25 +1221,25 @@
         <v>15</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1083</v>
+        <v>1128</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="L7" s="8" t="n">
@@ -1254,6 +1272,9 @@
       <c r="U7" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="V7" s="8" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -1280,25 +1301,25 @@
         <v>15</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>257</v>
+        <v>282</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="L8" s="7" t="n">
@@ -1331,21 +1352,24 @@
       <c r="U8" s="8" t="n">
         <v>57</v>
       </c>
+      <c r="V8" s="8" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>8d319562e65849c3a6e08eb73472a032</t>
+          <t>973769778869174272</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>25-全天-居民区-鸡公煲门口</t>
+          <t>长江后街小区渗透</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1354,70 +1378,73 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>227</v>
+        <v>1333</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>70%</t>
-        </is>
-      </c>
-      <c r="L9" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="M9" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="N9" s="8" t="n">
+          <t>未配置</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>265</v>
+      </c>
+      <c r="M9" s="10" t="n">
+        <v>264</v>
+      </c>
+      <c r="N9" s="10" t="n">
+        <v>298</v>
+      </c>
+      <c r="O9" s="10" t="n">
+        <v>278</v>
+      </c>
+      <c r="P9" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q9" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="O9" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="P9" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="8" t="n">
-        <v>25</v>
+      <c r="R9" s="10" t="n">
+        <v>39</v>
       </c>
       <c r="S9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v>25</v>
+      <c r="T9" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="U9" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="V9" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>1090491857237020672</t>
+          <t>948393128847777792</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>太平北路华海大厦(太平北路)投放点A</t>
+          <t>30-工作日-全天-地铁-明故宫2渗透</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1427,186 +1454,192 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>8</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>637</v>
+        <v>571</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="L10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="7" t="n">
-        <v>0</v>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="M10" s="8" t="n">
+        <v>68</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="O10" s="8" t="n">
-        <v>90</v>
-      </c>
-      <c r="P10" s="8" t="n">
-        <v>39</v>
+        <v>65</v>
+      </c>
+      <c r="O10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="R10" s="8" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>139</v>
+        <v>91</v>
       </c>
       <c r="T10" s="8" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="U10" s="8" t="n">
-        <v>110</v>
+        <v>58</v>
+      </c>
+      <c r="V10" s="9" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>948393128847777792</t>
+          <t>8d319562e65849c3a6e08eb73472a032</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>30-工作日-全天-地铁-明故宫2渗透</t>
+          <t>25-全天-居民区-鸡公煲门口</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>午峰</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>563</v>
+        <v>252</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="L11" s="8" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="O11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="8" t="n">
-        <v>31</v>
+        <v>26</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="P11" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q11" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="S11" s="8" t="n">
-        <v>91</v>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="S11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="U11" s="8" t="n">
-        <v>58</v>
+        <v>25</v>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>732955980949151744</t>
+          <t>1090491857237020672</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-天润城地铁站1号口</t>
+          <t>太平北路华海大厦(太平北路)投放点A</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>早峰+晚峰+夜间</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>467</v>
+        <v>724</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="L12" s="7" t="n">
@@ -1616,116 +1649,122 @@
         <v>0</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="P12" s="8" t="n">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="S12" s="8" t="n">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="T12" s="8" t="n">
+        <v>87</v>
+      </c>
+      <c r="U12" s="8" t="n">
         <v>110</v>
       </c>
-      <c r="U12" s="8" t="n">
-        <v>39</v>
+      <c r="V12" s="8" t="n">
+        <v>87</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>0a832068l1lrine348sx5fpj3daxcqc9</t>
+          <t>732955980949151744</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>剪子巷51号华静家园西区投放点</t>
+          <t>25-晚峰-地铁站-天润城地铁站1号口</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>午峰+夜间</t>
+          <t>早峰+晚峰+夜间</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>932</v>
+        <v>536</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="L13" s="8" t="n">
-        <v>155</v>
+          <t>82%</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="M13" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="7" t="n">
-        <v>0</v>
+      <c r="N13" s="8" t="n">
+        <v>25</v>
       </c>
       <c r="O13" s="8" t="n">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="P13" s="8" t="n">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="Q13" s="8" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="R13" s="8" t="n">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="S13" s="8" t="n">
-        <v>157</v>
+        <v>36</v>
       </c>
       <c r="T13" s="8" t="n">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="U13" s="8" t="n">
-        <v>115</v>
+        <v>39</v>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>732951617602912256</t>
+          <t>0a832068l1lrine348sx5fpj3daxcqc9</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区瑞金路街道西安门地铁站投放点</t>
+          <t>剪子巷51号华静家园西区投放点</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1735,140 +1774,146 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>午峰+夜间</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>596</v>
+        <v>1009</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>122</v>
-      </c>
-      <c r="M14" s="8" t="n">
+        <v>155</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>83</v>
+      </c>
+      <c r="P14" s="8" t="n">
         <v>104</v>
       </c>
-      <c r="N14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="P14" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="Q14" s="8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="S14" s="8" t="n">
-        <v>37</v>
+        <v>157</v>
       </c>
       <c r="T14" s="8" t="n">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="U14" s="8" t="n">
-        <v>119</v>
+        <v>115</v>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v>77</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>973769778869174272</t>
+          <t>732951617602912256</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>长江后街小区渗透</t>
+          <t>南京市秦淮区瑞金路街道西安门地铁站投放点</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>午峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>9</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1333</v>
+        <v>660</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>未配置</t>
-        </is>
-      </c>
-      <c r="L15" s="10" t="n">
-        <v>265</v>
-      </c>
-      <c r="M15" s="10" t="n">
-        <v>264</v>
-      </c>
-      <c r="N15" s="10" t="n">
-        <v>298</v>
-      </c>
-      <c r="O15" s="10" t="n">
-        <v>278</v>
-      </c>
-      <c r="P15" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q15" s="10" t="n">
-        <v>26</v>
-      </c>
-      <c r="R15" s="10" t="n">
-        <v>39</v>
-      </c>
-      <c r="S15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="U15" s="10" t="n">
-        <v>42</v>
+          <t>82%</t>
+        </is>
+      </c>
+      <c r="L15" s="8" t="n">
+        <v>122</v>
+      </c>
+      <c r="M15" s="8" t="n">
+        <v>104</v>
+      </c>
+      <c r="N15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="P15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="R15" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="S15" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v>119</v>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1896,20 +1941,20 @@
         <v>0</v>
       </c>
       <c r="F16" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G16" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="H16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1443</v>
+        <v>1584</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -1947,6 +1992,9 @@
       <c r="U16" s="10" t="n">
         <v>167</v>
       </c>
+      <c r="V16" s="10" t="n">
+        <v>141</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -1973,25 +2021,25 @@
         <v>20</v>
       </c>
       <c r="F17" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G17" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="H17" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="H17" s="3" t="n">
-        <v>8</v>
-      </c>
       <c r="I17" s="3" t="n">
-        <v>963</v>
+        <v>1087</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="L17" s="7" t="n">
@@ -2024,6 +2072,9 @@
       <c r="U17" s="8" t="n">
         <v>195</v>
       </c>
+      <c r="V17" s="8" t="n">
+        <v>124</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -2050,25 +2101,25 @@
         <v>15</v>
       </c>
       <c r="F18" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G18" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G18" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="H18" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>1202</v>
+        <v>1320</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="L18" s="8" t="n">
@@ -2101,6 +2152,9 @@
       <c r="U18" s="8" t="n">
         <v>49</v>
       </c>
+      <c r="V18" s="8" t="n">
+        <v>118</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -2127,25 +2181,25 @@
         <v>20</v>
       </c>
       <c r="F19" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G19" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G19" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="H19" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>713</v>
+        <v>772</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="L19" s="8" t="n">
@@ -2178,6 +2232,9 @@
       <c r="U19" s="8" t="n">
         <v>97</v>
       </c>
+      <c r="V19" s="8" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -2204,25 +2261,25 @@
         <v>20</v>
       </c>
       <c r="F20" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G20" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G20" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="H20" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>572</v>
+        <v>649</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="L20" s="8" t="n">
@@ -2255,6 +2312,9 @@
       <c r="U20" s="8" t="n">
         <v>76</v>
       </c>
+      <c r="V20" s="8" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -2281,25 +2341,25 @@
         <v>19</v>
       </c>
       <c r="F21" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G21" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G21" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="H21" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>361</v>
+        <v>421</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="L21" s="8" t="n">
@@ -2332,6 +2392,9 @@
       <c r="U21" s="8" t="n">
         <v>50</v>
       </c>
+      <c r="V21" s="8" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -2358,16 +2421,16 @@
         <v>0</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>712</v>
+        <v>737</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2409,6 +2472,9 @@
       <c r="U22" s="10" t="n">
         <v>15</v>
       </c>
+      <c r="V22" s="10" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -2435,16 +2501,16 @@
         <v>0</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>710</v>
+        <v>941</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2486,6 +2552,9 @@
       <c r="U23" s="10" t="n">
         <v>126</v>
       </c>
+      <c r="V23" s="10" t="n">
+        <v>231</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -2512,16 +2581,16 @@
         <v>15</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>1209</v>
+        <v>1375</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2530,7 +2599,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="L24" s="9" t="n">
@@ -2563,6 +2632,9 @@
       <c r="U24" s="8" t="n">
         <v>213</v>
       </c>
+      <c r="V24" s="8" t="n">
+        <v>166</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -2589,16 +2661,16 @@
         <v>19</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>504</v>
+        <v>679</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2607,7 +2679,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="L25" s="8" t="n">
@@ -2640,6 +2712,9 @@
       <c r="U25" s="8" t="n">
         <v>90</v>
       </c>
+      <c r="V25" s="8" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -2666,16 +2741,16 @@
         <v>19</v>
       </c>
       <c r="F26" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H26" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G26" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="I26" s="3" t="n">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2684,7 +2759,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="L26" s="8" t="n">
@@ -2717,6 +2792,9 @@
       <c r="U26" s="8" t="n">
         <v>20</v>
       </c>
+      <c r="V26" s="8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -2743,16 +2821,16 @@
         <v>15</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>973</v>
+        <v>1148</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2794,6 +2872,9 @@
       <c r="U27" s="8" t="n">
         <v>203</v>
       </c>
+      <c r="V27" s="8" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -2820,16 +2901,16 @@
         <v>20</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>955</v>
+        <v>1102</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -2871,6 +2952,9 @@
       <c r="U28" s="8" t="n">
         <v>87</v>
       </c>
+      <c r="V28" s="8" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -2897,16 +2981,16 @@
         <v>15</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>608</v>
+        <v>705</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2948,6 +3032,9 @@
       <c r="U29" s="8" t="n">
         <v>80</v>
       </c>
+      <c r="V29" s="8" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -2974,16 +3061,16 @@
         <v>20</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2016</v>
+        <v>2091</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -3025,6 +3112,9 @@
       <c r="U30" s="8" t="n">
         <v>100</v>
       </c>
+      <c r="V30" s="8" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -3051,16 +3141,16 @@
         <v>19</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>884</v>
+        <v>951</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -3102,6 +3192,9 @@
       <c r="U31" s="8" t="n">
         <v>77</v>
       </c>
+      <c r="V31" s="8" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -3128,16 +3221,16 @@
         <v>19</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>951</v>
+        <v>1106</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -3179,6 +3272,9 @@
       <c r="U32" s="8" t="n">
         <v>175</v>
       </c>
+      <c r="V32" s="8" t="n">
+        <v>155</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -3205,16 +3301,16 @@
         <v>19</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>821</v>
+        <v>861</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -3256,6 +3352,9 @@
       <c r="U33" s="8" t="n">
         <v>108</v>
       </c>
+      <c r="V33" s="8" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -3282,16 +3381,16 @@
         <v>19</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>937</v>
+        <v>1000</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -3333,6 +3432,9 @@
       <c r="U34" s="8" t="n">
         <v>112</v>
       </c>
+      <c r="V34" s="8" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -3359,16 +3461,16 @@
         <v>20</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>2762</v>
+        <v>2854</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -3410,6 +3512,9 @@
       <c r="U35" s="8" t="n">
         <v>89</v>
       </c>
+      <c r="V35" s="8" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -3436,16 +3541,16 @@
         <v>20</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>1219</v>
+        <v>1294</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -3487,6 +3592,9 @@
       <c r="U36" s="8" t="n">
         <v>75</v>
       </c>
+      <c r="V36" s="8" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -3513,16 +3621,16 @@
         <v>20</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1008</v>
+        <v>1168</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -3563,6 +3671,9 @@
       </c>
       <c r="U37" s="8" t="n">
         <v>150</v>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -5810,7 +5921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U54"/>
+  <dimension ref="A1:V54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5834,6 +5945,7 @@
     <col width="11" customWidth="1" min="19" max="19"/>
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5949,6 +6061,11 @@
           <t>10-14(三)</t>
         </is>
       </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>10-15(四)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -5975,25 +6092,25 @@
         <v>20</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="I3" s="3" t="n">
-        <v>39</v>
+        <v>117</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="L3" s="7" t="n">
@@ -6026,6 +6143,9 @@
       <c r="U3" s="9" t="n">
         <v>12</v>
       </c>
+      <c r="V3" s="8" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -6052,25 +6172,25 @@
         <v>20</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H4" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="I4" s="3" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="L4" s="7" t="n">
@@ -6103,6 +6223,9 @@
       <c r="U4" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="V4" s="8" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -6129,25 +6252,25 @@
         <v>10</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="L5" s="7" t="n">
@@ -6180,6 +6303,9 @@
       <c r="U5" s="8" t="n">
         <v>12</v>
       </c>
+      <c r="V5" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -6206,25 +6332,25 @@
         <v>10</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="L6" s="7" t="n">
@@ -6257,6 +6383,9 @@
       <c r="U6" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="V6" s="8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -6283,25 +6412,25 @@
         <v>10</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="L7" s="7" t="n">
@@ -6334,6 +6463,9 @@
       <c r="U7" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="V7" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -6360,25 +6492,25 @@
         <v>10</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="L8" s="7" t="n">
@@ -6411,6 +6543,9 @@
       <c r="U8" s="8" t="n">
         <v>12</v>
       </c>
+      <c r="V8" s="8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -6437,25 +6572,25 @@
         <v>20</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H9" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H9" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="I9" s="3" t="n">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="L9" s="7" t="n">
@@ -6488,6 +6623,9 @@
       <c r="U9" s="8" t="n">
         <v>22</v>
       </c>
+      <c r="V9" s="8" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -6514,25 +6652,25 @@
         <v>10</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="L10" s="8" t="n">
@@ -6565,6 +6703,9 @@
       <c r="U10" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="V10" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -6591,25 +6732,25 @@
         <v>20</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>105</v>
+        <v>153</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="L11" s="9" t="n">
@@ -6642,6 +6783,9 @@
       <c r="U11" s="8" t="n">
         <v>24</v>
       </c>
+      <c r="V11" s="8" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -6668,25 +6812,25 @@
         <v>30</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>217</v>
+        <v>272</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="L12" s="7" t="n">
@@ -6719,6 +6863,9 @@
       <c r="U12" s="8" t="n">
         <v>54</v>
       </c>
+      <c r="V12" s="8" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -6745,25 +6892,25 @@
         <v>20</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H13" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="H13" s="3" t="n">
-        <v>6</v>
-      </c>
       <c r="I13" s="3" t="n">
-        <v>408</v>
+        <v>509</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="L13" s="8" t="n">
@@ -6796,6 +6943,9 @@
       <c r="U13" s="8" t="n">
         <v>95</v>
       </c>
+      <c r="V13" s="8" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -6822,25 +6972,25 @@
         <v>10</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G14" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="H14" s="3" t="n">
-        <v>6</v>
-      </c>
       <c r="I14" s="3" t="n">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="L14" s="8" t="n">
@@ -6873,6 +7023,9 @@
       <c r="U14" s="8" t="n">
         <v>12</v>
       </c>
+      <c r="V14" s="8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -6899,25 +7052,25 @@
         <v>10</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H15" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="H15" s="3" t="n">
-        <v>6</v>
-      </c>
       <c r="I15" s="3" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="L15" s="8" t="n">
@@ -6950,6 +7103,9 @@
       <c r="U15" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="V15" s="8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -6976,25 +7132,25 @@
         <v>10</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="L16" s="7" t="n">
@@ -7027,6 +7183,9 @@
       <c r="U16" s="8" t="n">
         <v>13</v>
       </c>
+      <c r="V16" s="8" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -7053,25 +7212,25 @@
         <v>10</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="L17" s="8" t="n">
@@ -7104,6 +7263,9 @@
       <c r="U17" s="8" t="n">
         <v>12</v>
       </c>
+      <c r="V17" s="8" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -7130,25 +7292,25 @@
         <v>10</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="L18" s="8" t="n">
@@ -7181,6 +7343,9 @@
       <c r="U18" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="V18" s="8" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -7207,25 +7372,25 @@
         <v>10</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="L19" s="8" t="n">
@@ -7258,6 +7423,9 @@
       <c r="U19" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="V19" s="8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -7284,25 +7452,25 @@
         <v>20</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="L20" s="8" t="n">
@@ -7335,6 +7503,9 @@
       <c r="U20" s="8" t="n">
         <v>66</v>
       </c>
+      <c r="V20" s="8" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -7361,25 +7532,25 @@
         <v>20</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>194</v>
+        <v>227</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="L21" s="9" t="n">
@@ -7412,6 +7583,9 @@
       <c r="U21" s="8" t="n">
         <v>32</v>
       </c>
+      <c r="V21" s="8" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -7438,25 +7612,25 @@
         <v>20</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>261</v>
+        <v>317</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="L22" s="7" t="n">
@@ -7489,6 +7663,9 @@
       <c r="U22" s="8" t="n">
         <v>22</v>
       </c>
+      <c r="V22" s="8" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -7515,25 +7692,25 @@
         <v>20</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>264</v>
+        <v>308</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="L23" s="9" t="n">
@@ -7566,6 +7743,9 @@
       <c r="U23" s="8" t="n">
         <v>44</v>
       </c>
+      <c r="V23" s="8" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -7592,25 +7772,25 @@
         <v>20</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>503</v>
+        <v>591</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="L24" s="7" t="n">
@@ -7643,6 +7823,9 @@
       <c r="U24" s="8" t="n">
         <v>87</v>
       </c>
+      <c r="V24" s="8" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -7669,25 +7852,25 @@
         <v>50</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G25" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H25" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="H25" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="I25" s="3" t="n">
-        <v>543</v>
+        <v>615</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="L25" s="7" t="n">
@@ -7720,6 +7903,9 @@
       <c r="U25" s="8" t="n">
         <v>55</v>
       </c>
+      <c r="V25" s="8" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -7746,25 +7932,25 @@
         <v>10</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="L26" s="7" t="n">
@@ -7797,6 +7983,9 @@
       <c r="U26" s="8" t="n">
         <v>12</v>
       </c>
+      <c r="V26" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -7823,25 +8012,25 @@
         <v>10</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="L27" s="8" t="n">
@@ -7874,6 +8063,9 @@
       <c r="U27" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="V27" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -7900,25 +8092,25 @@
         <v>10</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="L28" s="7" t="n">
@@ -7951,6 +8143,9 @@
       <c r="U28" s="8" t="n">
         <v>23</v>
       </c>
+      <c r="V28" s="8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -7977,25 +8172,25 @@
         <v>10</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="L29" s="8" t="n">
@@ -8028,6 +8223,9 @@
       <c r="U29" s="8" t="n">
         <v>13</v>
       </c>
+      <c r="V29" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -8054,25 +8252,25 @@
         <v>10</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>277</v>
+        <v>307</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="L30" s="8" t="n">
@@ -8105,6 +8303,9 @@
       <c r="U30" s="8" t="n">
         <v>20</v>
       </c>
+      <c r="V30" s="8" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -8131,25 +8332,25 @@
         <v>10</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="L31" s="7" t="n">
@@ -8182,6 +8383,9 @@
       <c r="U31" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="V31" s="8" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -8208,25 +8412,25 @@
         <v>20</v>
       </c>
       <c r="F32" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G32" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G32" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="H32" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>329</v>
+        <v>372</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="L32" s="8" t="n">
@@ -8259,6 +8463,9 @@
       <c r="U32" s="9" t="n">
         <v>11</v>
       </c>
+      <c r="V32" s="8" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -8285,25 +8492,25 @@
         <v>10</v>
       </c>
       <c r="F33" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G33" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G33" s="3" t="n">
+      <c r="H33" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="H33" s="3" t="n">
-        <v>8</v>
-      </c>
       <c r="I33" s="3" t="n">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="L33" s="8" t="n">
@@ -8336,6 +8543,9 @@
       <c r="U33" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="V33" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -8362,25 +8572,25 @@
         <v>10</v>
       </c>
       <c r="F34" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G34" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G34" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="H34" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>215</v>
+        <v>242</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="L34" s="8" t="n">
@@ -8413,6 +8623,9 @@
       <c r="U34" s="8" t="n">
         <v>26</v>
       </c>
+      <c r="V34" s="8" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -8439,25 +8652,25 @@
         <v>10</v>
       </c>
       <c r="F35" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G35" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G35" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="H35" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="L35" s="8" t="n">
@@ -8490,6 +8703,9 @@
       <c r="U35" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="V35" s="8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -8516,25 +8732,25 @@
         <v>10</v>
       </c>
       <c r="F36" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G36" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G36" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="H36" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="L36" s="8" t="n">
@@ -8567,6 +8783,9 @@
       <c r="U36" s="8" t="n">
         <v>12</v>
       </c>
+      <c r="V36" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -8593,16 +8812,16 @@
         <v>50</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>737</v>
+        <v>869</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -8611,7 +8830,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="L37" s="8" t="n">
@@ -8644,6 +8863,9 @@
       <c r="U37" s="8" t="n">
         <v>242</v>
       </c>
+      <c r="V37" s="8" t="n">
+        <v>132</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -8670,16 +8892,16 @@
         <v>30</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>545</v>
+        <v>658</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -8688,7 +8910,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="L38" s="8" t="n">
@@ -8721,6 +8943,9 @@
       <c r="U38" s="8" t="n">
         <v>83</v>
       </c>
+      <c r="V38" s="8" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -8747,16 +8972,16 @@
         <v>30</v>
       </c>
       <c r="F39" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H39" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G39" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="I39" s="3" t="n">
-        <v>2831</v>
+        <v>2892</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -8765,7 +8990,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="L39" s="8" t="n">
@@ -8798,6 +9023,9 @@
       <c r="U39" s="8" t="n">
         <v>168</v>
       </c>
+      <c r="V39" s="8" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -8824,16 +9052,16 @@
         <v>10</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>455</v>
+        <v>527</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -8875,6 +9103,9 @@
       <c r="U40" s="8" t="n">
         <v>24</v>
       </c>
+      <c r="V40" s="8" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -8901,16 +9132,16 @@
         <v>20</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>550</v>
+        <v>649</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -8952,6 +9183,9 @@
       <c r="U41" s="8" t="n">
         <v>58</v>
       </c>
+      <c r="V41" s="8" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -8978,16 +9212,16 @@
         <v>10</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>373</v>
+        <v>404</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -9029,6 +9263,9 @@
       <c r="U42" s="8" t="n">
         <v>36</v>
       </c>
+      <c r="V42" s="8" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -9055,16 +9292,16 @@
         <v>11</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>249</v>
+        <v>281</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -9106,6 +9343,9 @@
       <c r="U43" s="8" t="n">
         <v>23</v>
       </c>
+      <c r="V43" s="8" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -9132,16 +9372,16 @@
         <v>10</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -9183,6 +9423,9 @@
       <c r="U44" s="8" t="n">
         <v>14</v>
       </c>
+      <c r="V44" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -9209,16 +9452,16 @@
         <v>40</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>1196</v>
+        <v>1316</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -9260,6 +9503,9 @@
       <c r="U45" s="8" t="n">
         <v>155</v>
       </c>
+      <c r="V45" s="8" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -9286,16 +9532,16 @@
         <v>10</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -9337,6 +9583,9 @@
       <c r="U46" s="8" t="n">
         <v>12</v>
       </c>
+      <c r="V46" s="8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -9363,16 +9612,16 @@
         <v>10</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -9414,6 +9663,9 @@
       <c r="U47" s="8" t="n">
         <v>22</v>
       </c>
+      <c r="V47" s="8" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -9440,16 +9692,16 @@
         <v>20</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>506</v>
+        <v>558</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -9491,6 +9743,9 @@
       <c r="U48" s="8" t="n">
         <v>52</v>
       </c>
+      <c r="V48" s="8" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -9517,16 +9772,16 @@
         <v>20</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>2035</v>
+        <v>2105</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -9568,6 +9823,9 @@
       <c r="U49" s="8" t="n">
         <v>60</v>
       </c>
+      <c r="V49" s="8" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -9594,16 +9852,16 @@
         <v>10</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>618</v>
+        <v>678</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -9645,6 +9903,9 @@
       <c r="U50" s="8" t="n">
         <v>40</v>
       </c>
+      <c r="V50" s="8" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -9671,16 +9932,16 @@
         <v>60</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>3410</v>
+        <v>3883</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -9722,6 +9983,9 @@
       <c r="U51" s="8" t="n">
         <v>438</v>
       </c>
+      <c r="V51" s="8" t="n">
+        <v>473</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -9748,16 +10012,16 @@
         <v>10</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>712</v>
+        <v>762</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -9799,6 +10063,9 @@
       <c r="U52" s="8" t="n">
         <v>30</v>
       </c>
+      <c r="V52" s="8" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -9825,16 +10092,16 @@
         <v>10</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>2403</v>
+        <v>2463</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -9876,6 +10143,9 @@
       <c r="U53" s="8" t="n">
         <v>60</v>
       </c>
+      <c r="V53" s="8" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -9902,16 +10172,16 @@
         <v>10</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -9952,6 +10222,9 @@
       </c>
       <c r="U54" s="8" t="n">
         <v>33</v>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -13012,25 +13285,25 @@
         <v>4</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.6%</t>
         </is>
       </c>
     </row>
@@ -13047,20 +13320,20 @@
         <v>5</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>88.3%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -13082,25 +13355,25 @@
         <v>11</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>87.3%</t>
+          <t>88.4%</t>
         </is>
       </c>
     </row>
@@ -13117,25 +13390,25 @@
         <v>2</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -13152,25 +13425,25 @@
         <v>1</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
     </row>
@@ -13187,25 +13460,25 @@
         <v>2</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F8" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G8" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G8" s="3" t="n">
-        <v>15</v>
-      </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.3%</t>
         </is>
       </c>
     </row>
@@ -13222,25 +13495,25 @@
         <v>6</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>86.4%</t>
         </is>
       </c>
     </row>
@@ -13660,25 +13933,25 @@
         <v>10</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>94.5%</t>
         </is>
       </c>
     </row>
@@ -13695,25 +13968,25 @@
         <v>12</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>78.8%</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>59.8%</t>
         </is>
       </c>
     </row>
@@ -13730,25 +14003,25 @@
         <v>10</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>65.5%</t>
         </is>
       </c>
     </row>
@@ -13765,25 +14038,25 @@
         <v>11</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>85.5%</t>
+          <t>86.8%</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>86.0%</t>
         </is>
       </c>
     </row>
@@ -13800,25 +14073,25 @@
         <v>9</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>60.6%</t>
         </is>
       </c>
     </row>

--- a/coverage.xlsx
+++ b/coverage.xlsx
@@ -51,11 +51,11 @@
     </font>
     <font>
       <name val="微软雅黑"/>
+      <color rgb="00888888"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="微软雅黑"/>
-      <color rgb="00888888"/>
       <sz val="10"/>
     </font>
     <font>
@@ -94,17 +94,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00BDD7EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -126,12 +126,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -140,13 +140,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -583,12 +583,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>87.4%</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>84.7%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -639,12 +639,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>82.1%</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -680,14 +680,14 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>数据范围: 20261001 ~ 20261018</t>
+          <t>数据范围: 20261001 ~ 20261019</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>工作日: 12天, 周末: 6天</t>
+          <t>工作日: 13天, 周末: 6天</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W37"/>
+  <dimension ref="A1:X37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -756,6 +756,7 @@
     <col width="11" customWidth="1" min="21" max="21"/>
     <col width="11" customWidth="1" min="22" max="22"/>
     <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -881,6 +882,11 @@
           <t>10-16(五)</t>
         </is>
       </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>10-19(一)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -964,6 +970,11 @@
       <c r="W3" s="8" t="n">
         <v>52</v>
       </c>
+      <c r="X3" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -1017,7 +1028,7 @@
       <c r="M4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N4" s="9" t="n">
+      <c r="N4" s="10" t="n">
         <v>5</v>
       </c>
       <c r="O4" s="7" t="n">
@@ -1035,18 +1046,23 @@
       <c r="S4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T4" s="9" t="n">
+      <c r="T4" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U4" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="V4" s="9" t="n">
+      <c r="V4" s="10" t="n">
         <v>15</v>
       </c>
       <c r="W4" s="8" t="n">
         <v>25</v>
       </c>
+      <c r="X4" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -1073,7 +1089,7 @@
         <v>19</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>8</v>
@@ -1086,12 +1102,12 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="L5" s="8" t="n">
@@ -1109,7 +1125,7 @@
       <c r="P5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" s="9" t="n">
+      <c r="Q5" s="10" t="n">
         <v>10</v>
       </c>
       <c r="R5" s="8" t="n">
@@ -1130,6 +1146,9 @@
       <c r="W5" s="8" t="n">
         <v>25</v>
       </c>
+      <c r="X5" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1213,6 +1232,11 @@
       <c r="W6" s="8" t="n">
         <v>32</v>
       </c>
+      <c r="X6" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -1239,7 +1263,7 @@
         <v>15</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>9</v>
@@ -1252,12 +1276,12 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="L7" s="8" t="n">
@@ -1296,6 +1320,9 @@
       <c r="W7" s="8" t="n">
         <v>54</v>
       </c>
+      <c r="X7" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -1322,7 +1349,7 @@
         <v>15</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>9</v>
@@ -1335,12 +1362,12 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="L8" s="7" t="n">
@@ -1379,6 +1406,9 @@
       <c r="W8" s="8" t="n">
         <v>75</v>
       </c>
+      <c r="X8" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -1405,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>10</v>
@@ -1418,7 +1448,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -1426,218 +1456,227 @@
           <t>未配置</t>
         </is>
       </c>
-      <c r="L9" s="10" t="n">
+      <c r="L9" s="11" t="n">
         <v>265</v>
       </c>
-      <c r="M9" s="10" t="n">
+      <c r="M9" s="11" t="n">
         <v>264</v>
       </c>
-      <c r="N9" s="10" t="n">
+      <c r="N9" s="11" t="n">
         <v>298</v>
       </c>
-      <c r="O9" s="10" t="n">
+      <c r="O9" s="11" t="n">
         <v>278</v>
       </c>
-      <c r="P9" s="10" t="n">
+      <c r="P9" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="Q9" s="10" t="n">
+      <c r="Q9" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="R9" s="10" t="n">
+      <c r="R9" s="11" t="n">
         <v>39</v>
       </c>
       <c r="S9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T9" s="10" t="n">
+      <c r="T9" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="U9" s="10" t="n">
+      <c r="U9" s="11" t="n">
         <v>42</v>
       </c>
       <c r="V9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="W9" s="10" t="n">
+      <c r="W9" s="11" t="n">
         <v>150</v>
+      </c>
+      <c r="X9" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>948393128847777792</t>
+          <t>8d319562e65849c3a6e08eb73472a032</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>30-工作日-全天-地铁-明故宫2渗透</t>
+          <t>25-全天-居民区-鸡公煲门口</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>午峰</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>10</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>578</v>
+        <v>277</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="O10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="8" t="n">
-        <v>31</v>
+        <v>26</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="P10" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q10" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="R10" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="S10" s="8" t="n">
-        <v>91</v>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="S10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U10" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="V10" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="W10" s="9" t="n">
-        <v>7</v>
+        <v>25</v>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="W10" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="X10" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>8d319562e65849c3a6e08eb73472a032</t>
+          <t>0a832068l1lrine348sx5fpj3daxcqc9</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>25-全天-居民区-鸡公煲门口</t>
+          <t>剪子巷51号华静家园西区投放点</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>午峰</t>
+          <t>午峰+夜间</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>10</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>277</v>
+        <v>1065</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="L11" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="N11" s="8" t="n">
-        <v>26</v>
+        <v>155</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="P11" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q11" s="7" t="n">
-        <v>0</v>
+        <v>104</v>
+      </c>
+      <c r="Q11" s="8" t="n">
+        <v>80</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="S11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="9" t="n">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="S11" s="8" t="n">
+        <v>157</v>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v>138</v>
       </c>
       <c r="U11" s="8" t="n">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="W11" s="8" t="n">
-        <v>25</v>
+        <v>56</v>
+      </c>
+      <c r="X11" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>1090491857237020672</t>
+          <t>948393128847777792</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>太平北路华海大厦(太平北路)投放点A</t>
+          <t>30-工作日-全天-地铁-明故宫2渗透</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1647,11 +1686,11 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>12</v>
@@ -1660,10 +1699,10 @@
         <v>10</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>854</v>
+        <v>598</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1672,69 +1711,74 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="7" t="n">
-        <v>0</v>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>68</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="O12" s="8" t="n">
-        <v>90</v>
-      </c>
-      <c r="P12" s="8" t="n">
-        <v>39</v>
+        <v>65</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="S12" s="8" t="n">
-        <v>139</v>
+        <v>91</v>
       </c>
       <c r="T12" s="8" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="U12" s="8" t="n">
-        <v>110</v>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v>87</v>
-      </c>
-      <c r="W12" s="8" t="n">
-        <v>130</v>
+        <v>58</v>
+      </c>
+      <c r="V12" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="W12" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="X12" s="9" t="inlineStr">
+        <is>
+          <t>20☂</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>732955980949151744</t>
+          <t>1090491857237020672</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-天润城地铁站1号口</t>
+          <t>太平北路华海大厦(太平北路)投放点A</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>早峰+晚峰+夜间</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>12</v>
@@ -1746,7 +1790,7 @@
         <v>10</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>578</v>
+        <v>910</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1765,59 +1809,64 @@
         <v>0</v>
       </c>
       <c r="N13" s="8" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O13" s="8" t="n">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="P13" s="8" t="n">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="Q13" s="8" t="n">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="R13" s="8" t="n">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="S13" s="8" t="n">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="T13" s="8" t="n">
+        <v>87</v>
+      </c>
+      <c r="U13" s="8" t="n">
         <v>110</v>
       </c>
-      <c r="U13" s="8" t="n">
-        <v>39</v>
-      </c>
       <c r="V13" s="8" t="n">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="W13" s="8" t="n">
-        <v>42</v>
+        <v>130</v>
+      </c>
+      <c r="X13" s="9" t="inlineStr">
+        <is>
+          <t>56☂</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>0a832068l1lrine348sx5fpj3daxcqc9</t>
+          <t>732955980949151744</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>剪子巷51号华静家园西区投放点</t>
+          <t>25-晚峰-地铁站-天润城地铁站1号口</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>午峰+夜间</t>
+          <t>早峰+晚峰+夜间</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>12</v>
@@ -1829,7 +1878,7 @@
         <v>10</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1065</v>
+        <v>578</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1841,41 +1890,46 @@
           <t>83%</t>
         </is>
       </c>
-      <c r="L14" s="8" t="n">
-        <v>155</v>
+      <c r="L14" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="M14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N14" s="7" t="n">
-        <v>0</v>
+      <c r="N14" s="8" t="n">
+        <v>25</v>
       </c>
       <c r="O14" s="8" t="n">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="P14" s="8" t="n">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="S14" s="8" t="n">
-        <v>157</v>
+        <v>36</v>
       </c>
       <c r="T14" s="8" t="n">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="U14" s="8" t="n">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="V14" s="8" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="W14" s="8" t="n">
-        <v>56</v>
+        <v>42</v>
+      </c>
+      <c r="X14" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1912,7 +1966,7 @@
         <v>10</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>732</v>
+        <v>775</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1960,16 +2014,21 @@
       <c r="W15" s="8" t="n">
         <v>72</v>
       </c>
+      <c r="X15" s="9" t="inlineStr">
+        <is>
+          <t>43☂</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>684038567596433408</t>
+          <t>843996095354019840</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路公交站台</t>
+          <t>25-晚峰-地铁站-柳州东路2号口</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1979,80 +2038,83 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>早峰+晚峰</t>
+          <t>午峰+晚峰</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>11</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1749</v>
+        <v>1215</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>未配置</t>
-        </is>
-      </c>
-      <c r="L16" s="10" t="n">
-        <v>139</v>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="M16" s="10" t="n">
-        <v>161</v>
-      </c>
-      <c r="N16" s="10" t="n">
-        <v>106</v>
-      </c>
-      <c r="O16" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="P16" s="10" t="n">
-        <v>111</v>
-      </c>
-      <c r="Q16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="10" t="n">
-        <v>241</v>
-      </c>
-      <c r="S16" s="10" t="n">
-        <v>233</v>
-      </c>
-      <c r="T16" s="10" t="n">
-        <v>253</v>
-      </c>
-      <c r="U16" s="10" t="n">
-        <v>167</v>
-      </c>
-      <c r="V16" s="10" t="n">
-        <v>141</v>
-      </c>
-      <c r="W16" s="10" t="n">
-        <v>165</v>
+        <v>7</v>
+      </c>
+      <c r="N16" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O16" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="P16" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q16" s="8" t="n">
+        <v>185</v>
+      </c>
+      <c r="R16" s="8" t="n">
+        <v>142</v>
+      </c>
+      <c r="S16" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v>219</v>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v>195</v>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v>124</v>
+      </c>
+      <c r="W16" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="X16" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>843996095354019840</t>
+          <t>684038567596433408</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路2号口</t>
+          <t>25-晚峰-地铁站-柳州东路公交站台</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -2062,11 +2124,11 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>午峰+晚峰</t>
+          <t>早峰+晚峰</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>12</v>
@@ -2075,10 +2137,10 @@
         <v>11</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1215</v>
+        <v>1749</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -2087,44 +2149,49 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="N17" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O17" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="P17" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q17" s="8" t="n">
-        <v>185</v>
-      </c>
-      <c r="R17" s="8" t="n">
-        <v>142</v>
-      </c>
-      <c r="S17" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v>219</v>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v>195</v>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v>124</v>
-      </c>
-      <c r="W17" s="8" t="n">
-        <v>128</v>
+          <t>未配置</t>
+        </is>
+      </c>
+      <c r="L17" s="11" t="n">
+        <v>139</v>
+      </c>
+      <c r="M17" s="11" t="n">
+        <v>161</v>
+      </c>
+      <c r="N17" s="11" t="n">
+        <v>106</v>
+      </c>
+      <c r="O17" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="P17" s="11" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="11" t="n">
+        <v>241</v>
+      </c>
+      <c r="S17" s="11" t="n">
+        <v>233</v>
+      </c>
+      <c r="T17" s="11" t="n">
+        <v>253</v>
+      </c>
+      <c r="U17" s="11" t="n">
+        <v>167</v>
+      </c>
+      <c r="V17" s="11" t="n">
+        <v>141</v>
+      </c>
+      <c r="W17" s="11" t="n">
+        <v>165</v>
+      </c>
+      <c r="X17" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -2161,7 +2228,7 @@
         <v>11</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>1419</v>
+        <v>1429</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -2209,6 +2276,11 @@
       <c r="W18" s="8" t="n">
         <v>99</v>
       </c>
+      <c r="X18" s="9" t="inlineStr">
+        <is>
+          <t>10☂</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -2292,6 +2364,11 @@
       <c r="W19" s="8" t="n">
         <v>40</v>
       </c>
+      <c r="X19" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -2375,6 +2452,11 @@
       <c r="W20" s="8" t="n">
         <v>77</v>
       </c>
+      <c r="X20" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -2458,6 +2540,11 @@
       <c r="W21" s="8" t="n">
         <v>25</v>
       </c>
+      <c r="X21" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -2484,16 +2571,16 @@
         <v>0</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>856</v>
+        <v>881</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2505,41 +2592,44 @@
           <t>未配置</t>
         </is>
       </c>
-      <c r="L22" s="10" t="n">
+      <c r="L22" s="11" t="n">
         <v>175</v>
       </c>
-      <c r="M22" s="10" t="n">
+      <c r="M22" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="N22" s="10" t="n">
+      <c r="N22" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="O22" s="10" t="n">
+      <c r="O22" s="11" t="n">
         <v>197</v>
       </c>
-      <c r="P22" s="10" t="n">
+      <c r="P22" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="Q22" s="10" t="n">
+      <c r="Q22" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="R22" s="10" t="n">
+      <c r="R22" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="S22" s="10" t="n">
+      <c r="S22" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="T22" s="10" t="n">
+      <c r="T22" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="U22" s="10" t="n">
+      <c r="U22" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="V22" s="10" t="n">
+      <c r="V22" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="W22" s="10" t="n">
+      <c r="W22" s="11" t="n">
         <v>119</v>
+      </c>
+      <c r="X22" s="11" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -2576,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1181</v>
+        <v>1233</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2588,41 +2678,46 @@
           <t>未配置</t>
         </is>
       </c>
-      <c r="L23" s="10" t="n">
+      <c r="L23" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="M23" s="10" t="n">
+      <c r="M23" s="11" t="n">
         <v>56</v>
       </c>
-      <c r="N23" s="10" t="n">
+      <c r="N23" s="11" t="n">
         <v>53</v>
       </c>
-      <c r="O23" s="10" t="n">
+      <c r="O23" s="11" t="n">
         <v>123</v>
       </c>
-      <c r="P23" s="10" t="n">
+      <c r="P23" s="11" t="n">
         <v>62</v>
       </c>
-      <c r="Q23" s="10" t="n">
+      <c r="Q23" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="R23" s="10" t="n">
+      <c r="R23" s="11" t="n">
         <v>68</v>
       </c>
-      <c r="S23" s="10" t="n">
+      <c r="S23" s="11" t="n">
         <v>78</v>
       </c>
-      <c r="T23" s="10" t="n">
+      <c r="T23" s="11" t="n">
         <v>74</v>
       </c>
-      <c r="U23" s="10" t="n">
+      <c r="U23" s="11" t="n">
         <v>126</v>
       </c>
-      <c r="V23" s="10" t="n">
+      <c r="V23" s="11" t="n">
         <v>231</v>
       </c>
-      <c r="W23" s="10" t="n">
+      <c r="W23" s="11" t="n">
         <v>240</v>
+      </c>
+      <c r="X23" s="9" t="inlineStr">
+        <is>
+          <t>52☂</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -2659,7 +2754,7 @@
         <v>10</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>1643</v>
+        <v>1668</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2671,10 +2766,10 @@
           <t>83%</t>
         </is>
       </c>
-      <c r="L24" s="9" t="n">
+      <c r="L24" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="M24" s="9" t="n">
+      <c r="M24" s="10" t="n">
         <v>2</v>
       </c>
       <c r="N24" s="8" t="n">
@@ -2707,6 +2802,11 @@
       <c r="W24" s="8" t="n">
         <v>268</v>
       </c>
+      <c r="X24" s="9" t="inlineStr">
+        <is>
+          <t>25☂</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -2742,7 +2842,7 @@
         <v>10</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>753</v>
+        <v>769</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2757,7 +2857,7 @@
       <c r="L25" s="8" t="n">
         <v>53</v>
       </c>
-      <c r="M25" s="9" t="n">
+      <c r="M25" s="10" t="n">
         <v>4</v>
       </c>
       <c r="N25" s="8" t="n">
@@ -2775,7 +2875,7 @@
       <c r="R25" s="8" t="n">
         <v>72</v>
       </c>
-      <c r="S25" s="9" t="n">
+      <c r="S25" s="10" t="n">
         <v>6</v>
       </c>
       <c r="T25" s="8" t="n">
@@ -2790,6 +2890,11 @@
       <c r="W25" s="8" t="n">
         <v>74</v>
       </c>
+      <c r="X25" s="9" t="inlineStr">
+        <is>
+          <t>16☂</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -2846,7 +2951,7 @@
       <c r="N26" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="O26" s="9" t="n">
+      <c r="O26" s="10" t="n">
         <v>11</v>
       </c>
       <c r="P26" s="8" t="n">
@@ -2873,6 +2978,11 @@
       <c r="W26" s="8" t="n">
         <v>20</v>
       </c>
+      <c r="X26" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -2956,6 +3066,11 @@
       <c r="W27" s="8" t="n">
         <v>133</v>
       </c>
+      <c r="X27" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -2991,7 +3106,7 @@
         <v>12</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1247</v>
+        <v>1303</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -3039,6 +3154,11 @@
       <c r="W28" s="8" t="n">
         <v>145</v>
       </c>
+      <c r="X28" s="9" t="inlineStr">
+        <is>
+          <t>56☂</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -3074,7 +3194,7 @@
         <v>12</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>798</v>
+        <v>863</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -3122,6 +3242,11 @@
       <c r="W29" s="8" t="n">
         <v>93</v>
       </c>
+      <c r="X29" s="9" t="inlineStr">
+        <is>
+          <t>65☂</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -3157,7 +3282,7 @@
         <v>12</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2171</v>
+        <v>2252</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -3205,6 +3330,11 @@
       <c r="W30" s="8" t="n">
         <v>80</v>
       </c>
+      <c r="X30" s="9" t="inlineStr">
+        <is>
+          <t>81☂</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -3240,7 +3370,7 @@
         <v>12</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1019</v>
+        <v>1059</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -3288,6 +3418,11 @@
       <c r="W31" s="8" t="n">
         <v>68</v>
       </c>
+      <c r="X31" s="9" t="inlineStr">
+        <is>
+          <t>40☂</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -3323,7 +3458,7 @@
         <v>12</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1209</v>
+        <v>1233</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -3371,6 +3506,11 @@
       <c r="W32" s="8" t="n">
         <v>103</v>
       </c>
+      <c r="X32" s="9" t="inlineStr">
+        <is>
+          <t>24☂</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -3454,6 +3594,11 @@
       <c r="W33" s="8" t="n">
         <v>41</v>
       </c>
+      <c r="X33" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -3489,7 +3634,7 @@
         <v>12</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -3537,6 +3682,11 @@
       <c r="W34" s="8" t="n">
         <v>59</v>
       </c>
+      <c r="X34" s="9" t="inlineStr">
+        <is>
+          <t>4☂</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -3572,7 +3722,7 @@
         <v>12</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>2996</v>
+        <v>3066</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -3620,6 +3770,11 @@
       <c r="W35" s="8" t="n">
         <v>142</v>
       </c>
+      <c r="X35" s="9" t="inlineStr">
+        <is>
+          <t>70☂</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -3655,7 +3810,7 @@
         <v>12</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>1475</v>
+        <v>1500</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -3703,6 +3858,11 @@
       <c r="W36" s="8" t="n">
         <v>181</v>
       </c>
+      <c r="X36" s="9" t="inlineStr">
+        <is>
+          <t>25☂</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -3785,6 +3945,11 @@
       </c>
       <c r="W37" s="8" t="n">
         <v>200</v>
+      </c>
+      <c r="X37" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3960,7 +4125,7 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="L3" s="11" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -4092,7 +4257,7 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="L5" s="11" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>40☂</t>
         </is>
@@ -4159,10 +4324,10 @@
           <t>17%</t>
         </is>
       </c>
-      <c r="L6" s="9" t="n">
+      <c r="L6" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="M6" s="9" t="n">
+      <c r="M6" s="10" t="n">
         <v>13</v>
       </c>
       <c r="N6" s="8" t="n">
@@ -4224,7 +4389,7 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="L7" s="11" t="inlineStr">
+      <c r="L7" s="9" t="inlineStr">
         <is>
           <t>37☂</t>
         </is>
@@ -4241,7 +4406,7 @@
       <c r="P7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" s="11" t="inlineStr">
+      <c r="Q7" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -4423,7 +4588,7 @@
           <t>未配置</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="L10" s="9" t="inlineStr">
         <is>
           <t>17☂</t>
         </is>
@@ -4431,13 +4596,13 @@
       <c r="M10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N10" s="10" t="n">
+      <c r="N10" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="O10" s="10" t="n">
+      <c r="O10" s="11" t="n">
         <v>66</v>
       </c>
-      <c r="P10" s="10" t="n">
+      <c r="P10" s="11" t="n">
         <v>55</v>
       </c>
       <c r="Q10" s="7" t="n">
@@ -4490,7 +4655,7 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="L11" s="11" t="inlineStr">
+      <c r="L11" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -4507,7 +4672,7 @@
       <c r="P11" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="Q11" s="9" t="n">
+      <c r="Q11" s="10" t="n">
         <v>14</v>
       </c>
     </row>
@@ -4557,7 +4722,7 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="L12" s="11" t="inlineStr">
+      <c r="L12" s="9" t="inlineStr">
         <is>
           <t>5☂</t>
         </is>
@@ -4689,24 +4854,24 @@
           <t>未配置</t>
         </is>
       </c>
-      <c r="L14" s="11" t="inlineStr">
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>94☂</t>
         </is>
       </c>
-      <c r="M14" s="10" t="n">
+      <c r="M14" s="11" t="n">
         <v>146</v>
       </c>
-      <c r="N14" s="10" t="n">
+      <c r="N14" s="11" t="n">
         <v>236</v>
       </c>
-      <c r="O14" s="10" t="n">
+      <c r="O14" s="11" t="n">
         <v>26</v>
       </c>
       <c r="P14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" s="11" t="inlineStr">
+      <c r="Q14" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -4758,12 +4923,12 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="L15" s="11" t="inlineStr">
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
       </c>
-      <c r="M15" s="9" t="n">
+      <c r="M15" s="10" t="n">
         <v>10</v>
       </c>
       <c r="N15" s="8" t="n">
@@ -4775,7 +4940,7 @@
       <c r="P15" s="8" t="n">
         <v>49</v>
       </c>
-      <c r="Q15" s="11" t="inlineStr">
+      <c r="Q15" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -4827,7 +4992,7 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="L16" s="11" t="inlineStr">
+      <c r="L16" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -4838,13 +5003,13 @@
       <c r="N16" s="8" t="n">
         <v>80</v>
       </c>
-      <c r="O16" s="9" t="n">
+      <c r="O16" s="10" t="n">
         <v>14</v>
       </c>
       <c r="P16" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" s="11" t="inlineStr">
+      <c r="Q16" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -4896,7 +5061,7 @@
           <t>75%</t>
         </is>
       </c>
-      <c r="L17" s="11" t="inlineStr">
+      <c r="L17" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -4913,7 +5078,7 @@
       <c r="P17" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="Q17" s="11" t="inlineStr">
+      <c r="Q17" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -4965,7 +5130,7 @@
           <t>80%</t>
         </is>
       </c>
-      <c r="L18" s="11" t="inlineStr">
+      <c r="L18" s="9" t="inlineStr">
         <is>
           <t>15☂</t>
         </is>
@@ -5032,7 +5197,7 @@
           <t>80%</t>
         </is>
       </c>
-      <c r="L19" s="11" t="inlineStr">
+      <c r="L19" s="9" t="inlineStr">
         <is>
           <t>87☂</t>
         </is>
@@ -5099,7 +5264,7 @@
           <t>80%</t>
         </is>
       </c>
-      <c r="L20" s="11" t="inlineStr">
+      <c r="L20" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -5166,7 +5331,7 @@
           <t>80%</t>
         </is>
       </c>
-      <c r="L21" s="11" t="inlineStr">
+      <c r="L21" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -5233,24 +5398,24 @@
           <t>未配置</t>
         </is>
       </c>
-      <c r="L22" s="11" t="inlineStr">
+      <c r="L22" s="9" t="inlineStr">
         <is>
           <t>17☂</t>
         </is>
       </c>
-      <c r="M22" s="10" t="n">
+      <c r="M22" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="N22" s="10" t="n">
+      <c r="N22" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="O22" s="10" t="n">
+      <c r="O22" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="P22" s="10" t="n">
+      <c r="P22" s="11" t="n">
         <v>125</v>
       </c>
-      <c r="Q22" s="11" t="inlineStr">
+      <c r="Q22" s="9" t="inlineStr">
         <is>
           <t>100☂</t>
         </is>
@@ -5302,22 +5467,22 @@
           <t>未配置</t>
         </is>
       </c>
-      <c r="L23" s="10" t="n">
+      <c r="L23" s="11" t="n">
         <v>94</v>
       </c>
-      <c r="M23" s="10" t="n">
+      <c r="M23" s="11" t="n">
         <v>147</v>
       </c>
-      <c r="N23" s="10" t="n">
+      <c r="N23" s="11" t="n">
         <v>167</v>
       </c>
-      <c r="O23" s="10" t="n">
+      <c r="O23" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="P23" s="10" t="n">
+      <c r="P23" s="11" t="n">
         <v>225</v>
       </c>
-      <c r="Q23" s="10" t="n">
+      <c r="Q23" s="11" t="n">
         <v>20</v>
       </c>
     </row>
@@ -5367,22 +5532,22 @@
           <t>未配置</t>
         </is>
       </c>
-      <c r="L24" s="10" t="n">
+      <c r="L24" s="11" t="n">
         <v>252</v>
       </c>
-      <c r="M24" s="10" t="n">
+      <c r="M24" s="11" t="n">
         <v>208</v>
       </c>
-      <c r="N24" s="10" t="n">
+      <c r="N24" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="O24" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="P24" s="10" t="n">
+      <c r="O24" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="P24" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="Q24" s="10" t="n">
+      <c r="Q24" s="11" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5432,7 +5597,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="L25" s="11" t="inlineStr">
+      <c r="L25" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -5449,7 +5614,7 @@
       <c r="P25" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="Q25" s="11" t="inlineStr">
+      <c r="Q25" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -5501,7 +5666,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="L26" s="11" t="inlineStr">
+      <c r="L26" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -5518,7 +5683,7 @@
       <c r="P26" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="Q26" s="11" t="inlineStr">
+      <c r="Q26" s="9" t="inlineStr">
         <is>
           <t>25☂</t>
         </is>
@@ -5570,7 +5735,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="L27" s="11" t="inlineStr">
+      <c r="L27" s="9" t="inlineStr">
         <is>
           <t>24☂</t>
         </is>
@@ -5587,7 +5752,7 @@
       <c r="P27" s="8" t="n">
         <v>163</v>
       </c>
-      <c r="Q27" s="11" t="inlineStr">
+      <c r="Q27" s="9" t="inlineStr">
         <is>
           <t>46☂</t>
         </is>
@@ -5639,7 +5804,7 @@
           <t>80%</t>
         </is>
       </c>
-      <c r="L28" s="11" t="inlineStr">
+      <c r="L28" s="9" t="inlineStr">
         <is>
           <t>25☂</t>
         </is>
@@ -5656,7 +5821,7 @@
       <c r="P28" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="Q28" s="9" t="n">
+      <c r="Q28" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5706,7 +5871,7 @@
           <t>80%</t>
         </is>
       </c>
-      <c r="L29" s="11" t="inlineStr">
+      <c r="L29" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -5714,7 +5879,7 @@
       <c r="M29" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="N29" s="9" t="n">
+      <c r="N29" s="10" t="n">
         <v>5</v>
       </c>
       <c r="O29" s="8" t="n">
@@ -5773,7 +5938,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="L30" s="11" t="inlineStr">
+      <c r="L30" s="9" t="inlineStr">
         <is>
           <t>21☂</t>
         </is>
@@ -5840,7 +6005,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="L31" s="11" t="inlineStr">
+      <c r="L31" s="9" t="inlineStr">
         <is>
           <t>93☂</t>
         </is>
@@ -5907,7 +6072,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="L32" s="11" t="inlineStr">
+      <c r="L32" s="9" t="inlineStr">
         <is>
           <t>263☂</t>
         </is>
@@ -5974,7 +6139,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="L33" s="11" t="inlineStr">
+      <c r="L33" s="9" t="inlineStr">
         <is>
           <t>29☂</t>
         </is>
@@ -6041,7 +6206,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="L34" s="11" t="inlineStr">
+      <c r="L34" s="9" t="inlineStr">
         <is>
           <t>41☂</t>
         </is>
@@ -6108,7 +6273,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="L35" s="11" t="inlineStr">
+      <c r="L35" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -6175,7 +6340,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="L36" s="11" t="inlineStr">
+      <c r="L36" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -6272,7 +6437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W54"/>
+  <dimension ref="A1:X54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6298,6 +6463,7 @@
     <col width="11" customWidth="1" min="21" max="21"/>
     <col width="11" customWidth="1" min="22" max="22"/>
     <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6423,6 +6589,11 @@
           <t>10-16(五)</t>
         </is>
       </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>10-19(一)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -6497,7 +6668,7 @@
       <c r="T3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U3" s="9" t="n">
+      <c r="U3" s="10" t="n">
         <v>12</v>
       </c>
       <c r="V3" s="8" t="n">
@@ -6506,6 +6677,11 @@
       <c r="W3" s="8" t="n">
         <v>26</v>
       </c>
+      <c r="X3" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -6541,7 +6717,7 @@
         <v>3</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>99</v>
+        <v>143</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -6556,7 +6732,7 @@
       <c r="L4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M4" s="9" t="n">
+      <c r="M4" s="10" t="n">
         <v>11</v>
       </c>
       <c r="N4" s="7" t="n">
@@ -6589,6 +6765,11 @@
       <c r="W4" s="8" t="n">
         <v>33</v>
       </c>
+      <c r="X4" s="9" t="inlineStr">
+        <is>
+          <t>44☂</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -6672,6 +6853,11 @@
       <c r="W5" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="X5" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -6731,7 +6917,7 @@
       <c r="O6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="9" t="n">
+      <c r="P6" s="10" t="n">
         <v>2</v>
       </c>
       <c r="Q6" s="7" t="n">
@@ -6755,6 +6941,11 @@
       <c r="W6" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="X6" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -6838,6 +7029,11 @@
       <c r="W7" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="X7" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -6873,7 +7069,7 @@
         <v>5</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -6921,6 +7117,11 @@
       <c r="W8" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="X8" s="9" t="inlineStr">
+        <is>
+          <t>12☂</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -7004,6 +7205,11 @@
       <c r="W9" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="X9" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -7039,7 +7245,7 @@
         <v>7</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>224</v>
+        <v>258</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -7069,7 +7275,7 @@
       <c r="Q10" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="R10" s="9" t="n">
+      <c r="R10" s="10" t="n">
         <v>6</v>
       </c>
       <c r="S10" s="8" t="n">
@@ -7087,6 +7293,11 @@
       <c r="W10" s="8" t="n">
         <v>38</v>
       </c>
+      <c r="X10" s="9" t="inlineStr">
+        <is>
+          <t>34☂</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -7170,6 +7381,11 @@
       <c r="W11" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="X11" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -7217,16 +7433,16 @@
           <t>33%</t>
         </is>
       </c>
-      <c r="L12" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="M12" s="9" t="n">
+      <c r="L12" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="M12" s="10" t="n">
         <v>12</v>
       </c>
       <c r="N12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="9" t="n">
+      <c r="O12" s="10" t="n">
         <v>8</v>
       </c>
       <c r="P12" s="7" t="n">
@@ -7235,10 +7451,10 @@
       <c r="Q12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="R12" s="9" t="n">
+      <c r="R12" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="S12" s="9" t="n">
+      <c r="S12" s="10" t="n">
         <v>12</v>
       </c>
       <c r="T12" s="8" t="n">
@@ -7253,30 +7469,35 @@
       <c r="W12" s="8" t="n">
         <v>24</v>
       </c>
+      <c r="X12" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>0a8399c6l1lafj2jwu8mjgfk6ey4azv5</t>
+          <t>889717813217533952</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>翔凤路南京传媒学院(滨江校区)站点A</t>
+          <t>高新-高校-交院东门-全周-全天-50</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>午峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>12</v>
@@ -7285,10 +7506,10 @@
         <v>9</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>335</v>
+        <v>664</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -7297,69 +7518,74 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="9" t="n">
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="M13" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="O13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q13" s="9" t="n">
-        <v>22</v>
-      </c>
       <c r="R13" s="8" t="n">
-        <v>54</v>
-      </c>
-      <c r="S13" s="9" t="n">
-        <v>21</v>
+        <v>40</v>
+      </c>
+      <c r="S13" s="8" t="n">
+        <v>100</v>
       </c>
       <c r="T13" s="8" t="n">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="U13" s="8" t="n">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="V13" s="8" t="n">
-        <v>55</v>
+        <v>101</v>
       </c>
       <c r="W13" s="8" t="n">
-        <v>63</v>
+        <v>155</v>
+      </c>
+      <c r="X13" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>889717813217533952</t>
+          <t>889466722646794240</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>高新-高校-交院东门-全周-全天-50</t>
+          <t>胜太东路江宁供销商厦站点</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>李小凯</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>12</v>
@@ -7371,7 +7597,7 @@
         <v>8</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>664</v>
+        <v>109</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -7384,56 +7610,61 @@
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="N14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="7" t="n">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="N14" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="O14" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="P14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" s="9" t="n">
+      <c r="Q14" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="R14" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="S14" s="8" t="n">
-        <v>100</v>
+      <c r="R14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T14" s="8" t="n">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="U14" s="8" t="n">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="V14" s="8" t="n">
-        <v>101</v>
+        <v>12</v>
       </c>
       <c r="W14" s="8" t="n">
-        <v>155</v>
+        <v>10</v>
+      </c>
+      <c r="X14" s="9" t="inlineStr">
+        <is>
+          <t>11☂</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>889466722646794240</t>
+          <t>0a837fbbl1lcvvfvrrb6nbtsxdr5xk2w</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>胜太东路江宁供销商厦站点</t>
+          <t>天元东路辅路南京义乌小商品城站点H</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>李小凯</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -7454,7 +7685,7 @@
         <v>8</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>98</v>
+        <v>182</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -7467,51 +7698,56 @@
         </is>
       </c>
       <c r="L15" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="M15" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N15" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="O15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q15" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="R15" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="S15" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="O15" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="P15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="R15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v>12</v>
+      <c r="T15" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U15" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="V15" s="8" t="n">
         <v>12</v>
       </c>
       <c r="W15" s="8" t="n">
-        <v>10</v>
+        <v>24</v>
+      </c>
+      <c r="X15" s="9" t="inlineStr">
+        <is>
+          <t>24☂</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>0a837fbbl1lcvvfvrrb6nbtsxdr5xk2w</t>
+          <t>889935238642700288</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>天元东路辅路南京义乌小商品城站点H</t>
+          <t>南京市江宁区淳化街道博观路保利·梧桐语</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -7534,10 +7770,10 @@
         <v>9</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -7546,60 +7782,65 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L16" s="8" t="n">
-        <v>12</v>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="M16" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="O16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="8" t="n">
-        <v>24</v>
+        <v>13</v>
+      </c>
+      <c r="O16" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="P16" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="Q16" s="8" t="n">
         <v>12</v>
       </c>
       <c r="R16" s="8" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="S16" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="T16" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="T16" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="U16" s="7" t="n">
-        <v>0</v>
+      <c r="U16" s="8" t="n">
+        <v>13</v>
       </c>
       <c r="V16" s="8" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>24</v>
+        <v>13</v>
+      </c>
+      <c r="X16" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>889935238642700288</t>
+          <t>0a838d77l1lhvwurirt76tdpsj4f7z4m</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>南京市江宁区淳化街道博观路保利·梧桐语</t>
+          <t>龙昌路中南·上悦城站点A</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>李小凯</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -7620,7 +7861,7 @@
         <v>9</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -7632,52 +7873,57 @@
           <t>75%</t>
         </is>
       </c>
-      <c r="L17" s="7" t="n">
-        <v>0</v>
+      <c r="L17" s="8" t="n">
+        <v>11</v>
       </c>
       <c r="M17" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N17" s="8" t="n">
-        <v>13</v>
+      <c r="N17" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="O17" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="P17" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="P17" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="Q17" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="R17" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="R17" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="S17" s="8" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="T17" s="8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="U17" s="8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="W17" s="8" t="n">
-        <v>13</v>
+        <v>11</v>
+      </c>
+      <c r="X17" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>0a838d77l1lhvwurirt76tdpsj4f7z4m</t>
+          <t>1084739124625276928</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>龙昌路中南·上悦城站点A</t>
+          <t>骆村路骆村新寓A区站点A</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -7703,7 +7949,7 @@
         <v>9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -7721,14 +7967,14 @@
       <c r="M18" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N18" s="7" t="n">
-        <v>0</v>
+      <c r="N18" s="8" t="n">
+        <v>23</v>
       </c>
       <c r="O18" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="P18" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="P18" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="Q18" s="8" t="n">
         <v>10</v>
@@ -7737,113 +7983,121 @@
         <v>0</v>
       </c>
       <c r="S18" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T18" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="U18" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="U18" s="8" t="n">
-        <v>11</v>
-      </c>
       <c r="V18" s="8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W18" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="X18" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>1084739124625276928</t>
+          <t>0a8399c6l1lafj2jwu8mjgfk6ey4azv5</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>骆村路骆村新寓A区站点A</t>
+          <t>翔凤路南京传媒学院(滨江校区)站点A</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>李小凯</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>午峰</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="G19" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="H19" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>112</v>
+        <v>401</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="L19" s="8" t="n">
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="M19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="O19" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="P19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="R19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="8" t="n">
-        <v>12</v>
+      <c r="O19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q19" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="R19" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="S19" s="10" t="n">
+        <v>21</v>
       </c>
       <c r="T19" s="8" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="U19" s="8" t="n">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="V19" s="8" t="n">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="W19" s="8" t="n">
-        <v>11</v>
+        <v>63</v>
+      </c>
+      <c r="X19" s="8" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>0a8302d5l1lir2dxfqaeqgk2ktn2mjev</t>
+          <t>0a83a414l1lef7k2csswc8vwddi6uiwm</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>高新-高校-金科北门2-全周-全天-30</t>
+          <t>鹏山路东方·龙湖湾站点Z2</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -7860,83 +8114,86 @@
         <v>20</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>10</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
-        </is>
-      </c>
-      <c r="L20" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="M20" s="9" t="n">
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="L20" s="10" t="n">
         <v>11</v>
       </c>
+      <c r="M20" s="10" t="n">
+        <v>11</v>
+      </c>
       <c r="N20" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O20" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="P20" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q20" s="9" t="n">
+      <c r="O20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="R20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="T20" s="9" t="n">
-        <v>11</v>
+      <c r="Q20" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="R20" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="S20" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v>33</v>
       </c>
       <c r="U20" s="8" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="V20" s="8" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="W20" s="8" t="n">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="X20" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1lef7k2csswc8vwddi6uiwm</t>
+          <t>0a83266cl1lk3m5wqzw62amyv92hkd8u</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>鹏山路东方·龙湖湾站点Z2</t>
+          <t>吉印大道融信·铂岸中心站点</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
@@ -7952,7 +8209,7 @@
         <v>7</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>260</v>
+        <v>388</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -7964,57 +8221,62 @@
           <t>58%</t>
         </is>
       </c>
-      <c r="L21" s="9" t="n">
+      <c r="L21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="N21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="M21" s="9" t="n">
+      <c r="P21" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="N21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="9" t="n">
-        <v>11</v>
-      </c>
       <c r="Q21" s="8" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="R21" s="8" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="S21" s="8" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="T21" s="8" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="U21" s="8" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="V21" s="8" t="n">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="W21" s="8" t="n">
         <v>33</v>
       </c>
+      <c r="X21" s="9" t="inlineStr">
+        <is>
+          <t>38☂</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>0a83266cl1lk3m5wqzw62amyv92hkd8u</t>
+          <t>0a83e97al1lc2u39m23hpc95reridhru</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>吉印大道融信·铂岸中心站点</t>
+          <t>飞鹰路江苏诗奈德环境科技有限公司站点</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -8035,7 +8297,7 @@
         <v>7</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>350</v>
+        <v>385</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -8047,26 +8309,26 @@
           <t>58%</t>
         </is>
       </c>
-      <c r="L22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="9" t="n">
-        <v>19</v>
+      <c r="L22" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="M22" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N22" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O22" s="9" t="n">
+      <c r="O22" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="P22" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q22" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="P22" s="9" t="n">
+      <c r="R22" s="10" t="n">
         <v>11</v>
-      </c>
-      <c r="Q22" s="8" t="n">
-        <v>66</v>
-      </c>
-      <c r="R22" s="8" t="n">
-        <v>22</v>
       </c>
       <c r="S22" s="8" t="n">
         <v>55</v>
@@ -8075,24 +8337,29 @@
         <v>55</v>
       </c>
       <c r="U22" s="8" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="V22" s="8" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="W22" s="8" t="n">
-        <v>33</v>
+        <v>55</v>
+      </c>
+      <c r="X22" s="9" t="inlineStr">
+        <is>
+          <t>22☂</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>0a83e97al1lc2u39m23hpc95reridhru</t>
+          <t>0a8399del1lpatica57gdhs2ewi7n3bb</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>飞鹰路江苏诗奈德环境科技有限公司站点</t>
+          <t>景明大街南京工艺装备制造股份有限公司站点</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -8115,10 +8382,10 @@
         <v>10</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>363</v>
+        <v>712</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -8127,55 +8394,60 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>58%</t>
-        </is>
-      </c>
-      <c r="L23" s="9" t="n">
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="M23" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="O23" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="P23" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q23" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="P23" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="R23" s="9" t="n">
-        <v>11</v>
+      <c r="Q23" s="8" t="n">
+        <v>130</v>
+      </c>
+      <c r="R23" s="8" t="n">
+        <v>66</v>
       </c>
       <c r="S23" s="8" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="T23" s="8" t="n">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="U23" s="8" t="n">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="V23" s="8" t="n">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="W23" s="8" t="n">
         <v>55</v>
       </c>
+      <c r="X23" s="9" t="inlineStr">
+        <is>
+          <t>66☂</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>0a8399del1lpatica57gdhs2ewi7n3bb</t>
+          <t>0a837b0dl1lkxirtat6acfd4praab85m</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>景明大街南京工艺装备制造股份有限公司站点</t>
+          <t>兴城路弘阳禹州燕澜新苑站点B</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -8189,7 +8461,7 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>12</v>
@@ -8198,10 +8470,10 @@
         <v>10</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>646</v>
+        <v>774</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -8210,7 +8482,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L24" s="7" t="n">
@@ -8219,60 +8491,65 @@
       <c r="M24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N24" s="9" t="n">
-        <v>11</v>
+      <c r="N24" s="8" t="n">
+        <v>55</v>
       </c>
       <c r="O24" s="8" t="n">
-        <v>49</v>
-      </c>
-      <c r="P24" s="9" t="n">
-        <v>11</v>
+        <v>88</v>
+      </c>
+      <c r="P24" s="8" t="n">
+        <v>78</v>
       </c>
       <c r="Q24" s="8" t="n">
-        <v>130</v>
-      </c>
-      <c r="R24" s="8" t="n">
         <v>66</v>
       </c>
+      <c r="R24" s="10" t="n">
+        <v>38</v>
+      </c>
       <c r="S24" s="8" t="n">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="T24" s="8" t="n">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="U24" s="8" t="n">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="V24" s="8" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="W24" s="8" t="n">
-        <v>55</v>
+        <v>104</v>
+      </c>
+      <c r="X24" s="9" t="inlineStr">
+        <is>
+          <t>55☂</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>0a837b0dl1lkxirtat6acfd4praab85m</t>
+          <t>1158030571808550912</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>兴城路弘阳禹州燕澜新苑站点B</t>
+          <t>1号门</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>王兴星</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>12</v>
@@ -8281,10 +8558,10 @@
         <v>10</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>719</v>
+        <v>137</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -8293,65 +8570,70 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="L25" s="7" t="n">
-        <v>0</v>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="M25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="8" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="O25" s="8" t="n">
-        <v>88</v>
-      </c>
-      <c r="P25" s="8" t="n">
-        <v>78</v>
+        <v>13</v>
+      </c>
+      <c r="P25" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="Q25" s="8" t="n">
-        <v>66</v>
-      </c>
-      <c r="R25" s="9" t="n">
-        <v>38</v>
+        <v>11</v>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>11</v>
       </c>
       <c r="S25" s="8" t="n">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="T25" s="8" t="n">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="U25" s="8" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="V25" s="8" t="n">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="W25" s="8" t="n">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="X25" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>0a83e076l1lkwmm8yrm9y6xcfj5ha9z5</t>
+          <t>1158030563076009984</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>土山路东域城站点A</t>
+          <t>灵谷寺公园1</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>李小凯</t>
+          <t>王兴星</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>午峰+晚峰+夜间</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
@@ -8367,7 +8649,7 @@
         <v>10</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>118</v>
+        <v>441</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -8383,48 +8665,53 @@
         <v>0</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="N26" s="8" t="n">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="O26" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="P26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="8" t="n">
-        <v>12</v>
+        <v>129</v>
+      </c>
+      <c r="P26" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q26" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="R26" s="8" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="S26" s="8" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="T26" s="8" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="U26" s="8" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="V26" s="8" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="W26" s="8" t="n">
-        <v>11</v>
+        <v>24</v>
+      </c>
+      <c r="X26" s="9" t="inlineStr">
+        <is>
+          <t>10☂</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>1158030571808550912</t>
+          <t>1158030574945890304</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>1号门</t>
+          <t>灵谷寺2</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -8450,7 +8737,7 @@
         <v>10</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>137</v>
+        <v>465</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -8463,51 +8750,56 @@
         </is>
       </c>
       <c r="L27" s="8" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="M27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="8" t="n">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="O27" s="8" t="n">
+        <v>104</v>
+      </c>
+      <c r="P27" s="8" t="n">
+        <v>106</v>
+      </c>
+      <c r="Q27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="S27" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="U27" s="8" t="n">
         <v>13</v>
-      </c>
-      <c r="P27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="R27" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="S27" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v>10</v>
       </c>
       <c r="V27" s="8" t="n">
         <v>10</v>
       </c>
       <c r="W27" s="8" t="n">
-        <v>10</v>
+        <v>24</v>
+      </c>
+      <c r="X27" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>1158030563076009984</t>
+          <t>1222113693250682880</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>灵谷寺公园1</t>
+          <t>灵谷寺3</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -8517,7 +8809,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
@@ -8533,7 +8825,7 @@
         <v>10</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>431</v>
+        <v>338</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -8545,223 +8837,234 @@
           <t>83%</t>
         </is>
       </c>
-      <c r="L28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="8" t="n">
+      <c r="L28" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="M28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="O28" s="8" t="n">
+        <v>66</v>
+      </c>
+      <c r="P28" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="S28" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="U28" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="N28" s="8" t="n">
-        <v>80</v>
-      </c>
-      <c r="O28" s="8" t="n">
-        <v>129</v>
-      </c>
-      <c r="P28" s="8" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="8" t="n">
+      <c r="V28" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="S28" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v>20</v>
-      </c>
       <c r="W28" s="8" t="n">
-        <v>24</v>
+        <v>21</v>
+      </c>
+      <c r="X28" s="9" t="inlineStr">
+        <is>
+          <t>10☂</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>1158030574945890304</t>
+          <t>0a8302d5l1lir2dxfqaeqgk2ktn2mjev</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>灵谷寺2</t>
+          <t>高新-高校-金科北门2-全周-全天-30</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>王兴星</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>午峰</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>465</v>
+        <v>270</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="L29" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="M29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="8" t="n">
-        <v>57</v>
-      </c>
-      <c r="O29" s="8" t="n">
-        <v>104</v>
+        <v>55</v>
+      </c>
+      <c r="M29" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="P29" s="8" t="n">
-        <v>106</v>
-      </c>
-      <c r="Q29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="S29" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v>31</v>
+        <v>25</v>
+      </c>
+      <c r="Q29" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="R29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="T29" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="U29" s="8" t="n">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="V29" s="8" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="W29" s="8" t="n">
-        <v>24</v>
+        <v>35</v>
+      </c>
+      <c r="X29" s="10" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>1222113693250682880</t>
+          <t>0a83e076l1lkwmm8yrm9y6xcfj5ha9z5</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>灵谷寺3</t>
+          <t>土山路东域城站点A</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>王兴星</t>
+          <t>李小凯</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>午峰+晚峰+夜间</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
         <v>10</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G30" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="N30" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="O30" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="P30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="R30" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="S30" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="V30" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="W30" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="X30" s="8" t="n">
         <v>10</v>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="I30" s="3" t="n">
-        <v>328</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="L30" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="M30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="O30" s="8" t="n">
-        <v>66</v>
-      </c>
-      <c r="P30" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="S30" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="W30" s="8" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>0a835a71l1l3k4hsv7kqv4cjjbdf3smm</t>
+          <t>0a83ff7al1lumpmtrhu6whvwegs9i6ai</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>盛安大道南京富特莱数码科技实业有限公司站点</t>
+          <t>金箔路989号黄金海岸广场站点</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>李小凯</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -8773,161 +9076,167 @@
         <v>10</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G31" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="L31" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="M31" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="H31" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>296</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="L31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="N31" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="O31" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="P31" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="O31" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="P31" s="8" t="n">
-        <v>54</v>
-      </c>
       <c r="Q31" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="R31" s="8" t="n">
-        <v>22</v>
+        <v>11</v>
+      </c>
+      <c r="R31" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="S31" s="8" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="T31" s="8" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="U31" s="8" t="n">
         <v>11</v>
       </c>
       <c r="V31" s="8" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="W31" s="8" t="n">
-        <v>44</v>
+        <v>13</v>
+      </c>
+      <c r="X31" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>0a837fa4l1l27tpydpm8gjqn4qaqm6ef</t>
+          <t>0a835a71l1l3k4hsv7kqv4cjjbdf3smm</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>高新-商圈-中粮药膳鸡-全周-午晚高峰-30</t>
+          <t>盛安大道南京富特莱数码科技实业有限公司站点</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>午峰</t>
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>11</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>406</v>
+        <v>318</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="L32" s="8" t="n">
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="L32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="M32" s="8" t="n">
+      <c r="O32" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="N32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="8" t="n">
-        <v>36</v>
-      </c>
       <c r="P32" s="8" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="Q32" s="8" t="n">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="R32" s="8" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="S32" s="8" t="n">
-        <v>78</v>
-      </c>
-      <c r="T32" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="U32" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="U32" s="9" t="n">
-        <v>11</v>
-      </c>
       <c r="V32" s="8" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="W32" s="8" t="n">
-        <v>34</v>
+        <v>44</v>
+      </c>
+      <c r="X32" s="8" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>0a837fa4l1lv5e55p7dge7kmrvhzzvky</t>
+          <t>0a837fa4l1l27tpydpm8gjqn4qaqm6ef</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>东山--2</t>
+          <t>高新-商圈-中粮药膳鸡-全周-午晚高峰-30</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>李小凯</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -8936,7 +9245,7 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>12</v>
@@ -8945,10 +9254,10 @@
         <v>11</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>113</v>
+        <v>425</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -8957,65 +9266,70 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L33" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="M33" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="N33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="P33" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q33" s="8" t="n">
+        <v>82</v>
+      </c>
+      <c r="R33" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="S33" s="8" t="n">
+        <v>78</v>
+      </c>
+      <c r="T33" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="M33" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="8" t="n">
+      <c r="U33" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="O33" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="P33" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q33" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="R33" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="S33" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v>11</v>
-      </c>
       <c r="V33" s="8" t="n">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="W33" s="8" t="n">
-        <v>11</v>
+        <v>34</v>
+      </c>
+      <c r="X33" s="9" t="inlineStr">
+        <is>
+          <t>19☂</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>0a8399c6l1lyqmcfy95bgdbwqabrgty5</t>
+          <t>0a837fa4l1lv5e55p7dge7kmrvhzzvky</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>平泰街太平花苑站点</t>
+          <t>东山--2</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>李小凯</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
@@ -9028,72 +9342,77 @@
         <v>11</v>
       </c>
       <c r="H34" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>121</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="L34" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="I34" s="3" t="n">
-        <v>256</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>92%</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>92%</t>
-        </is>
-      </c>
-      <c r="L34" s="8" t="n">
-        <v>21</v>
-      </c>
       <c r="M34" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N34" s="8" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="O34" s="8" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="P34" s="8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q34" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="R34" s="8" t="n">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="R34" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="S34" s="8" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="T34" s="8" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="U34" s="8" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="V34" s="8" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="W34" s="8" t="n">
-        <v>14</v>
+        <v>11</v>
+      </c>
+      <c r="X34" s="9" t="inlineStr">
+        <is>
+          <t>8☂</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>0a83ff7al1lumpmtrhu6whvwegs9i6ai</t>
+          <t>0a8399c6l1lyqmcfy95bgdbwqabrgty5</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>金箔路989号黄金海岸广场站点</t>
+          <t>平泰街太平花苑站点</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>李小凯</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -9105,16 +9424,16 @@
         <v>10</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>138</v>
+        <v>270</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -9127,40 +9446,43 @@
         </is>
       </c>
       <c r="L35" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="M35" s="8" t="n">
-        <v>10</v>
+        <v>21</v>
+      </c>
+      <c r="M35" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N35" s="8" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="O35" s="8" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="Q35" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="R35" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="R35" s="8" t="n">
+        <v>14</v>
       </c>
       <c r="S35" s="8" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="T35" s="8" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="U35" s="8" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="V35" s="8" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="W35" s="8" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="X35" s="8" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="36">
@@ -9188,16 +9510,16 @@
         <v>10</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -9245,6 +9567,9 @@
       <c r="W36" s="8" t="n">
         <v>12</v>
       </c>
+      <c r="X36" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -9295,25 +9620,25 @@
       <c r="L37" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="M37" s="9" t="n">
+      <c r="M37" s="10" t="n">
         <v>36</v>
       </c>
       <c r="N37" s="8" t="n">
         <v>53</v>
       </c>
-      <c r="O37" s="9" t="n">
+      <c r="O37" s="10" t="n">
         <v>42</v>
       </c>
       <c r="P37" s="8" t="n">
         <v>53</v>
       </c>
-      <c r="Q37" s="9" t="n">
+      <c r="Q37" s="10" t="n">
         <v>34</v>
       </c>
       <c r="R37" s="8" t="n">
         <v>73</v>
       </c>
-      <c r="S37" s="9" t="n">
+      <c r="S37" s="10" t="n">
         <v>42</v>
       </c>
       <c r="T37" s="8" t="n">
@@ -9328,6 +9653,11 @@
       <c r="W37" s="8" t="n">
         <v>325</v>
       </c>
+      <c r="X37" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -9387,16 +9717,16 @@
       <c r="O38" s="8" t="n">
         <v>78</v>
       </c>
-      <c r="P38" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q38" s="9" t="n">
+      <c r="P38" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q38" s="10" t="n">
         <v>12</v>
       </c>
       <c r="R38" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="S38" s="9" t="n">
+      <c r="S38" s="10" t="n">
         <v>8</v>
       </c>
       <c r="T38" s="8" t="n">
@@ -9411,6 +9741,11 @@
       <c r="W38" s="8" t="n">
         <v>173</v>
       </c>
+      <c r="X38" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -9446,7 +9781,7 @@
         <v>11</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>3002</v>
+        <v>3012</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -9479,7 +9814,7 @@
       <c r="R39" s="8" t="n">
         <v>104</v>
       </c>
-      <c r="S39" s="9" t="n">
+      <c r="S39" s="10" t="n">
         <v>20</v>
       </c>
       <c r="T39" s="8" t="n">
@@ -9494,30 +9829,35 @@
       <c r="W39" s="8" t="n">
         <v>110</v>
       </c>
+      <c r="X39" s="9" t="inlineStr">
+        <is>
+          <t>10☂</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>0a836758l1lnzcr39623ggbxyhbddncg</t>
+          <t>0a83d79bl1lpdksp2k3xft245nxum95d</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>天元东路辅路南京义乌小商品城站点G</t>
+          <t>胜太西路辅路南京晨伟智慧医疗技术创新中心站点C</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>12</v>
@@ -9529,7 +9869,7 @@
         <v>12</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>551</v>
+        <v>745</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -9542,51 +9882,56 @@
         </is>
       </c>
       <c r="L40" s="8" t="n">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="O40" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="P40" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q40" s="8" t="n">
         <v>82</v>
       </c>
-      <c r="P40" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q40" s="8" t="n">
-        <v>24</v>
-      </c>
       <c r="R40" s="8" t="n">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="S40" s="8" t="n">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="T40" s="8" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="U40" s="8" t="n">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="V40" s="8" t="n">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="W40" s="8" t="n">
-        <v>24</v>
+        <v>70</v>
+      </c>
+      <c r="X40" s="9" t="inlineStr">
+        <is>
+          <t>26☂</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>0a83d79bl1lpdksp2k3xft245nxum95d</t>
+          <t>0a837fbbl1l2mga28qk2ua9idgju7ay3</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>胜太西路辅路南京晨伟智慧医疗技术创新中心站点C</t>
+          <t>胜太西路47号汇金新天地广场站点</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -9596,11 +9941,11 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰+晚峰</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>12</v>
@@ -9612,7 +9957,7 @@
         <v>12</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>719</v>
+        <v>492</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -9628,48 +9973,53 @@
         <v>33</v>
       </c>
       <c r="M41" s="8" t="n">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="N41" s="8" t="n">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="O41" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="P41" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q41" s="8" t="n">
+        <v>53</v>
+      </c>
+      <c r="R41" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="S41" s="8" t="n">
+        <v>63</v>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="W41" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="P41" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q41" s="8" t="n">
-        <v>82</v>
-      </c>
-      <c r="R41" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="S41" s="8" t="n">
-        <v>81</v>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v>99</v>
-      </c>
-      <c r="W41" s="8" t="n">
-        <v>70</v>
+      <c r="X41" s="9" t="inlineStr">
+        <is>
+          <t>33☂</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>0a837fbbl1l2mga28qk2ua9idgju7ay3</t>
+          <t>0a8327a1l1l2i45kzhd965ga45mfsnmd</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>胜太西路47号汇金新天地广场站点</t>
+          <t>胜太西路45号汇金新天地广场站点</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -9683,7 +10033,7 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>12</v>
@@ -9695,7 +10045,7 @@
         <v>12</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>459</v>
+        <v>312</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -9708,51 +10058,56 @@
         </is>
       </c>
       <c r="L42" s="8" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M42" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="N42" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="O42" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="P42" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q42" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="N42" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="O42" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="P42" s="8" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q42" s="8" t="n">
-        <v>53</v>
-      </c>
       <c r="R42" s="8" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="S42" s="8" t="n">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="T42" s="8" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="U42" s="8" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="V42" s="8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="W42" s="8" t="n">
-        <v>55</v>
+        <v>21</v>
+      </c>
+      <c r="X42" s="9" t="inlineStr">
+        <is>
+          <t>10☂</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>0a8327a1l1l2i45kzhd965ga45mfsnmd</t>
+          <t>0a8327a1l1l9znhti7amyny5jau6s88v</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>胜太西路45号汇金新天地广场站点</t>
+          <t>胜太西路天琪雅居站点</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -9762,80 +10117,85 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰+晚峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>247</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L43" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="I43" s="3" t="n">
-        <v>302</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L43" s="8" t="n">
-        <v>37</v>
-      </c>
       <c r="M43" s="8" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="N43" s="8" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="O43" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="P43" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q43" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="R43" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="S43" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="V43" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="P43" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q43" s="8" t="n">
-        <v>31</v>
-      </c>
-      <c r="R43" s="8" t="n">
-        <v>41</v>
-      </c>
-      <c r="S43" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v>32</v>
-      </c>
       <c r="W43" s="8" t="n">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="X43" s="9" t="inlineStr">
+        <is>
+          <t>13☂</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>0a8327a1l1l9znhti7amyny5jau6s88v</t>
+          <t>0a83f7a2l1l6vmcxbhqt6iytqih598fa</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>胜太西路天琪雅居站点</t>
+          <t>怡园路南京航空航天大学(将军路校区)站点Z</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -9849,7 +10209,7 @@
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F44" s="3" t="n">
         <v>12</v>
@@ -9861,7 +10221,7 @@
         <v>12</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>234</v>
+        <v>1471</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -9874,51 +10234,56 @@
         </is>
       </c>
       <c r="L44" s="8" t="n">
-        <v>11</v>
+        <v>124</v>
       </c>
       <c r="M44" s="8" t="n">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="N44" s="8" t="n">
-        <v>14</v>
+        <v>141</v>
       </c>
       <c r="O44" s="8" t="n">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="P44" s="8" t="n">
-        <v>19</v>
+        <v>186</v>
       </c>
       <c r="Q44" s="8" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="R44" s="8" t="n">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="S44" s="8" t="n">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="T44" s="8" t="n">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="U44" s="8" t="n">
-        <v>14</v>
+        <v>155</v>
       </c>
       <c r="V44" s="8" t="n">
-        <v>11</v>
+        <v>120</v>
       </c>
       <c r="W44" s="8" t="n">
-        <v>24</v>
+        <v>92</v>
+      </c>
+      <c r="X44" s="9" t="inlineStr">
+        <is>
+          <t>63☂</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>0a83f7a2l1l6vmcxbhqt6iytqih598fa</t>
+          <t>0a8327a1l1lvvssa38rf3eqprenmxv2y</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>怡园路南京航空航天大学(将军路校区)站点Z</t>
+          <t>胜太西路辅路南京航空航天大学(将军路校区)站点J</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -9928,11 +10293,11 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F45" s="3" t="n">
         <v>12</v>
@@ -9944,7 +10309,7 @@
         <v>12</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>1408</v>
+        <v>206</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -9957,51 +10322,56 @@
         </is>
       </c>
       <c r="L45" s="8" t="n">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="M45" s="8" t="n">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="N45" s="8" t="n">
-        <v>141</v>
+        <v>14</v>
       </c>
       <c r="O45" s="8" t="n">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="P45" s="8" t="n">
-        <v>186</v>
+        <v>26</v>
       </c>
       <c r="Q45" s="8" t="n">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="R45" s="8" t="n">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="S45" s="8" t="n">
-        <v>127</v>
+        <v>14</v>
       </c>
       <c r="T45" s="8" t="n">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="U45" s="8" t="n">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="V45" s="8" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="W45" s="8" t="n">
-        <v>92</v>
+        <v>11</v>
+      </c>
+      <c r="X45" s="9" t="inlineStr">
+        <is>
+          <t>14☂</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>0a8327a1l1lvvssa38rf3eqprenmxv2y</t>
+          <t>0a8399c6l1l4y8jhxjgrp6t9eecq3anb</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>胜太西路辅路南京航空航天大学(将军路校区)站点J</t>
+          <t>胜太路77-4号胜泰新寓站点</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -10027,7 +10397,7 @@
         <v>12</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>192</v>
+        <v>229</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -10040,56 +10410,61 @@
         </is>
       </c>
       <c r="L46" s="8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M46" s="8" t="n">
         <v>10</v>
       </c>
       <c r="N46" s="8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O46" s="8" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="P46" s="8" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="Q46" s="8" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="R46" s="8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="S46" s="8" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="T46" s="8" t="n">
         <v>11</v>
       </c>
       <c r="U46" s="8" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="V46" s="8" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="W46" s="8" t="n">
-        <v>11</v>
+        <v>31</v>
+      </c>
+      <c r="X46" s="9" t="inlineStr">
+        <is>
+          <t>10☂</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>0a8399c6l1l4y8jhxjgrp6t9eecq3anb</t>
+          <t>0a83933al1l9u8y6b894j6jxgvg9a7ye</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>胜太路77-4号胜泰新寓站点</t>
+          <t>锦文大道辅路龙湖·水晶郦城站点C</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -10098,7 +10473,7 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F47" s="3" t="n">
         <v>12</v>
@@ -10110,7 +10485,7 @@
         <v>12</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>219</v>
+        <v>656</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -10123,61 +10498,66 @@
         </is>
       </c>
       <c r="L47" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="M47" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="N47" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="M47" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="N47" s="8" t="n">
-        <v>10</v>
-      </c>
       <c r="O47" s="8" t="n">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="P47" s="8" t="n">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="Q47" s="8" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="R47" s="8" t="n">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="S47" s="8" t="n">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="T47" s="8" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="U47" s="8" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="V47" s="8" t="n">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="W47" s="8" t="n">
-        <v>31</v>
+        <v>56</v>
+      </c>
+      <c r="X47" s="9" t="inlineStr">
+        <is>
+          <t>42☂</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>0a83933al1l9u8y6b894j6jxgvg9a7ye</t>
+          <t>1158030569614929920</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>锦文大道辅路龙湖·水晶郦城站点C</t>
+          <t>海底世界站台</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>王兴星</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
@@ -10193,7 +10573,7 @@
         <v>12</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>614</v>
+        <v>2145</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -10206,51 +10586,56 @@
         </is>
       </c>
       <c r="L48" s="8" t="n">
-        <v>20</v>
+        <v>388</v>
       </c>
       <c r="M48" s="8" t="n">
-        <v>33</v>
+        <v>529</v>
       </c>
       <c r="N48" s="8" t="n">
-        <v>22</v>
+        <v>349</v>
       </c>
       <c r="O48" s="8" t="n">
-        <v>88</v>
+        <v>313</v>
       </c>
       <c r="P48" s="8" t="n">
-        <v>63</v>
+        <v>200</v>
       </c>
       <c r="Q48" s="8" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="R48" s="8" t="n">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="S48" s="8" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="T48" s="8" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="U48" s="8" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="V48" s="8" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="W48" s="8" t="n">
-        <v>56</v>
+        <v>40</v>
+      </c>
+      <c r="X48" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>1158030569614929920</t>
+          <t>1158030568570548224</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>海底世界站台</t>
+          <t>海底世界</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -10264,76 +10649,81 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>752</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L49" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M49" s="8" t="n">
+        <v>140</v>
+      </c>
+      <c r="N49" s="8" t="n">
+        <v>140</v>
+      </c>
+      <c r="O49" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="P49" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q49" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="H49" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="I49" s="3" t="n">
-        <v>2145</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L49" s="8" t="n">
-        <v>388</v>
-      </c>
-      <c r="M49" s="8" t="n">
-        <v>529</v>
-      </c>
-      <c r="N49" s="8" t="n">
-        <v>349</v>
-      </c>
-      <c r="O49" s="8" t="n">
-        <v>313</v>
-      </c>
-      <c r="P49" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q49" s="8" t="n">
-        <v>51</v>
-      </c>
       <c r="R49" s="8" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="S49" s="8" t="n">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="T49" s="8" t="n">
         <v>50</v>
       </c>
       <c r="U49" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="V49" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="V49" s="8" t="n">
-        <v>70</v>
-      </c>
       <c r="W49" s="8" t="n">
-        <v>40</v>
+        <v>53</v>
+      </c>
+      <c r="X49" s="9" t="inlineStr">
+        <is>
+          <t>21☂</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>1158030568570548224</t>
+          <t>1158030570667700224</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>海底世界</t>
+          <t>美龄宫</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -10347,7 +10737,7 @@
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F50" s="3" t="n">
         <v>12</v>
@@ -10359,7 +10749,7 @@
         <v>12</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>731</v>
+        <v>4467</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -10372,51 +10762,56 @@
         </is>
       </c>
       <c r="L50" s="8" t="n">
-        <v>50</v>
+        <v>441</v>
       </c>
       <c r="M50" s="8" t="n">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="N50" s="8" t="n">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="O50" s="8" t="n">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="P50" s="8" t="n">
-        <v>50</v>
+        <v>496</v>
       </c>
       <c r="Q50" s="8" t="n">
-        <v>20</v>
+        <v>258</v>
       </c>
       <c r="R50" s="8" t="n">
-        <v>15</v>
+        <v>471</v>
       </c>
       <c r="S50" s="8" t="n">
-        <v>23</v>
+        <v>426</v>
       </c>
       <c r="T50" s="8" t="n">
-        <v>50</v>
+        <v>462</v>
       </c>
       <c r="U50" s="8" t="n">
-        <v>40</v>
+        <v>438</v>
       </c>
       <c r="V50" s="8" t="n">
-        <v>60</v>
+        <v>473</v>
       </c>
       <c r="W50" s="8" t="n">
-        <v>53</v>
+        <v>452</v>
+      </c>
+      <c r="X50" s="9" t="inlineStr">
+        <is>
+          <t>132☂</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>1158030570667700224</t>
+          <t>1158025287508230144</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>美龄宫</t>
+          <t>3号门</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -10430,7 +10825,7 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="F51" s="3" t="n">
         <v>12</v>
@@ -10442,7 +10837,7 @@
         <v>12</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>4335</v>
+        <v>792</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -10455,51 +10850,56 @@
         </is>
       </c>
       <c r="L51" s="8" t="n">
-        <v>441</v>
+        <v>130</v>
       </c>
       <c r="M51" s="8" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="N51" s="8" t="n">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="O51" s="8" t="n">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="P51" s="8" t="n">
-        <v>496</v>
+        <v>10</v>
       </c>
       <c r="Q51" s="8" t="n">
-        <v>258</v>
+        <v>10</v>
       </c>
       <c r="R51" s="8" t="n">
-        <v>471</v>
+        <v>35</v>
       </c>
       <c r="S51" s="8" t="n">
-        <v>426</v>
+        <v>94</v>
       </c>
       <c r="T51" s="8" t="n">
-        <v>462</v>
+        <v>105</v>
       </c>
       <c r="U51" s="8" t="n">
-        <v>438</v>
+        <v>30</v>
       </c>
       <c r="V51" s="8" t="n">
-        <v>473</v>
+        <v>50</v>
       </c>
       <c r="W51" s="8" t="n">
-        <v>452</v>
+        <v>10</v>
+      </c>
+      <c r="X51" s="9" t="inlineStr">
+        <is>
+          <t>20☂</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>1158025287508230144</t>
+          <t>1158030573943451648</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>3号门</t>
+          <t>中山陵7号门</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -10525,7 +10925,7 @@
         <v>12</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>772</v>
+        <v>2543</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -10538,61 +10938,66 @@
         </is>
       </c>
       <c r="L52" s="8" t="n">
-        <v>130</v>
+        <v>715</v>
       </c>
       <c r="M52" s="8" t="n">
-        <v>155</v>
+        <v>442</v>
       </c>
       <c r="N52" s="8" t="n">
-        <v>94</v>
+        <v>493</v>
       </c>
       <c r="O52" s="8" t="n">
-        <v>49</v>
+        <v>330</v>
       </c>
       <c r="P52" s="8" t="n">
-        <v>10</v>
+        <v>162</v>
       </c>
       <c r="Q52" s="8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R52" s="8" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="S52" s="8" t="n">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="T52" s="8" t="n">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="U52" s="8" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="V52" s="8" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="W52" s="8" t="n">
-        <v>10</v>
+        <v>80</v>
+      </c>
+      <c r="X52" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>1158030573943451648</t>
+          <t>0a83a358l1lqdy2ba4s82zvgvr2zwiuj</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>中山陵7号门</t>
+          <t>严南路金辉禹洲金陵铭著站点A</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>王兴星</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
@@ -10608,7 +11013,7 @@
         <v>12</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>2543</v>
+        <v>348</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -10621,77 +11026,82 @@
         </is>
       </c>
       <c r="L53" s="8" t="n">
-        <v>715</v>
+        <v>20</v>
       </c>
       <c r="M53" s="8" t="n">
-        <v>442</v>
+        <v>11</v>
       </c>
       <c r="N53" s="8" t="n">
-        <v>493</v>
+        <v>33</v>
       </c>
       <c r="O53" s="8" t="n">
-        <v>330</v>
+        <v>10</v>
       </c>
       <c r="P53" s="8" t="n">
-        <v>162</v>
+        <v>21</v>
       </c>
       <c r="Q53" s="8" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="R53" s="8" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="S53" s="8" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="T53" s="8" t="n">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="U53" s="8" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="V53" s="8" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="W53" s="8" t="n">
-        <v>80</v>
+        <v>32</v>
+      </c>
+      <c r="X53" s="9" t="inlineStr">
+        <is>
+          <t>10☂</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>0a83a358l1lqdy2ba4s82zvgvr2zwiuj</t>
+          <t>0a836758l1lnzcr39623ggbxyhbddncg</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>严南路金辉禹洲金陵铭著站点A</t>
+          <t>天元东路辅路南京义乌小商品城站点G</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>午峰</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
         <v>10</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>338</v>
+        <v>563</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -10704,40 +11114,43 @@
         </is>
       </c>
       <c r="L54" s="8" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="M54" s="8" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="N54" s="8" t="n">
+        <v>106</v>
+      </c>
+      <c r="O54" s="8" t="n">
+        <v>82</v>
+      </c>
+      <c r="P54" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q54" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="R54" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="S54" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="O54" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="P54" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q54" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="R54" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="S54" s="8" t="n">
-        <v>52</v>
-      </c>
       <c r="T54" s="8" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="U54" s="8" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="V54" s="8" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="W54" s="8" t="n">
-        <v>32</v>
+        <v>24</v>
+      </c>
+      <c r="X54" s="8" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -10913,7 +11326,7 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="L3" s="11" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -10927,7 +11340,7 @@
       <c r="O3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P3" s="9" t="n">
+      <c r="P3" s="10" t="n">
         <v>4</v>
       </c>
       <c r="Q3" s="7" t="n">
@@ -10980,7 +11393,7 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="L4" s="11" t="inlineStr">
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -11047,7 +11460,7 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="L5" s="11" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>1☂</t>
         </is>
@@ -11114,7 +11527,7 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="L6" s="11" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -11131,7 +11544,7 @@
       <c r="P6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="9" t="n">
+      <c r="Q6" s="10" t="n">
         <v>11</v>
       </c>
     </row>
@@ -11181,7 +11594,7 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="L7" s="11" t="inlineStr">
+      <c r="L7" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -11248,7 +11661,7 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="L8" s="11" t="inlineStr">
+      <c r="L8" s="9" t="inlineStr">
         <is>
           <t>11☂</t>
         </is>
@@ -11315,7 +11728,7 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="L9" s="11" t="inlineStr">
+      <c r="L9" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -11329,10 +11742,10 @@
       <c r="O9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P9" s="9" t="n">
+      <c r="P9" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="Q9" s="9" t="n">
+      <c r="Q9" s="10" t="n">
         <v>12</v>
       </c>
     </row>
@@ -11382,7 +11795,7 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="L10" s="9" t="inlineStr">
         <is>
           <t>3☂</t>
         </is>
@@ -11390,10 +11803,10 @@
       <c r="M10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N10" s="9" t="n">
+      <c r="N10" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="O10" s="9" t="n">
+      <c r="O10" s="10" t="n">
         <v>4</v>
       </c>
       <c r="P10" s="8" t="n">
@@ -11449,12 +11862,12 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="L11" s="11" t="inlineStr">
+      <c r="L11" s="9" t="inlineStr">
         <is>
           <t>11☂</t>
         </is>
       </c>
-      <c r="M11" s="9" t="n">
+      <c r="M11" s="10" t="n">
         <v>8</v>
       </c>
       <c r="N11" s="7" t="n">
@@ -11516,7 +11929,7 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="L12" s="11" t="inlineStr">
+      <c r="L12" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -11583,7 +11996,7 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="L13" s="11" t="inlineStr">
+      <c r="L13" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -11650,7 +12063,7 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="L14" s="11" t="inlineStr">
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -11717,7 +12130,7 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="L15" s="11" t="inlineStr">
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -11784,7 +12197,7 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="L16" s="11" t="inlineStr">
+      <c r="L16" s="9" t="inlineStr">
         <is>
           <t>12☂</t>
         </is>
@@ -11866,7 +12279,7 @@
       <c r="P17" s="8" t="n">
         <v>77</v>
       </c>
-      <c r="Q17" s="9" t="n">
+      <c r="Q17" s="10" t="n">
         <v>11</v>
       </c>
     </row>
@@ -12046,7 +12459,7 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="L20" s="11" t="inlineStr">
+      <c r="L20" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -12063,7 +12476,7 @@
       <c r="P20" s="8" t="n">
         <v>217</v>
       </c>
-      <c r="Q20" s="9" t="n">
+      <c r="Q20" s="10" t="n">
         <v>49</v>
       </c>
     </row>
@@ -12113,7 +12526,7 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="L21" s="11" t="inlineStr">
+      <c r="L21" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -12130,7 +12543,7 @@
       <c r="P21" s="8" t="n">
         <v>61</v>
       </c>
-      <c r="Q21" s="9" t="n">
+      <c r="Q21" s="10" t="n">
         <v>13</v>
       </c>
     </row>
@@ -12180,7 +12593,7 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="L22" s="11" t="inlineStr">
+      <c r="L22" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -12191,7 +12604,7 @@
       <c r="N22" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="O22" s="9" t="n">
+      <c r="O22" s="10" t="n">
         <v>11</v>
       </c>
       <c r="P22" s="8" t="n">
@@ -12247,12 +12660,12 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="L23" s="11" t="inlineStr">
+      <c r="L23" s="9" t="inlineStr">
         <is>
           <t>10☂</t>
         </is>
       </c>
-      <c r="M23" s="9" t="n">
+      <c r="M23" s="10" t="n">
         <v>11</v>
       </c>
       <c r="N23" s="8" t="n">
@@ -12314,7 +12727,7 @@
           <t>80%</t>
         </is>
       </c>
-      <c r="L24" s="11" t="inlineStr">
+      <c r="L24" s="9" t="inlineStr">
         <is>
           <t>11☂</t>
         </is>
@@ -12381,7 +12794,7 @@
           <t>80%</t>
         </is>
       </c>
-      <c r="L25" s="11" t="inlineStr">
+      <c r="L25" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -12448,7 +12861,7 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="L26" s="9" t="n">
+      <c r="L26" s="10" t="n">
         <v>11</v>
       </c>
       <c r="M26" s="7" t="n">
@@ -12463,7 +12876,7 @@
       <c r="P26" s="8" t="n">
         <v>86</v>
       </c>
-      <c r="Q26" s="9" t="n">
+      <c r="Q26" s="10" t="n">
         <v>10</v>
       </c>
     </row>
@@ -12513,7 +12926,7 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="L27" s="9" t="n">
+      <c r="L27" s="10" t="n">
         <v>11</v>
       </c>
       <c r="M27" s="7" t="n">
@@ -12522,7 +12935,7 @@
       <c r="N27" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="O27" s="9" t="n">
+      <c r="O27" s="10" t="n">
         <v>17</v>
       </c>
       <c r="P27" s="8" t="n">
@@ -12643,7 +13056,7 @@
           <t>80%</t>
         </is>
       </c>
-      <c r="L29" s="11" t="inlineStr">
+      <c r="L29" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -12654,7 +13067,7 @@
       <c r="N29" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="O29" s="9" t="n">
+      <c r="O29" s="10" t="n">
         <v>11</v>
       </c>
       <c r="P29" s="8" t="n">
@@ -12710,12 +13123,12 @@
           <t>80%</t>
         </is>
       </c>
-      <c r="L30" s="11" t="inlineStr">
+      <c r="L30" s="9" t="inlineStr">
         <is>
           <t>51☂</t>
         </is>
       </c>
-      <c r="M30" s="9" t="n">
+      <c r="M30" s="10" t="n">
         <v>33</v>
       </c>
       <c r="N30" s="8" t="n">
@@ -12777,7 +13190,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="L31" s="11" t="inlineStr">
+      <c r="L31" s="9" t="inlineStr">
         <is>
           <t>6☂</t>
         </is>
@@ -12794,7 +13207,7 @@
       <c r="P31" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="Q31" s="11" t="inlineStr">
+      <c r="Q31" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -12846,7 +13259,7 @@
           <t>80%</t>
         </is>
       </c>
-      <c r="L32" s="11" t="inlineStr">
+      <c r="L32" s="9" t="inlineStr">
         <is>
           <t>30☂</t>
         </is>
@@ -12863,7 +13276,7 @@
       <c r="P32" s="8" t="n">
         <v>43</v>
       </c>
-      <c r="Q32" s="9" t="n">
+      <c r="Q32" s="10" t="n">
         <v>9</v>
       </c>
     </row>
@@ -12913,7 +13326,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="L33" s="11" t="inlineStr">
+      <c r="L33" s="9" t="inlineStr">
         <is>
           <t>11☂</t>
         </is>
@@ -12980,7 +13393,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="L34" s="11" t="inlineStr">
+      <c r="L34" s="9" t="inlineStr">
         <is>
           <t>21☂</t>
         </is>
@@ -13047,7 +13460,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="L35" s="11" t="inlineStr">
+      <c r="L35" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -13114,7 +13527,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="L36" s="11" t="inlineStr">
+      <c r="L36" s="9" t="inlineStr">
         <is>
           <t>34☂</t>
         </is>
@@ -13181,7 +13594,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="L37" s="11" t="inlineStr">
+      <c r="L37" s="9" t="inlineStr">
         <is>
           <t>11☂</t>
         </is>
@@ -13248,7 +13661,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="L38" s="11" t="inlineStr">
+      <c r="L38" s="9" t="inlineStr">
         <is>
           <t>10☂</t>
         </is>
@@ -13315,7 +13728,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="L39" s="11" t="inlineStr">
+      <c r="L39" s="9" t="inlineStr">
         <is>
           <t>304☂</t>
         </is>
@@ -13382,7 +13795,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="L40" s="11" t="inlineStr">
+      <c r="L40" s="9" t="inlineStr">
         <is>
           <t>102☂</t>
         </is>
@@ -13449,7 +13862,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="L41" s="11" t="inlineStr">
+      <c r="L41" s="9" t="inlineStr">
         <is>
           <t>379☂</t>
         </is>
@@ -13516,7 +13929,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="L42" s="11" t="inlineStr">
+      <c r="L42" s="9" t="inlineStr">
         <is>
           <t>81☂</t>
         </is>
@@ -13583,7 +13996,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="L43" s="11" t="inlineStr">
+      <c r="L43" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -13650,7 +14063,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="L44" s="11" t="inlineStr">
+      <c r="L44" s="9" t="inlineStr">
         <is>
           <t>330☂</t>
         </is>
@@ -13717,7 +14130,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="L45" s="11" t="inlineStr">
+      <c r="L45" s="9" t="inlineStr">
         <is>
           <t>70☂</t>
         </is>
@@ -13784,7 +14197,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="L46" s="11" t="inlineStr">
+      <c r="L46" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -13851,7 +14264,7 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="L47" s="11" t="inlineStr">
+      <c r="L47" s="9" t="inlineStr">
         <is>
           <t>70☂</t>
         </is>
@@ -14094,10 +14507,10 @@
         <v>4</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>67</v>
@@ -14107,12 +14520,12 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>93.1%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>87.8%</t>
         </is>
       </c>
     </row>
@@ -14129,25 +14542,25 @@
         <v>5</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>49</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>80.3%</t>
         </is>
       </c>
     </row>
@@ -14164,10 +14577,10 @@
         <v>11</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>122</v>
@@ -14177,12 +14590,12 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>88.1%</t>
         </is>
       </c>
     </row>
@@ -14269,10 +14682,10 @@
         <v>2</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>21</v>
@@ -14282,12 +14695,12 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>76.0%</t>
         </is>
       </c>
     </row>
@@ -14304,10 +14717,10 @@
         <v>6</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>74</v>
@@ -14317,12 +14730,12 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>88.1%</t>
+          <t>86.0%</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>86.1%</t>
+          <t>84.9%</t>
         </is>
       </c>
     </row>
@@ -14742,16 +15155,16 @@
         <v>10</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -14777,25 +15190,25 @@
         <v>12</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>79.6%</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>61.9%</t>
         </is>
       </c>
     </row>
@@ -14812,20 +15225,20 @@
         <v>10</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -14882,25 +15295,25 @@
         <v>9</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>

--- a/coverage.xlsx
+++ b/coverage.xlsx
@@ -583,12 +583,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>87.4%</t>
+          <t>86.6%</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>82.4%</t>
         </is>
       </c>
     </row>
@@ -639,12 +639,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>74.5%</t>
         </is>
       </c>
     </row>
@@ -680,14 +680,14 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>数据范围: 20261001 ~ 20261019</t>
+          <t>数据范围: 20261001 ~ 20261020</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>工作日: 13天, 周末: 6天</t>
+          <t>工作日: 14天, 周末: 6天</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X37"/>
+  <dimension ref="A1:Y37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -757,6 +757,7 @@
     <col width="11" customWidth="1" min="22" max="22"/>
     <col width="11" customWidth="1" min="23" max="23"/>
     <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -887,6 +888,11 @@
           <t>10-19(一)</t>
         </is>
       </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>10-20(二)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -913,7 +919,7 @@
         <v>10</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>4</v>
@@ -926,12 +932,12 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="L3" s="7" t="n">
@@ -975,6 +981,9 @@
           <t>0☂</t>
         </is>
       </c>
+      <c r="Y3" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -1001,25 +1010,25 @@
         <v>20</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>4</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="L4" s="8" t="n">
@@ -1063,6 +1072,9 @@
           <t>0☂</t>
         </is>
       </c>
+      <c r="Y4" s="10" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -1089,25 +1101,25 @@
         <v>19</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H5" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="I5" s="3" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="L5" s="8" t="n">
@@ -1149,6 +1161,9 @@
       <c r="X5" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" s="8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1175,25 +1190,25 @@
         <v>15</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="L6" s="8" t="n">
@@ -1237,26 +1252,29 @@
           <t>0☂</t>
         </is>
       </c>
+      <c r="Y6" s="8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>1176722757207629824</t>
+          <t>1130000746265899008</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>规划建设展览馆渗透</t>
+          <t>城北万象汇</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>午峰</t>
+          <t>午峰+晚峰</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
@@ -1272,7 +1290,7 @@
         <v>9</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1182</v>
+        <v>357</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1284,237 +1302,248 @@
           <t>69%</t>
         </is>
       </c>
-      <c r="L7" s="8" t="n">
-        <v>174</v>
-      </c>
-      <c r="M7" s="8" t="n">
-        <v>292</v>
+      <c r="L7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>241</v>
-      </c>
-      <c r="O7" s="8" t="n">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="O7" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>197</v>
-      </c>
-      <c r="Q7" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="Q7" s="8" t="n">
+        <v>37</v>
       </c>
       <c r="R7" s="8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="S7" s="8" t="n">
-        <v>39</v>
-      </c>
-      <c r="T7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v>57</v>
       </c>
       <c r="V7" s="8" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="W7" s="8" t="n">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="X7" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>1130000746265899008</t>
+          <t>1176722757207629824</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>城北万象汇</t>
+          <t>规划建设展览馆渗透</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>午峰+晚峰</t>
+          <t>午峰</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>357</v>
+        <v>1257</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>69%</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>0</v>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>174</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>292</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="O8" s="7" t="n">
-        <v>0</v>
+        <v>241</v>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>100</v>
       </c>
       <c r="P8" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q8" s="8" t="n">
-        <v>37</v>
+        <v>197</v>
+      </c>
+      <c r="Q8" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="R8" s="8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v>57</v>
+        <v>39</v>
+      </c>
+      <c r="T8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="V8" s="8" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="W8" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="X8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="8" t="n">
         <v>75</v>
-      </c>
-      <c r="X8" s="7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>973769778869174272</t>
+          <t>0a832068l1lrine348sx5fpj3daxcqc9</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>长江后街小区渗透</t>
+          <t>剪子巷51号华静家园西区投放点</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>午峰</t>
+          <t>午峰+夜间</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>10</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1483</v>
+        <v>1065</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>未配置</t>
-        </is>
-      </c>
-      <c r="L9" s="11" t="n">
-        <v>265</v>
-      </c>
-      <c r="M9" s="11" t="n">
-        <v>264</v>
-      </c>
-      <c r="N9" s="11" t="n">
-        <v>298</v>
-      </c>
-      <c r="O9" s="11" t="n">
-        <v>278</v>
-      </c>
-      <c r="P9" s="11" t="n">
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="n">
+        <v>155</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="8" t="n">
+        <v>83</v>
+      </c>
+      <c r="P9" s="8" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q9" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="R9" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="Q9" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="R9" s="11" t="n">
-        <v>39</v>
-      </c>
-      <c r="S9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="11" t="n">
-        <v>21</v>
-      </c>
-      <c r="U9" s="11" t="n">
-        <v>42</v>
-      </c>
-      <c r="V9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" s="11" t="n">
-        <v>150</v>
+      <c r="S9" s="8" t="n">
+        <v>157</v>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v>138</v>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v>115</v>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v>77</v>
+      </c>
+      <c r="W9" s="8" t="n">
+        <v>56</v>
       </c>
       <c r="X9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>8d319562e65849c3a6e08eb73472a032</t>
+          <t>948393128847777792</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>25-全天-居民区-鸡公煲门口</t>
+          <t>30-工作日-全天-地铁-明故宫2渗透</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>午峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
@@ -1527,10 +1556,10 @@
         <v>10</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>277</v>
+        <v>598</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1539,246 +1568,255 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="O10" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="P10" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q10" s="7" t="n">
-        <v>0</v>
+        <v>65</v>
+      </c>
+      <c r="O10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="8" t="n">
+        <v>31</v>
       </c>
       <c r="R10" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="S10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="10" t="n">
-        <v>1</v>
+        <v>75</v>
+      </c>
+      <c r="S10" s="8" t="n">
+        <v>91</v>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v>100</v>
       </c>
       <c r="U10" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="W10" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="X10" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="V10" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="W10" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="X10" s="9" t="inlineStr">
+        <is>
+          <t>20☂</t>
+        </is>
+      </c>
+      <c r="Y10" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>0a832068l1lrine348sx5fpj3daxcqc9</t>
+          <t>973769778869174272</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>剪子巷51号华静家园西区投放点</t>
+          <t>长江后街小区渗透</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>午峰+夜间</t>
+          <t>午峰</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1065</v>
+        <v>1504</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>155</v>
-      </c>
-      <c r="M11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="8" t="n">
-        <v>83</v>
-      </c>
-      <c r="P11" s="8" t="n">
-        <v>104</v>
-      </c>
-      <c r="Q11" s="8" t="n">
-        <v>80</v>
-      </c>
-      <c r="R11" s="8" t="n">
+          <t>未配置</t>
+        </is>
+      </c>
+      <c r="L11" s="11" t="n">
+        <v>265</v>
+      </c>
+      <c r="M11" s="11" t="n">
+        <v>264</v>
+      </c>
+      <c r="N11" s="11" t="n">
+        <v>298</v>
+      </c>
+      <c r="O11" s="11" t="n">
+        <v>278</v>
+      </c>
+      <c r="P11" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="S11" s="8" t="n">
-        <v>157</v>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v>138</v>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v>115</v>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v>77</v>
-      </c>
-      <c r="W11" s="8" t="n">
-        <v>56</v>
+      <c r="Q11" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="R11" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="S11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="U11" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="V11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="11" t="n">
+        <v>150</v>
       </c>
       <c r="X11" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y11" s="11" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>948393128847777792</t>
+          <t>8d319562e65849c3a6e08eb73472a032</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>30-工作日-全天-地铁-明故宫2渗透</t>
+          <t>25-全天-居民区-鸡公煲门口</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>午峰</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G12" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H12" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H12" s="3" t="n">
-        <v>8</v>
-      </c>
       <c r="I12" s="3" t="n">
-        <v>598</v>
+        <v>302</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="L12" s="8" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="O12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="8" t="n">
-        <v>31</v>
+        <v>26</v>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="P12" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q12" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="S12" s="8" t="n">
-        <v>91</v>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="S12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U12" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="V12" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="W12" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="X12" s="9" t="inlineStr">
-        <is>
-          <t>20☂</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="W12" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="X12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="8" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>1090491857237020672</t>
+          <t>732955980949151744</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>太平北路华海大厦(太平北路)投放点A</t>
+          <t>25-晚峰-地铁站-天润城地铁站1号口</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+晚峰+夜间</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>12</v>
@@ -1790,7 +1828,7 @@
         <v>10</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>910</v>
+        <v>578</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1809,50 +1847,55 @@
         <v>0</v>
       </c>
       <c r="N13" s="8" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="O13" s="8" t="n">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="P13" s="8" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q13" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="R13" s="8" t="n">
+        <v>53</v>
+      </c>
+      <c r="S13" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v>110</v>
+      </c>
+      <c r="U13" s="8" t="n">
         <v>39</v>
       </c>
-      <c r="Q13" s="8" t="n">
-        <v>66</v>
-      </c>
-      <c r="R13" s="8" t="n">
-        <v>87</v>
-      </c>
-      <c r="S13" s="8" t="n">
-        <v>139</v>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v>87</v>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v>110</v>
-      </c>
       <c r="V13" s="8" t="n">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="W13" s="8" t="n">
-        <v>130</v>
+        <v>42</v>
       </c>
       <c r="X13" s="9" t="inlineStr">
         <is>
-          <t>56☂</t>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y13" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>732955980949151744</t>
+          <t>843996095354019840</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-天润城地铁站1号口</t>
+          <t>25-晚峰-地铁站-柳州东路2号口</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1862,71 +1905,74 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>早峰+晚峰+夜间</t>
+          <t>午峰+晚峰</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>10</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>578</v>
+        <v>1215</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="L14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M14" s="7" t="n">
-        <v>0</v>
+      <c r="M14" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="N14" s="8" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="O14" s="8" t="n">
         <v>25</v>
       </c>
       <c r="P14" s="8" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>120</v>
+        <v>185</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="S14" s="8" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="T14" s="8" t="n">
-        <v>110</v>
+        <v>219</v>
       </c>
       <c r="U14" s="8" t="n">
-        <v>39</v>
+        <v>195</v>
       </c>
       <c r="V14" s="8" t="n">
-        <v>69</v>
+        <v>124</v>
       </c>
       <c r="W14" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="X14" s="9" t="inlineStr">
+        <v>128</v>
+      </c>
+      <c r="X14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -1935,114 +1981,117 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>732951617602912256</t>
+          <t>1090491857237020672</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区瑞金路街道西安门地铁站投放点</t>
+          <t>太平北路华海大厦(太平北路)投放点A</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>954</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>775</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>122</v>
-      </c>
-      <c r="M15" s="8" t="n">
-        <v>104</v>
-      </c>
-      <c r="N15" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="O15" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="P15" s="7" t="n">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="P15" s="8" t="n">
+        <v>39</v>
       </c>
       <c r="Q15" s="8" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="R15" s="8" t="n">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="S15" s="8" t="n">
-        <v>37</v>
+        <v>139</v>
       </c>
       <c r="T15" s="8" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="U15" s="8" t="n">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="V15" s="8" t="n">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="W15" s="8" t="n">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="X15" s="9" t="inlineStr">
         <is>
-          <t>43☂</t>
-        </is>
+          <t>56☂</t>
+        </is>
+      </c>
+      <c r="Y15" s="8" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>843996095354019840</t>
+          <t>732955142450266112</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路2号口</t>
+          <t>南京市秦淮区双塘街道中山南路夫子庙秦淮风光带</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>午峰+晚峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>13</v>
@@ -2051,10 +2100,10 @@
         <v>11</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1215</v>
+        <v>446</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -2063,17 +2112,17 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="10" t="n">
-        <v>7</v>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N16" s="8" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="O16" s="8" t="n">
         <v>25</v>
@@ -2082,141 +2131,149 @@
         <v>50</v>
       </c>
       <c r="Q16" s="8" t="n">
-        <v>185</v>
+        <v>25</v>
       </c>
       <c r="R16" s="8" t="n">
-        <v>142</v>
+        <v>60</v>
       </c>
       <c r="S16" s="8" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="T16" s="8" t="n">
-        <v>219</v>
+        <v>54</v>
       </c>
       <c r="U16" s="8" t="n">
-        <v>195</v>
+        <v>50</v>
       </c>
       <c r="V16" s="8" t="n">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>128</v>
-      </c>
-      <c r="X16" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="X16" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y16" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>684038567596433408</t>
+          <t>732951617602912256</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路公交站台</t>
+          <t>南京市秦淮区瑞金路街道西安门地铁站投放点</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>早峰+晚峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>11</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1749</v>
+        <v>863</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>未配置</t>
-        </is>
-      </c>
-      <c r="L17" s="11" t="n">
-        <v>139</v>
-      </c>
-      <c r="M17" s="11" t="n">
-        <v>161</v>
-      </c>
-      <c r="N17" s="11" t="n">
-        <v>106</v>
-      </c>
-      <c r="O17" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="P17" s="11" t="n">
-        <v>111</v>
-      </c>
-      <c r="Q17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="11" t="n">
-        <v>241</v>
-      </c>
-      <c r="S17" s="11" t="n">
-        <v>233</v>
-      </c>
-      <c r="T17" s="11" t="n">
-        <v>253</v>
-      </c>
-      <c r="U17" s="11" t="n">
-        <v>167</v>
-      </c>
-      <c r="V17" s="11" t="n">
-        <v>141</v>
-      </c>
-      <c r="W17" s="11" t="n">
-        <v>165</v>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>122</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>104</v>
+      </c>
+      <c r="N17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="P17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="R17" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="S17" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v>119</v>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="W17" s="8" t="n">
+        <v>72</v>
       </c>
       <c r="X17" s="9" t="inlineStr">
         <is>
-          <t>0☂</t>
-        </is>
+          <t>43☂</t>
+        </is>
+      </c>
+      <c r="Y17" s="8" t="n">
+        <v>88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1lp8ayqb5m6m5jv9xbfnhd9</t>
+          <t>684038567596433408</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>中山东路原国民政府旧址-国民党中央监察委员会办公楼旧址投放点</t>
+          <t>25-晚峰-地铁站-柳州东路公交站台</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+晚峰</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>12</v>
@@ -2225,10 +2282,10 @@
         <v>11</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>1429</v>
+        <v>1749</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -2237,48 +2294,53 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
-        </is>
-      </c>
-      <c r="L18" s="8" t="n">
-        <v>195</v>
-      </c>
-      <c r="M18" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="N18" s="8" t="n">
-        <v>267</v>
-      </c>
-      <c r="O18" s="8" t="n">
-        <v>195</v>
-      </c>
-      <c r="P18" s="8" t="n">
-        <v>97</v>
-      </c>
-      <c r="Q18" s="8" t="n">
-        <v>177</v>
-      </c>
-      <c r="R18" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="S18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v>122</v>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v>49</v>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v>118</v>
-      </c>
-      <c r="W18" s="8" t="n">
-        <v>99</v>
+          <t>未配置</t>
+        </is>
+      </c>
+      <c r="L18" s="11" t="n">
+        <v>139</v>
+      </c>
+      <c r="M18" s="11" t="n">
+        <v>161</v>
+      </c>
+      <c r="N18" s="11" t="n">
+        <v>106</v>
+      </c>
+      <c r="O18" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="P18" s="11" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="11" t="n">
+        <v>241</v>
+      </c>
+      <c r="S18" s="11" t="n">
+        <v>233</v>
+      </c>
+      <c r="T18" s="11" t="n">
+        <v>253</v>
+      </c>
+      <c r="U18" s="11" t="n">
+        <v>167</v>
+      </c>
+      <c r="V18" s="11" t="n">
+        <v>141</v>
+      </c>
+      <c r="W18" s="11" t="n">
+        <v>165</v>
       </c>
       <c r="X18" s="9" t="inlineStr">
         <is>
-          <t>10☂</t>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y18" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2378,7 @@
         <v>11</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>812</v>
+        <v>869</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -2369,16 +2431,21 @@
           <t>0☂</t>
         </is>
       </c>
+      <c r="Y19" s="9" t="inlineStr">
+        <is>
+          <t>57☂</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>0a836a6al1l268p7ak2p5yn7sfzs2tsg</t>
+          <t>1101025367910903808</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>中山东路228号新世纪广场A幢投放点</t>
+          <t>中山南路379号南京夫子庙秦淮风光带投放点A渗透</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -2388,23 +2455,23 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F20" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="G20" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G20" s="3" t="n">
-        <v>11</v>
-      </c>
       <c r="H20" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>726</v>
+        <v>769</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -2413,60 +2480,63 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="M20" s="8" t="n">
+        <v>53</v>
+      </c>
+      <c r="M20" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N20" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="P20" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="N20" s="8" t="n">
-        <v>107</v>
-      </c>
-      <c r="O20" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="P20" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="Q20" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="R20" s="8" t="n">
         <v>72</v>
       </c>
-      <c r="R20" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="S20" s="8" t="n">
-        <v>113</v>
+      <c r="S20" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="T20" s="8" t="n">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="U20" s="8" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="V20" s="8" t="n">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="W20" s="8" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="X20" s="9" t="inlineStr">
         <is>
-          <t>0☂</t>
-        </is>
+          <t>16☂</t>
+        </is>
+      </c>
+      <c r="Y20" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>732955142450266112</t>
+          <t>1174627254806421504</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区双塘街道中山南路夫子庙秦淮风光带</t>
+          <t>南京市秦淮区五老村街道淮海路淮海路31号院</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -2483,16 +2553,16 @@
         <v>19</v>
       </c>
       <c r="F21" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="G21" s="3" t="n">
         <v>12</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>11</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>11</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>446</v>
+        <v>348</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -2501,348 +2571,362 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="L21" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="M21" s="7" t="n">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="M21" s="8" t="n">
+        <v>40</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="O21" s="8" t="n">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="O21" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="P21" s="8" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="Q21" s="8" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="R21" s="8" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="S21" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="T21" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="T21" s="8" t="n">
-        <v>54</v>
-      </c>
       <c r="U21" s="8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="V21" s="8" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="W21" s="8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="X21" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
+      </c>
+      <c r="Y21" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>0a83eb4fl1lz4hvkvkpdqc8mwis9httv</t>
+          <t>732956028185985024</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>仙林中心（地铁站）投放点A</t>
+          <t>下马坊地铁站</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>13</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>881</v>
+        <v>1281</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>未配置</t>
-        </is>
-      </c>
-      <c r="L22" s="11" t="n">
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="M22" s="8" t="n">
+        <v>67</v>
+      </c>
+      <c r="N22" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="O22" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="P22" s="8" t="n">
+        <v>114</v>
+      </c>
+      <c r="Q22" s="8" t="n">
+        <v>109</v>
+      </c>
+      <c r="R22" s="8" t="n">
+        <v>117</v>
+      </c>
+      <c r="S22" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v>145</v>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v>203</v>
+      </c>
+      <c r="V22" s="8" t="n">
         <v>175</v>
       </c>
-      <c r="M22" s="11" t="n">
-        <v>75</v>
-      </c>
-      <c r="N22" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="O22" s="11" t="n">
-        <v>197</v>
-      </c>
-      <c r="P22" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q22" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="R22" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="S22" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="T22" s="11" t="n">
-        <v>50</v>
-      </c>
-      <c r="U22" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="V22" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="W22" s="11" t="n">
-        <v>119</v>
-      </c>
-      <c r="X22" s="11" t="n">
-        <v>25</v>
+      <c r="W22" s="8" t="n">
+        <v>133</v>
+      </c>
+      <c r="X22" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y22" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>732955258519240704</t>
+          <t>0a836587l1lp8ayqb5m6m5jv9xbfnhd9</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路1号口</t>
+          <t>中山东路原国民政府旧址-国民党中央监察委员会办公楼旧址投放点</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰+晚峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>12</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1233</v>
+        <v>1524</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>未配置</t>
-        </is>
-      </c>
-      <c r="L23" s="11" t="n">
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="L23" s="8" t="n">
+        <v>195</v>
+      </c>
+      <c r="M23" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="M23" s="11" t="n">
-        <v>56</v>
-      </c>
-      <c r="N23" s="11" t="n">
-        <v>53</v>
-      </c>
-      <c r="O23" s="11" t="n">
-        <v>123</v>
-      </c>
-      <c r="P23" s="11" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q23" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="R23" s="11" t="n">
-        <v>68</v>
-      </c>
-      <c r="S23" s="11" t="n">
-        <v>78</v>
-      </c>
-      <c r="T23" s="11" t="n">
-        <v>74</v>
-      </c>
-      <c r="U23" s="11" t="n">
-        <v>126</v>
-      </c>
-      <c r="V23" s="11" t="n">
-        <v>231</v>
-      </c>
-      <c r="W23" s="11" t="n">
-        <v>240</v>
+      <c r="N23" s="8" t="n">
+        <v>267</v>
+      </c>
+      <c r="O23" s="8" t="n">
+        <v>195</v>
+      </c>
+      <c r="P23" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="Q23" s="8" t="n">
+        <v>177</v>
+      </c>
+      <c r="R23" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="S23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v>122</v>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v>118</v>
+      </c>
+      <c r="W23" s="8" t="n">
+        <v>99</v>
       </c>
       <c r="X23" s="9" t="inlineStr">
         <is>
-          <t>52☂</t>
-        </is>
+          <t>10☂</t>
+        </is>
+      </c>
+      <c r="Y23" s="8" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>554207268614606848</t>
+          <t>0a836a6al1l268p7ak2p5yn7sfzs2tsg</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁-迈皋桥地铁站4号口</t>
+          <t>中山东路228号新世纪广场A幢投放点</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>早峰+晚峰+夜间</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>12</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>1668</v>
+        <v>805</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="L24" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M24" s="10" t="n">
-        <v>2</v>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="L24" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="M24" s="8" t="n">
+        <v>40</v>
       </c>
       <c r="N24" s="8" t="n">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="O24" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="P24" s="8" t="n">
-        <v>75</v>
+        <v>60</v>
+      </c>
+      <c r="P24" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="Q24" s="8" t="n">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="R24" s="8" t="n">
-        <v>168</v>
+        <v>40</v>
       </c>
       <c r="S24" s="8" t="n">
-        <v>250</v>
+        <v>113</v>
       </c>
       <c r="T24" s="8" t="n">
-        <v>284</v>
+        <v>40</v>
       </c>
       <c r="U24" s="8" t="n">
-        <v>213</v>
+        <v>76</v>
       </c>
       <c r="V24" s="8" t="n">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="W24" s="8" t="n">
-        <v>268</v>
+        <v>77</v>
       </c>
       <c r="X24" s="9" t="inlineStr">
         <is>
-          <t>25☂</t>
-        </is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y24" s="8" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>1101025367910903808</t>
+          <t>0a83eb4fl1lz4hvkvkpdqc8mwis9httv</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>中山南路379号南京夫子庙秦淮风光带投放点A渗透</t>
+          <t>仙林中心（地铁站）投放点A</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>769</v>
+        <v>906</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2851,74 +2935,75 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="L25" s="8" t="n">
-        <v>53</v>
-      </c>
-      <c r="M25" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="N25" s="8" t="n">
+          <t>未配置</t>
+        </is>
+      </c>
+      <c r="L25" s="11" t="n">
+        <v>175</v>
+      </c>
+      <c r="M25" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="N25" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="O25" s="11" t="n">
+        <v>197</v>
+      </c>
+      <c r="P25" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q25" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="R25" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="S25" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="O25" s="8" t="n">
+      <c r="U25" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="V25" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="P25" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q25" s="8" t="n">
-        <v>73</v>
-      </c>
-      <c r="R25" s="8" t="n">
-        <v>72</v>
-      </c>
-      <c r="S25" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v>91</v>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v>90</v>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v>175</v>
-      </c>
-      <c r="W25" s="8" t="n">
-        <v>74</v>
-      </c>
-      <c r="X25" s="9" t="inlineStr">
-        <is>
-          <t>16☂</t>
-        </is>
+      <c r="W25" s="11" t="n">
+        <v>119</v>
+      </c>
+      <c r="X25" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y25" s="11" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>1174627254806421504</t>
+          <t>732955258519240704</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区五老村街道淮海路淮海路31号院</t>
+          <t>25-晚峰-地铁站-柳州东路1号口</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰+晚峰</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>12</v>
@@ -2927,10 +3012,10 @@
         <v>12</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>348</v>
+        <v>1268</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2939,70 +3024,75 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
-        </is>
-      </c>
-      <c r="L26" s="8" t="n">
+          <t>未配置</t>
+        </is>
+      </c>
+      <c r="L26" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="M26" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="N26" s="11" t="n">
+        <v>53</v>
+      </c>
+      <c r="O26" s="11" t="n">
+        <v>123</v>
+      </c>
+      <c r="P26" s="11" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q26" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="M26" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="N26" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="O26" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="P26" s="8" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q26" s="8" t="n">
-        <v>34</v>
-      </c>
-      <c r="R26" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="S26" s="8" t="n">
-        <v>57</v>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="W26" s="8" t="n">
-        <v>20</v>
+      <c r="R26" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="S26" s="11" t="n">
+        <v>78</v>
+      </c>
+      <c r="T26" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="U26" s="11" t="n">
+        <v>126</v>
+      </c>
+      <c r="V26" s="11" t="n">
+        <v>231</v>
+      </c>
+      <c r="W26" s="11" t="n">
+        <v>240</v>
       </c>
       <c r="X26" s="9" t="inlineStr">
         <is>
-          <t>0☂</t>
+          <t>52☂</t>
+        </is>
+      </c>
+      <c r="Y26" s="9" t="inlineStr">
+        <is>
+          <t>35☂</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>732956028185985024</t>
+          <t>554207268614606848</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>下马坊地铁站</t>
+          <t>25-晚峰-地铁-迈皋桥地铁站4号口</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+晚峰+夜间</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
@@ -3015,10 +3105,10 @@
         <v>12</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1281</v>
+        <v>1788</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -3027,70 +3117,75 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L27" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="M27" s="8" t="n">
-        <v>67</v>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="L27" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M27" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="N27" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="O27" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="P27" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="O27" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="P27" s="8" t="n">
-        <v>114</v>
-      </c>
       <c r="Q27" s="8" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="R27" s="8" t="n">
-        <v>117</v>
+        <v>168</v>
       </c>
       <c r="S27" s="8" t="n">
-        <v>33</v>
+        <v>250</v>
       </c>
       <c r="T27" s="8" t="n">
-        <v>145</v>
+        <v>284</v>
       </c>
       <c r="U27" s="8" t="n">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="V27" s="8" t="n">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="W27" s="8" t="n">
-        <v>133</v>
+        <v>268</v>
       </c>
       <c r="X27" s="9" t="inlineStr">
         <is>
-          <t>0☂</t>
+          <t>25☂</t>
+        </is>
+      </c>
+      <c r="Y27" s="9" t="inlineStr">
+        <is>
+          <t>120☂</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>95ed3168228b4cf19a39b9efbb70b87a</t>
+          <t>554207268778184704</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>大行宫6号口渗透</t>
+          <t>25-晚峰-地铁站-柳州东路3号口</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+晚峰</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
@@ -3106,7 +3201,7 @@
         <v>12</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1303</v>
+        <v>1368</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -3119,56 +3214,61 @@
         </is>
       </c>
       <c r="L28" s="8" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="N28" s="8" t="n">
-        <v>143</v>
+        <v>50</v>
       </c>
       <c r="O28" s="8" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="P28" s="8" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q28" s="8" t="n">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="R28" s="8" t="n">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="S28" s="8" t="n">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="T28" s="8" t="n">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="U28" s="8" t="n">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="V28" s="8" t="n">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="W28" s="8" t="n">
-        <v>145</v>
+        <v>200</v>
       </c>
       <c r="X28" s="9" t="inlineStr">
         <is>
-          <t>56☂</t>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y28" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>816513511474413568</t>
+          <t>95ed3168228b4cf19a39b9efbb70b87a</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>熊猫</t>
+          <t>大行宫6号口渗透</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -3182,19 +3282,19 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>863</v>
+        <v>1457</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -3207,82 +3307,85 @@
         </is>
       </c>
       <c r="L29" s="8" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="N29" s="8" t="n">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="O29" s="8" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P29" s="8" t="n">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="Q29" s="8" t="n">
-        <v>65</v>
+        <v>177</v>
       </c>
       <c r="R29" s="8" t="n">
-        <v>52</v>
+        <v>132</v>
       </c>
       <c r="S29" s="8" t="n">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="T29" s="8" t="n">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="U29" s="8" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="V29" s="8" t="n">
-        <v>97</v>
+        <v>147</v>
       </c>
       <c r="W29" s="8" t="n">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="X29" s="9" t="inlineStr">
         <is>
-          <t>65☂</t>
-        </is>
+          <t>56☂</t>
+        </is>
+      </c>
+      <c r="Y29" s="8" t="n">
+        <v>154</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>584636981105418240</t>
+          <t>816513511474413568</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁-羊山公园2号口</t>
+          <t>熊猫</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2252</v>
+        <v>931</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -3295,82 +3398,85 @@
         </is>
       </c>
       <c r="L30" s="8" t="n">
-        <v>200</v>
+        <v>21</v>
       </c>
       <c r="M30" s="8" t="n">
-        <v>294</v>
+        <v>54</v>
       </c>
       <c r="N30" s="8" t="n">
-        <v>303</v>
+        <v>51</v>
       </c>
       <c r="O30" s="8" t="n">
-        <v>449</v>
+        <v>39</v>
       </c>
       <c r="P30" s="8" t="n">
-        <v>223</v>
+        <v>94</v>
       </c>
       <c r="Q30" s="8" t="n">
-        <v>192</v>
+        <v>65</v>
       </c>
       <c r="R30" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="S30" s="8" t="n">
+        <v>84</v>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v>68</v>
+      </c>
+      <c r="U30" s="8" t="n">
         <v>80</v>
       </c>
-      <c r="S30" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v>100</v>
-      </c>
       <c r="V30" s="8" t="n">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="W30" s="8" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="X30" s="9" t="inlineStr">
         <is>
-          <t>81☂</t>
-        </is>
+          <t>65☂</t>
+        </is>
+      </c>
+      <c r="Y30" s="8" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>939767915811442688</t>
+          <t>584636981105418240</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区五老村街道延龄巷魔方公寓（新街口店）</t>
+          <t>25-全天-地铁-羊山公园2号口</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1059</v>
+        <v>2435</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -3383,56 +3489,59 @@
         </is>
       </c>
       <c r="L31" s="8" t="n">
-        <v>98</v>
+        <v>200</v>
       </c>
       <c r="M31" s="8" t="n">
+        <v>294</v>
+      </c>
+      <c r="N31" s="8" t="n">
+        <v>303</v>
+      </c>
+      <c r="O31" s="8" t="n">
+        <v>449</v>
+      </c>
+      <c r="P31" s="8" t="n">
+        <v>223</v>
+      </c>
+      <c r="Q31" s="8" t="n">
+        <v>192</v>
+      </c>
+      <c r="R31" s="8" t="n">
         <v>80</v>
       </c>
-      <c r="N31" s="8" t="n">
-        <v>117</v>
-      </c>
-      <c r="O31" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="P31" s="8" t="n">
-        <v>119</v>
-      </c>
-      <c r="Q31" s="8" t="n">
+      <c r="S31" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="T31" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="R31" s="8" t="n">
-        <v>90</v>
-      </c>
-      <c r="S31" s="8" t="n">
-        <v>123</v>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v>20</v>
-      </c>
       <c r="U31" s="8" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="V31" s="8" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="W31" s="8" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="X31" s="9" t="inlineStr">
         <is>
-          <t>40☂</t>
-        </is>
+          <t>81☂</t>
+        </is>
+      </c>
+      <c r="Y31" s="8" t="n">
+        <v>183</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>0a83a497l1luic2g4wtq27rx7tzt6rwm</t>
+          <t>939767915811442688</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>长乐路167-4夫子庙秦淮风光带投放点A</t>
+          <t>南京市秦淮区五老村街道延龄巷魔方公寓（新街口店）</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -3449,16 +3558,16 @@
         <v>19</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1233</v>
+        <v>1099</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -3471,56 +3580,59 @@
         </is>
       </c>
       <c r="L32" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="M32" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="N32" s="8" t="n">
+        <v>117</v>
+      </c>
+      <c r="O32" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="P32" s="8" t="n">
+        <v>119</v>
+      </c>
+      <c r="Q32" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="R32" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="S32" s="8" t="n">
+        <v>123</v>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v>77</v>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v>67</v>
+      </c>
+      <c r="W32" s="8" t="n">
         <v>68</v>
       </c>
-      <c r="M32" s="8" t="n">
-        <v>63</v>
-      </c>
-      <c r="N32" s="8" t="n">
-        <v>87</v>
-      </c>
-      <c r="O32" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="P32" s="8" t="n">
-        <v>80</v>
-      </c>
-      <c r="Q32" s="8" t="n">
-        <v>118</v>
-      </c>
-      <c r="R32" s="8" t="n">
-        <v>112</v>
-      </c>
-      <c r="S32" s="8" t="n">
-        <v>119</v>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v>81</v>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v>175</v>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v>155</v>
-      </c>
-      <c r="W32" s="8" t="n">
-        <v>103</v>
-      </c>
       <c r="X32" s="9" t="inlineStr">
         <is>
-          <t>24☂</t>
-        </is>
+          <t>40☂</t>
+        </is>
+      </c>
+      <c r="Y32" s="8" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>1174622373773963264</t>
+          <t>0a83a497l1luic2g4wtq27rx7tzt6rwm</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区洪武路街道常府街地铁站</t>
+          <t>长乐路167-4夫子庙秦淮风光带投放点A</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -3537,16 +3649,16 @@
         <v>19</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>902</v>
+        <v>1407</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -3559,56 +3671,59 @@
         </is>
       </c>
       <c r="L33" s="8" t="n">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="M33" s="8" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="N33" s="8" t="n">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="O33" s="8" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="P33" s="8" t="n">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="Q33" s="8" t="n">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="R33" s="8" t="n">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="S33" s="8" t="n">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="T33" s="8" t="n">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="U33" s="8" t="n">
-        <v>108</v>
+        <v>175</v>
       </c>
       <c r="V33" s="8" t="n">
-        <v>40</v>
+        <v>155</v>
       </c>
       <c r="W33" s="8" t="n">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="X33" s="9" t="inlineStr">
         <is>
-          <t>0☂</t>
-        </is>
+          <t>24☂</t>
+        </is>
+      </c>
+      <c r="Y33" s="8" t="n">
+        <v>174</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>1153706291117858816</t>
+          <t>1174622373773963264</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区夫子庙街道马道街夫子庙秦淮风光带</t>
+          <t>南京市秦淮区洪武路街道常府街地铁站</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -3625,16 +3740,16 @@
         <v>19</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>1063</v>
+        <v>922</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -3647,61 +3762,64 @@
         </is>
       </c>
       <c r="L34" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="M34" s="8" t="n">
+        <v>99</v>
+      </c>
+      <c r="N34" s="8" t="n">
+        <v>67</v>
+      </c>
+      <c r="O34" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="P34" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="M34" s="8" t="n">
-        <v>133</v>
-      </c>
-      <c r="N34" s="8" t="n">
-        <v>103</v>
-      </c>
-      <c r="O34" s="8" t="n">
-        <v>141</v>
-      </c>
-      <c r="P34" s="8" t="n">
-        <v>73</v>
-      </c>
       <c r="Q34" s="8" t="n">
-        <v>177</v>
+        <v>66</v>
       </c>
       <c r="R34" s="8" t="n">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="S34" s="8" t="n">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="T34" s="8" t="n">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="U34" s="8" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="V34" s="8" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="W34" s="8" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="X34" s="9" t="inlineStr">
         <is>
-          <t>4☂</t>
-        </is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y34" s="8" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>6b76f4e6b1c642129d31dd0fc4d95c4f</t>
+          <t>1153706291117858816</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>25-全天-地铁口-仙林中心站1号口</t>
+          <t>南京市秦淮区夫子庙街道马道街夫子庙秦淮风光带</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -3710,19 +3828,19 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>3066</v>
+        <v>1084</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -3735,56 +3853,59 @@
         </is>
       </c>
       <c r="L35" s="8" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="M35" s="8" t="n">
-        <v>305</v>
+        <v>133</v>
       </c>
       <c r="N35" s="8" t="n">
-        <v>462</v>
+        <v>103</v>
       </c>
       <c r="O35" s="8" t="n">
-        <v>491</v>
+        <v>141</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>739</v>
+        <v>73</v>
       </c>
       <c r="Q35" s="8" t="n">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="R35" s="8" t="n">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="S35" s="8" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T35" s="8" t="n">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="U35" s="8" t="n">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="V35" s="8" t="n">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="W35" s="8" t="n">
-        <v>142</v>
+        <v>59</v>
       </c>
       <c r="X35" s="9" t="inlineStr">
         <is>
-          <t>70☂</t>
-        </is>
+          <t>4☂</t>
+        </is>
+      </c>
+      <c r="Y35" s="8" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>1123869911569338368</t>
+          <t>6b76f4e6b1c642129d31dd0fc4d95c4f</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>学衡路南京师范大学仙林校区投放点B</t>
+          <t>25-全天-地铁口-仙林中心站1号口</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -3801,16 +3922,16 @@
         <v>20</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>1500</v>
+        <v>3213</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -3823,82 +3944,85 @@
         </is>
       </c>
       <c r="L36" s="8" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="M36" s="8" t="n">
-        <v>100</v>
+        <v>305</v>
       </c>
       <c r="N36" s="8" t="n">
-        <v>175</v>
+        <v>462</v>
       </c>
       <c r="O36" s="8" t="n">
-        <v>175</v>
+        <v>491</v>
       </c>
       <c r="P36" s="8" t="n">
-        <v>75</v>
+        <v>739</v>
       </c>
       <c r="Q36" s="8" t="n">
-        <v>181</v>
+        <v>140</v>
       </c>
       <c r="R36" s="8" t="n">
         <v>150</v>
       </c>
       <c r="S36" s="8" t="n">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="T36" s="8" t="n">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="U36" s="8" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="V36" s="8" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="W36" s="8" t="n">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="X36" s="9" t="inlineStr">
         <is>
-          <t>25☂</t>
-        </is>
+          <t>70☂</t>
+        </is>
+      </c>
+      <c r="Y36" s="8" t="n">
+        <v>147</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>554207268778184704</t>
+          <t>1123869911569338368</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路3号口</t>
+          <t>学衡路南京师范大学仙林校区投放点B</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>早峰+晚峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1368</v>
+        <v>1625</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -3911,45 +4035,48 @@
         </is>
       </c>
       <c r="L37" s="8" t="n">
-        <v>37</v>
+        <v>150</v>
       </c>
       <c r="M37" s="8" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N37" s="8" t="n">
-        <v>50</v>
+        <v>175</v>
       </c>
       <c r="O37" s="8" t="n">
-        <v>75</v>
+        <v>175</v>
       </c>
       <c r="P37" s="8" t="n">
         <v>75</v>
       </c>
       <c r="Q37" s="8" t="n">
+        <v>181</v>
+      </c>
+      <c r="R37" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="S37" s="8" t="n">
+        <v>51</v>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v>87</v>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="W37" s="8" t="n">
+        <v>181</v>
+      </c>
+      <c r="X37" s="9" t="inlineStr">
+        <is>
+          <t>25☂</t>
+        </is>
+      </c>
+      <c r="Y37" s="8" t="n">
         <v>125</v>
-      </c>
-      <c r="R37" s="8" t="n">
-        <v>147</v>
-      </c>
-      <c r="S37" s="8" t="n">
-        <v>149</v>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v>150</v>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v>160</v>
-      </c>
-      <c r="W37" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="X37" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -6437,7 +6564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X54"/>
+  <dimension ref="A1:Y54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6464,6 +6591,7 @@
     <col width="11" customWidth="1" min="22" max="22"/>
     <col width="11" customWidth="1" min="23" max="23"/>
     <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6594,6 +6722,11 @@
           <t>10-19(一)</t>
         </is>
       </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>10-20(二)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -6620,7 +6753,7 @@
         <v>20</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>4</v>
@@ -6633,12 +6766,12 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="L3" s="7" t="n">
@@ -6682,6 +6815,9 @@
           <t>0☂</t>
         </is>
       </c>
+      <c r="Y3" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -6708,25 +6844,25 @@
         <v>20</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H4" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="I4" s="3" t="n">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="L4" s="7" t="n">
@@ -6770,21 +6906,24 @@
           <t>44☂</t>
         </is>
       </c>
+      <c r="Y4" s="8" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>0a83e824l1lbnte698jzx9rudh6mt9tj</t>
+          <t>893732199694139392</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>南京市玄武区孝陵卫街道梅花谷路梅花谷公园</t>
+          <t>东新南路瓯江大厦站点</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>王兴星</t>
+          <t>李小凯</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -6796,25 +6935,25 @@
         <v>10</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>4</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="L5" s="7" t="n">
@@ -6829,8 +6968,8 @@
       <c r="O5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="7" t="n">
-        <v>0</v>
+      <c r="P5" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="Q5" s="7" t="n">
         <v>0</v>
@@ -6838,36 +6977,39 @@
       <c r="R5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S5" s="8" t="n">
+      <c r="S5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="T5" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="U5" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="V5" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="V5" s="8" t="n">
-        <v>10</v>
-      </c>
       <c r="W5" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X5" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
+      </c>
+      <c r="Y5" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>893732199694139392</t>
+          <t>0a838d5dl1lpybxf2cm2vhfyih32kncd</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>东新南路瓯江大厦站点</t>
+          <t>润发路南方时代广场群发路D站点D</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -6884,25 +7026,25 @@
         <v>10</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>5</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="L6" s="7" t="n">
@@ -6917,8 +7059,8 @@
       <c r="O6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="10" t="n">
-        <v>2</v>
+      <c r="P6" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="Q6" s="7" t="n">
         <v>0</v>
@@ -6926,36 +7068,39 @@
       <c r="R6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S6" s="7" t="n">
-        <v>0</v>
+      <c r="S6" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U6" s="8" t="n">
         <v>11</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W6" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X6" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
+      </c>
+      <c r="Y6" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>0a838d5dl1lpybxf2cm2vhfyih32kncd</t>
+          <t>893715809572151296</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>润发路南方时代广场群发路D站点D</t>
+          <t>土山路华意泰富花苑站点A</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -6972,7 +7117,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>5</v>
@@ -6981,16 +7126,16 @@
         <v>5</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="L7" s="7" t="n">
@@ -7015,40 +7160,43 @@
         <v>0</v>
       </c>
       <c r="S7" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="T7" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="T7" s="8" t="n">
+      <c r="U7" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="U7" s="8" t="n">
+      <c r="V7" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="W7" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="V7" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="W7" s="8" t="n">
-        <v>10</v>
-      </c>
       <c r="X7" s="9" t="inlineStr">
         <is>
-          <t>0☂</t>
-        </is>
+          <t>12☂</t>
+        </is>
+      </c>
+      <c r="Y7" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>893715809572151296</t>
+          <t>0a83e824l1lbnte698jzx9rudh6mt9tj</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>土山路华意泰富花苑站点A</t>
+          <t>南京市玄武区孝陵卫街道梅花谷路梅花谷公园</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>李小凯</t>
+          <t>王兴星</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -7060,7 +7208,7 @@
         <v>10</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>5</v>
@@ -7069,16 +7217,16 @@
         <v>5</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="L8" s="7" t="n">
@@ -7103,104 +7251,107 @@
         <v>0</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="T8" s="8" t="n">
         <v>10</v>
+      </c>
+      <c r="T8" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="U8" s="8" t="n">
         <v>12</v>
       </c>
       <c r="V8" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W8" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X8" s="9" t="inlineStr">
         <is>
-          <t>12☂</t>
-        </is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y8" s="8" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>0a83f096l1l8jjun6xxt9t7uxyibq9b9</t>
+          <t>0a8320ecl1lvbzz3tyzcnk28dt6w9vz4</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>弘利路龙湖·水晶郦城站点B</t>
+          <t>逸夫医院门口左手</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
         <v>10</v>
       </c>
       <c r="F9" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>201</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="G9" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>58%</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>58%</t>
-        </is>
-      </c>
-      <c r="L9" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="M9" s="7" t="n">
-        <v>0</v>
+      <c r="M9" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="N9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="8" t="n">
-        <v>11</v>
+      <c r="O9" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="P9" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="Q9" s="8" t="n">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="R9" s="8" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="S9" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="U9" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="T9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="V9" s="8" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="W9" s="7" t="n">
         <v>0</v>
@@ -7209,17 +7360,20 @@
         <is>
           <t>0☂</t>
         </is>
+      </c>
+      <c r="Y9" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>0a83d695l1lz6m3vbn8zbatt525u6cbu</t>
+          <t>0a83f096l1l8jjun6xxt9t7uxyibq9b9</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>景明北大街站点B</t>
+          <t>弘利路龙湖·水晶郦城站点B</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -7233,32 +7387,32 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>258</v>
+        <v>109</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>58%</t>
-        </is>
-      </c>
-      <c r="L10" s="7" t="n">
-        <v>0</v>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="n">
+        <v>32</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>0</v>
@@ -7270,44 +7424,47 @@
         <v>0</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="R10" s="10" t="n">
-        <v>6</v>
+        <v>11</v>
+      </c>
+      <c r="R10" s="8" t="n">
+        <v>11</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="T10" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v>22</v>
+        <v>11</v>
+      </c>
+      <c r="U10" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="V10" s="8" t="n">
-        <v>49</v>
-      </c>
-      <c r="W10" s="8" t="n">
-        <v>38</v>
+        <v>11</v>
+      </c>
+      <c r="W10" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="X10" s="9" t="inlineStr">
         <is>
-          <t>34☂</t>
-        </is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y10" s="8" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>0a8320ecl1lvbzz3tyzcnk28dt6w9vz4</t>
+          <t>889717813217533952</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>逸夫医院门口左手</t>
+          <t>高新-高校-交院东门-全周-全天-50</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -7321,86 +7478,89 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>201</v>
+        <v>664</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="L11" s="8" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="N11" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O11" s="8" t="n">
-        <v>23</v>
+      <c r="O11" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="P11" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" s="8" t="n">
-        <v>64</v>
+      <c r="Q11" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="S11" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="T11" s="7" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v>86</v>
       </c>
       <c r="U11" s="8" t="n">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="W11" s="7" t="n">
-        <v>0</v>
+        <v>101</v>
+      </c>
+      <c r="W11" s="8" t="n">
+        <v>155</v>
       </c>
       <c r="X11" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
+      </c>
+      <c r="Y11" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>897028622557294592</t>
+          <t>0a83d695l1lz6m3vbn8zbatt525u6cbu</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>南京工程学院5号门左手</t>
+          <t>景明北大街站点B</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -7412,166 +7572,172 @@
         <v>20</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>9</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>177</v>
+        <v>291</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="L12" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="M12" s="10" t="n">
-        <v>12</v>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="P12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="7" t="n">
-        <v>0</v>
+      <c r="O12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q12" s="8" t="n">
+        <v>22</v>
       </c>
       <c r="R12" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="S12" s="10" t="n">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="S12" s="8" t="n">
+        <v>33</v>
       </c>
       <c r="T12" s="8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="U12" s="8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="V12" s="8" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="W12" s="8" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="X12" s="9" t="inlineStr">
         <is>
-          <t>0☂</t>
-        </is>
+          <t>34☂</t>
+        </is>
+      </c>
+      <c r="Y12" s="8" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>889717813217533952</t>
+          <t>0a838d77l1lhvwurirt76tdpsj4f7z4m</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>高新-高校-交院东门-全周-全天-50</t>
+          <t>龙昌路中南·上悦城站点A</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>李小凯</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>9</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>664</v>
+        <v>101</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="L13" s="8" t="n">
-        <v>43</v>
-      </c>
-      <c r="M13" s="8" t="n">
-        <v>33</v>
+        <v>11</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N13" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="10" t="n">
+      <c r="O13" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="P13" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q13" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="R13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="R13" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="S13" s="8" t="n">
-        <v>100</v>
-      </c>
       <c r="T13" s="8" t="n">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="U13" s="8" t="n">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="V13" s="8" t="n">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="W13" s="8" t="n">
-        <v>155</v>
+        <v>11</v>
       </c>
       <c r="X13" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
+      </c>
+      <c r="Y13" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>889466722646794240</t>
+          <t>1084739124625276928</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>胜太东路江宁供销商厦站点</t>
+          <t>骆村路骆村新寓A区站点A</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -7588,78 +7754,81 @@
         <v>10</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>9</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="L14" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="O14" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="N14" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="O14" s="10" t="n">
-        <v>5</v>
-      </c>
       <c r="P14" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S14" s="7" t="n">
-        <v>0</v>
+      <c r="S14" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="T14" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U14" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V14" s="8" t="n">
         <v>12</v>
       </c>
       <c r="W14" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X14" s="9" t="inlineStr">
         <is>
-          <t>11☂</t>
-        </is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y14" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>0a837fbbl1lcvvfvrrb6nbtsxdr5xk2w</t>
+          <t>897028622557294592</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>天元东路辅路南京义乌小商品城站点H</t>
+          <t>南京工程学院5号门左手</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -7673,86 +7842,89 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="G15" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="H15" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="L15" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="G15" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="H15" s="3" t="n">
+      <c r="M15" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="N15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="I15" s="3" t="n">
-        <v>182</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L15" s="8" t="n">
+      <c r="P15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="S15" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="M15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="O15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="8" t="n">
+      <c r="T15" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="Q15" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="R15" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="S15" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="T15" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="U15" s="7" t="n">
-        <v>0</v>
+      <c r="U15" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="V15" s="8" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="W15" s="8" t="n">
         <v>24</v>
       </c>
       <c r="X15" s="9" t="inlineStr">
         <is>
-          <t>24☂</t>
-        </is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y15" s="10" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>889935238642700288</t>
+          <t>889466722646794240</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>南京市江宁区淳化街道博观路保利·梧桐语</t>
+          <t>胜太东路江宁供销商厦站点</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>李小凯</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -7764,83 +7936,86 @@
         <v>10</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>9</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="7" t="n">
-        <v>0</v>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="M16" s="8" t="n">
+        <v>11</v>
       </c>
       <c r="N16" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="O16" s="8" t="n">
-        <v>12</v>
+      <c r="O16" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="P16" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="R16" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="S16" s="8" t="n">
-        <v>21</v>
+        <v>11</v>
+      </c>
+      <c r="R16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T16" s="8" t="n">
         <v>13</v>
       </c>
       <c r="U16" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V16" s="8" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="X16" s="9" t="inlineStr">
         <is>
-          <t>0☂</t>
-        </is>
+          <t>11☂</t>
+        </is>
+      </c>
+      <c r="Y16" s="8" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>0a838d77l1lhvwurirt76tdpsj4f7z4m</t>
+          <t>0a837fbbl1lcvvfvrrb6nbtsxdr5xk2w</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>龙昌路中南·上悦城站点A</t>
+          <t>天元东路辅路南京义乌小商品城站点H</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>李小凯</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -7852,83 +8027,86 @@
         <v>10</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>9</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>101</v>
+        <v>194</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="L17" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M17" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="8" t="n">
-        <v>10</v>
+      <c r="N17" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="O17" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="P17" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q17" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="Q17" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="R17" s="7" t="n">
-        <v>0</v>
+      <c r="R17" s="8" t="n">
+        <v>23</v>
       </c>
       <c r="S17" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="T17" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U17" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W17" s="8" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="X17" s="9" t="inlineStr">
         <is>
-          <t>0☂</t>
-        </is>
+          <t>24☂</t>
+        </is>
+      </c>
+      <c r="Y17" s="8" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>1084739124625276928</t>
+          <t>889935238642700288</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>骆村路骆村新寓A区站点A</t>
+          <t>南京市江宁区淳化街道博观路保利·梧桐语</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>李小凯</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -7940,92 +8118,95 @@
         <v>10</v>
       </c>
       <c r="F18" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="O18" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="G18" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>112</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="L18" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="M18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="O18" s="8" t="n">
-        <v>11</v>
-      </c>
       <c r="P18" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="R18" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="R18" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="S18" s="8" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="T18" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U18" s="8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V18" s="8" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="W18" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="X18" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
+      </c>
+      <c r="Y18" s="8" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>0a8399c6l1lafj2jwu8mjgfk6ey4azv5</t>
+          <t>1222113693250682880</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>翔凤路南京传媒学院(滨江校区)站点A</t>
+          <t>灵谷寺3</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>王兴星</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>13</v>
@@ -8034,10 +8215,10 @@
         <v>10</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>401</v>
+        <v>338</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -8046,58 +8227,63 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>46%</t>
-        </is>
-      </c>
-      <c r="L19" s="7" t="n">
-        <v>0</v>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>70</v>
       </c>
       <c r="M19" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N19" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="O19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q19" s="10" t="n">
-        <v>22</v>
+      <c r="N19" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>66</v>
+      </c>
+      <c r="P19" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q19" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="R19" s="8" t="n">
-        <v>54</v>
-      </c>
-      <c r="S19" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="S19" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="W19" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="T19" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v>54</v>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="W19" s="8" t="n">
-        <v>63</v>
-      </c>
-      <c r="X19" s="8" t="n">
-        <v>66</v>
+      <c r="X19" s="9" t="inlineStr">
+        <is>
+          <t>10☂</t>
+        </is>
+      </c>
+      <c r="Y19" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1lef7k2csswc8vwddi6uiwm</t>
+          <t>0a8302d5l1lir2dxfqaeqgk2ktn2mjev</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>鹏山路东方·龙湖湾站点Z2</t>
+          <t>高新-高校-金科北门2-全周-全天-30</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -8114,29 +8300,29 @@
         <v>20</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>54%</t>
-        </is>
-      </c>
-      <c r="L20" s="10" t="n">
-        <v>11</v>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>55</v>
       </c>
       <c r="M20" s="10" t="n">
         <v>11</v>
@@ -8144,227 +8330,232 @@
       <c r="N20" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="10" t="n">
+      <c r="O20" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="P20" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q20" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="Q20" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="R20" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="S20" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v>33</v>
+      <c r="R20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="T20" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="U20" s="8" t="n">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="V20" s="8" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="W20" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="X20" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="X20" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y20" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>0a83266cl1lk3m5wqzw62amyv92hkd8u</t>
+          <t>0a8399c6l1lafj2jwu8mjgfk6ey4azv5</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>吉印大道融信·铂岸中心站点</t>
+          <t>翔凤路南京传媒学院(滨江校区)站点A</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>午峰</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>388</v>
+        <v>424</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="L21" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M21" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="N21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="10" t="n">
+      <c r="M21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="10" t="n">
         <v>11</v>
       </c>
+      <c r="O21" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="P21" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q21" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q21" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="R21" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="S21" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="W21" s="8" t="n">
+        <v>63</v>
+      </c>
+      <c r="X21" s="8" t="n">
         <v>66</v>
       </c>
-      <c r="R21" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="S21" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="W21" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="X21" s="9" t="inlineStr">
-        <is>
-          <t>38☂</t>
-        </is>
+      <c r="Y21" s="10" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>0a83e97al1lc2u39m23hpc95reridhru</t>
+          <t>0a83a414l1lef7k2csswc8vwddi6uiwm</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>飞鹰路江苏诗奈德环境科技有限公司站点</t>
+          <t>鹏山路东方·龙湖湾站点Z2</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>午峰</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>385</v>
+        <v>295</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="L22" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="M22" s="7" t="n">
-        <v>0</v>
+      <c r="M22" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="N22" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O22" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="P22" s="8" t="n">
+      <c r="O22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q22" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="Q22" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="R22" s="10" t="n">
-        <v>11</v>
+      <c r="R22" s="8" t="n">
+        <v>33</v>
       </c>
       <c r="S22" s="8" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="T22" s="8" t="n">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="U22" s="8" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="V22" s="8" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="W22" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="X22" s="9" t="inlineStr">
-        <is>
-          <t>22☂</t>
-        </is>
+        <v>33</v>
+      </c>
+      <c r="X22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="8" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>0a8399del1lpatica57gdhs2ewi7n3bb</t>
+          <t>0a83266cl1lk3m5wqzw62amyv92hkd8u</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>景明大街南京工艺装备制造股份有限公司站点</t>
+          <t>吉印大道融信·铂岸中心站点</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -8376,78 +8567,81 @@
         <v>20</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>712</v>
+        <v>436</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="L23" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M23" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="10" t="n">
+      <c r="M23" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="N23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="10" t="n">
         <v>11</v>
-      </c>
-      <c r="O23" s="8" t="n">
-        <v>49</v>
       </c>
       <c r="P23" s="10" t="n">
         <v>11</v>
       </c>
       <c r="Q23" s="8" t="n">
-        <v>130</v>
+        <v>66</v>
       </c>
       <c r="R23" s="8" t="n">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="S23" s="8" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="T23" s="8" t="n">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="U23" s="8" t="n">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c r="V23" s="8" t="n">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="W23" s="8" t="n">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="X23" s="9" t="inlineStr">
         <is>
-          <t>66☂</t>
-        </is>
+          <t>38☂</t>
+        </is>
+      </c>
+      <c r="Y23" s="8" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>0a837b0dl1lkxirtat6acfd4praab85m</t>
+          <t>0a83e97al1lc2u39m23hpc95reridhru</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>兴城路弘阳禹州燕澜新苑站点B</t>
+          <t>飞鹰路江苏诗奈德环境科技有限公司站点</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -8461,331 +8655,343 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>774</v>
+        <v>440</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="L24" s="7" t="n">
-        <v>0</v>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="L24" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="M24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N24" s="8" t="n">
+      <c r="N24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="P24" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q24" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="R24" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="S24" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="O24" s="8" t="n">
-        <v>88</v>
-      </c>
-      <c r="P24" s="8" t="n">
-        <v>78</v>
-      </c>
-      <c r="Q24" s="8" t="n">
-        <v>66</v>
-      </c>
-      <c r="R24" s="10" t="n">
-        <v>38</v>
-      </c>
-      <c r="S24" s="8" t="n">
-        <v>99</v>
-      </c>
       <c r="T24" s="8" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="U24" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="W24" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="V24" s="8" t="n">
-        <v>72</v>
-      </c>
-      <c r="W24" s="8" t="n">
-        <v>104</v>
-      </c>
       <c r="X24" s="9" t="inlineStr">
         <is>
-          <t>55☂</t>
-        </is>
+          <t>22☂</t>
+        </is>
+      </c>
+      <c r="Y24" s="8" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>1158030571808550912</t>
+          <t>0a8399del1lpatica57gdhs2ewi7n3bb</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>1号门</t>
+          <t>景明大街南京工艺装备制造股份有限公司站点</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>王兴星</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>137</v>
+        <v>789</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="L25" s="8" t="n">
-        <v>10</v>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N25" s="8" t="n">
-        <v>10</v>
+      <c r="N25" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="O25" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="P25" s="7" t="n">
-        <v>0</v>
+        <v>49</v>
+      </c>
+      <c r="P25" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="Q25" s="8" t="n">
-        <v>11</v>
+        <v>130</v>
       </c>
       <c r="R25" s="8" t="n">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="S25" s="8" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="T25" s="8" t="n">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="U25" s="8" t="n">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="V25" s="8" t="n">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="W25" s="8" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="X25" s="9" t="inlineStr">
         <is>
-          <t>0☂</t>
-        </is>
+          <t>66☂</t>
+        </is>
+      </c>
+      <c r="Y25" s="8" t="n">
+        <v>77</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>1158030563076009984</t>
+          <t>0a837b0dl1lkxirtat6acfd4praab85m</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>灵谷寺公园1</t>
+          <t>兴城路弘阳禹州燕澜新苑站点B</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>王兴星</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>10</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>441</v>
+        <v>827</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="L26" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M26" s="8" t="n">
-        <v>20</v>
+      <c r="M26" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N26" s="8" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="O26" s="8" t="n">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="P26" s="8" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="8" t="n">
-        <v>30</v>
+        <v>78</v>
+      </c>
+      <c r="Q26" s="8" t="n">
+        <v>66</v>
+      </c>
+      <c r="R26" s="10" t="n">
+        <v>38</v>
       </c>
       <c r="S26" s="8" t="n">
-        <v>23</v>
+        <v>99</v>
       </c>
       <c r="T26" s="8" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="U26" s="8" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="V26" s="8" t="n">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="W26" s="8" t="n">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="X26" s="9" t="inlineStr">
         <is>
-          <t>10☂</t>
-        </is>
+          <t>55☂</t>
+        </is>
+      </c>
+      <c r="Y26" s="8" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>1158030574945890304</t>
+          <t>0a83e076l1lkwmm8yrm9y6xcfj5ha9z5</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>灵谷寺2</t>
+          <t>土山路东域城站点A</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>王兴星</t>
+          <t>李小凯</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>午峰+晚峰+夜间</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
         <v>10</v>
       </c>
       <c r="F27" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="G27" s="3" t="n">
+      <c r="N27" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="O27" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="P27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="R27" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="S27" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="W27" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="X27" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="H27" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>465</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="L27" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="M27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="8" t="n">
-        <v>57</v>
-      </c>
-      <c r="O27" s="8" t="n">
-        <v>104</v>
-      </c>
-      <c r="P27" s="8" t="n">
-        <v>106</v>
-      </c>
-      <c r="Q27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="S27" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v>31</v>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="W27" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="X27" s="9" t="inlineStr">
+      <c r="Y27" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
@@ -8794,12 +9000,12 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>1222113693250682880</t>
+          <t>1158030571808550912</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>灵谷寺3</t>
+          <t>1号门</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -8809,99 +9015,102 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
         <v>10</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G28" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>147</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="H28" s="3" t="n">
+      <c r="M28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="I28" s="3" t="n">
-        <v>338</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="M28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="8" t="n">
-        <v>44</v>
-      </c>
       <c r="O28" s="8" t="n">
-        <v>66</v>
-      </c>
-      <c r="P28" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="P28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="R28" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="S28" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="U28" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="Q28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="8" t="n">
+      <c r="V28" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="S28" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v>30</v>
-      </c>
       <c r="W28" s="8" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="X28" s="9" t="inlineStr">
         <is>
-          <t>10☂</t>
-        </is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y28" s="8" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>0a8302d5l1lir2dxfqaeqgk2ktn2mjev</t>
+          <t>1158030563076009984</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>高新-高校-金科北门2-全周-全天-30</t>
+          <t>灵谷寺公园1</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>王兴星</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>午峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>13</v>
@@ -8910,10 +9119,10 @@
         <v>11</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>270</v>
+        <v>451</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -8922,68 +9131,73 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>38%</t>
-        </is>
-      </c>
-      <c r="L29" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="M29" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="N29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="10" t="n">
-        <v>12</v>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="N29" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="O29" s="8" t="n">
+        <v>129</v>
       </c>
       <c r="P29" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q29" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="R29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="T29" s="10" t="n">
-        <v>11</v>
+        <v>46</v>
+      </c>
+      <c r="Q29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="S29" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v>36</v>
       </c>
       <c r="U29" s="8" t="n">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="V29" s="8" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W29" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="X29" s="10" t="n">
-        <v>11</v>
+        <v>24</v>
+      </c>
+      <c r="X29" s="9" t="inlineStr">
+        <is>
+          <t>10☂</t>
+        </is>
+      </c>
+      <c r="Y29" s="8" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>0a83e076l1lkwmm8yrm9y6xcfj5ha9z5</t>
+          <t>1158030574945890304</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>土山路东域城站点A</t>
+          <t>灵谷寺2</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>李小凯</t>
+          <t>王兴星</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>午峰+晚峰+夜间</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
@@ -8999,7 +9213,7 @@
         <v>11</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>128</v>
+        <v>475</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -9011,43 +9225,48 @@
           <t>85%</t>
         </is>
       </c>
-      <c r="L30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="8" t="n">
-        <v>12</v>
+      <c r="L30" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="M30" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N30" s="8" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="O30" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="P30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="8" t="n">
-        <v>12</v>
+        <v>104</v>
+      </c>
+      <c r="P30" s="8" t="n">
+        <v>106</v>
+      </c>
+      <c r="Q30" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="R30" s="8" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="S30" s="8" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T30" s="8" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="U30" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V30" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W30" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="X30" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="X30" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y30" s="8" t="n">
         <v>10</v>
       </c>
     </row>
@@ -9076,25 +9295,25 @@
         <v>10</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="L31" s="8" t="n">
@@ -9136,6 +9355,9 @@
       <c r="X31" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="Y31" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -9162,25 +9384,25 @@
         <v>10</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="L32" s="7" t="n">
@@ -9222,6 +9444,9 @@
       <c r="X32" s="8" t="n">
         <v>22</v>
       </c>
+      <c r="Y32" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -9248,16 +9473,16 @@
         <v>20</v>
       </c>
       <c r="F33" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="G33" s="3" t="n">
         <v>12</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>11</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>9</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -9266,7 +9491,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="L33" s="8" t="n">
@@ -9310,6 +9535,9 @@
           <t>19☂</t>
         </is>
       </c>
+      <c r="Y33" s="10" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -9336,16 +9564,16 @@
         <v>10</v>
       </c>
       <c r="F34" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="G34" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="H34" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="H34" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="I34" s="3" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -9354,7 +9582,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="L34" s="8" t="n">
@@ -9398,16 +9626,19 @@
           <t>8☂</t>
         </is>
       </c>
+      <c r="Y34" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>0a8399c6l1lyqmcfy95bgdbwqabrgty5</t>
+          <t>0a8399c6l1l4y8jhxjgrp6t9eecq3anb</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>平泰街太平花苑站点</t>
+          <t>胜太路77-4号胜泰新寓站点</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -9417,7 +9648,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
@@ -9433,7 +9664,7 @@
         <v>12</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>270</v>
+        <v>229</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -9446,59 +9677,64 @@
         </is>
       </c>
       <c r="L35" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="M35" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O35" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="P35" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q35" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="M35" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="O35" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="P35" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q35" s="8" t="n">
-        <v>25</v>
-      </c>
       <c r="R35" s="8" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="S35" s="8" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="T35" s="8" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="U35" s="8" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="V35" s="8" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="W35" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="X35" s="8" t="n">
-        <v>14</v>
+        <v>31</v>
+      </c>
+      <c r="X35" s="9" t="inlineStr">
+        <is>
+          <t>10☂</t>
+        </is>
+      </c>
+      <c r="Y35" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>0a83677al1le5riuz94ztwxrizakym55</t>
+          <t>0a8399c6l1lyqmcfy95bgdbwqabrgty5</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>东山-31</t>
+          <t>平泰街太平花苑站点</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>李小凯</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -9510,164 +9746,168 @@
         <v>10</v>
       </c>
       <c r="F36" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G36" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="G36" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="H36" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>159</v>
+        <v>283</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="L36" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="M36" s="8" t="n">
-        <v>11</v>
+        <v>21</v>
+      </c>
+      <c r="M36" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N36" s="8" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="O36" s="8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P36" s="8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q36" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="R36" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="R36" s="8" t="n">
+        <v>14</v>
       </c>
       <c r="S36" s="8" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="T36" s="8" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="U36" s="8" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="V36" s="8" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="W36" s="8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="X36" s="8" t="n">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="Y36" s="8" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1l8wxq7ggvbwv6ueqbp4nwi</t>
+          <t>0a83677al1le5riuz94ztwxrizakym55</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>南京工程学院4号门右侧</t>
+          <t>东山-31</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>李小凯</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>午峰</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F37" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="L37" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="M37" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="N37" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="O37" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="P37" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q37" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="R37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="U37" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="G37" s="3" t="n">
+      <c r="V37" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="W37" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="H37" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="I37" s="3" t="n">
-        <v>1194</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="L37" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="M37" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="N37" s="8" t="n">
-        <v>53</v>
-      </c>
-      <c r="O37" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="P37" s="8" t="n">
-        <v>53</v>
-      </c>
-      <c r="Q37" s="10" t="n">
-        <v>34</v>
-      </c>
-      <c r="R37" s="8" t="n">
-        <v>73</v>
-      </c>
-      <c r="S37" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v>92</v>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v>242</v>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v>132</v>
-      </c>
-      <c r="W37" s="8" t="n">
-        <v>325</v>
-      </c>
-      <c r="X37" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+      <c r="X37" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y37" s="8" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>889665664809402368</t>
+          <t>0a83a414l1l8wxq7ggvbwv6ueqbp4nwi</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>高新-高校-金科南门C-全周-全天-20</t>
+          <t>南京工程学院4号门右侧</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -9677,23 +9917,23 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>831</v>
+        <v>1231</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -9702,65 +9942,68 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="L38" s="8" t="n">
-        <v>68</v>
-      </c>
-      <c r="M38" s="8" t="n">
-        <v>44</v>
+        <v>70</v>
+      </c>
+      <c r="M38" s="10" t="n">
+        <v>36</v>
       </c>
       <c r="N38" s="8" t="n">
-        <v>57</v>
-      </c>
-      <c r="O38" s="8" t="n">
-        <v>78</v>
-      </c>
-      <c r="P38" s="10" t="n">
-        <v>12</v>
+        <v>53</v>
+      </c>
+      <c r="O38" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="P38" s="8" t="n">
+        <v>53</v>
       </c>
       <c r="Q38" s="10" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="R38" s="8" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="S38" s="10" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="T38" s="8" t="n">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="U38" s="8" t="n">
-        <v>83</v>
+        <v>242</v>
       </c>
       <c r="V38" s="8" t="n">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="W38" s="8" t="n">
-        <v>173</v>
+        <v>325</v>
       </c>
       <c r="X38" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
+      </c>
+      <c r="Y38" s="10" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>1158030572869709824</t>
+          <t>889665664809402368</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>东沟停车场</t>
+          <t>高新-高校-金科南门C-全周-全天-20</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>王兴星</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -9772,78 +10015,81 @@
         <v>30</v>
       </c>
       <c r="F39" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>68</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="O39" s="8" t="n">
+        <v>78</v>
+      </c>
+      <c r="P39" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="G39" s="3" t="n">
+      <c r="Q39" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="H39" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>3012</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>92%</t>
-        </is>
-      </c>
-      <c r="L39" s="8" t="n">
-        <v>650</v>
-      </c>
-      <c r="M39" s="8" t="n">
-        <v>323</v>
-      </c>
-      <c r="N39" s="8" t="n">
-        <v>562</v>
-      </c>
-      <c r="O39" s="8" t="n">
-        <v>475</v>
-      </c>
-      <c r="P39" s="8" t="n">
-        <v>335</v>
-      </c>
-      <c r="Q39" s="8" t="n">
-        <v>31</v>
-      </c>
       <c r="R39" s="8" t="n">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="S39" s="10" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T39" s="8" t="n">
-        <v>163</v>
+        <v>123</v>
       </c>
       <c r="U39" s="8" t="n">
-        <v>168</v>
+        <v>83</v>
       </c>
       <c r="V39" s="8" t="n">
-        <v>61</v>
+        <v>113</v>
       </c>
       <c r="W39" s="8" t="n">
-        <v>110</v>
+        <v>173</v>
       </c>
       <c r="X39" s="9" t="inlineStr">
         <is>
-          <t>10☂</t>
-        </is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y39" s="8" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>0a83d79bl1lpdksp2k3xft245nxum95d</t>
+          <t>0a837fbbl1l2mga28qk2ua9idgju7ay3</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>胜太西路辅路南京晨伟智慧医疗技术创新中心站点C</t>
+          <t>胜太西路47号汇金新天地广场站点</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -9853,11 +10099,11 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰+晚峰</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>12</v>
@@ -9869,7 +10115,7 @@
         <v>12</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>745</v>
+        <v>514</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -9885,53 +10131,58 @@
         <v>33</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="O40" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="P40" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q40" s="8" t="n">
+        <v>53</v>
+      </c>
+      <c r="R40" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="S40" s="8" t="n">
+        <v>63</v>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="W40" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="P40" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q40" s="8" t="n">
-        <v>82</v>
-      </c>
-      <c r="R40" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="S40" s="8" t="n">
-        <v>81</v>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="V40" s="8" t="n">
-        <v>99</v>
-      </c>
-      <c r="W40" s="8" t="n">
-        <v>70</v>
-      </c>
       <c r="X40" s="9" t="inlineStr">
         <is>
-          <t>26☂</t>
+          <t>33☂</t>
+        </is>
+      </c>
+      <c r="Y40" s="9" t="inlineStr">
+        <is>
+          <t>22☂</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>0a837fbbl1l2mga28qk2ua9idgju7ay3</t>
+          <t>0a8327a1l1l2i45kzhd965ga45mfsnmd</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>胜太西路47号汇金新天地广场站点</t>
+          <t>胜太西路45号汇金新天地广场站点</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -9945,7 +10196,7 @@
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>12</v>
@@ -9957,7 +10208,7 @@
         <v>12</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>492</v>
+        <v>332</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -9970,82 +10221,87 @@
         </is>
       </c>
       <c r="L41" s="8" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M41" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="N41" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="O41" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="P41" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q41" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="N41" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="O41" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="P41" s="8" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q41" s="8" t="n">
-        <v>53</v>
-      </c>
       <c r="R41" s="8" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="S41" s="8" t="n">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="T41" s="8" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="U41" s="8" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="V41" s="8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="W41" s="8" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="X41" s="9" t="inlineStr">
         <is>
-          <t>33☂</t>
+          <t>10☂</t>
+        </is>
+      </c>
+      <c r="Y41" s="9" t="inlineStr">
+        <is>
+          <t>20☂</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>0a8327a1l1l2i45kzhd965ga45mfsnmd</t>
+          <t>1158030569614929920</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>胜太西路45号汇金新天地广场站点</t>
+          <t>海底世界站台</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>王兴星</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰+晚峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>12</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>312</v>
+        <v>2155</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -10054,86 +10310,89 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="L42" s="8" t="n">
-        <v>37</v>
+        <v>388</v>
       </c>
       <c r="M42" s="8" t="n">
-        <v>21</v>
+        <v>529</v>
       </c>
       <c r="N42" s="8" t="n">
-        <v>21</v>
+        <v>349</v>
       </c>
       <c r="O42" s="8" t="n">
-        <v>11</v>
+        <v>313</v>
       </c>
       <c r="P42" s="8" t="n">
-        <v>32</v>
+        <v>200</v>
       </c>
       <c r="Q42" s="8" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="R42" s="8" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="S42" s="8" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="T42" s="8" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="U42" s="8" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="V42" s="8" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="W42" s="8" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="X42" s="9" t="inlineStr">
         <is>
-          <t>10☂</t>
-        </is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y42" s="10" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>0a8327a1l1l9znhti7amyny5jau6s88v</t>
+          <t>1158030572869709824</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>胜太西路天琪雅居站点</t>
+          <t>东沟停车场</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>王兴星</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>12</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>247</v>
+        <v>3042</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -10142,60 +10401,63 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="L43" s="8" t="n">
-        <v>11</v>
+        <v>650</v>
       </c>
       <c r="M43" s="8" t="n">
-        <v>11</v>
+        <v>323</v>
       </c>
       <c r="N43" s="8" t="n">
-        <v>14</v>
+        <v>562</v>
       </c>
       <c r="O43" s="8" t="n">
-        <v>24</v>
+        <v>475</v>
       </c>
       <c r="P43" s="8" t="n">
-        <v>19</v>
+        <v>335</v>
       </c>
       <c r="Q43" s="8" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="R43" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="S43" s="8" t="n">
-        <v>26</v>
+        <v>104</v>
+      </c>
+      <c r="S43" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="T43" s="8" t="n">
-        <v>14</v>
+        <v>163</v>
       </c>
       <c r="U43" s="8" t="n">
-        <v>14</v>
+        <v>168</v>
       </c>
       <c r="V43" s="8" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="W43" s="8" t="n">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="X43" s="9" t="inlineStr">
         <is>
-          <t>13☂</t>
-        </is>
+          <t>10☂</t>
+        </is>
+      </c>
+      <c r="Y43" s="8" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>0a83f7a2l1l6vmcxbhqt6iytqih598fa</t>
+          <t>0a83d79bl1lpdksp2k3xft245nxum95d</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>怡园路南京航空航天大学(将军路校区)站点Z</t>
+          <t>胜太西路辅路南京晨伟智慧医疗技术创新中心站点C</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -10205,23 +10467,23 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>1471</v>
+        <v>770</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -10234,56 +10496,59 @@
         </is>
       </c>
       <c r="L44" s="8" t="n">
-        <v>124</v>
+        <v>33</v>
       </c>
       <c r="M44" s="8" t="n">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="N44" s="8" t="n">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="O44" s="8" t="n">
-        <v>121</v>
+        <v>55</v>
       </c>
       <c r="P44" s="8" t="n">
-        <v>186</v>
+        <v>24</v>
       </c>
       <c r="Q44" s="8" t="n">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="R44" s="8" t="n">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="S44" s="8" t="n">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="T44" s="8" t="n">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="U44" s="8" t="n">
-        <v>155</v>
+        <v>58</v>
       </c>
       <c r="V44" s="8" t="n">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="W44" s="8" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="X44" s="9" t="inlineStr">
         <is>
-          <t>63☂</t>
-        </is>
+          <t>26☂</t>
+        </is>
+      </c>
+      <c r="Y44" s="8" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>0a8327a1l1lvvssa38rf3eqprenmxv2y</t>
+          <t>0a8327a1l1l9znhti7amyny5jau6s88v</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>胜太西路辅路南京航空航天大学(将军路校区)站点J</t>
+          <t>胜太西路天琪雅居站点</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -10293,23 +10558,23 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
         <v>10</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>206</v>
+        <v>271</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -10322,56 +10587,59 @@
         </is>
       </c>
       <c r="L45" s="8" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="M45" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N45" s="8" t="n">
         <v>14</v>
       </c>
       <c r="O45" s="8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P45" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q45" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="R45" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="S45" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="Q45" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="R45" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="S45" s="8" t="n">
+      <c r="T45" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="T45" s="8" t="n">
+      <c r="U45" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="V45" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="U45" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="V45" s="8" t="n">
-        <v>12</v>
-      </c>
       <c r="W45" s="8" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="X45" s="9" t="inlineStr">
         <is>
-          <t>14☂</t>
-        </is>
+          <t>13☂</t>
+        </is>
+      </c>
+      <c r="Y45" s="8" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>0a8399c6l1l4y8jhxjgrp6t9eecq3anb</t>
+          <t>0a83f7a2l1l6vmcxbhqt6iytqih598fa</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>胜太路77-4号胜泰新寓站点</t>
+          <t>怡园路南京航空航天大学(将军路校区)站点Z</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -10381,23 +10649,23 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>229</v>
+        <v>1564</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -10410,61 +10678,64 @@
         </is>
       </c>
       <c r="L46" s="8" t="n">
-        <v>22</v>
+        <v>124</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="N46" s="8" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="O46" s="8" t="n">
-        <v>10</v>
+        <v>121</v>
       </c>
       <c r="P46" s="8" t="n">
-        <v>20</v>
+        <v>186</v>
       </c>
       <c r="Q46" s="8" t="n">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="R46" s="8" t="n">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="S46" s="8" t="n">
-        <v>21</v>
+        <v>127</v>
       </c>
       <c r="T46" s="8" t="n">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="U46" s="8" t="n">
-        <v>22</v>
+        <v>155</v>
       </c>
       <c r="V46" s="8" t="n">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="W46" s="8" t="n">
-        <v>31</v>
+        <v>92</v>
       </c>
       <c r="X46" s="9" t="inlineStr">
         <is>
-          <t>10☂</t>
-        </is>
+          <t>63☂</t>
+        </is>
+      </c>
+      <c r="Y46" s="8" t="n">
+        <v>93</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>0a83933al1l9u8y6b894j6jxgvg9a7ye</t>
+          <t>0a8327a1l1lvvssa38rf3eqprenmxv2y</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>锦文大道辅路龙湖·水晶郦城站点C</t>
+          <t>胜太西路辅路南京航空航天大学(将军路校区)站点J</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -10473,107 +10744,110 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F47" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L47" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="M47" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="N47" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="O47" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="P47" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q47" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="R47" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="S47" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="U47" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="G47" s="3" t="n">
+      <c r="V47" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="H47" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="I47" s="3" t="n">
-        <v>656</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L47" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="M47" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="N47" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="O47" s="8" t="n">
-        <v>88</v>
-      </c>
-      <c r="P47" s="8" t="n">
-        <v>63</v>
-      </c>
-      <c r="Q47" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="R47" s="8" t="n">
-        <v>77</v>
-      </c>
-      <c r="S47" s="8" t="n">
-        <v>74</v>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="V47" s="8" t="n">
-        <v>52</v>
-      </c>
       <c r="W47" s="8" t="n">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="X47" s="9" t="inlineStr">
         <is>
-          <t>42☂</t>
-        </is>
+          <t>14☂</t>
+        </is>
+      </c>
+      <c r="Y47" s="8" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>1158030569614929920</t>
+          <t>0a83933al1l9u8y6b894j6jxgvg9a7ye</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>海底世界站台</t>
+          <t>锦文大道辅路龙湖·水晶郦城站点C</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>王兴星</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2145</v>
+        <v>689</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -10586,45 +10860,48 @@
         </is>
       </c>
       <c r="L48" s="8" t="n">
-        <v>388</v>
+        <v>20</v>
       </c>
       <c r="M48" s="8" t="n">
-        <v>529</v>
+        <v>33</v>
       </c>
       <c r="N48" s="8" t="n">
-        <v>349</v>
+        <v>22</v>
       </c>
       <c r="O48" s="8" t="n">
-        <v>313</v>
+        <v>88</v>
       </c>
       <c r="P48" s="8" t="n">
-        <v>200</v>
+        <v>63</v>
       </c>
       <c r="Q48" s="8" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="R48" s="8" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="S48" s="8" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="T48" s="8" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="U48" s="8" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="V48" s="8" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="W48" s="8" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="X48" s="9" t="inlineStr">
         <is>
-          <t>0☂</t>
-        </is>
+          <t>42☂</t>
+        </is>
+      </c>
+      <c r="Y48" s="8" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="49">
@@ -10652,16 +10929,16 @@
         <v>10</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>752</v>
+        <v>782</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -10714,6 +10991,9 @@
           <t>21☂</t>
         </is>
       </c>
+      <c r="Y49" s="8" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -10740,16 +11020,16 @@
         <v>60</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>4467</v>
+        <v>4597</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -10802,6 +11082,9 @@
           <t>132☂</t>
         </is>
       </c>
+      <c r="Y50" s="8" t="n">
+        <v>130</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -10828,16 +11111,16 @@
         <v>10</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>792</v>
+        <v>802</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -10890,6 +11173,9 @@
           <t>20☂</t>
         </is>
       </c>
+      <c r="Y51" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -10916,16 +11202,16 @@
         <v>10</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>2543</v>
+        <v>2563</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -10978,6 +11264,9 @@
           <t>0☂</t>
         </is>
       </c>
+      <c r="Y52" s="8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -11004,16 +11293,16 @@
         <v>10</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -11066,6 +11355,9 @@
           <t>10☂</t>
         </is>
       </c>
+      <c r="Y53" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -11092,16 +11384,16 @@
         <v>10</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>563</v>
+        <v>587</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -11151,6 +11443,9 @@
       </c>
       <c r="X54" s="8" t="n">
         <v>12</v>
+      </c>
+      <c r="Y54" s="8" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -14542,20 +14837,20 @@
         <v>5</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -14577,25 +14872,25 @@
         <v>11</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>88.1%</t>
+          <t>86.2%</t>
         </is>
       </c>
     </row>
@@ -14612,25 +14907,25 @@
         <v>2</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>80.8%</t>
         </is>
       </c>
     </row>
@@ -14647,10 +14942,10 @@
         <v>1</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>4</v>
@@ -14660,12 +14955,12 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
     </row>
@@ -14717,16 +15012,16 @@
         <v>6</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -14735,7 +15030,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>84.8%</t>
         </is>
       </c>
     </row>
@@ -15155,25 +15450,25 @@
         <v>10</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>94.6%</t>
         </is>
       </c>
     </row>
@@ -15190,25 +15485,25 @@
         <v>12</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>60.4%</t>
         </is>
       </c>
     </row>
@@ -15225,25 +15520,25 @@
         <v>10</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -15260,25 +15555,25 @@
         <v>11</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>87.9%</t>
+          <t>88.1%</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
@@ -15295,25 +15590,25 @@
         <v>9</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
     </row>

--- a/coverage.xlsx
+++ b/coverage.xlsx
@@ -583,12 +583,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>86.6%</t>
+          <t>86.9%</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>82.7%</t>
         </is>
       </c>
     </row>
@@ -639,12 +639,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>82.7%</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>75.3%</t>
         </is>
       </c>
     </row>
@@ -680,14 +680,14 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>数据范围: 20261001 ~ 20261020</t>
+          <t>数据范围: 20261001 ~ 20261021</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>工作日: 14天, 周末: 6天</t>
+          <t>工作日: 15天, 周末: 6天</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y37"/>
+  <dimension ref="A1:Z37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -758,6 +758,7 @@
     <col width="11" customWidth="1" min="23" max="23"/>
     <col width="11" customWidth="1" min="24" max="24"/>
     <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -893,6 +894,11 @@
           <t>10-20(二)</t>
         </is>
       </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>10-21(三)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -919,25 +925,25 @@
         <v>10</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="L3" s="7" t="n">
@@ -984,6 +990,9 @@
       <c r="Y3" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="Z3" s="8" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -1010,25 +1019,25 @@
         <v>20</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="L4" s="8" t="n">
@@ -1075,30 +1084,33 @@
       <c r="Y4" s="10" t="n">
         <v>11</v>
       </c>
+      <c r="Z4" s="8" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>1174627346911133696</t>
+          <t>0a8331d4l1lrsht99jr5si9gwy5xrc6x</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区洪武路街道户部街长发银座</t>
+          <t>钟灵街2A</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>14</v>
@@ -1107,10 +1119,10 @@
         <v>9</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>200</v>
+        <v>311</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -1119,141 +1131,147 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="L5" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="M5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>65</v>
       </c>
       <c r="O5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="R5" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="S5" s="8" t="n">
-        <v>20</v>
+      <c r="P5" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T5" s="8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U5" s="8" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="V5" s="8" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="W5" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="X5" s="7" t="n">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="X5" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
       <c r="Y5" s="8" t="n">
-        <v>20</v>
+        <v>19</v>
+      </c>
+      <c r="Z5" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>0a8331d4l1lrsht99jr5si9gwy5xrc6x</t>
+          <t>1174627346911133696</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>钟灵街2A</t>
+          <t>南京市秦淮区洪武路街道户部街长发银座</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>午峰</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>13</v>
-      </c>
       <c r="G6" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>9</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>311</v>
+        <v>220</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="L6" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="R6" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="S6" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="V6" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="M6" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="N6" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="O6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v>43</v>
-      </c>
       <c r="W6" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="X6" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="X6" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="Y6" s="8" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="Z6" s="8" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -1281,25 +1299,25 @@
         <v>15</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>357</v>
+        <v>457</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="L7" s="7" t="n">
@@ -1346,6 +1364,9 @@
           <t>0☂</t>
         </is>
       </c>
+      <c r="Z7" s="8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -1372,25 +1393,25 @@
         <v>15</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1257</v>
+        <v>1353</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="L8" s="8" t="n">
@@ -1435,6 +1456,9 @@
       <c r="Y8" s="8" t="n">
         <v>75</v>
       </c>
+      <c r="Z8" s="8" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -1461,25 +1485,25 @@
         <v>15</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1065</v>
+        <v>1105</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="L9" s="8" t="n">
@@ -1524,6 +1548,9 @@
       <c r="Y9" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="Z9" s="8" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -1550,25 +1577,25 @@
         <v>20</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>8</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>598</v>
+        <v>612</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="L10" s="8" t="n">
@@ -1615,6 +1642,9 @@
       <c r="Y10" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="Z10" s="10" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -1641,20 +1671,20 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1504</v>
+        <v>1540</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -1704,6 +1734,9 @@
       <c r="Y11" s="11" t="n">
         <v>21</v>
       </c>
+      <c r="Z11" s="11" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -1730,25 +1763,25 @@
         <v>20</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G12" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="H12" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="I12" s="3" t="n">
-        <v>302</v>
+        <v>327</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="L12" s="8" t="n">
@@ -1793,6 +1826,9 @@
       <c r="Y12" s="8" t="n">
         <v>25</v>
       </c>
+      <c r="Z12" s="8" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -1819,25 +1855,25 @@
         <v>20</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>578</v>
+        <v>620</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="L13" s="7" t="n">
@@ -1886,6 +1922,9 @@
           <t>0☂</t>
         </is>
       </c>
+      <c r="Z13" s="8" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -1912,25 +1951,25 @@
         <v>20</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G14" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H14" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="H14" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="I14" s="3" t="n">
-        <v>1215</v>
+        <v>1390</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="L14" s="7" t="n">
@@ -1977,6 +2016,9 @@
           <t>0☂</t>
         </is>
       </c>
+      <c r="Z14" s="8" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -2003,25 +2045,25 @@
         <v>15</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>954</v>
+        <v>1112</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="L15" s="7" t="n">
@@ -2068,16 +2110,19 @@
       <c r="Y15" s="8" t="n">
         <v>44</v>
       </c>
+      <c r="Z15" s="8" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>732955142450266112</t>
+          <t>0a836a6al1l268p7ak2p5yn7sfzs2tsg</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区双塘街道中山南路夫子庙秦淮风光带</t>
+          <t>中山东路228号新世纪广场A幢投放点</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -2091,84 +2136,87 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>446</v>
+        <v>805</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="L16" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="M16" s="7" t="n">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="M16" s="8" t="n">
+        <v>40</v>
       </c>
       <c r="N16" s="8" t="n">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="P16" s="8" t="n">
-        <v>50</v>
+        <v>60</v>
+      </c>
+      <c r="P16" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="Q16" s="8" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="R16" s="8" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="S16" s="8" t="n">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="T16" s="8" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="U16" s="8" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="V16" s="8" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="X16" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
       </c>
-      <c r="Y16" s="7" t="n">
+      <c r="Y16" s="8" t="n">
+        <v>79</v>
+      </c>
+      <c r="Z16" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>732951617602912256</t>
+          <t>732955142450266112</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区瑞金路街道西安门地铁站投放点</t>
+          <t>南京市秦淮区双塘街道中山南路夫子庙秦淮风光带</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -2178,181 +2226,185 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
         <v>19</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>863</v>
+        <v>543</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="L17" s="8" t="n">
-        <v>122</v>
-      </c>
-      <c r="M17" s="8" t="n">
-        <v>104</v>
-      </c>
-      <c r="N17" s="7" t="n">
-        <v>0</v>
+        <v>52</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="8" t="n">
+        <v>25</v>
       </c>
       <c r="O17" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="P17" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="P17" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="Q17" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="R17" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="S17" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="U17" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="R17" s="8" t="n">
-        <v>37</v>
-      </c>
-      <c r="S17" s="8" t="n">
-        <v>37</v>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v>98</v>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v>119</v>
-      </c>
       <c r="V17" s="8" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="W17" s="8" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="X17" s="9" t="inlineStr">
         <is>
-          <t>43☂</t>
-        </is>
-      </c>
-      <c r="Y17" s="8" t="n">
-        <v>88</v>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="8" t="n">
+        <v>97</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>684038567596433408</t>
+          <t>732951617602912256</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路公交站台</t>
+          <t>南京市秦淮区瑞金路街道西安门地铁站投放点</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>早峰+晚峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F18" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G18" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G18" s="3" t="n">
-        <v>11</v>
-      </c>
       <c r="H18" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>1749</v>
+        <v>908</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>未配置</t>
-        </is>
-      </c>
-      <c r="L18" s="11" t="n">
-        <v>139</v>
-      </c>
-      <c r="M18" s="11" t="n">
-        <v>161</v>
-      </c>
-      <c r="N18" s="11" t="n">
-        <v>106</v>
-      </c>
-      <c r="O18" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="P18" s="11" t="n">
-        <v>111</v>
-      </c>
-      <c r="Q18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="11" t="n">
-        <v>241</v>
-      </c>
-      <c r="S18" s="11" t="n">
-        <v>233</v>
-      </c>
-      <c r="T18" s="11" t="n">
-        <v>253</v>
-      </c>
-      <c r="U18" s="11" t="n">
-        <v>167</v>
-      </c>
-      <c r="V18" s="11" t="n">
-        <v>141</v>
-      </c>
-      <c r="W18" s="11" t="n">
-        <v>165</v>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="n">
+        <v>122</v>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>104</v>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="P18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="R18" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="S18" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v>119</v>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="W18" s="8" t="n">
+        <v>72</v>
       </c>
       <c r="X18" s="9" t="inlineStr">
         <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Y18" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+          <t>43☂</t>
+        </is>
+      </c>
+      <c r="Y18" s="8" t="n">
+        <v>88</v>
+      </c>
+      <c r="Z18" s="8" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>e5189cd954054116aa19db28790cc606</t>
+          <t>684038567596433408</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-高新地铁站-30</t>
+          <t>25-晚峰-地铁站-柳州东路公交站台</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -2366,19 +2418,19 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F19" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="G19" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G19" s="3" t="n">
-        <v>11</v>
-      </c>
       <c r="H19" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>869</v>
+        <v>1774</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -2387,44 +2439,44 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
-        </is>
-      </c>
-      <c r="L19" s="8" t="n">
+          <t>未配置</t>
+        </is>
+      </c>
+      <c r="L19" s="11" t="n">
+        <v>139</v>
+      </c>
+      <c r="M19" s="11" t="n">
+        <v>161</v>
+      </c>
+      <c r="N19" s="11" t="n">
+        <v>106</v>
+      </c>
+      <c r="O19" s="11" t="n">
         <v>32</v>
       </c>
-      <c r="M19" s="8" t="n">
-        <v>62</v>
-      </c>
-      <c r="N19" s="8" t="n">
-        <v>31</v>
-      </c>
-      <c r="O19" s="8" t="n">
-        <v>54</v>
-      </c>
-      <c r="P19" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q19" s="8" t="n">
-        <v>158</v>
-      </c>
-      <c r="R19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="8" t="n">
-        <v>121</v>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v>138</v>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v>97</v>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v>59</v>
-      </c>
-      <c r="W19" s="8" t="n">
-        <v>40</v>
+      <c r="P19" s="11" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="11" t="n">
+        <v>241</v>
+      </c>
+      <c r="S19" s="11" t="n">
+        <v>233</v>
+      </c>
+      <c r="T19" s="11" t="n">
+        <v>253</v>
+      </c>
+      <c r="U19" s="11" t="n">
+        <v>167</v>
+      </c>
+      <c r="V19" s="11" t="n">
+        <v>141</v>
+      </c>
+      <c r="W19" s="11" t="n">
+        <v>165</v>
       </c>
       <c r="X19" s="9" t="inlineStr">
         <is>
@@ -2433,33 +2485,36 @@
       </c>
       <c r="Y19" s="9" t="inlineStr">
         <is>
-          <t>57☂</t>
-        </is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Z19" s="11" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>1101025367910903808</t>
+          <t>e5189cd954054116aa19db28790cc606</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>中山南路379号南京夫子庙秦淮风光带投放点A渗透</t>
+          <t>25-晚峰-地铁站-高新地铁站-30</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰+晚峰</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>13</v>
@@ -2468,10 +2523,10 @@
         <v>12</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>769</v>
+        <v>970</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -2480,77 +2535,82 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>53</v>
-      </c>
-      <c r="M20" s="10" t="n">
-        <v>4</v>
+        <v>32</v>
+      </c>
+      <c r="M20" s="8" t="n">
+        <v>62</v>
       </c>
       <c r="N20" s="8" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="O20" s="8" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="P20" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q20" s="8" t="n">
+        <v>158</v>
+      </c>
+      <c r="R20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="8" t="n">
+        <v>121</v>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v>138</v>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v>59</v>
+      </c>
+      <c r="W20" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="Q20" s="8" t="n">
-        <v>73</v>
-      </c>
-      <c r="R20" s="8" t="n">
-        <v>72</v>
-      </c>
-      <c r="S20" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v>91</v>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v>90</v>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v>175</v>
-      </c>
-      <c r="W20" s="8" t="n">
-        <v>74</v>
-      </c>
       <c r="X20" s="9" t="inlineStr">
         <is>
-          <t>16☂</t>
-        </is>
-      </c>
-      <c r="Y20" s="7" t="n">
-        <v>0</v>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y20" s="9" t="inlineStr">
+        <is>
+          <t>57☂</t>
+        </is>
+      </c>
+      <c r="Z20" s="8" t="n">
+        <v>101</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>1174627254806421504</t>
+          <t>554207268778184704</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区五老村街道淮海路淮海路31号院</t>
+          <t>25-晚峰-地铁站-柳州东路3号口</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+晚峰</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>13</v>
@@ -2559,10 +2619,10 @@
         <v>12</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>348</v>
+        <v>1368</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -2571,159 +2631,167 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="L21" s="8" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="O21" s="10" t="n">
-        <v>11</v>
+        <v>50</v>
+      </c>
+      <c r="O21" s="8" t="n">
+        <v>75</v>
       </c>
       <c r="P21" s="8" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="Q21" s="8" t="n">
-        <v>34</v>
+        <v>125</v>
       </c>
       <c r="R21" s="8" t="n">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="S21" s="8" t="n">
-        <v>57</v>
+        <v>149</v>
       </c>
       <c r="T21" s="8" t="n">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="U21" s="8" t="n">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="V21" s="8" t="n">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="W21" s="8" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="X21" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
       </c>
-      <c r="Y21" s="7" t="n">
+      <c r="Y21" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Z21" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>732956028185985024</t>
+          <t>1101025367910903808</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>下马坊地铁站</t>
+          <t>中山南路379号南京夫子庙秦淮风光带投放点A渗透</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F22" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G22" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="H22" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>1281</v>
+        <v>872</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="L22" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="M22" s="8" t="n">
-        <v>67</v>
+        <v>53</v>
+      </c>
+      <c r="M22" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="N22" s="8" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="O22" s="8" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="P22" s="8" t="n">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="R22" s="8" t="n">
-        <v>117</v>
-      </c>
-      <c r="S22" s="8" t="n">
-        <v>33</v>
+        <v>72</v>
+      </c>
+      <c r="S22" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="T22" s="8" t="n">
-        <v>145</v>
+        <v>91</v>
       </c>
       <c r="U22" s="8" t="n">
-        <v>203</v>
+        <v>90</v>
       </c>
       <c r="V22" s="8" t="n">
         <v>175</v>
       </c>
       <c r="W22" s="8" t="n">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="X22" s="9" t="inlineStr">
         <is>
-          <t>0☂</t>
+          <t>16☂</t>
         </is>
       </c>
       <c r="Y22" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="Z22" s="8" t="n">
+        <v>103</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1lp8ayqb5m6m5jv9xbfnhd9</t>
+          <t>1174627254806421504</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>中山东路原国民政府旧址-国民党中央监察委员会办公楼旧址投放点</t>
+          <t>南京市秦淮区五老村街道淮海路淮海路31号院</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -2732,89 +2800,92 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F23" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G23" s="3" t="n">
         <v>13</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>12</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>12</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1524</v>
+        <v>383</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="L23" s="8" t="n">
-        <v>195</v>
+        <v>20</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="N23" s="8" t="n">
-        <v>267</v>
-      </c>
-      <c r="O23" s="8" t="n">
-        <v>195</v>
+        <v>20</v>
+      </c>
+      <c r="O23" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="P23" s="8" t="n">
-        <v>97</v>
+        <v>46</v>
       </c>
       <c r="Q23" s="8" t="n">
-        <v>177</v>
+        <v>34</v>
       </c>
       <c r="R23" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="S23" s="7" t="n">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="S23" s="8" t="n">
+        <v>57</v>
       </c>
       <c r="T23" s="8" t="n">
-        <v>122</v>
+        <v>20</v>
       </c>
       <c r="U23" s="8" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="V23" s="8" t="n">
-        <v>118</v>
+        <v>20</v>
       </c>
       <c r="W23" s="8" t="n">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="X23" s="9" t="inlineStr">
         <is>
-          <t>10☂</t>
-        </is>
-      </c>
-      <c r="Y23" s="8" t="n">
-        <v>95</v>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="8" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>0a836a6al1l268p7ak2p5yn7sfzs2tsg</t>
+          <t>732956028185985024</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>中山东路228号新世纪广场A幢投放点</t>
+          <t>下马坊地铁站</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -2823,199 +2894,207 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F24" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G24" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="G24" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="H24" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>805</v>
+        <v>1374</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="L24" s="8" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="N24" s="8" t="n">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="O24" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="P24" s="7" t="n">
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="P24" s="8" t="n">
+        <v>114</v>
       </c>
       <c r="Q24" s="8" t="n">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="R24" s="8" t="n">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="S24" s="8" t="n">
-        <v>113</v>
+        <v>33</v>
       </c>
       <c r="T24" s="8" t="n">
-        <v>40</v>
+        <v>145</v>
       </c>
       <c r="U24" s="8" t="n">
-        <v>76</v>
+        <v>203</v>
       </c>
       <c r="V24" s="8" t="n">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="W24" s="8" t="n">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="X24" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
       </c>
-      <c r="Y24" s="8" t="n">
-        <v>79</v>
+      <c r="Y24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="8" t="n">
+        <v>93</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>0a83eb4fl1lz4hvkvkpdqc8mwis9httv</t>
+          <t>0a836587l1lp8ayqb5m6m5jv9xbfnhd9</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>仙林中心（地铁站）投放点A</t>
+          <t>中山东路原国民政府旧址-国民党中央监察委员会办公楼旧址投放点</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>全天点位</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>14</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>906</v>
+        <v>1637</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>未配置</t>
-        </is>
-      </c>
-      <c r="L25" s="11" t="n">
-        <v>175</v>
-      </c>
-      <c r="M25" s="11" t="n">
-        <v>75</v>
-      </c>
-      <c r="N25" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="O25" s="11" t="n">
-        <v>197</v>
-      </c>
-      <c r="P25" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q25" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="R25" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="S25" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="T25" s="11" t="n">
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>195</v>
+      </c>
+      <c r="M25" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="U25" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="V25" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="W25" s="11" t="n">
-        <v>119</v>
-      </c>
-      <c r="X25" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y25" s="11" t="n">
-        <v>25</v>
+      <c r="N25" s="8" t="n">
+        <v>267</v>
+      </c>
+      <c r="O25" s="8" t="n">
+        <v>195</v>
+      </c>
+      <c r="P25" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>177</v>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="S25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v>122</v>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>118</v>
+      </c>
+      <c r="W25" s="8" t="n">
+        <v>99</v>
+      </c>
+      <c r="X25" s="9" t="inlineStr">
+        <is>
+          <t>10☂</t>
+        </is>
+      </c>
+      <c r="Y25" s="8" t="n">
+        <v>95</v>
+      </c>
+      <c r="Z25" s="8" t="n">
+        <v>113</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>732955258519240704</t>
+          <t>0a83eb4fl1lz4hvkvkpdqc8mwis9httv</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路1号口</t>
+          <t>仙林中心（地铁站）投放点A</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰+晚峰</t>
+          <t>全天点位</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>1268</v>
+        <v>931</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -3028,87 +3107,86 @@
         </is>
       </c>
       <c r="L26" s="11" t="n">
+        <v>175</v>
+      </c>
+      <c r="M26" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="N26" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="O26" s="11" t="n">
+        <v>197</v>
+      </c>
+      <c r="P26" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q26" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="R26" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="S26" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="M26" s="11" t="n">
-        <v>56</v>
-      </c>
-      <c r="N26" s="11" t="n">
-        <v>53</v>
-      </c>
-      <c r="O26" s="11" t="n">
-        <v>123</v>
-      </c>
-      <c r="P26" s="11" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q26" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="R26" s="11" t="n">
-        <v>68</v>
-      </c>
-      <c r="S26" s="11" t="n">
-        <v>78</v>
-      </c>
-      <c r="T26" s="11" t="n">
-        <v>74</v>
-      </c>
       <c r="U26" s="11" t="n">
-        <v>126</v>
+        <v>15</v>
       </c>
       <c r="V26" s="11" t="n">
-        <v>231</v>
+        <v>25</v>
       </c>
       <c r="W26" s="11" t="n">
-        <v>240</v>
-      </c>
-      <c r="X26" s="9" t="inlineStr">
-        <is>
-          <t>52☂</t>
-        </is>
-      </c>
-      <c r="Y26" s="9" t="inlineStr">
-        <is>
-          <t>35☂</t>
-        </is>
+        <v>119</v>
+      </c>
+      <c r="X26" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y26" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z26" s="11" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>554207268614606848</t>
+          <t>732955258519240704</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁-迈皋桥地铁站4号口</t>
+          <t>25-晚峰-地铁站-柳州东路1号口</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>早峰+晚峰+夜间</t>
+          <t>早峰+午峰+晚峰</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1788</v>
+        <v>1456</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -3117,91 +3195,94 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="L27" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M27" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N27" s="8" t="n">
-        <v>85</v>
-      </c>
-      <c r="O27" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="P27" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="Q27" s="8" t="n">
-        <v>104</v>
-      </c>
-      <c r="R27" s="8" t="n">
-        <v>168</v>
-      </c>
-      <c r="S27" s="8" t="n">
-        <v>250</v>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v>284</v>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v>213</v>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v>166</v>
-      </c>
-      <c r="W27" s="8" t="n">
-        <v>268</v>
+          <t>未配置</t>
+        </is>
+      </c>
+      <c r="L27" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="M27" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="N27" s="11" t="n">
+        <v>53</v>
+      </c>
+      <c r="O27" s="11" t="n">
+        <v>123</v>
+      </c>
+      <c r="P27" s="11" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q27" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="R27" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="S27" s="11" t="n">
+        <v>78</v>
+      </c>
+      <c r="T27" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="U27" s="11" t="n">
+        <v>126</v>
+      </c>
+      <c r="V27" s="11" t="n">
+        <v>231</v>
+      </c>
+      <c r="W27" s="11" t="n">
+        <v>240</v>
       </c>
       <c r="X27" s="9" t="inlineStr">
         <is>
-          <t>25☂</t>
+          <t>52☂</t>
         </is>
       </c>
       <c r="Y27" s="9" t="inlineStr">
         <is>
-          <t>120☂</t>
-        </is>
+          <t>35☂</t>
+        </is>
+      </c>
+      <c r="Z27" s="11" t="n">
+        <v>188</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>554207268778184704</t>
+          <t>554207268614606848</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路3号口</t>
+          <t>25-晚峰-地铁-迈皋桥地铁站4号口</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>早峰+晚峰</t>
+          <t>早峰+晚峰+夜间</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1368</v>
+        <v>2001</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -3210,54 +3291,57 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="n">
-        <v>37</v>
-      </c>
-      <c r="M28" s="8" t="n">
-        <v>50</v>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="L28" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M28" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="N28" s="8" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="O28" s="8" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="P28" s="8" t="n">
         <v>75</v>
       </c>
       <c r="Q28" s="8" t="n">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="R28" s="8" t="n">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="S28" s="8" t="n">
-        <v>149</v>
+        <v>250</v>
       </c>
       <c r="T28" s="8" t="n">
-        <v>150</v>
+        <v>284</v>
       </c>
       <c r="U28" s="8" t="n">
-        <v>150</v>
+        <v>213</v>
       </c>
       <c r="V28" s="8" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="W28" s="8" t="n">
-        <v>200</v>
+        <v>268</v>
       </c>
       <c r="X28" s="9" t="inlineStr">
         <is>
-          <t>0☂</t>
+          <t>25☂</t>
         </is>
       </c>
       <c r="Y28" s="9" t="inlineStr">
         <is>
-          <t>0☂</t>
-        </is>
+          <t>120☂</t>
+        </is>
+      </c>
+      <c r="Z28" s="8" t="n">
+        <v>213</v>
       </c>
     </row>
     <row r="29">
@@ -3285,16 +3369,16 @@
         <v>20</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1457</v>
+        <v>1569</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -3350,6 +3434,9 @@
       <c r="Y29" s="8" t="n">
         <v>154</v>
       </c>
+      <c r="Z29" s="8" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -3376,16 +3463,16 @@
         <v>15</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>931</v>
+        <v>978</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -3441,6 +3528,9 @@
       <c r="Y30" s="8" t="n">
         <v>68</v>
       </c>
+      <c r="Z30" s="8" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -3467,16 +3557,16 @@
         <v>20</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>2435</v>
+        <v>2505</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -3532,6 +3622,9 @@
       <c r="Y31" s="8" t="n">
         <v>183</v>
       </c>
+      <c r="Z31" s="8" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -3558,16 +3651,16 @@
         <v>19</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1099</v>
+        <v>1159</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -3623,6 +3716,9 @@
       <c r="Y32" s="8" t="n">
         <v>40</v>
       </c>
+      <c r="Z32" s="8" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -3649,16 +3745,16 @@
         <v>19</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1407</v>
+        <v>1566</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -3714,6 +3810,9 @@
       <c r="Y33" s="8" t="n">
         <v>174</v>
       </c>
+      <c r="Z33" s="8" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -3740,16 +3839,16 @@
         <v>19</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>922</v>
+        <v>1102</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -3805,6 +3904,9 @@
       <c r="Y34" s="8" t="n">
         <v>20</v>
       </c>
+      <c r="Z34" s="8" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -3831,16 +3933,16 @@
         <v>19</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1084</v>
+        <v>1240</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -3896,6 +3998,9 @@
       <c r="Y35" s="8" t="n">
         <v>21</v>
       </c>
+      <c r="Z35" s="8" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -3922,16 +4027,16 @@
         <v>20</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3213</v>
+        <v>3393</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -3987,6 +4092,9 @@
       <c r="Y36" s="8" t="n">
         <v>147</v>
       </c>
+      <c r="Z36" s="8" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -4013,16 +4121,16 @@
         <v>20</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1625</v>
+        <v>1739</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -4077,6 +4185,9 @@
       </c>
       <c r="Y37" s="8" t="n">
         <v>125</v>
+      </c>
+      <c r="Z37" s="8" t="n">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -6564,7 +6675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y54"/>
+  <dimension ref="A1:Z54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6592,6 +6703,7 @@
     <col width="11" customWidth="1" min="23" max="23"/>
     <col width="11" customWidth="1" min="24" max="24"/>
     <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6727,6 +6839,11 @@
           <t>10-20(二)</t>
         </is>
       </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>10-21(三)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -6753,25 +6870,25 @@
         <v>20</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>3</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="L3" s="7" t="n">
@@ -6818,21 +6935,24 @@
       <c r="Y3" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="Z3" s="10" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>0a8321fcl1ljahethcjq9qq42q3axjr8</t>
+          <t>0a838d5dl1lpybxf2cm2vhfyih32kncd</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>锦文大道鲁能硅谷公馆站点A</t>
+          <t>润发路南方时代广场群发路D站点D</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>李小凯</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -6841,89 +6961,92 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>5</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>165</v>
+        <v>54</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="L4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M4" s="10" t="n">
+      <c r="M4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="U4" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="N4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="U4" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="V4" s="8" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="W4" s="8" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="X4" s="9" t="inlineStr">
         <is>
-          <t>44☂</t>
-        </is>
-      </c>
-      <c r="Y4" s="8" t="n">
-        <v>22</v>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>893732199694139392</t>
+          <t>0a8321fcl1ljahethcjq9qq42q3axjr8</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>东新南路瓯江大厦站点</t>
+          <t>锦文大道鲁能硅谷公馆站点A</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>李小凯</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -6932,35 +7055,35 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="I5" s="3" t="n">
-        <v>46</v>
+        <v>201</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="L5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="7" t="n">
-        <v>0</v>
+      <c r="M5" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="N5" s="7" t="n">
         <v>0</v>
@@ -6968,8 +7091,8 @@
       <c r="O5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="10" t="n">
-        <v>2</v>
+      <c r="P5" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="Q5" s="7" t="n">
         <v>0</v>
@@ -6981,35 +7104,38 @@
         <v>0</v>
       </c>
       <c r="T5" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v>11</v>
+        <v>22</v>
+      </c>
+      <c r="U5" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="V5" s="8" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="W5" s="8" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="X5" s="9" t="inlineStr">
         <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Y5" s="7" t="n">
-        <v>0</v>
+          <t>44☂</t>
+        </is>
+      </c>
+      <c r="Y5" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z5" s="8" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>0a838d5dl1lpybxf2cm2vhfyih32kncd</t>
+          <t>893732199694139392</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>润发路南方时代广场群发路D站点D</t>
+          <t>东新南路瓯江大厦站点</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -7026,25 +7152,25 @@
         <v>10</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>5</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="L6" s="7" t="n">
@@ -7059,8 +7185,8 @@
       <c r="O6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="7" t="n">
-        <v>0</v>
+      <c r="P6" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="Q6" s="7" t="n">
         <v>0</v>
@@ -7068,21 +7194,21 @@
       <c r="R6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S6" s="8" t="n">
+      <c r="S6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="8" t="n">
         <v>10</v>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v>12</v>
       </c>
       <c r="U6" s="8" t="n">
         <v>11</v>
       </c>
       <c r="V6" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="W6" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="W6" s="8" t="n">
-        <v>10</v>
-      </c>
       <c r="X6" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
@@ -7090,6 +7216,9 @@
       </c>
       <c r="Y6" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="Z6" s="8" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -7117,25 +7246,25 @@
         <v>10</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="L7" s="7" t="n">
@@ -7182,6 +7311,9 @@
       <c r="Y7" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="Z7" s="8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -7208,25 +7340,25 @@
         <v>10</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="L8" s="7" t="n">
@@ -7273,6 +7405,9 @@
       <c r="Y8" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="Z8" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -7299,25 +7434,25 @@
         <v>10</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="L9" s="8" t="n">
@@ -7364,6 +7499,9 @@
       <c r="Y9" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="Z9" s="8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -7390,25 +7528,25 @@
         <v>10</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="L10" s="8" t="n">
@@ -7455,6 +7593,9 @@
       <c r="Y10" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="Z10" s="8" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -7481,25 +7622,25 @@
         <v>20</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="H11" s="3" t="n">
-        <v>8</v>
-      </c>
       <c r="I11" s="3" t="n">
-        <v>664</v>
+        <v>701</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="L11" s="8" t="n">
@@ -7546,6 +7687,9 @@
       <c r="Y11" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="Z11" s="8" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -7572,25 +7716,25 @@
         <v>20</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="H12" s="3" t="n">
-        <v>8</v>
-      </c>
       <c r="I12" s="3" t="n">
-        <v>291</v>
+        <v>324</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="L12" s="7" t="n">
@@ -7637,21 +7781,24 @@
       <c r="Y12" s="8" t="n">
         <v>33</v>
       </c>
+      <c r="Z12" s="8" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>0a838d77l1lhvwurirt76tdpsj4f7z4m</t>
+          <t>0a837fbbl1lcvvfvrrb6nbtsxdr5xk2w</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>龙昌路中南·上悦城站点A</t>
+          <t>天元东路辅路南京义乌小商品城站点H</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>李小凯</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -7663,81 +7810,84 @@
         <v>10</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>9</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>101</v>
+        <v>194</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="L13" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M13" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="8" t="n">
-        <v>10</v>
+      <c r="N13" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="O13" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="P13" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q13" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="Q13" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="R13" s="7" t="n">
-        <v>0</v>
+      <c r="R13" s="8" t="n">
+        <v>23</v>
       </c>
       <c r="S13" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="T13" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U13" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="V13" s="8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W13" s="8" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="X13" s="9" t="inlineStr">
         <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Y13" s="7" t="n">
+          <t>24☂</t>
+        </is>
+      </c>
+      <c r="Y13" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z13" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>1084739124625276928</t>
+          <t>0a838d77l1lhvwurirt76tdpsj4f7z4m</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>骆村路骆村新寓A区站点A</t>
+          <t>龙昌路中南·上悦城站点A</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -7754,25 +7904,25 @@
         <v>10</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>112</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="L14" s="8" t="n">
@@ -7781,14 +7931,14 @@
       <c r="M14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N14" s="8" t="n">
-        <v>23</v>
+      <c r="N14" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="O14" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="P14" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="P14" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="Q14" s="8" t="n">
         <v>10</v>
@@ -7797,16 +7947,16 @@
         <v>0</v>
       </c>
       <c r="S14" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T14" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U14" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V14" s="8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W14" s="8" t="n">
         <v>11</v>
@@ -7819,21 +7969,24 @@
       <c r="Y14" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="Z14" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>897028622557294592</t>
+          <t>1084739124625276928</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>南京工程学院5号门左手</t>
+          <t>骆村路骆村新寓A区站点A</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>李小凯</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -7842,89 +7995,92 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>10</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>190</v>
+        <v>135</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>31%</t>
-        </is>
-      </c>
-      <c r="L15" s="10" t="n">
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="L15" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="O15" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="P15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="R15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="M15" s="10" t="n">
+      <c r="T15" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="N15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="P15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="S15" s="10" t="n">
+      <c r="U15" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="V15" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="T15" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v>48</v>
-      </c>
       <c r="W15" s="8" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="X15" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
       </c>
-      <c r="Y15" s="10" t="n">
-        <v>13</v>
+      <c r="Y15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="8" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>889466722646794240</t>
+          <t>897028622557294592</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>胜太东路江宁供销商厦站点</t>
+          <t>南京工程学院5号门左手</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>李小凯</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -7933,89 +8089,92 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F16" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="L16" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="M16" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="P16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="G16" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>69%</t>
-        </is>
-      </c>
-      <c r="L16" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="M16" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="N16" s="8" t="n">
+      <c r="S16" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="W16" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="X16" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y16" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="O16" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="P16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="R16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="U16" s="8" t="n">
+      <c r="Z16" s="10" t="n">
         <v>12</v>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="W16" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="X16" s="9" t="inlineStr">
-        <is>
-          <t>11☂</t>
-        </is>
-      </c>
-      <c r="Y16" s="8" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>0a837fbbl1lcvvfvrrb6nbtsxdr5xk2w</t>
+          <t>889466722646794240</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>天元东路辅路南京义乌小商品城站点H</t>
+          <t>胜太东路江宁供销商厦站点</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>李小凯</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -8027,69 +8186,72 @@
         <v>10</v>
       </c>
       <c r="F17" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="N17" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="G17" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>194</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>69%</t>
-        </is>
-      </c>
-      <c r="L17" s="8" t="n">
+      <c r="O17" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="R17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="U17" s="8" t="n">
         <v>12</v>
-      </c>
-      <c r="M17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="O17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q17" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="R17" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="S17" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="T17" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="U17" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="V17" s="8" t="n">
         <v>12</v>
       </c>
       <c r="W17" s="8" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="X17" s="9" t="inlineStr">
         <is>
-          <t>24☂</t>
+          <t>11☂</t>
         </is>
       </c>
       <c r="Y17" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z17" s="8" t="n">
         <v>12</v>
       </c>
     </row>
@@ -8118,25 +8280,25 @@
         <v>10</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="L18" s="7" t="n">
@@ -8183,6 +8345,9 @@
       <c r="Y18" s="8" t="n">
         <v>38</v>
       </c>
+      <c r="Z18" s="8" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -8209,25 +8374,25 @@
         <v>10</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="L19" s="8" t="n">
@@ -8274,6 +8439,9 @@
       <c r="Y19" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="Z19" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -8300,25 +8468,25 @@
         <v>20</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="L20" s="8" t="n">
@@ -8363,6 +8531,9 @@
       <c r="Y20" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="Z20" s="8" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -8389,25 +8560,25 @@
         <v>30</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="L21" s="7" t="n">
@@ -8452,6 +8623,9 @@
       <c r="Y21" s="10" t="n">
         <v>23</v>
       </c>
+      <c r="Z21" s="8" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -8478,25 +8652,25 @@
         <v>20</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>295</v>
+        <v>339</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="L22" s="10" t="n">
@@ -8541,6 +8715,9 @@
       <c r="Y22" s="8" t="n">
         <v>35</v>
       </c>
+      <c r="Z22" s="8" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -8567,25 +8744,25 @@
         <v>20</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>436</v>
+        <v>479</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="L23" s="7" t="n">
@@ -8632,6 +8809,9 @@
       <c r="Y23" s="8" t="n">
         <v>48</v>
       </c>
+      <c r="Z23" s="8" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -8658,25 +8838,25 @@
         <v>20</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>440</v>
+        <v>484</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="L24" s="10" t="n">
@@ -8723,16 +8903,19 @@
       <c r="Y24" s="8" t="n">
         <v>55</v>
       </c>
+      <c r="Z24" s="8" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>0a8399del1lpatica57gdhs2ewi7n3bb</t>
+          <t>0a837b0dl1lkxirtat6acfd4praab85m</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>景明大街南京工艺装备制造股份有限公司站点</t>
+          <t>兴城路弘阳禹州燕澜新苑站点B</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -8746,28 +8929,28 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>789</v>
+        <v>875</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="L25" s="7" t="n">
@@ -8776,54 +8959,57 @@
       <c r="M25" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N25" s="10" t="n">
-        <v>11</v>
+      <c r="N25" s="8" t="n">
+        <v>55</v>
       </c>
       <c r="O25" s="8" t="n">
-        <v>49</v>
-      </c>
-      <c r="P25" s="10" t="n">
-        <v>11</v>
+        <v>88</v>
+      </c>
+      <c r="P25" s="8" t="n">
+        <v>78</v>
       </c>
       <c r="Q25" s="8" t="n">
-        <v>130</v>
-      </c>
-      <c r="R25" s="8" t="n">
         <v>66</v>
       </c>
+      <c r="R25" s="10" t="n">
+        <v>38</v>
+      </c>
       <c r="S25" s="8" t="n">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="T25" s="8" t="n">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="U25" s="8" t="n">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="V25" s="8" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="W25" s="8" t="n">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="X25" s="9" t="inlineStr">
         <is>
-          <t>66☂</t>
+          <t>55☂</t>
         </is>
       </c>
       <c r="Y25" s="8" t="n">
-        <v>77</v>
+        <v>53</v>
+      </c>
+      <c r="Z25" s="10" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>0a837b0dl1lkxirtat6acfd4praab85m</t>
+          <t>0a8399del1lpatica57gdhs2ewi7n3bb</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>兴城路弘阳禹州燕澜新苑站点B</t>
+          <t>景明大街南京工艺装备制造股份有限公司站点</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -8837,28 +9023,28 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>10</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>827</v>
+        <v>866</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="L26" s="7" t="n">
@@ -8867,43 +9053,46 @@
       <c r="M26" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N26" s="8" t="n">
+      <c r="N26" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="O26" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="P26" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q26" s="8" t="n">
+        <v>130</v>
+      </c>
+      <c r="R26" s="8" t="n">
+        <v>66</v>
+      </c>
+      <c r="S26" s="8" t="n">
+        <v>63</v>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v>86</v>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v>87</v>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v>88</v>
+      </c>
+      <c r="W26" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="O26" s="8" t="n">
-        <v>88</v>
-      </c>
-      <c r="P26" s="8" t="n">
-        <v>78</v>
-      </c>
-      <c r="Q26" s="8" t="n">
-        <v>66</v>
-      </c>
-      <c r="R26" s="10" t="n">
-        <v>38</v>
-      </c>
-      <c r="S26" s="8" t="n">
-        <v>99</v>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v>64</v>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v>72</v>
-      </c>
-      <c r="W26" s="8" t="n">
-        <v>104</v>
-      </c>
       <c r="X26" s="9" t="inlineStr">
         <is>
-          <t>55☂</t>
+          <t>66☂</t>
         </is>
       </c>
       <c r="Y26" s="8" t="n">
-        <v>53</v>
+        <v>77</v>
+      </c>
+      <c r="Z26" s="8" t="n">
+        <v>77</v>
       </c>
     </row>
     <row r="27">
@@ -8931,25 +9120,25 @@
         <v>10</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="L27" s="7" t="n">
@@ -8996,6 +9185,9 @@
           <t>0☂</t>
         </is>
       </c>
+      <c r="Z27" s="8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -9022,25 +9214,25 @@
         <v>10</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="L28" s="8" t="n">
@@ -9087,6 +9279,9 @@
       <c r="Y28" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="Z28" s="8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -9113,25 +9308,25 @@
         <v>10</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="L29" s="7" t="n">
@@ -9178,6 +9373,9 @@
       <c r="Y29" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="Z29" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -9204,25 +9402,25 @@
         <v>10</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="L30" s="8" t="n">
@@ -9269,6 +9467,9 @@
       <c r="Y30" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="Z30" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -9295,25 +9496,25 @@
         <v>10</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="L31" s="8" t="n">
@@ -9358,6 +9559,9 @@
       <c r="Y31" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="Z31" s="8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -9384,25 +9588,25 @@
         <v>10</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="L32" s="7" t="n">
@@ -9447,6 +9651,9 @@
       <c r="Y32" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="Z32" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -9473,25 +9680,25 @@
         <v>20</v>
       </c>
       <c r="F33" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G33" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="G33" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="H33" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="L33" s="8" t="n">
@@ -9538,6 +9745,9 @@
       <c r="Y33" s="10" t="n">
         <v>11</v>
       </c>
+      <c r="Z33" s="8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -9564,25 +9774,25 @@
         <v>10</v>
       </c>
       <c r="F34" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G34" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="H34" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="H34" s="3" t="n">
-        <v>11</v>
-      </c>
       <c r="I34" s="3" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="L34" s="8" t="n">
@@ -9629,6 +9839,9 @@
       <c r="Y34" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="Z34" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -9655,25 +9868,25 @@
         <v>10</v>
       </c>
       <c r="F35" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G35" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="G35" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="H35" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="L35" s="8" t="n">
@@ -9720,21 +9933,24 @@
       <c r="Y35" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="Z35" s="8" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>0a8399c6l1lyqmcfy95bgdbwqabrgty5</t>
+          <t>0a836758l1lnzcr39623ggbxyhbddncg</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>平泰街太平花苑站点</t>
+          <t>天元东路辅路南京义乌小商品城站点G</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -9746,16 +9962,16 @@
         <v>10</v>
       </c>
       <c r="F36" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G36" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="G36" s="3" t="n">
-        <v>13</v>
-      </c>
       <c r="H36" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>283</v>
+        <v>587</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -9768,62 +9984,65 @@
         </is>
       </c>
       <c r="L36" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="M36" s="7" t="n">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>48</v>
       </c>
       <c r="N36" s="8" t="n">
+        <v>106</v>
+      </c>
+      <c r="O36" s="8" t="n">
+        <v>82</v>
+      </c>
+      <c r="P36" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q36" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="O36" s="8" t="n">
+      <c r="R36" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="P36" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q36" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="R36" s="8" t="n">
-        <v>14</v>
-      </c>
       <c r="S36" s="8" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="T36" s="8" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="U36" s="8" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="V36" s="8" t="n">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="W36" s="8" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="X36" s="8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Y36" s="8" t="n">
-        <v>13</v>
+        <v>24</v>
+      </c>
+      <c r="Z36" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>0a83677al1le5riuz94ztwxrizakym55</t>
+          <t>0a8399c6l1lyqmcfy95bgdbwqabrgty5</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>东山-31</t>
+          <t>平泰街太平花苑站点</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>李小凯</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -9835,170 +10054,174 @@
         <v>10</v>
       </c>
       <c r="F37" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G37" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="G37" s="3" t="n">
+      <c r="H37" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>307</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="L37" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="M37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="O37" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="P37" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q37" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="R37" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="S37" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="W37" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="X37" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y37" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="H37" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="I37" s="3" t="n">
-        <v>180</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>93%</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>93%</t>
-        </is>
-      </c>
-      <c r="L37" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="M37" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="N37" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="O37" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="P37" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q37" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="R37" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="W37" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="X37" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y37" s="8" t="n">
-        <v>21</v>
+      <c r="Z37" s="8" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>0a83a414l1l8wxq7ggvbwv6ueqbp4nwi</t>
+          <t>0a83677al1le5riuz94ztwxrizakym55</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>南京工程学院4号门右侧</t>
+          <t>东山-31</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>李小凯</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>午峰</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>1231</v>
+        <v>192</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="L38" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="M38" s="10" t="n">
-        <v>36</v>
+        <v>11</v>
+      </c>
+      <c r="M38" s="8" t="n">
+        <v>11</v>
       </c>
       <c r="N38" s="8" t="n">
-        <v>53</v>
-      </c>
-      <c r="O38" s="10" t="n">
-        <v>42</v>
+        <v>11</v>
+      </c>
+      <c r="O38" s="8" t="n">
+        <v>22</v>
       </c>
       <c r="P38" s="8" t="n">
-        <v>53</v>
-      </c>
-      <c r="Q38" s="10" t="n">
-        <v>34</v>
-      </c>
-      <c r="R38" s="8" t="n">
-        <v>73</v>
-      </c>
-      <c r="S38" s="10" t="n">
-        <v>42</v>
+        <v>11</v>
+      </c>
+      <c r="Q38" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="R38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="8" t="n">
+        <v>11</v>
       </c>
       <c r="T38" s="8" t="n">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="U38" s="8" t="n">
-        <v>242</v>
+        <v>12</v>
       </c>
       <c r="V38" s="8" t="n">
-        <v>132</v>
+        <v>11</v>
       </c>
       <c r="W38" s="8" t="n">
-        <v>325</v>
-      </c>
-      <c r="X38" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Y38" s="10" t="n">
-        <v>37</v>
+        <v>12</v>
+      </c>
+      <c r="X38" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y38" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z38" s="8" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>889665664809402368</t>
+          <t>0a83a414l1l8wxq7ggvbwv6ueqbp4nwi</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>高新-高校-金科南门C-全周-全天-20</t>
+          <t>南京工程学院4号门右侧</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -10008,23 +10231,23 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>866</v>
+        <v>1357</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -10033,156 +10256,160 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="L39" s="8" t="n">
-        <v>68</v>
-      </c>
-      <c r="M39" s="8" t="n">
-        <v>44</v>
+        <v>70</v>
+      </c>
+      <c r="M39" s="10" t="n">
+        <v>36</v>
       </c>
       <c r="N39" s="8" t="n">
-        <v>57</v>
-      </c>
-      <c r="O39" s="8" t="n">
-        <v>78</v>
-      </c>
-      <c r="P39" s="10" t="n">
-        <v>12</v>
+        <v>53</v>
+      </c>
+      <c r="O39" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="P39" s="8" t="n">
+        <v>53</v>
       </c>
       <c r="Q39" s="10" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="R39" s="8" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="S39" s="10" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="T39" s="8" t="n">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="U39" s="8" t="n">
-        <v>83</v>
+        <v>242</v>
       </c>
       <c r="V39" s="8" t="n">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="W39" s="8" t="n">
-        <v>173</v>
+        <v>325</v>
       </c>
       <c r="X39" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
       </c>
-      <c r="Y39" s="8" t="n">
-        <v>35</v>
+      <c r="Y39" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="Z39" s="8" t="n">
+        <v>126</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>0a837fbbl1l2mga28qk2ua9idgju7ay3</t>
+          <t>889665664809402368</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>胜太西路47号汇金新天地广场站点</t>
+          <t>高新-高校-金科南门C-全周-全天-20</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰+晚峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F40" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>981</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="L40" s="8" t="n">
+        <v>68</v>
+      </c>
+      <c r="M40" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="N40" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="O40" s="8" t="n">
+        <v>78</v>
+      </c>
+      <c r="P40" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="G40" s="3" t="n">
+      <c r="Q40" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="H40" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>514</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L40" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="M40" s="8" t="n">
-        <v>31</v>
-      </c>
-      <c r="N40" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="O40" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="P40" s="8" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q40" s="8" t="n">
-        <v>53</v>
-      </c>
       <c r="R40" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="S40" s="8" t="n">
-        <v>63</v>
+        <v>60</v>
+      </c>
+      <c r="S40" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="T40" s="8" t="n">
-        <v>22</v>
+        <v>123</v>
       </c>
       <c r="U40" s="8" t="n">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="V40" s="8" t="n">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="W40" s="8" t="n">
-        <v>55</v>
+        <v>173</v>
       </c>
       <c r="X40" s="9" t="inlineStr">
         <is>
-          <t>33☂</t>
-        </is>
-      </c>
-      <c r="Y40" s="9" t="inlineStr">
-        <is>
-          <t>22☂</t>
-        </is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y40" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="Z40" s="8" t="n">
+        <v>115</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>0a8327a1l1l2i45kzhd965ga45mfsnmd</t>
+          <t>0a837fbbl1l2mga28qk2ua9idgju7ay3</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>胜太西路45号汇金新天地广场站点</t>
+          <t>胜太西路47号汇金新天地广场站点</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -10196,19 +10423,19 @@
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>332</v>
+        <v>568</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -10221,75 +10448,78 @@
         </is>
       </c>
       <c r="L41" s="8" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="M41" s="8" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="N41" s="8" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="O41" s="8" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="P41" s="8" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="Q41" s="8" t="n">
+        <v>53</v>
+      </c>
+      <c r="R41" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="S41" s="8" t="n">
+        <v>63</v>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="V41" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="R41" s="8" t="n">
-        <v>41</v>
-      </c>
-      <c r="S41" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v>32</v>
-      </c>
       <c r="W41" s="8" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="X41" s="9" t="inlineStr">
         <is>
-          <t>10☂</t>
+          <t>33☂</t>
         </is>
       </c>
       <c r="Y41" s="9" t="inlineStr">
         <is>
-          <t>20☂</t>
-        </is>
+          <t>22☂</t>
+        </is>
+      </c>
+      <c r="Z41" s="8" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>1158030569614929920</t>
+          <t>0a8327a1l1l2i45kzhd965ga45mfsnmd</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>海底世界站台</t>
+          <t>胜太西路45号汇金新天地广场站点</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>王兴星</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰+午峰+晚峰</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>13</v>
@@ -10298,10 +10528,10 @@
         <v>13</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>2155</v>
+        <v>354</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -10310,68 +10540,73 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="L42" s="8" t="n">
-        <v>388</v>
+        <v>37</v>
       </c>
       <c r="M42" s="8" t="n">
-        <v>529</v>
+        <v>21</v>
       </c>
       <c r="N42" s="8" t="n">
-        <v>349</v>
+        <v>21</v>
       </c>
       <c r="O42" s="8" t="n">
-        <v>313</v>
+        <v>11</v>
       </c>
       <c r="P42" s="8" t="n">
-        <v>200</v>
+        <v>32</v>
       </c>
       <c r="Q42" s="8" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="R42" s="8" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="S42" s="8" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="T42" s="8" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="U42" s="8" t="n">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="V42" s="8" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="W42" s="8" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="X42" s="9" t="inlineStr">
         <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Y42" s="10" t="n">
-        <v>10</v>
+          <t>10☂</t>
+        </is>
+      </c>
+      <c r="Y42" s="9" t="inlineStr">
+        <is>
+          <t>20☂</t>
+        </is>
+      </c>
+      <c r="Z42" s="8" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>1158030572869709824</t>
+          <t>0a83933al1l9u8y6b894j6jxgvg9a7ye</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>东沟停车场</t>
+          <t>锦文大道辅路龙湖·水晶郦城站点C</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>王兴星</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -10380,19 +10615,19 @@
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F43" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H43" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="G43" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="I43" s="3" t="n">
-        <v>3042</v>
+        <v>708</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -10401,89 +10636,92 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="L43" s="8" t="n">
-        <v>650</v>
+        <v>20</v>
       </c>
       <c r="M43" s="8" t="n">
-        <v>323</v>
+        <v>33</v>
       </c>
       <c r="N43" s="8" t="n">
-        <v>562</v>
+        <v>22</v>
       </c>
       <c r="O43" s="8" t="n">
-        <v>475</v>
+        <v>88</v>
       </c>
       <c r="P43" s="8" t="n">
-        <v>335</v>
+        <v>63</v>
       </c>
       <c r="Q43" s="8" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="R43" s="8" t="n">
-        <v>104</v>
-      </c>
-      <c r="S43" s="10" t="n">
-        <v>20</v>
+        <v>77</v>
+      </c>
+      <c r="S43" s="8" t="n">
+        <v>74</v>
       </c>
       <c r="T43" s="8" t="n">
-        <v>163</v>
+        <v>33</v>
       </c>
       <c r="U43" s="8" t="n">
-        <v>168</v>
+        <v>52</v>
       </c>
       <c r="V43" s="8" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="W43" s="8" t="n">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="X43" s="9" t="inlineStr">
         <is>
-          <t>10☂</t>
+          <t>42☂</t>
         </is>
       </c>
       <c r="Y43" s="8" t="n">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="Z43" s="10" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>0a83d79bl1lpdksp2k3xft245nxum95d</t>
+          <t>1158030569614929920</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>胜太西路辅路南京晨伟智慧医疗技术创新中心站点C</t>
+          <t>海底世界站台</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>王兴星</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>13</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>770</v>
+        <v>2186</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -10492,89 +10730,92 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="L44" s="8" t="n">
-        <v>33</v>
+        <v>388</v>
       </c>
       <c r="M44" s="8" t="n">
-        <v>54</v>
+        <v>529</v>
       </c>
       <c r="N44" s="8" t="n">
-        <v>61</v>
+        <v>349</v>
       </c>
       <c r="O44" s="8" t="n">
-        <v>55</v>
+        <v>313</v>
       </c>
       <c r="P44" s="8" t="n">
-        <v>24</v>
+        <v>200</v>
       </c>
       <c r="Q44" s="8" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="R44" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="S44" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="V44" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="S44" s="8" t="n">
-        <v>81</v>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v>99</v>
-      </c>
       <c r="W44" s="8" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="X44" s="9" t="inlineStr">
         <is>
-          <t>26☂</t>
-        </is>
-      </c>
-      <c r="Y44" s="8" t="n">
-        <v>25</v>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y44" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z44" s="8" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>0a8327a1l1l9znhti7amyny5jau6s88v</t>
+          <t>1158030572869709824</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>胜太西路天琪雅居站点</t>
+          <t>东沟停车场</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>王兴星</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>13</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>271</v>
+        <v>3141</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -10583,63 +10824,66 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="L45" s="8" t="n">
-        <v>11</v>
+        <v>650</v>
       </c>
       <c r="M45" s="8" t="n">
-        <v>11</v>
+        <v>323</v>
       </c>
       <c r="N45" s="8" t="n">
-        <v>14</v>
+        <v>562</v>
       </c>
       <c r="O45" s="8" t="n">
-        <v>24</v>
+        <v>475</v>
       </c>
       <c r="P45" s="8" t="n">
-        <v>19</v>
+        <v>335</v>
       </c>
       <c r="Q45" s="8" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="R45" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="S45" s="8" t="n">
-        <v>26</v>
+        <v>104</v>
+      </c>
+      <c r="S45" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="T45" s="8" t="n">
-        <v>14</v>
+        <v>163</v>
       </c>
       <c r="U45" s="8" t="n">
-        <v>14</v>
+        <v>168</v>
       </c>
       <c r="V45" s="8" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="W45" s="8" t="n">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="X45" s="9" t="inlineStr">
         <is>
-          <t>13☂</t>
+          <t>10☂</t>
         </is>
       </c>
       <c r="Y45" s="8" t="n">
-        <v>24</v>
+        <v>30</v>
+      </c>
+      <c r="Z45" s="8" t="n">
+        <v>99</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>0a83f7a2l1l6vmcxbhqt6iytqih598fa</t>
+          <t>0a83d79bl1lpdksp2k3xft245nxum95d</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>怡园路南京航空航天大学(将军路校区)站点Z</t>
+          <t>胜太西路辅路南京晨伟智慧医疗技术创新中心站点C</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -10649,23 +10893,23 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>1564</v>
+        <v>807</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -10678,59 +10922,62 @@
         </is>
       </c>
       <c r="L46" s="8" t="n">
-        <v>124</v>
+        <v>33</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="N46" s="8" t="n">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="O46" s="8" t="n">
-        <v>121</v>
+        <v>55</v>
       </c>
       <c r="P46" s="8" t="n">
-        <v>186</v>
+        <v>24</v>
       </c>
       <c r="Q46" s="8" t="n">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="R46" s="8" t="n">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="S46" s="8" t="n">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="T46" s="8" t="n">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="U46" s="8" t="n">
-        <v>155</v>
+        <v>58</v>
       </c>
       <c r="V46" s="8" t="n">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="W46" s="8" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="X46" s="9" t="inlineStr">
         <is>
-          <t>63☂</t>
+          <t>26☂</t>
         </is>
       </c>
       <c r="Y46" s="8" t="n">
-        <v>93</v>
+        <v>25</v>
+      </c>
+      <c r="Z46" s="8" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>0a8327a1l1lvvssa38rf3eqprenmxv2y</t>
+          <t>0a8327a1l1l9znhti7amyny5jau6s88v</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>胜太西路辅路南京航空航天大学(将军路校区)站点J</t>
+          <t>胜太西路天琪雅居站点</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -10740,23 +10987,23 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
         <v>10</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>217</v>
+        <v>284</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -10769,85 +11016,88 @@
         </is>
       </c>
       <c r="L47" s="8" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="M47" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N47" s="8" t="n">
         <v>14</v>
       </c>
       <c r="O47" s="8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P47" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q47" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="R47" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="S47" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="Q47" s="8" t="n">
+      <c r="T47" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="V47" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="W47" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="X47" s="9" t="inlineStr">
+        <is>
+          <t>13☂</t>
+        </is>
+      </c>
+      <c r="Y47" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z47" s="8" t="n">
         <v>13</v>
-      </c>
-      <c r="R47" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="S47" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="V47" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="W47" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="X47" s="9" t="inlineStr">
-        <is>
-          <t>14☂</t>
-        </is>
-      </c>
-      <c r="Y47" s="8" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>0a83933al1l9u8y6b894j6jxgvg9a7ye</t>
+          <t>0a83f7a2l1l6vmcxbhqt6iytqih598fa</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>锦文大道辅路龙湖·水晶郦城站点C</t>
+          <t>怡园路南京航空航天大学(将军路校区)站点Z</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>689</v>
+        <v>1647</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -10860,150 +11110,156 @@
         </is>
       </c>
       <c r="L48" s="8" t="n">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="M48" s="8" t="n">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="N48" s="8" t="n">
-        <v>22</v>
+        <v>141</v>
       </c>
       <c r="O48" s="8" t="n">
+        <v>121</v>
+      </c>
+      <c r="P48" s="8" t="n">
+        <v>186</v>
+      </c>
+      <c r="Q48" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="R48" s="8" t="n">
+        <v>106</v>
+      </c>
+      <c r="S48" s="8" t="n">
+        <v>127</v>
+      </c>
+      <c r="T48" s="8" t="n">
         <v>88</v>
       </c>
-      <c r="P48" s="8" t="n">
-        <v>63</v>
-      </c>
-      <c r="Q48" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="R48" s="8" t="n">
-        <v>77</v>
-      </c>
-      <c r="S48" s="8" t="n">
-        <v>74</v>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v>33</v>
-      </c>
       <c r="U48" s="8" t="n">
-        <v>52</v>
+        <v>155</v>
       </c>
       <c r="V48" s="8" t="n">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="W48" s="8" t="n">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="X48" s="9" t="inlineStr">
         <is>
-          <t>42☂</t>
+          <t>63☂</t>
         </is>
       </c>
       <c r="Y48" s="8" t="n">
-        <v>33</v>
+        <v>93</v>
+      </c>
+      <c r="Z48" s="8" t="n">
+        <v>83</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>1158030568570548224</t>
+          <t>0a8327a1l1lvvssa38rf3eqprenmxv2y</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>海底世界</t>
+          <t>胜太西路辅路南京航空航天大学(将军路校区)站点J</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>王兴星</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
         <v>10</v>
       </c>
       <c r="F49" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>249</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L49" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="M49" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="N49" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="O49" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="P49" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q49" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="G49" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="H49" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="I49" s="3" t="n">
-        <v>782</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L49" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="M49" s="8" t="n">
-        <v>140</v>
-      </c>
-      <c r="N49" s="8" t="n">
-        <v>140</v>
-      </c>
-      <c r="O49" s="8" t="n">
-        <v>90</v>
-      </c>
-      <c r="P49" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q49" s="8" t="n">
-        <v>20</v>
-      </c>
       <c r="R49" s="8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="S49" s="8" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="T49" s="8" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="U49" s="8" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="V49" s="8" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="W49" s="8" t="n">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="X49" s="9" t="inlineStr">
         <is>
-          <t>21☂</t>
+          <t>14☂</t>
         </is>
       </c>
       <c r="Y49" s="8" t="n">
-        <v>30</v>
+        <v>11</v>
+      </c>
+      <c r="Z49" s="8" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>1158030570667700224</t>
+          <t>1158030568570548224</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>美龄宫</t>
+          <t>海底世界</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -11017,84 +11273,87 @@
         </is>
       </c>
       <c r="E50" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>831</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="L50" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M50" s="8" t="n">
+        <v>140</v>
+      </c>
+      <c r="N50" s="8" t="n">
+        <v>140</v>
+      </c>
+      <c r="O50" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="P50" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q50" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="R50" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="S50" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="V50" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="F50" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="G50" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="H50" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="I50" s="3" t="n">
-        <v>4597</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K50" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="L50" s="8" t="n">
-        <v>441</v>
-      </c>
-      <c r="M50" s="8" t="n">
-        <v>157</v>
-      </c>
-      <c r="N50" s="8" t="n">
-        <v>114</v>
-      </c>
-      <c r="O50" s="8" t="n">
-        <v>147</v>
-      </c>
-      <c r="P50" s="8" t="n">
-        <v>496</v>
-      </c>
-      <c r="Q50" s="8" t="n">
-        <v>258</v>
-      </c>
-      <c r="R50" s="8" t="n">
-        <v>471</v>
-      </c>
-      <c r="S50" s="8" t="n">
-        <v>426</v>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v>462</v>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v>438</v>
-      </c>
-      <c r="V50" s="8" t="n">
-        <v>473</v>
-      </c>
       <c r="W50" s="8" t="n">
-        <v>452</v>
+        <v>53</v>
       </c>
       <c r="X50" s="9" t="inlineStr">
         <is>
-          <t>132☂</t>
+          <t>21☂</t>
         </is>
       </c>
       <c r="Y50" s="8" t="n">
-        <v>130</v>
+        <v>30</v>
+      </c>
+      <c r="Z50" s="8" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>1158025287508230144</t>
+          <t>1158030570667700224</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>3号门</t>
+          <t>美龄宫</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -11108,19 +11367,19 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>802</v>
+        <v>4788</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -11133,59 +11392,62 @@
         </is>
       </c>
       <c r="L51" s="8" t="n">
+        <v>441</v>
+      </c>
+      <c r="M51" s="8" t="n">
+        <v>157</v>
+      </c>
+      <c r="N51" s="8" t="n">
+        <v>114</v>
+      </c>
+      <c r="O51" s="8" t="n">
+        <v>147</v>
+      </c>
+      <c r="P51" s="8" t="n">
+        <v>496</v>
+      </c>
+      <c r="Q51" s="8" t="n">
+        <v>258</v>
+      </c>
+      <c r="R51" s="8" t="n">
+        <v>471</v>
+      </c>
+      <c r="S51" s="8" t="n">
+        <v>426</v>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v>462</v>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v>438</v>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v>473</v>
+      </c>
+      <c r="W51" s="8" t="n">
+        <v>452</v>
+      </c>
+      <c r="X51" s="9" t="inlineStr">
+        <is>
+          <t>132☂</t>
+        </is>
+      </c>
+      <c r="Y51" s="8" t="n">
         <v>130</v>
       </c>
-      <c r="M51" s="8" t="n">
-        <v>155</v>
-      </c>
-      <c r="N51" s="8" t="n">
-        <v>94</v>
-      </c>
-      <c r="O51" s="8" t="n">
-        <v>49</v>
-      </c>
-      <c r="P51" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q51" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="R51" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="S51" s="8" t="n">
-        <v>94</v>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v>105</v>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="V51" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="W51" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="X51" s="9" t="inlineStr">
-        <is>
-          <t>20☂</t>
-        </is>
-      </c>
-      <c r="Y51" s="8" t="n">
-        <v>10</v>
+      <c r="Z51" s="8" t="n">
+        <v>191</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>1158030573943451648</t>
+          <t>1158025287508230144</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>中山陵7号门</t>
+          <t>3号门</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -11202,16 +11464,16 @@
         <v>10</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>2563</v>
+        <v>853</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -11224,85 +11486,88 @@
         </is>
       </c>
       <c r="L52" s="8" t="n">
-        <v>715</v>
+        <v>130</v>
       </c>
       <c r="M52" s="8" t="n">
-        <v>442</v>
+        <v>155</v>
       </c>
       <c r="N52" s="8" t="n">
-        <v>493</v>
+        <v>94</v>
       </c>
       <c r="O52" s="8" t="n">
-        <v>330</v>
+        <v>49</v>
       </c>
       <c r="P52" s="8" t="n">
-        <v>162</v>
+        <v>10</v>
       </c>
       <c r="Q52" s="8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R52" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="S52" s="8" t="n">
+        <v>94</v>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v>105</v>
+      </c>
+      <c r="U52" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="S52" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v>81</v>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v>60</v>
-      </c>
       <c r="V52" s="8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="W52" s="8" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="X52" s="9" t="inlineStr">
         <is>
-          <t>0☂</t>
+          <t>20☂</t>
         </is>
       </c>
       <c r="Y52" s="8" t="n">
-        <v>20</v>
+        <v>10</v>
+      </c>
+      <c r="Z52" s="8" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>0a83a358l1lqdy2ba4s82zvgvr2zwiuj</t>
+          <t>1158030573943451648</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>严南路金辉禹洲金陵铭著站点A</t>
+          <t>中山陵7号门</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>王兴星</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
         <v>10</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>359</v>
+        <v>2614</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -11315,69 +11580,72 @@
         </is>
       </c>
       <c r="L53" s="8" t="n">
+        <v>715</v>
+      </c>
+      <c r="M53" s="8" t="n">
+        <v>442</v>
+      </c>
+      <c r="N53" s="8" t="n">
+        <v>493</v>
+      </c>
+      <c r="O53" s="8" t="n">
+        <v>330</v>
+      </c>
+      <c r="P53" s="8" t="n">
+        <v>162</v>
+      </c>
+      <c r="Q53" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="M53" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="N53" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="O53" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="P53" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q53" s="8" t="n">
-        <v>33</v>
-      </c>
       <c r="R53" s="8" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="S53" s="8" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="T53" s="8" t="n">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="U53" s="8" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="V53" s="8" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="W53" s="8" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="X53" s="9" t="inlineStr">
         <is>
-          <t>10☂</t>
+          <t>0☂</t>
         </is>
       </c>
       <c r="Y53" s="8" t="n">
-        <v>11</v>
+        <v>20</v>
+      </c>
+      <c r="Z53" s="8" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>0a836758l1lnzcr39623ggbxyhbddncg</t>
+          <t>0a83a358l1lqdy2ba4s82zvgvr2zwiuj</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>天元东路辅路南京义乌小商品城站点G</t>
+          <t>严南路金辉禹洲金陵铭著站点A</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
@@ -11393,7 +11661,7 @@
         <v>14</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>587</v>
+        <v>387</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -11406,46 +11674,51 @@
         </is>
       </c>
       <c r="L54" s="8" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="M54" s="8" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="N54" s="8" t="n">
-        <v>106</v>
+        <v>33</v>
       </c>
       <c r="O54" s="8" t="n">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="P54" s="8" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="Q54" s="8" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="R54" s="8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="S54" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="T54" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="T54" s="8" t="n">
-        <v>12</v>
-      </c>
       <c r="U54" s="8" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="V54" s="8" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="W54" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="X54" s="8" t="n">
-        <v>12</v>
+        <v>32</v>
+      </c>
+      <c r="X54" s="9" t="inlineStr">
+        <is>
+          <t>10☂</t>
+        </is>
       </c>
       <c r="Y54" s="8" t="n">
-        <v>24</v>
+        <v>11</v>
+      </c>
+      <c r="Z54" s="8" t="n">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -14802,25 +15075,25 @@
         <v>4</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>86.8%</t>
         </is>
       </c>
     </row>
@@ -14837,25 +15110,25 @@
         <v>5</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>81.7%</t>
         </is>
       </c>
     </row>
@@ -14872,25 +15145,25 @@
         <v>11</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>86.5%</t>
         </is>
       </c>
     </row>
@@ -14907,25 +15180,25 @@
         <v>2</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -14942,25 +15215,25 @@
         <v>1</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>35.7%</t>
         </is>
       </c>
     </row>
@@ -14977,25 +15250,25 @@
         <v>2</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F8" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="G8" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="G8" s="3" t="n">
-        <v>19</v>
-      </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -15012,25 +15285,25 @@
         <v>6</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>84.7%</t>
         </is>
       </c>
     </row>
@@ -15450,25 +15723,25 @@
         <v>10</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>94.6%</t>
+          <t>95.0%</t>
         </is>
       </c>
     </row>
@@ -15485,25 +15758,25 @@
         <v>12</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>60.8%</t>
         </is>
       </c>
     </row>
@@ -15520,25 +15793,25 @@
         <v>10</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.3%</t>
         </is>
       </c>
     </row>
@@ -15555,25 +15828,25 @@
         <v>11</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>88.1%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>87.7%</t>
         </is>
       </c>
     </row>
@@ -15590,25 +15863,25 @@
         <v>9</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
     </row>

--- a/coverage.xlsx
+++ b/coverage.xlsx
@@ -583,12 +583,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>86.9%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>83.4%</t>
         </is>
       </c>
     </row>
@@ -639,12 +639,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>83.8%</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>76.7%</t>
         </is>
       </c>
     </row>
@@ -680,14 +680,14 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>数据范围: 20261001 ~ 20261021</t>
+          <t>数据范围: 20261001 ~ 20261022</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>工作日: 15天, 周末: 6天</t>
+          <t>工作日: 16天, 周末: 6天</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z37"/>
+  <dimension ref="A1:AA37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -759,6 +759,7 @@
     <col width="11" customWidth="1" min="24" max="24"/>
     <col width="11" customWidth="1" min="25" max="25"/>
     <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -899,6 +900,11 @@
           <t>10-21(三)</t>
         </is>
       </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>10-22(四)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -925,25 +931,25 @@
         <v>10</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>164</v>
+        <v>234</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="L3" s="7" t="n">
@@ -993,21 +999,24 @@
       <c r="Z3" s="8" t="n">
         <v>32</v>
       </c>
+      <c r="AA3" s="8" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>778851422965239808</t>
+          <t>0a8331d4l1lrsht99jr5si9gwy5xrc6x</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-仙林新村</t>
+          <t>钟灵街2A</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1016,92 +1025,95 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>9</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>160</v>
+        <v>311</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="L4" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="M4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="10" t="n">
-        <v>5</v>
+        <v>25</v>
+      </c>
+      <c r="M4" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>65</v>
       </c>
       <c r="O4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P4" s="7" t="n">
-        <v>0</v>
+      <c r="P4" s="8" t="n">
+        <v>44</v>
       </c>
       <c r="Q4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="R4" s="8" t="n">
-        <v>25</v>
+      <c r="R4" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="S4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T4" s="10" t="n">
-        <v>1</v>
+      <c r="T4" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="U4" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="V4" s="10" t="n">
-        <v>15</v>
+        <v>22</v>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v>43</v>
       </c>
       <c r="W4" s="8" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="X4" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
       </c>
-      <c r="Y4" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z4" s="8" t="n">
-        <v>25</v>
+      <c r="Y4" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>0a8331d4l1lrsht99jr5si9gwy5xrc6x</t>
+          <t>778851422965239808</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>钟灵街2A</t>
+          <t>25-早峰-居民区-仙林新村</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1110,76 +1122,79 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>14</v>
-      </c>
       <c r="G5" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>311</v>
+        <v>185</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="L5" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="O5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="M5" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="N5" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="O5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="S5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T5" s="8" t="n">
-        <v>19</v>
+      <c r="T5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U5" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v>43</v>
+        <v>25</v>
+      </c>
+      <c r="V5" s="10" t="n">
+        <v>15</v>
       </c>
       <c r="W5" s="8" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="X5" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
       </c>
-      <c r="Y5" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z5" s="7" t="n">
-        <v>0</v>
+      <c r="Y5" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z5" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA5" s="8" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -1207,25 +1222,25 @@
         <v>19</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="I6" s="3" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="L6" s="8" t="n">
@@ -1273,6 +1288,9 @@
       <c r="Z6" s="8" t="n">
         <v>20</v>
       </c>
+      <c r="AA6" s="8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -1299,25 +1317,25 @@
         <v>15</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>457</v>
+        <v>557</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="L7" s="7" t="n">
@@ -1367,6 +1385,9 @@
       <c r="Z7" s="8" t="n">
         <v>100</v>
       </c>
+      <c r="AA7" s="8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -1393,25 +1414,25 @@
         <v>15</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1353</v>
+        <v>1442</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L8" s="8" t="n">
@@ -1459,6 +1480,9 @@
       <c r="Z8" s="8" t="n">
         <v>96</v>
       </c>
+      <c r="AA8" s="8" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -1485,25 +1509,25 @@
         <v>15</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1105</v>
+        <v>1180</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L9" s="8" t="n">
@@ -1551,6 +1575,9 @@
       <c r="Z9" s="8" t="n">
         <v>40</v>
       </c>
+      <c r="AA9" s="8" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -1577,25 +1604,25 @@
         <v>20</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>8</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="L10" s="8" t="n">
@@ -1645,6 +1672,9 @@
       <c r="Z10" s="10" t="n">
         <v>14</v>
       </c>
+      <c r="AA10" s="10" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -1671,20 +1701,20 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1540</v>
+        <v>1566</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -1737,6 +1767,9 @@
       <c r="Z11" s="11" t="n">
         <v>36</v>
       </c>
+      <c r="AA11" s="11" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -1763,25 +1796,25 @@
         <v>20</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G12" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="H12" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="H12" s="3" t="n">
-        <v>11</v>
-      </c>
       <c r="I12" s="3" t="n">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L12" s="8" t="n">
@@ -1829,16 +1862,19 @@
       <c r="Z12" s="8" t="n">
         <v>25</v>
       </c>
+      <c r="AA12" s="8" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>732955980949151744</t>
+          <t>684038567596433408</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-天润城地铁站1号口</t>
+          <t>25-晚峰-地铁站-柳州东路公交站台</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1848,93 +1884,96 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>早峰+晚峰+夜间</t>
+          <t>早峰+晚峰</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>620</v>
+        <v>1774</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="8" t="n">
+          <t>未配置</t>
+        </is>
+      </c>
+      <c r="L13" s="11" t="n">
+        <v>139</v>
+      </c>
+      <c r="M13" s="11" t="n">
+        <v>161</v>
+      </c>
+      <c r="N13" s="11" t="n">
+        <v>106</v>
+      </c>
+      <c r="O13" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="P13" s="11" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="11" t="n">
+        <v>241</v>
+      </c>
+      <c r="S13" s="11" t="n">
+        <v>233</v>
+      </c>
+      <c r="T13" s="11" t="n">
+        <v>253</v>
+      </c>
+      <c r="U13" s="11" t="n">
+        <v>167</v>
+      </c>
+      <c r="V13" s="11" t="n">
+        <v>141</v>
+      </c>
+      <c r="W13" s="11" t="n">
+        <v>165</v>
+      </c>
+      <c r="X13" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y13" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Z13" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="O13" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="P13" s="8" t="n">
-        <v>59</v>
-      </c>
-      <c r="Q13" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="R13" s="8" t="n">
-        <v>53</v>
-      </c>
-      <c r="S13" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v>110</v>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v>39</v>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v>69</v>
-      </c>
-      <c r="W13" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="X13" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Y13" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Z13" s="8" t="n">
-        <v>42</v>
+      <c r="AA13" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>843996095354019840</t>
+          <t>732955980949151744</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路2号口</t>
+          <t>25-晚峰-地铁站-天润城地铁站1号口</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1944,7 +1983,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>午峰+晚峰</t>
+          <t>早峰+晚峰+夜间</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
@@ -1957,10 +1996,10 @@
         <v>12</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1390</v>
+        <v>672</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1969,47 +2008,49 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="L14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M14" s="10" t="n">
-        <v>7</v>
+      <c r="M14" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N14" s="8" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="O14" s="8" t="n">
         <v>25</v>
       </c>
       <c r="P14" s="8" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>185</v>
+        <v>120</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>142</v>
+        <v>53</v>
       </c>
       <c r="S14" s="8" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="T14" s="8" t="n">
-        <v>219</v>
+        <v>110</v>
       </c>
       <c r="U14" s="8" t="n">
-        <v>195</v>
+        <v>39</v>
       </c>
       <c r="V14" s="8" t="n">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="W14" s="8" t="n">
-        <v>128</v>
-      </c>
-      <c r="X14" s="7" t="n">
-        <v>0</v>
+        <v>42</v>
+      </c>
+      <c r="X14" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
       <c r="Y14" s="9" t="inlineStr">
         <is>
@@ -2017,117 +2058,123 @@
         </is>
       </c>
       <c r="Z14" s="8" t="n">
-        <v>175</v>
+        <v>42</v>
+      </c>
+      <c r="AA14" s="8" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>1090491857237020672</t>
+          <t>843996095354019840</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>太平北路华海大厦(太平北路)投放点A</t>
+          <t>25-晚峰-地铁站-柳州东路2号口</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>午峰+晚峰</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F15" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>14</v>
-      </c>
       <c r="G15" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>12</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1112</v>
+        <v>1465</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="L15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M15" s="7" t="n">
-        <v>0</v>
+      <c r="M15" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="N15" s="8" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="O15" s="8" t="n">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="P15" s="8" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="Q15" s="8" t="n">
-        <v>66</v>
+        <v>185</v>
       </c>
       <c r="R15" s="8" t="n">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="S15" s="8" t="n">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="T15" s="8" t="n">
-        <v>87</v>
+        <v>219</v>
       </c>
       <c r="U15" s="8" t="n">
-        <v>110</v>
+        <v>195</v>
       </c>
       <c r="V15" s="8" t="n">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="W15" s="8" t="n">
-        <v>130</v>
-      </c>
-      <c r="X15" s="9" t="inlineStr">
-        <is>
-          <t>56☂</t>
-        </is>
-      </c>
-      <c r="Y15" s="8" t="n">
-        <v>44</v>
+        <v>128</v>
+      </c>
+      <c r="X15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
       <c r="Z15" s="8" t="n">
-        <v>158</v>
+        <v>175</v>
+      </c>
+      <c r="AA15" s="8" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>0a836a6al1l268p7ak2p5yn7sfzs2tsg</t>
+          <t>1090491857237020672</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>中山东路228号新世纪广场A幢投放点</t>
+          <t>太平北路华海大厦(太平北路)投放点A</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -2136,87 +2183,90 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>805</v>
+        <v>1158</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
-        </is>
-      </c>
-      <c r="L16" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="M16" s="8" t="n">
-        <v>40</v>
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N16" s="8" t="n">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="P16" s="7" t="n">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="P16" s="8" t="n">
+        <v>39</v>
       </c>
       <c r="Q16" s="8" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="R16" s="8" t="n">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="S16" s="8" t="n">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="T16" s="8" t="n">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="U16" s="8" t="n">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="V16" s="8" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="X16" s="9" t="inlineStr">
         <is>
-          <t>0☂</t>
+          <t>56☂</t>
         </is>
       </c>
       <c r="Y16" s="8" t="n">
-        <v>79</v>
-      </c>
-      <c r="Z16" s="7" t="n">
-        <v>0</v>
+        <v>44</v>
+      </c>
+      <c r="Z16" s="8" t="n">
+        <v>158</v>
+      </c>
+      <c r="AA16" s="8" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>732955142450266112</t>
+          <t>0a836a6al1l268p7ak2p5yn7sfzs2tsg</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区双塘街道中山南路夫子庙秦淮风光带</t>
+          <t>中山东路228号新世纪广场A幢投放点</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -2230,87 +2280,90 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>543</v>
+        <v>924</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="L17" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="M17" s="7" t="n">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>40</v>
       </c>
       <c r="N17" s="8" t="n">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="O17" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="P17" s="8" t="n">
-        <v>50</v>
+        <v>60</v>
+      </c>
+      <c r="P17" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="Q17" s="8" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="R17" s="8" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="S17" s="8" t="n">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="T17" s="8" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="U17" s="8" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="W17" s="8" t="n">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="X17" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
       </c>
-      <c r="Y17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="8" t="n">
-        <v>97</v>
+      <c r="Y17" s="8" t="n">
+        <v>79</v>
+      </c>
+      <c r="Z17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="8" t="n">
+        <v>119</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>732951617602912256</t>
+          <t>732955142450266112</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区瑞金路街道西安门地铁站投放点</t>
+          <t>南京市秦淮区双塘街道中山南路夫子庙秦淮风光带</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -2320,176 +2373,180 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
         <v>19</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>908</v>
+        <v>635</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>122</v>
-      </c>
-      <c r="M18" s="8" t="n">
-        <v>104</v>
-      </c>
-      <c r="N18" s="7" t="n">
-        <v>0</v>
+        <v>52</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="8" t="n">
+        <v>25</v>
       </c>
       <c r="O18" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="P18" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="P18" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="Q18" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="R18" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="S18" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="U18" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="R18" s="8" t="n">
-        <v>37</v>
-      </c>
-      <c r="S18" s="8" t="n">
-        <v>37</v>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v>98</v>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v>119</v>
-      </c>
       <c r="V18" s="8" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="W18" s="8" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="X18" s="9" t="inlineStr">
         <is>
-          <t>43☂</t>
-        </is>
-      </c>
-      <c r="Y18" s="8" t="n">
-        <v>88</v>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y18" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="Z18" s="8" t="n">
-        <v>45</v>
+        <v>97</v>
+      </c>
+      <c r="AA18" s="8" t="n">
+        <v>92</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>684038567596433408</t>
+          <t>732951617602912256</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路公交站台</t>
+          <t>南京市秦淮区瑞金路街道西安门地铁站投放点</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>早峰+晚峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F19" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G19" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="G19" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="H19" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1774</v>
+        <v>1006</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>未配置</t>
-        </is>
-      </c>
-      <c r="L19" s="11" t="n">
-        <v>139</v>
-      </c>
-      <c r="M19" s="11" t="n">
-        <v>161</v>
-      </c>
-      <c r="N19" s="11" t="n">
-        <v>106</v>
-      </c>
-      <c r="O19" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="P19" s="11" t="n">
-        <v>111</v>
-      </c>
-      <c r="Q19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="11" t="n">
-        <v>241</v>
-      </c>
-      <c r="S19" s="11" t="n">
-        <v>233</v>
-      </c>
-      <c r="T19" s="11" t="n">
-        <v>253</v>
-      </c>
-      <c r="U19" s="11" t="n">
-        <v>167</v>
-      </c>
-      <c r="V19" s="11" t="n">
-        <v>141</v>
-      </c>
-      <c r="W19" s="11" t="n">
-        <v>165</v>
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>122</v>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>104</v>
+      </c>
+      <c r="N19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="P19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="R19" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="S19" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v>119</v>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="W19" s="8" t="n">
+        <v>72</v>
       </c>
       <c r="X19" s="9" t="inlineStr">
         <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Y19" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Z19" s="11" t="n">
-        <v>25</v>
+          <t>43☂</t>
+        </is>
+      </c>
+      <c r="Y19" s="8" t="n">
+        <v>88</v>
+      </c>
+      <c r="Z19" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA19" s="8" t="n">
+        <v>98</v>
       </c>
     </row>
     <row r="20">
@@ -2517,25 +2574,25 @@
         <v>20</v>
       </c>
       <c r="F20" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G20" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="G20" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="H20" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>970</v>
+        <v>1090</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="L20" s="8" t="n">
@@ -2587,6 +2644,9 @@
       <c r="Z20" s="8" t="n">
         <v>101</v>
       </c>
+      <c r="AA20" s="8" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -2613,25 +2673,25 @@
         <v>20</v>
       </c>
       <c r="F21" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G21" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="G21" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="H21" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1368</v>
+        <v>1466</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="L21" s="8" t="n">
@@ -2683,6 +2743,9 @@
       <c r="Z21" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="AA21" s="8" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -2709,16 +2772,16 @@
         <v>19</v>
       </c>
       <c r="F22" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G22" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>13</v>
-      </c>
       <c r="H22" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>872</v>
+        <v>966</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2727,7 +2790,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="L22" s="8" t="n">
@@ -2777,6 +2840,9 @@
       <c r="Z22" s="8" t="n">
         <v>103</v>
       </c>
+      <c r="AA22" s="8" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -2803,16 +2869,16 @@
         <v>19</v>
       </c>
       <c r="F23" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G23" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="G23" s="3" t="n">
+      <c r="H23" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="H23" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="I23" s="3" t="n">
-        <v>383</v>
+        <v>403</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2821,7 +2887,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="L23" s="8" t="n">
@@ -2871,6 +2937,9 @@
       <c r="Z23" s="8" t="n">
         <v>35</v>
       </c>
+      <c r="AA23" s="8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -2897,16 +2966,16 @@
         <v>15</v>
       </c>
       <c r="F24" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G24" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="G24" s="3" t="n">
-        <v>13</v>
-      </c>
       <c r="H24" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>1374</v>
+        <v>1502</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2965,6 +3034,9 @@
       <c r="Z24" s="8" t="n">
         <v>93</v>
       </c>
+      <c r="AA24" s="8" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -2991,16 +3063,16 @@
         <v>15</v>
       </c>
       <c r="F25" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G25" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="G25" s="3" t="n">
-        <v>13</v>
-      </c>
       <c r="H25" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1637</v>
+        <v>1738</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -3059,6 +3131,9 @@
       <c r="Z25" s="8" t="n">
         <v>113</v>
       </c>
+      <c r="AA25" s="8" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -3085,7 +3160,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>15</v>
@@ -3098,7 +3173,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
@@ -3151,6 +3226,9 @@
       <c r="Z26" s="11" t="n">
         <v>25</v>
       </c>
+      <c r="AA26" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -3177,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1456</v>
+        <v>1684</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -3247,6 +3325,9 @@
       <c r="Z27" s="11" t="n">
         <v>188</v>
       </c>
+      <c r="AA27" s="11" t="n">
+        <v>228</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -3273,16 +3354,16 @@
         <v>15</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2001</v>
+        <v>2254</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -3291,7 +3372,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="L28" s="10" t="n">
@@ -3343,6 +3424,9 @@
       <c r="Z28" s="8" t="n">
         <v>213</v>
       </c>
+      <c r="AA28" s="8" t="n">
+        <v>253</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -3369,16 +3453,16 @@
         <v>20</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1569</v>
+        <v>1706</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -3437,6 +3521,9 @@
       <c r="Z29" s="8" t="n">
         <v>112</v>
       </c>
+      <c r="AA29" s="8" t="n">
+        <v>137</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -3463,16 +3550,16 @@
         <v>15</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>978</v>
+        <v>1020</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -3531,6 +3618,9 @@
       <c r="Z30" s="8" t="n">
         <v>47</v>
       </c>
+      <c r="AA30" s="8" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -3557,16 +3647,16 @@
         <v>20</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>2505</v>
+        <v>2730</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -3625,6 +3715,9 @@
       <c r="Z31" s="8" t="n">
         <v>70</v>
       </c>
+      <c r="AA31" s="8" t="n">
+        <v>225</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -3651,16 +3744,16 @@
         <v>19</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1159</v>
+        <v>1259</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -3719,6 +3812,9 @@
       <c r="Z32" s="8" t="n">
         <v>60</v>
       </c>
+      <c r="AA32" s="8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -3745,16 +3841,16 @@
         <v>19</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1566</v>
+        <v>1708</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -3813,6 +3909,9 @@
       <c r="Z33" s="8" t="n">
         <v>159</v>
       </c>
+      <c r="AA33" s="8" t="n">
+        <v>142</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -3839,16 +3938,16 @@
         <v>19</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>1102</v>
+        <v>1193</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -3907,6 +4006,9 @@
       <c r="Z34" s="8" t="n">
         <v>180</v>
       </c>
+      <c r="AA34" s="8" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -3933,16 +4035,16 @@
         <v>19</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1240</v>
+        <v>1371</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -4001,6 +4103,9 @@
       <c r="Z35" s="8" t="n">
         <v>156</v>
       </c>
+      <c r="AA35" s="8" t="n">
+        <v>131</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -4027,16 +4132,16 @@
         <v>20</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3393</v>
+        <v>3743</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -4095,6 +4200,9 @@
       <c r="Z36" s="8" t="n">
         <v>180</v>
       </c>
+      <c r="AA36" s="8" t="n">
+        <v>350</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -4121,16 +4229,16 @@
         <v>20</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1739</v>
+        <v>2059</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -4188,6 +4296,9 @@
       </c>
       <c r="Z37" s="8" t="n">
         <v>114</v>
+      </c>
+      <c r="AA37" s="8" t="n">
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -6675,7 +6786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z54"/>
+  <dimension ref="A1:AA54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6704,6 +6815,7 @@
     <col width="11" customWidth="1" min="24" max="24"/>
     <col width="11" customWidth="1" min="25" max="25"/>
     <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6844,6 +6956,11 @@
           <t>10-21(三)</t>
         </is>
       </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>10-22(四)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -6870,25 +6987,25 @@
         <v>20</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>3</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="L3" s="7" t="n">
@@ -6938,6 +7055,9 @@
       <c r="Z3" s="10" t="n">
         <v>13</v>
       </c>
+      <c r="AA3" s="10" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -6964,25 +7084,25 @@
         <v>10</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="L4" s="7" t="n">
@@ -7032,6 +7152,9 @@
       <c r="Z4" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="AA4" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -7058,25 +7181,25 @@
         <v>20</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H5" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="I5" s="3" t="n">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="L5" s="7" t="n">
@@ -7126,6 +7249,9 @@
       <c r="Z5" s="8" t="n">
         <v>36</v>
       </c>
+      <c r="AA5" s="8" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -7152,25 +7278,25 @@
         <v>10</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="I6" s="3" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="L6" s="7" t="n">
@@ -7220,6 +7346,9 @@
       <c r="Z6" s="8" t="n">
         <v>15</v>
       </c>
+      <c r="AA6" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -7246,25 +7375,25 @@
         <v>10</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="L7" s="7" t="n">
@@ -7314,6 +7443,9 @@
       <c r="Z7" s="8" t="n">
         <v>12</v>
       </c>
+      <c r="AA7" s="8" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -7340,25 +7472,25 @@
         <v>10</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="L8" s="7" t="n">
@@ -7408,6 +7540,9 @@
       <c r="Z8" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="AA8" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -7434,25 +7569,25 @@
         <v>10</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L9" s="8" t="n">
@@ -7502,6 +7637,9 @@
       <c r="Z9" s="8" t="n">
         <v>12</v>
       </c>
+      <c r="AA9" s="8" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -7528,25 +7666,25 @@
         <v>10</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L10" s="8" t="n">
@@ -7596,6 +7734,9 @@
       <c r="Z10" s="8" t="n">
         <v>22</v>
       </c>
+      <c r="AA10" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -7622,25 +7763,25 @@
         <v>20</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G11" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H11" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="I11" s="3" t="n">
-        <v>701</v>
+        <v>734</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L11" s="8" t="n">
@@ -7690,6 +7831,9 @@
       <c r="Z11" s="8" t="n">
         <v>37</v>
       </c>
+      <c r="AA11" s="8" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -7716,25 +7860,25 @@
         <v>20</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G12" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H12" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H12" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="I12" s="3" t="n">
-        <v>324</v>
+        <v>373</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L12" s="7" t="n">
@@ -7784,6 +7928,9 @@
       <c r="Z12" s="8" t="n">
         <v>33</v>
       </c>
+      <c r="AA12" s="8" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -7810,25 +7957,25 @@
         <v>10</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G13" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H13" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H13" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="I13" s="3" t="n">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L13" s="8" t="n">
@@ -7878,6 +8025,9 @@
       <c r="Z13" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="AA13" s="8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -7904,25 +8054,25 @@
         <v>10</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="L14" s="8" t="n">
@@ -7972,6 +8122,9 @@
       <c r="Z14" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="AA14" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -7998,25 +8151,25 @@
         <v>10</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="L15" s="8" t="n">
@@ -8066,6 +8219,9 @@
       <c r="Z15" s="8" t="n">
         <v>23</v>
       </c>
+      <c r="AA15" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -8092,25 +8248,25 @@
         <v>20</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="L16" s="10" t="n">
@@ -8160,6 +8316,9 @@
       <c r="Z16" s="10" t="n">
         <v>12</v>
       </c>
+      <c r="AA16" s="8" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -8186,25 +8345,25 @@
         <v>10</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G17" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H17" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="H17" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="I17" s="3" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="L17" s="8" t="n">
@@ -8254,6 +8413,9 @@
       <c r="Z17" s="8" t="n">
         <v>12</v>
       </c>
+      <c r="AA17" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -8280,25 +8442,25 @@
         <v>10</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="L18" s="7" t="n">
@@ -8348,6 +8510,9 @@
       <c r="Z18" s="8" t="n">
         <v>25</v>
       </c>
+      <c r="AA18" s="8" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -8374,25 +8539,25 @@
         <v>10</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="L19" s="8" t="n">
@@ -8442,6 +8607,9 @@
       <c r="Z19" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="AA19" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -8468,25 +8636,25 @@
         <v>20</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>304</v>
+        <v>336</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="L20" s="8" t="n">
@@ -8534,6 +8702,9 @@
       <c r="Z20" s="8" t="n">
         <v>34</v>
       </c>
+      <c r="AA20" s="8" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -8560,25 +8731,25 @@
         <v>30</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>497</v>
+        <v>589</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L21" s="7" t="n">
@@ -8626,6 +8797,9 @@
       <c r="Z21" s="8" t="n">
         <v>73</v>
       </c>
+      <c r="AA21" s="8" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -8652,25 +8826,25 @@
         <v>20</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>339</v>
+        <v>379</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="L22" s="10" t="n">
@@ -8718,6 +8892,9 @@
       <c r="Z22" s="8" t="n">
         <v>44</v>
       </c>
+      <c r="AA22" s="8" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -8744,25 +8921,25 @@
         <v>20</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L23" s="7" t="n">
@@ -8812,6 +8989,9 @@
       <c r="Z23" s="8" t="n">
         <v>43</v>
       </c>
+      <c r="AA23" s="8" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -8838,25 +9018,25 @@
         <v>20</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>484</v>
+        <v>517</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L24" s="10" t="n">
@@ -8906,6 +9086,9 @@
       <c r="Z24" s="8" t="n">
         <v>44</v>
       </c>
+      <c r="AA24" s="8" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -8932,25 +9115,25 @@
         <v>50</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>875</v>
+        <v>929</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="L25" s="7" t="n">
@@ -9000,6 +9183,9 @@
       <c r="Z25" s="10" t="n">
         <v>48</v>
       </c>
+      <c r="AA25" s="8" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -9026,25 +9212,25 @@
         <v>20</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>866</v>
+        <v>954</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="L26" s="7" t="n">
@@ -9094,6 +9280,9 @@
       <c r="Z26" s="8" t="n">
         <v>77</v>
       </c>
+      <c r="AA26" s="8" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -9120,25 +9309,25 @@
         <v>10</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="L27" s="7" t="n">
@@ -9188,6 +9377,9 @@
       <c r="Z27" s="8" t="n">
         <v>12</v>
       </c>
+      <c r="AA27" s="8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -9214,25 +9406,25 @@
         <v>10</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="L28" s="8" t="n">
@@ -9282,6 +9474,9 @@
       <c r="Z28" s="8" t="n">
         <v>20</v>
       </c>
+      <c r="AA28" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -9308,25 +9503,25 @@
         <v>10</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="L29" s="7" t="n">
@@ -9376,6 +9571,9 @@
       <c r="Z29" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="AA29" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -9402,25 +9600,25 @@
         <v>10</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="L30" s="8" t="n">
@@ -9470,6 +9668,9 @@
       <c r="Z30" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="AA30" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -9496,25 +9697,25 @@
         <v>10</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="L31" s="8" t="n">
@@ -9562,6 +9763,9 @@
       <c r="Z31" s="8" t="n">
         <v>12</v>
       </c>
+      <c r="AA31" s="8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -9588,25 +9792,25 @@
         <v>10</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="L32" s="7" t="n">
@@ -9654,6 +9858,9 @@
       <c r="Z32" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="AA32" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -9680,16 +9887,16 @@
         <v>20</v>
       </c>
       <c r="F33" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G33" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="G33" s="3" t="n">
-        <v>13</v>
-      </c>
       <c r="H33" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>456</v>
+        <v>480</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -9698,7 +9905,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="L33" s="8" t="n">
@@ -9748,6 +9955,9 @@
       <c r="Z33" s="8" t="n">
         <v>20</v>
       </c>
+      <c r="AA33" s="8" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -9774,16 +9984,16 @@
         <v>10</v>
       </c>
       <c r="F34" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G34" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="H34" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="H34" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="I34" s="3" t="n">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -9792,7 +10002,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="L34" s="8" t="n">
@@ -9842,6 +10052,9 @@
       <c r="Z34" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="AA34" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -9868,16 +10081,16 @@
         <v>10</v>
       </c>
       <c r="F35" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G35" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="G35" s="3" t="n">
-        <v>13</v>
-      </c>
       <c r="H35" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -9936,6 +10149,9 @@
       <c r="Z35" s="8" t="n">
         <v>21</v>
       </c>
+      <c r="AA35" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -9962,25 +10178,25 @@
         <v>10</v>
       </c>
       <c r="F36" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G36" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G36" s="3" t="n">
-        <v>14</v>
-      </c>
       <c r="H36" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>587</v>
+        <v>641</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="L36" s="8" t="n">
@@ -10028,6 +10244,9 @@
       <c r="Z36" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="AA36" s="8" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -10054,25 +10273,25 @@
         <v>10</v>
       </c>
       <c r="F37" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G37" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G37" s="3" t="n">
-        <v>14</v>
-      </c>
       <c r="H37" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>307</v>
+        <v>347</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="L37" s="8" t="n">
@@ -10120,6 +10339,9 @@
       <c r="Z37" s="8" t="n">
         <v>24</v>
       </c>
+      <c r="AA37" s="8" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -10146,25 +10368,25 @@
         <v>10</v>
       </c>
       <c r="F38" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G38" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G38" s="3" t="n">
-        <v>14</v>
-      </c>
       <c r="H38" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="L38" s="8" t="n">
@@ -10212,6 +10434,9 @@
       <c r="Z38" s="8" t="n">
         <v>12</v>
       </c>
+      <c r="AA38" s="8" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -10238,16 +10463,16 @@
         <v>50</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1357</v>
+        <v>1430</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -10256,7 +10481,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L39" s="8" t="n">
@@ -10306,6 +10531,9 @@
       <c r="Z39" s="8" t="n">
         <v>126</v>
       </c>
+      <c r="AA39" s="8" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -10332,16 +10560,16 @@
         <v>30</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>981</v>
+        <v>1044</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -10350,7 +10578,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="L40" s="8" t="n">
@@ -10400,42 +10628,45 @@
       <c r="Z40" s="8" t="n">
         <v>115</v>
       </c>
+      <c r="AA40" s="8" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>0a837fbbl1l2mga28qk2ua9idgju7ay3</t>
+          <t>0a83933al1l9u8y6b894j6jxgvg9a7ye</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>胜太西路47号汇金新天地广场站点</t>
+          <t>锦文大道辅路龙湖·水晶郦城站点C</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰+晚峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>13</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>568</v>
+        <v>711</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -10444,68 +10675,69 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="L41" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="M41" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="M41" s="8" t="n">
-        <v>31</v>
-      </c>
       <c r="N41" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="O41" s="8" t="n">
+        <v>88</v>
+      </c>
+      <c r="P41" s="8" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q41" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="R41" s="8" t="n">
+        <v>77</v>
+      </c>
+      <c r="S41" s="8" t="n">
+        <v>74</v>
+      </c>
+      <c r="T41" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="O41" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="P41" s="8" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q41" s="8" t="n">
-        <v>53</v>
-      </c>
-      <c r="R41" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="S41" s="8" t="n">
-        <v>63</v>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v>22</v>
-      </c>
       <c r="U41" s="8" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="V41" s="8" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="W41" s="8" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="X41" s="9" t="inlineStr">
         <is>
-          <t>33☂</t>
-        </is>
-      </c>
-      <c r="Y41" s="9" t="inlineStr">
-        <is>
-          <t>22☂</t>
-        </is>
-      </c>
-      <c r="Z41" s="8" t="n">
-        <v>54</v>
+          <t>42☂</t>
+        </is>
+      </c>
+      <c r="Y41" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z41" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA41" s="10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>0a8327a1l1l2i45kzhd965ga45mfsnmd</t>
+          <t>0a837fbbl1l2mga28qk2ua9idgju7ay3</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>胜太西路45号汇金新天地广场站点</t>
+          <t>胜太西路47号汇金新天地广场站点</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -10519,19 +10751,19 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>354</v>
+        <v>613</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -10544,78 +10776,81 @@
         </is>
       </c>
       <c r="L42" s="8" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="M42" s="8" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="N42" s="8" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="O42" s="8" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="P42" s="8" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="Q42" s="8" t="n">
+        <v>53</v>
+      </c>
+      <c r="R42" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="S42" s="8" t="n">
+        <v>63</v>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="V42" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="R42" s="8" t="n">
-        <v>41</v>
-      </c>
-      <c r="S42" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="V42" s="8" t="n">
-        <v>32</v>
-      </c>
       <c r="W42" s="8" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="X42" s="9" t="inlineStr">
         <is>
-          <t>10☂</t>
+          <t>33☂</t>
         </is>
       </c>
       <c r="Y42" s="9" t="inlineStr">
         <is>
-          <t>20☂</t>
+          <t>22☂</t>
         </is>
       </c>
       <c r="Z42" s="8" t="n">
-        <v>22</v>
+        <v>54</v>
+      </c>
+      <c r="AA42" s="8" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>0a83933al1l9u8y6b894j6jxgvg9a7ye</t>
+          <t>0a8327a1l1l2i45kzhd965ga45mfsnmd</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>锦文大道辅路龙湖·水晶郦城站点C</t>
+          <t>胜太西路45号汇金新天地广场站点</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰+晚峰</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>14</v>
@@ -10624,10 +10859,10 @@
         <v>14</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>708</v>
+        <v>378</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -10636,55 +10871,60 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="L43" s="8" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="M43" s="8" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="N43" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="O43" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="P43" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q43" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="R43" s="8" t="n">
+        <v>41</v>
+      </c>
+      <c r="S43" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="W43" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="X43" s="9" t="inlineStr">
+        <is>
+          <t>10☂</t>
+        </is>
+      </c>
+      <c r="Y43" s="9" t="inlineStr">
+        <is>
+          <t>20☂</t>
+        </is>
+      </c>
+      <c r="Z43" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="O43" s="8" t="n">
-        <v>88</v>
-      </c>
-      <c r="P43" s="8" t="n">
-        <v>63</v>
-      </c>
-      <c r="Q43" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="R43" s="8" t="n">
-        <v>77</v>
-      </c>
-      <c r="S43" s="8" t="n">
-        <v>74</v>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="W43" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="X43" s="9" t="inlineStr">
-        <is>
-          <t>42☂</t>
-        </is>
-      </c>
-      <c r="Y43" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="Z43" s="10" t="n">
-        <v>19</v>
+      <c r="AA43" s="8" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="44">
@@ -10712,16 +10952,16 @@
         <v>20</v>
       </c>
       <c r="F44" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="H44" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="G44" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>13</v>
-      </c>
       <c r="I44" s="3" t="n">
-        <v>2186</v>
+        <v>2236</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -10780,6 +11020,9 @@
       <c r="Z44" s="8" t="n">
         <v>31</v>
       </c>
+      <c r="AA44" s="8" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -10806,16 +11049,16 @@
         <v>30</v>
       </c>
       <c r="F45" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="H45" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="G45" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>13</v>
-      </c>
       <c r="I45" s="3" t="n">
-        <v>3141</v>
+        <v>3292</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -10874,6 +11117,9 @@
       <c r="Z45" s="8" t="n">
         <v>99</v>
       </c>
+      <c r="AA45" s="8" t="n">
+        <v>151</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -10900,16 +11146,16 @@
         <v>20</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>807</v>
+        <v>833</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -10968,6 +11214,9 @@
       <c r="Z46" s="8" t="n">
         <v>37</v>
       </c>
+      <c r="AA46" s="8" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -10994,16 +11243,16 @@
         <v>10</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -11062,6 +11311,9 @@
       <c r="Z47" s="8" t="n">
         <v>13</v>
       </c>
+      <c r="AA47" s="8" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -11088,16 +11340,16 @@
         <v>40</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1647</v>
+        <v>1840</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -11156,6 +11408,9 @@
       <c r="Z48" s="8" t="n">
         <v>83</v>
       </c>
+      <c r="AA48" s="8" t="n">
+        <v>193</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -11182,16 +11437,16 @@
         <v>10</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>249</v>
+        <v>284</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -11250,6 +11505,9 @@
       <c r="Z49" s="8" t="n">
         <v>32</v>
       </c>
+      <c r="AA49" s="8" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -11276,16 +11534,16 @@
         <v>10</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>831</v>
+        <v>891</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -11344,6 +11602,9 @@
       <c r="Z50" s="8" t="n">
         <v>49</v>
       </c>
+      <c r="AA50" s="8" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -11370,16 +11631,16 @@
         <v>60</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>4788</v>
+        <v>5080</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -11438,6 +11699,9 @@
       <c r="Z51" s="8" t="n">
         <v>191</v>
       </c>
+      <c r="AA51" s="8" t="n">
+        <v>292</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -11464,16 +11728,16 @@
         <v>10</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>853</v>
+        <v>883</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -11532,6 +11796,9 @@
       <c r="Z52" s="8" t="n">
         <v>51</v>
       </c>
+      <c r="AA52" s="8" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -11558,16 +11825,16 @@
         <v>10</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>2614</v>
+        <v>2674</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -11626,6 +11893,9 @@
       <c r="Z53" s="8" t="n">
         <v>51</v>
       </c>
+      <c r="AA53" s="8" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -11652,16 +11922,16 @@
         <v>10</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>387</v>
+        <v>416</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -11719,6 +11989,9 @@
       </c>
       <c r="Z54" s="8" t="n">
         <v>28</v>
+      </c>
+      <c r="AA54" s="8" t="n">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -15075,25 +15348,25 @@
         <v>4</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>87.7%</t>
         </is>
       </c>
     </row>
@@ -15110,25 +15383,25 @@
         <v>5</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>82.9%</t>
         </is>
       </c>
     </row>
@@ -15145,25 +15418,25 @@
         <v>11</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>86.5%</t>
+          <t>87.4%</t>
         </is>
       </c>
     </row>
@@ -15180,25 +15453,25 @@
         <v>2</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>76.7%</t>
         </is>
       </c>
     </row>
@@ -15215,25 +15488,25 @@
         <v>1</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -15250,25 +15523,25 @@
         <v>2</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F8" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G8" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="G8" s="3" t="n">
-        <v>21</v>
-      </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>86.2%</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>79.3%</t>
         </is>
       </c>
     </row>
@@ -15285,25 +15558,25 @@
         <v>6</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>87.0%</t>
+          <t>87.9%</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>84.7%</t>
+          <t>84.6%</t>
         </is>
       </c>
     </row>
@@ -15723,25 +15996,25 @@
         <v>10</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>95.3%</t>
         </is>
       </c>
     </row>
@@ -15758,25 +16031,25 @@
         <v>12</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>80.3%</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>62.8%</t>
         </is>
       </c>
     </row>
@@ -15793,25 +16066,25 @@
         <v>10</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
+          <t>72.4%</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
           <t>70.4%</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>68.3%</t>
         </is>
       </c>
     </row>
@@ -15828,25 +16101,25 @@
         <v>11</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>88.5%</t>
         </is>
       </c>
     </row>
@@ -15863,25 +16136,25 @@
         <v>9</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>79.6%</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>67.9%</t>
         </is>
       </c>
     </row>

--- a/coverage.xlsx
+++ b/coverage.xlsx
@@ -583,12 +583,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>87.9%</t>
+          <t>88.2%</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>84.4%</t>
         </is>
       </c>
     </row>
@@ -639,12 +639,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>84.4%</t>
+          <t>84.8%</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>77.9%</t>
         </is>
       </c>
     </row>
@@ -680,14 +680,14 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>数据范围: 20261001 ~ 20261025</t>
+          <t>数据范围: 20261001 ~ 20261026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>工作日: 17天, 周末: 8天</t>
+          <t>工作日: 18天, 周末: 8天</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB37"/>
+  <dimension ref="A1:AC37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -761,6 +761,7 @@
     <col width="11" customWidth="1" min="26" max="26"/>
     <col width="11" customWidth="1" min="27" max="27"/>
     <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -911,6 +912,11 @@
           <t>10-23(五)</t>
         </is>
       </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>10-26(一)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -937,25 +943,25 @@
         <v>10</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>300</v>
+        <v>365</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="L3" s="7" t="n">
@@ -1011,6 +1017,9 @@
       <c r="AB3" s="8" t="n">
         <v>66</v>
       </c>
+      <c r="AC3" s="8" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -1037,25 +1046,25 @@
         <v>15</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>336</v>
+        <v>365</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="L4" s="8" t="n">
@@ -1111,6 +1120,9 @@
       <c r="AB4" s="8" t="n">
         <v>25</v>
       </c>
+      <c r="AC4" s="8" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -1137,25 +1149,25 @@
         <v>20</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="L5" s="8" t="n">
@@ -1211,6 +1223,9 @@
       <c r="AB5" s="8" t="n">
         <v>26</v>
       </c>
+      <c r="AC5" s="8" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1237,25 +1252,25 @@
         <v>19</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G6" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>11</v>
-      </c>
       <c r="I6" s="3" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L6" s="8" t="n">
@@ -1309,6 +1324,9 @@
       <c r="AB6" s="8" t="n">
         <v>20</v>
       </c>
+      <c r="AC6" s="8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -1335,25 +1353,25 @@
         <v>15</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>657</v>
+        <v>734</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="L7" s="7" t="n">
@@ -1409,16 +1427,19 @@
       <c r="AB7" s="8" t="n">
         <v>100</v>
       </c>
+      <c r="AC7" s="8" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>1176722757207629824</t>
+          <t>973769778869174272</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>规划建设展览馆渗透</t>
+          <t>长江后街小区渗透</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1432,305 +1453,310 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1493</v>
+        <v>1640</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>76%</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="n">
-        <v>174</v>
-      </c>
-      <c r="M8" s="8" t="n">
-        <v>292</v>
-      </c>
-      <c r="N8" s="8" t="n">
-        <v>241</v>
-      </c>
-      <c r="O8" s="8" t="n">
+          <t>未配置</t>
+        </is>
+      </c>
+      <c r="L8" s="11" t="n">
+        <v>265</v>
+      </c>
+      <c r="M8" s="11" t="n">
+        <v>264</v>
+      </c>
+      <c r="N8" s="11" t="n">
+        <v>298</v>
+      </c>
+      <c r="O8" s="11" t="n">
+        <v>278</v>
+      </c>
+      <c r="P8" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="P8" s="8" t="n">
-        <v>197</v>
-      </c>
-      <c r="Q8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="S8" s="8" t="n">
+      <c r="Q8" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="R8" s="11" t="n">
         <v>39</v>
       </c>
-      <c r="T8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="W8" s="8" t="n">
-        <v>54</v>
+      <c r="S8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="U8" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="V8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="11" t="n">
+        <v>150</v>
       </c>
       <c r="X8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="Y8" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="Z8" s="8" t="n">
-        <v>96</v>
-      </c>
-      <c r="AA8" s="8" t="n">
-        <v>89</v>
-      </c>
-      <c r="AB8" s="8" t="n">
-        <v>51</v>
+      <c r="Y8" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z8" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA8" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB8" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="AC8" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>0a832068l1lrine348sx5fpj3daxcqc9</t>
+          <t>1176722757207629824</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>剪子巷51号华静家园西区投放点</t>
+          <t>规划建设展览馆渗透</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>午峰+夜间</t>
+          <t>午峰</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1285</v>
+        <v>1628</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="L9" s="8" t="n">
-        <v>155</v>
-      </c>
-      <c r="M9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="7" t="n">
-        <v>0</v>
+        <v>174</v>
+      </c>
+      <c r="M9" s="8" t="n">
+        <v>292</v>
+      </c>
+      <c r="N9" s="8" t="n">
+        <v>241</v>
       </c>
       <c r="O9" s="8" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="P9" s="8" t="n">
-        <v>104</v>
-      </c>
-      <c r="Q9" s="8" t="n">
-        <v>80</v>
+        <v>197</v>
+      </c>
+      <c r="Q9" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="R9" s="8" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="S9" s="8" t="n">
-        <v>157</v>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v>138</v>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v>115</v>
+        <v>39</v>
+      </c>
+      <c r="T9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="V9" s="8" t="n">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="W9" s="8" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="Y9" s="7" t="n">
-        <v>0</v>
+      <c r="Y9" s="8" t="n">
+        <v>75</v>
       </c>
       <c r="Z9" s="8" t="n">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="AA9" s="8" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AB9" s="8" t="n">
-        <v>105</v>
+        <v>51</v>
+      </c>
+      <c r="AC9" s="8" t="n">
+        <v>135</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>684038567596433408</t>
+          <t>0a832068l1lrine348sx5fpj3daxcqc9</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路公交站台</t>
+          <t>剪子巷51号华静家园西区投放点</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>早峰+晚峰</t>
+          <t>午峰+夜间</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1774</v>
+        <v>1365</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>未配置</t>
-        </is>
-      </c>
-      <c r="L10" s="11" t="n">
-        <v>139</v>
-      </c>
-      <c r="M10" s="11" t="n">
-        <v>161</v>
-      </c>
-      <c r="N10" s="11" t="n">
-        <v>106</v>
-      </c>
-      <c r="O10" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="P10" s="11" t="n">
-        <v>111</v>
-      </c>
-      <c r="Q10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="11" t="n">
-        <v>241</v>
-      </c>
-      <c r="S10" s="11" t="n">
-        <v>233</v>
-      </c>
-      <c r="T10" s="11" t="n">
-        <v>253</v>
-      </c>
-      <c r="U10" s="11" t="n">
-        <v>167</v>
-      </c>
-      <c r="V10" s="11" t="n">
-        <v>141</v>
-      </c>
-      <c r="W10" s="11" t="n">
-        <v>165</v>
-      </c>
-      <c r="X10" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Y10" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Z10" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="7" t="n">
-        <v>0</v>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="n">
+        <v>155</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>83</v>
+      </c>
+      <c r="P10" s="8" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q10" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="R10" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="S10" s="8" t="n">
+        <v>157</v>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v>138</v>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v>115</v>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v>77</v>
+      </c>
+      <c r="W10" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="X10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA10" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB10" s="8" t="n">
+        <v>105</v>
+      </c>
+      <c r="AC10" s="8" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>948393128847777792</t>
+          <t>684038567596433408</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>30-工作日-全天-地铁-明故宫2渗透</t>
+          <t>25-晚峰-地铁站-柳州东路公交站台</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰+晚峰</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>16</v>
@@ -1739,10 +1765,10 @@
         <v>13</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>642</v>
+        <v>1799</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1751,72 +1777,77 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>68</v>
-      </c>
-      <c r="N11" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="O11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="8" t="n">
-        <v>31</v>
-      </c>
-      <c r="R11" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="S11" s="8" t="n">
-        <v>91</v>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="V11" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="W11" s="10" t="n">
-        <v>7</v>
+          <t>未配置</t>
+        </is>
+      </c>
+      <c r="L11" s="11" t="n">
+        <v>139</v>
+      </c>
+      <c r="M11" s="11" t="n">
+        <v>161</v>
+      </c>
+      <c r="N11" s="11" t="n">
+        <v>106</v>
+      </c>
+      <c r="O11" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="P11" s="11" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="11" t="n">
+        <v>241</v>
+      </c>
+      <c r="S11" s="11" t="n">
+        <v>233</v>
+      </c>
+      <c r="T11" s="11" t="n">
+        <v>253</v>
+      </c>
+      <c r="U11" s="11" t="n">
+        <v>167</v>
+      </c>
+      <c r="V11" s="11" t="n">
+        <v>141</v>
+      </c>
+      <c r="W11" s="11" t="n">
+        <v>165</v>
       </c>
       <c r="X11" s="9" t="inlineStr">
         <is>
-          <t>20☂</t>
-        </is>
-      </c>
-      <c r="Y11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA11" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB11" s="10" t="n">
-        <v>14</v>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y11" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Z11" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="11" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>973769778869174272</t>
+          <t>948393128847777792</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>长江后街小区渗透</t>
+          <t>30-工作日-全天-地铁-明故宫2渗透</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1826,11 +1857,11 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>午峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>17</v>
@@ -1839,10 +1870,10 @@
         <v>14</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1640</v>
+        <v>658</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1851,84 +1882,89 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>未配置</t>
-        </is>
-      </c>
-      <c r="L12" s="11" t="n">
-        <v>265</v>
-      </c>
-      <c r="M12" s="11" t="n">
-        <v>264</v>
-      </c>
-      <c r="N12" s="11" t="n">
-        <v>298</v>
-      </c>
-      <c r="O12" s="11" t="n">
-        <v>278</v>
-      </c>
-      <c r="P12" s="11" t="n">
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>68</v>
+      </c>
+      <c r="N12" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="R12" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="S12" s="8" t="n">
+        <v>91</v>
+      </c>
+      <c r="T12" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="Q12" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="R12" s="11" t="n">
-        <v>39</v>
-      </c>
-      <c r="S12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="11" t="n">
-        <v>21</v>
-      </c>
-      <c r="U12" s="11" t="n">
-        <v>42</v>
-      </c>
-      <c r="V12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" s="11" t="n">
-        <v>150</v>
-      </c>
-      <c r="X12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="11" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z12" s="11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA12" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB12" s="11" t="n">
-        <v>74</v>
+      <c r="U12" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="V12" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="W12" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="X12" s="9" t="inlineStr">
+        <is>
+          <t>20☂</t>
+        </is>
+      </c>
+      <c r="Y12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA12" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB12" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC12" s="10" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>8d319562e65849c3a6e08eb73472a032</t>
+          <t>1090491857237020672</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>25-全天-居民区-鸡公煲门口</t>
+          <t>太平北路华海大厦(太平北路)投放点A</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>17</v>
@@ -1937,10 +1973,10 @@
         <v>14</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>377</v>
+        <v>1224</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1949,172 +1985,176 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>76%</t>
-        </is>
-      </c>
-      <c r="L13" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="M13" s="8" t="n">
-        <v>50</v>
+          <t>82%</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N13" s="8" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="O13" s="8" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="P13" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q13" s="7" t="n">
-        <v>0</v>
+        <v>39</v>
+      </c>
+      <c r="Q13" s="8" t="n">
+        <v>66</v>
       </c>
       <c r="R13" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="S13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="10" t="n">
-        <v>1</v>
+        <v>87</v>
+      </c>
+      <c r="S13" s="8" t="n">
+        <v>139</v>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v>87</v>
       </c>
       <c r="U13" s="8" t="n">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="V13" s="8" t="n">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="W13" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="X13" s="7" t="n">
-        <v>0</v>
+        <v>130</v>
+      </c>
+      <c r="X13" s="9" t="inlineStr">
+        <is>
+          <t>56☂</t>
+        </is>
       </c>
       <c r="Y13" s="8" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="Z13" s="8" t="n">
-        <v>25</v>
+        <v>158</v>
       </c>
       <c r="AA13" s="8" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="AB13" s="8" t="n">
-        <v>25</v>
+        <v>66</v>
+      </c>
+      <c r="AC13" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>732955980949151744</t>
+          <t>8d319562e65849c3a6e08eb73472a032</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-天润城地铁站1号口</t>
+          <t>25-全天-居民区-鸡公煲门口</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>早峰+晚峰+夜间</t>
+          <t>午峰</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F14" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G14" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G14" s="3" t="n">
-        <v>13</v>
-      </c>
       <c r="H14" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>688</v>
+        <v>402</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="7" t="n">
-        <v>0</v>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="N14" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="P14" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="O14" s="8" t="n">
+      <c r="Q14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="P14" s="8" t="n">
-        <v>59</v>
-      </c>
-      <c r="Q14" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="R14" s="8" t="n">
-        <v>53</v>
-      </c>
-      <c r="S14" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v>110</v>
+      <c r="S14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U14" s="8" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="V14" s="8" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="W14" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="X14" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Y14" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="X14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="8" t="n">
+        <v>25</v>
       </c>
       <c r="Z14" s="8" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AA14" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="AB14" s="10" t="n">
-        <v>16</v>
+        <v>25</v>
+      </c>
+      <c r="AB14" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC14" s="8" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>843996095354019840</t>
+          <t>732955980949151744</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路2号口</t>
+          <t>25-晚峰-地铁站-天润城地铁站1号口</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -2124,7 +2164,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>午峰+晚峰</t>
+          <t>早峰+晚峰+夜间</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
@@ -2140,7 +2180,7 @@
         <v>13</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1609</v>
+        <v>741</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -2155,41 +2195,43 @@
       <c r="L15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M15" s="10" t="n">
-        <v>7</v>
+      <c r="M15" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N15" s="8" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="O15" s="8" t="n">
         <v>25</v>
       </c>
       <c r="P15" s="8" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q15" s="8" t="n">
-        <v>185</v>
+        <v>120</v>
       </c>
       <c r="R15" s="8" t="n">
-        <v>142</v>
+        <v>53</v>
       </c>
       <c r="S15" s="8" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="T15" s="8" t="n">
-        <v>219</v>
+        <v>110</v>
       </c>
       <c r="U15" s="8" t="n">
-        <v>195</v>
+        <v>39</v>
       </c>
       <c r="V15" s="8" t="n">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="W15" s="8" t="n">
-        <v>128</v>
-      </c>
-      <c r="X15" s="7" t="n">
-        <v>0</v>
+        <v>42</v>
+      </c>
+      <c r="X15" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
       <c r="Y15" s="9" t="inlineStr">
         <is>
@@ -2197,50 +2239,53 @@
         </is>
       </c>
       <c r="Z15" s="8" t="n">
-        <v>175</v>
+        <v>42</v>
       </c>
       <c r="AA15" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB15" s="8" t="n">
-        <v>144</v>
+        <v>52</v>
+      </c>
+      <c r="AB15" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC15" s="8" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>1090491857237020672</t>
+          <t>843996095354019840</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>太平北路华海大厦(太平北路)投放点A</t>
+          <t>25-晚峰-地铁站-柳州东路2号口</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>午峰+晚峰</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v>15</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>14</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>14</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1224</v>
+        <v>1880</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -2249,61 +2294,64 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="L16" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="7" t="n">
-        <v>0</v>
+      <c r="M16" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="N16" s="8" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="P16" s="8" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="Q16" s="8" t="n">
-        <v>66</v>
+        <v>185</v>
       </c>
       <c r="R16" s="8" t="n">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="S16" s="8" t="n">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="T16" s="8" t="n">
-        <v>87</v>
+        <v>219</v>
       </c>
       <c r="U16" s="8" t="n">
-        <v>110</v>
+        <v>195</v>
       </c>
       <c r="V16" s="8" t="n">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>130</v>
-      </c>
-      <c r="X16" s="9" t="inlineStr">
-        <is>
-          <t>56☂</t>
-        </is>
-      </c>
-      <c r="Y16" s="8" t="n">
-        <v>44</v>
+        <v>128</v>
+      </c>
+      <c r="X16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
       <c r="Z16" s="8" t="n">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="AA16" s="8" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="AB16" s="8" t="n">
-        <v>66</v>
+        <v>144</v>
+      </c>
+      <c r="AC16" s="8" t="n">
+        <v>271</v>
       </c>
     </row>
     <row r="17">
@@ -2331,16 +2379,16 @@
         <v>20</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>965</v>
+        <v>1101</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -2405,6 +2453,9 @@
       <c r="AB17" s="8" t="n">
         <v>41</v>
       </c>
+      <c r="AC17" s="8" t="n">
+        <v>136</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -2431,16 +2482,16 @@
         <v>19</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>735</v>
+        <v>757</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -2505,6 +2556,9 @@
       <c r="AB18" s="8" t="n">
         <v>100</v>
       </c>
+      <c r="AC18" s="8" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -2531,16 +2585,16 @@
         <v>19</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1144</v>
+        <v>1181</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -2605,6 +2659,9 @@
       <c r="AB19" s="8" t="n">
         <v>138</v>
       </c>
+      <c r="AC19" s="8" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -2631,25 +2688,25 @@
         <v>20</v>
       </c>
       <c r="F20" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G20" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G20" s="3" t="n">
-        <v>14</v>
-      </c>
       <c r="H20" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1112</v>
+        <v>1234</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="L20" s="8" t="n">
@@ -2707,6 +2764,9 @@
       <c r="AB20" s="8" t="n">
         <v>22</v>
       </c>
+      <c r="AC20" s="8" t="n">
+        <v>122</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -2733,25 +2793,25 @@
         <v>20</v>
       </c>
       <c r="F21" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G21" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G21" s="3" t="n">
-        <v>14</v>
-      </c>
       <c r="H21" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1614</v>
+        <v>1763</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="L21" s="8" t="n">
@@ -2809,6 +2869,9 @@
       <c r="AB21" s="8" t="n">
         <v>148</v>
       </c>
+      <c r="AC21" s="8" t="n">
+        <v>149</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -2835,16 +2898,16 @@
         <v>19</v>
       </c>
       <c r="F22" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G22" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>15</v>
-      </c>
       <c r="H22" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>1084</v>
+        <v>1116</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2853,7 +2916,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="L22" s="8" t="n">
@@ -2909,21 +2972,24 @@
       <c r="AB22" s="8" t="n">
         <v>118</v>
       </c>
+      <c r="AC22" s="8" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>1174627254806421504</t>
+          <t>0a836587l1lp8ayqb5m6m5jv9xbfnhd9</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区五老村街道淮海路淮海路31号院</t>
+          <t>中山东路原国民政府旧址-国民党中央监察委员会办公楼旧址投放点</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -2932,98 +2998,101 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F23" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G23" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="G23" s="3" t="n">
+      <c r="H23" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H23" s="3" t="n">
+      <c r="I23" s="3" t="n">
+        <v>1878</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="L23" s="8" t="n">
+        <v>195</v>
+      </c>
+      <c r="M23" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="N23" s="8" t="n">
+        <v>267</v>
+      </c>
+      <c r="O23" s="8" t="n">
+        <v>195</v>
+      </c>
+      <c r="P23" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="Q23" s="8" t="n">
+        <v>177</v>
+      </c>
+      <c r="R23" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="S23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v>122</v>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v>118</v>
+      </c>
+      <c r="W23" s="8" t="n">
+        <v>99</v>
+      </c>
+      <c r="X23" s="9" t="inlineStr">
+        <is>
+          <t>10☂</t>
+        </is>
+      </c>
+      <c r="Y23" s="8" t="n">
+        <v>95</v>
+      </c>
+      <c r="Z23" s="8" t="n">
+        <v>113</v>
+      </c>
+      <c r="AA23" s="8" t="n">
+        <v>101</v>
+      </c>
+      <c r="AB23" s="8" t="n">
+        <v>126</v>
+      </c>
+      <c r="AC23" s="10" t="n">
         <v>14</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>423</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="L23" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="M23" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="N23" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="O23" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="P23" s="8" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q23" s="8" t="n">
-        <v>34</v>
-      </c>
-      <c r="R23" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="S23" s="8" t="n">
-        <v>57</v>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="W23" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="X23" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Y23" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="AA23" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB23" s="8" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>732956028185985024</t>
+          <t>1174627254806421504</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>下马坊地铁站</t>
+          <t>南京市秦淮区五老村街道淮海路淮海路31号院</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3032,19 +3101,19 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F24" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G24" s="3" t="n">
         <v>16</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>15</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>15</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>1675</v>
+        <v>443</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -3053,44 +3122,44 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="L24" s="8" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="N24" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="O24" s="8" t="n">
-        <v>45</v>
+        <v>20</v>
+      </c>
+      <c r="O24" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="P24" s="8" t="n">
-        <v>114</v>
+        <v>46</v>
       </c>
       <c r="Q24" s="8" t="n">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="R24" s="8" t="n">
-        <v>117</v>
+        <v>40</v>
       </c>
       <c r="S24" s="8" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="T24" s="8" t="n">
-        <v>145</v>
+        <v>20</v>
       </c>
       <c r="U24" s="8" t="n">
-        <v>203</v>
+        <v>20</v>
       </c>
       <c r="V24" s="8" t="n">
-        <v>175</v>
+        <v>20</v>
       </c>
       <c r="W24" s="8" t="n">
-        <v>133</v>
+        <v>20</v>
       </c>
       <c r="X24" s="9" t="inlineStr">
         <is>
@@ -3101,29 +3170,32 @@
         <v>0</v>
       </c>
       <c r="Z24" s="8" t="n">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="AA24" s="8" t="n">
-        <v>128</v>
+        <v>20</v>
       </c>
       <c r="AB24" s="8" t="n">
-        <v>173</v>
+        <v>20</v>
+      </c>
+      <c r="AC24" s="8" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>0a836587l1lp8ayqb5m6m5jv9xbfnhd9</t>
+          <t>732956028185985024</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>中山东路原国民政府旧址-国民党中央监察委员会办公楼旧址投放点</t>
+          <t>下马坊地铁站</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -3135,16 +3207,16 @@
         <v>15</v>
       </c>
       <c r="F25" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G25" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="G25" s="3" t="n">
-        <v>15</v>
-      </c>
       <c r="H25" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1864</v>
+        <v>1739</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -3157,57 +3229,60 @@
         </is>
       </c>
       <c r="L25" s="8" t="n">
-        <v>195</v>
+        <v>65</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="N25" s="8" t="n">
-        <v>267</v>
+        <v>75</v>
       </c>
       <c r="O25" s="8" t="n">
-        <v>195</v>
+        <v>45</v>
       </c>
       <c r="P25" s="8" t="n">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="Q25" s="8" t="n">
-        <v>177</v>
+        <v>109</v>
       </c>
       <c r="R25" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="S25" s="7" t="n">
-        <v>0</v>
+        <v>117</v>
+      </c>
+      <c r="S25" s="8" t="n">
+        <v>33</v>
       </c>
       <c r="T25" s="8" t="n">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="U25" s="8" t="n">
-        <v>49</v>
+        <v>203</v>
       </c>
       <c r="V25" s="8" t="n">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="W25" s="8" t="n">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="X25" s="9" t="inlineStr">
         <is>
-          <t>10☂</t>
-        </is>
-      </c>
-      <c r="Y25" s="8" t="n">
-        <v>95</v>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y25" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="Z25" s="8" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="AA25" s="8" t="n">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="AB25" s="8" t="n">
-        <v>126</v>
+        <v>173</v>
+      </c>
+      <c r="AC25" s="8" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="26">
@@ -3235,16 +3310,16 @@
         <v>0</v>
       </c>
       <c r="F26" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G26" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G26" s="3" t="n">
-        <v>16</v>
-      </c>
       <c r="H26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>956</v>
+        <v>981</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -3307,6 +3382,9 @@
       <c r="AB26" s="11" t="n">
         <v>25</v>
       </c>
+      <c r="AC26" s="11" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -3333,16 +3411,16 @@
         <v>0</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1992</v>
+        <v>2235</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -3409,6 +3487,9 @@
       <c r="AB27" s="11" t="n">
         <v>308</v>
       </c>
+      <c r="AC27" s="11" t="n">
+        <v>243</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -3435,16 +3516,16 @@
         <v>15</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2395</v>
+        <v>2543</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -3453,7 +3534,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="L28" s="10" t="n">
@@ -3511,6 +3592,9 @@
       <c r="AB28" s="8" t="n">
         <v>141</v>
       </c>
+      <c r="AC28" s="8" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -3537,16 +3621,16 @@
         <v>20</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1792</v>
+        <v>1908</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -3611,6 +3695,9 @@
       <c r="AB29" s="8" t="n">
         <v>86</v>
       </c>
+      <c r="AC29" s="8" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -3637,16 +3724,16 @@
         <v>15</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>1041</v>
+        <v>1088</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -3711,6 +3798,9 @@
       <c r="AB30" s="8" t="n">
         <v>21</v>
       </c>
+      <c r="AC30" s="8" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -3737,16 +3827,16 @@
         <v>20</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>2855</v>
+        <v>3030</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -3811,6 +3901,9 @@
       <c r="AB31" s="8" t="n">
         <v>125</v>
       </c>
+      <c r="AC31" s="8" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -3837,16 +3930,16 @@
         <v>19</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1340</v>
+        <v>1430</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -3911,6 +4004,9 @@
       <c r="AB32" s="8" t="n">
         <v>81</v>
       </c>
+      <c r="AC32" s="8" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -3937,16 +4033,16 @@
         <v>19</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1790</v>
+        <v>1957</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -4011,6 +4107,9 @@
       <c r="AB33" s="8" t="n">
         <v>82</v>
       </c>
+      <c r="AC33" s="8" t="n">
+        <v>167</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -4037,16 +4136,16 @@
         <v>19</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>1328</v>
+        <v>1450</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -4111,6 +4210,9 @@
       <c r="AB34" s="8" t="n">
         <v>135</v>
       </c>
+      <c r="AC34" s="8" t="n">
+        <v>122</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -4137,16 +4239,16 @@
         <v>19</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1708</v>
+        <v>1791</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -4211,6 +4313,9 @@
       <c r="AB35" s="8" t="n">
         <v>337</v>
       </c>
+      <c r="AC35" s="8" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -4237,16 +4342,16 @@
         <v>20</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3948</v>
+        <v>4273</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -4311,6 +4416,9 @@
       <c r="AB36" s="8" t="n">
         <v>205</v>
       </c>
+      <c r="AC36" s="8" t="n">
+        <v>325</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -4337,16 +4445,16 @@
         <v>20</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>2470</v>
+        <v>2688</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -4410,6 +4518,9 @@
       </c>
       <c r="AB37" s="8" t="n">
         <v>411</v>
+      </c>
+      <c r="AC37" s="8" t="n">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -7169,7 +7280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB54"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7200,6 +7311,7 @@
     <col width="11" customWidth="1" min="26" max="26"/>
     <col width="11" customWidth="1" min="27" max="27"/>
     <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7350,6 +7462,11 @@
           <t>10-23(五)</t>
         </is>
       </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>10-26(一)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -7376,7 +7493,7 @@
         <v>20</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>7</v>
@@ -7389,12 +7506,12 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="L3" s="7" t="n">
@@ -7450,6 +7567,9 @@
       <c r="AB3" s="8" t="n">
         <v>38</v>
       </c>
+      <c r="AC3" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -7476,25 +7596,25 @@
         <v>10</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="L4" s="7" t="n">
@@ -7550,6 +7670,9 @@
       <c r="AB4" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="AC4" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -7576,25 +7699,25 @@
         <v>20</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H5" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="I5" s="3" t="n">
-        <v>256</v>
+        <v>311</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="L5" s="7" t="n">
@@ -7650,6 +7773,9 @@
       <c r="AB5" s="8" t="n">
         <v>33</v>
       </c>
+      <c r="AC5" s="8" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -7676,25 +7802,25 @@
         <v>10</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="I6" s="3" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="L6" s="7" t="n">
@@ -7750,6 +7876,9 @@
       <c r="AB6" s="8" t="n">
         <v>15</v>
       </c>
+      <c r="AC6" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -7776,25 +7905,25 @@
         <v>10</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="L7" s="7" t="n">
@@ -7850,6 +7979,9 @@
       <c r="AB7" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="AC7" s="8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -7876,25 +8008,25 @@
         <v>10</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="L8" s="7" t="n">
@@ -7950,33 +8082,36 @@
       <c r="AB8" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="AC8" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>0a8320ecl1lvbzz3tyzcnk28dt6w9vz4</t>
+          <t>0a83f096l1l8jjun6xxt9t7uxyibq9b9</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>逸夫医院门口左手</t>
+          <t>弘利路龙湖·水晶郦城站点B</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
         <v>10</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>10</v>
@@ -7985,50 +8120,50 @@
         <v>10</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>237</v>
+        <v>142</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="L9" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="M9" s="8" t="n">
-        <v>12</v>
+        <v>32</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O9" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="P9" s="7" t="n">
-        <v>0</v>
+      <c r="O9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="8" t="n">
+        <v>11</v>
       </c>
       <c r="Q9" s="8" t="n">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="R9" s="8" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="S9" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="T9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="U9" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="V9" s="8" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="W9" s="7" t="n">
         <v>0</v>
@@ -8038,97 +8173,100 @@
           <t>0☂</t>
         </is>
       </c>
-      <c r="Y9" s="7" t="n">
-        <v>0</v>
+      <c r="Y9" s="8" t="n">
+        <v>11</v>
       </c>
       <c r="Z9" s="8" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AA9" s="8" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="AB9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>0a83f096l1l8jjun6xxt9t7uxyibq9b9</t>
+          <t>0a8320ecl1lvbzz3tyzcnk28dt6w9vz4</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>弘利路龙湖·水晶郦城站点B</t>
+          <t>逸夫医院门口左手</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
         <v>10</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>142</v>
+        <v>273</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="M10" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="M10" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="N10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="8" t="n">
-        <v>11</v>
+      <c r="O10" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="P10" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="R10" s="8" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="U10" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="T10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="V10" s="8" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="W10" s="7" t="n">
         <v>0</v>
@@ -8138,28 +8276,31 @@
           <t>0☂</t>
         </is>
       </c>
-      <c r="Y10" s="8" t="n">
-        <v>11</v>
+      <c r="Y10" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AA10" s="8" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="AB10" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="AC10" s="8" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>889717813217533952</t>
+          <t>897028622557294592</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>高新-高校-交院东门-全周-全天-50</t>
+          <t>南京工程学院5号门左手</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -8169,139 +8310,142 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G11" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>238</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="H11" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>872</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>69%</t>
-        </is>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>43</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>33</v>
+      <c r="M11" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="N11" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O11" s="7" t="n">
-        <v>0</v>
+      <c r="O11" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="P11" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="R11" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="S11" s="8" t="n">
-        <v>100</v>
+      <c r="Q11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="S11" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="T11" s="8" t="n">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="U11" s="8" t="n">
-        <v>95</v>
+        <v>24</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="W11" s="8" t="n">
-        <v>155</v>
+        <v>24</v>
       </c>
       <c r="X11" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
       </c>
-      <c r="Y11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="8" t="n">
-        <v>37</v>
+      <c r="Y11" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z11" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="AA11" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="AB11" s="8" t="n">
-        <v>138</v>
+        <v>24</v>
+      </c>
+      <c r="AB11" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC11" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>0a83d695l1lz6m3vbn8zbatt525u6cbu</t>
+          <t>889717813217533952</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>景明北大街站点B</t>
+          <t>高新-高校-交院东门-全周-全天-50</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>11</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>422</v>
+        <v>881</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>69%</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="7" t="n">
-        <v>0</v>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>33</v>
       </c>
       <c r="N12" s="7" t="n">
         <v>0</v>
@@ -8309,62 +8453,65 @@
       <c r="O12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P12" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q12" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="R12" s="10" t="n">
-        <v>6</v>
+      <c r="P12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="R12" s="8" t="n">
+        <v>40</v>
       </c>
       <c r="S12" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v>86</v>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v>95</v>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v>101</v>
+      </c>
+      <c r="W12" s="8" t="n">
+        <v>155</v>
+      </c>
+      <c r="X12" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA12" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="T12" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v>49</v>
-      </c>
-      <c r="W12" s="8" t="n">
-        <v>38</v>
-      </c>
-      <c r="X12" s="9" t="inlineStr">
-        <is>
-          <t>34☂</t>
-        </is>
-      </c>
-      <c r="Y12" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="Z12" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="AA12" s="8" t="n">
-        <v>49</v>
-      </c>
       <c r="AB12" s="8" t="n">
-        <v>49</v>
+        <v>138</v>
+      </c>
+      <c r="AC12" s="10" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>0a837fbbl1lcvvfvrrb6nbtsxdr5xk2w</t>
+          <t>0a83d695l1lz6m3vbn8zbatt525u6cbu</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>天元东路辅路南京义乌小商品城站点H</t>
+          <t>景明北大街站点B</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -8373,93 +8520,96 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G13" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="H13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="H13" s="3" t="n">
-        <v>11</v>
-      </c>
       <c r="I13" s="3" t="n">
-        <v>242</v>
+        <v>473</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>69%</t>
-        </is>
-      </c>
-      <c r="L13" s="8" t="n">
-        <v>12</v>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="M13" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="8" t="n">
+      <c r="N13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="O13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="8" t="n">
-        <v>24</v>
-      </c>
       <c r="Q13" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="R13" s="8" t="n">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="R13" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="S13" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="T13" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="U13" s="7" t="n">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v>22</v>
       </c>
       <c r="V13" s="8" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="W13" s="8" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="X13" s="9" t="inlineStr">
         <is>
-          <t>24☂</t>
+          <t>34☂</t>
         </is>
       </c>
       <c r="Y13" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z13" s="7" t="n">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="Z13" s="8" t="n">
+        <v>33</v>
       </c>
       <c r="AA13" s="8" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="AB13" s="8" t="n">
-        <v>36</v>
+        <v>49</v>
+      </c>
+      <c r="AC13" s="8" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>889935238642700288</t>
+          <t>0a837fbbl1lcvvfvrrb6nbtsxdr5xk2w</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>南京市江宁区淳化街道博观路保利·梧桐语</t>
+          <t>天元东路辅路南京义乌小商品城站点H</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -8476,95 +8626,98 @@
         <v>10</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>12</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>206</v>
+        <v>278</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="n">
-        <v>0</v>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="M14" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="O14" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="P14" s="7" t="n">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="O14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="Q14" s="8" t="n">
         <v>12</v>
       </c>
       <c r="R14" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="S14" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="T14" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="S14" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v>21</v>
-      </c>
       <c r="W14" s="8" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="X14" s="9" t="inlineStr">
         <is>
-          <t>0☂</t>
+          <t>24☂</t>
         </is>
       </c>
       <c r="Y14" s="8" t="n">
-        <v>38</v>
-      </c>
-      <c r="Z14" s="8" t="n">
-        <v>25</v>
+        <v>12</v>
+      </c>
+      <c r="Z14" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="AA14" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AB14" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="AB14" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AC14" s="8" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>0a838d77l1lhvwurirt76tdpsj4f7z4m</t>
+          <t>889935238642700288</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>龙昌路中南·上悦城站点A</t>
+          <t>南京市江宁区淳化街道博观路保利·梧桐语</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>李小凯</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -8576,90 +8729,93 @@
         <v>10</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G15" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>242</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="O15" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="P15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="I15" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="M15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="P15" s="8" t="n">
+      <c r="R15" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="Q15" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="R15" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="S15" s="8" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="T15" s="8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="U15" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V15" s="8" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="W15" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="X15" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
       </c>
-      <c r="Y15" s="7" t="n">
-        <v>0</v>
+      <c r="Y15" s="8" t="n">
+        <v>38</v>
       </c>
       <c r="Z15" s="8" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="AA15" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB15" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="AB15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="8" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>1084739124625276928</t>
+          <t>0a838d77l1lhvwurirt76tdpsj4f7z4m</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>骆村路骆村新寓A区站点A</t>
+          <t>龙昌路中南·上悦城站点A</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -8676,25 +8832,25 @@
         <v>10</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="L16" s="8" t="n">
@@ -8703,14 +8859,14 @@
       <c r="M16" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="8" t="n">
-        <v>23</v>
+      <c r="N16" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="P16" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="P16" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="Q16" s="8" t="n">
         <v>10</v>
@@ -8719,16 +8875,16 @@
         <v>0</v>
       </c>
       <c r="S16" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T16" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U16" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V16" s="8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W16" s="8" t="n">
         <v>11</v>
@@ -8742,29 +8898,32 @@
         <v>0</v>
       </c>
       <c r="Z16" s="8" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AA16" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB16" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="AB16" s="8" t="n">
-        <v>12</v>
+      <c r="AC16" s="8" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>897028622557294592</t>
+          <t>1084739124625276928</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>南京工程学院5号门左手</t>
+          <t>骆村路骆村新寓A区站点A</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>李小凯</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -8773,198 +8932,202 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>13</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>238</v>
+        <v>169</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>31%</t>
-        </is>
-      </c>
-      <c r="L17" s="10" t="n">
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="P17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="R17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="M17" s="10" t="n">
+      <c r="T17" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="N17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="P17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="S17" s="10" t="n">
+      <c r="U17" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="V17" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="T17" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v>48</v>
-      </c>
       <c r="W17" s="8" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="X17" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
       </c>
-      <c r="Y17" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z17" s="10" t="n">
+      <c r="Y17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA17" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB17" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="AA17" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB17" s="10" t="n">
-        <v>12</v>
+      <c r="AC17" s="8" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>889466722646794240</t>
+          <t>0a8302d5l1lir2dxfqaeqgk2ktn2mjev</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>胜太东路江宁供销商厦站点</t>
+          <t>高新-高校-金科北门2-全周-全天-30</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>李小凯</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>午峰</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>425</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="M18" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="I18" s="3" t="n">
-        <v>153</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>81%</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="L18" s="8" t="n">
+      <c r="P18" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q18" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="M18" s="8" t="n">
+      <c r="R18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="O18" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="P18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="8" t="n">
+      <c r="T18" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="R18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v>13</v>
-      </c>
       <c r="U18" s="8" t="n">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="V18" s="8" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="W18" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="X18" s="9" t="inlineStr">
-        <is>
-          <t>11☂</t>
-        </is>
-      </c>
-      <c r="Y18" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="X18" s="10" t="n">
         <v>11</v>
       </c>
+      <c r="Y18" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="Z18" s="8" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="AA18" s="8" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="AB18" s="8" t="n">
-        <v>11</v>
+        <v>89</v>
+      </c>
+      <c r="AC18" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>1222113693250682880</t>
+          <t>889466722646794240</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>灵谷寺3</t>
+          <t>胜太东路江宁供销商厦站点</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>王兴星</t>
+          <t>李小凯</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -8976,104 +9139,107 @@
         <v>10</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>13</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>368</v>
+        <v>174</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="L19" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="M19" s="7" t="n">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>11</v>
       </c>
       <c r="N19" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="O19" s="8" t="n">
-        <v>66</v>
-      </c>
-      <c r="P19" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="O19" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="R19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="W19" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="Q19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="S19" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="W19" s="8" t="n">
-        <v>21</v>
-      </c>
       <c r="X19" s="9" t="inlineStr">
         <is>
-          <t>10☂</t>
-        </is>
-      </c>
-      <c r="Y19" s="7" t="n">
-        <v>0</v>
+          <t>11☂</t>
+        </is>
+      </c>
+      <c r="Y19" s="8" t="n">
+        <v>11</v>
       </c>
       <c r="Z19" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA19" s="8" t="n">
         <v>10</v>
       </c>
       <c r="AB19" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="AC19" s="8" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>0a8302d5l1lir2dxfqaeqgk2ktn2mjev</t>
+          <t>1222113693250682880</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>高新-高校-金科北门2-全周-全天-30</t>
+          <t>灵谷寺3</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>王兴星</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>17</v>
@@ -9082,10 +9248,10 @@
         <v>14</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>425</v>
+        <v>378</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -9094,59 +9260,64 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="L20" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="M20" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="N20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="10" t="n">
-        <v>12</v>
+        <v>70</v>
+      </c>
+      <c r="M20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>66</v>
       </c>
       <c r="P20" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q20" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="R20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="T20" s="10" t="n">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="Q20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="S20" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="U20" s="8" t="n">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="V20" s="8" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="W20" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="X20" s="10" t="n">
-        <v>11</v>
+        <v>21</v>
+      </c>
+      <c r="X20" s="9" t="inlineStr">
+        <is>
+          <t>10☂</t>
+        </is>
       </c>
       <c r="Y20" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Z20" s="8" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="AA20" s="8" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="AB20" s="8" t="n">
-        <v>89</v>
+        <v>10</v>
+      </c>
+      <c r="AC20" s="8" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -9174,25 +9345,25 @@
         <v>30</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>9</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>673</v>
+        <v>684</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L21" s="7" t="n">
@@ -9246,6 +9417,9 @@
       <c r="AB21" s="8" t="n">
         <v>84</v>
       </c>
+      <c r="AC21" s="10" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -9272,25 +9446,25 @@
         <v>20</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>401</v>
+        <v>448</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L22" s="10" t="n">
@@ -9344,6 +9518,9 @@
       <c r="AB22" s="8" t="n">
         <v>22</v>
       </c>
+      <c r="AC22" s="8" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -9370,16 +9547,16 @@
         <v>20</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>480</v>
+        <v>514</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -9388,7 +9565,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="L23" s="8" t="n">
@@ -9444,6 +9621,9 @@
       <c r="AB23" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="AC23" s="8" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -9470,16 +9650,16 @@
         <v>20</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>527</v>
+        <v>565</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -9488,7 +9668,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="L24" s="7" t="n">
@@ -9544,6 +9724,9 @@
       <c r="AB24" s="8" t="n">
         <v>26</v>
       </c>
+      <c r="AC24" s="8" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -9570,16 +9753,16 @@
         <v>20</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>550</v>
+        <v>594</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -9588,7 +9771,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="L25" s="10" t="n">
@@ -9644,6 +9827,9 @@
       <c r="AB25" s="8" t="n">
         <v>33</v>
       </c>
+      <c r="AC25" s="8" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -9670,16 +9856,16 @@
         <v>50</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>1011</v>
+        <v>1067</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -9688,7 +9874,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="L26" s="7" t="n">
@@ -9744,6 +9930,9 @@
       <c r="AB26" s="8" t="n">
         <v>82</v>
       </c>
+      <c r="AC26" s="8" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -9770,16 +9959,16 @@
         <v>20</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>976</v>
+        <v>1086</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -9788,7 +9977,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="L27" s="7" t="n">
@@ -9844,6 +10033,9 @@
       <c r="AB27" s="8" t="n">
         <v>22</v>
       </c>
+      <c r="AC27" s="8" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -9870,16 +10062,16 @@
         <v>10</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -9944,6 +10136,9 @@
       <c r="AB28" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="AC28" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -9970,16 +10165,16 @@
         <v>10</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -10044,6 +10239,9 @@
       <c r="AB29" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="AC29" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -10070,16 +10268,16 @@
         <v>10</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -10144,6 +10342,9 @@
       <c r="AB30" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="AC30" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -10170,16 +10371,16 @@
         <v>10</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -10244,6 +10445,9 @@
       <c r="AB31" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="AC31" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -10270,25 +10474,25 @@
         <v>10</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="L32" s="8" t="n">
@@ -10342,6 +10546,9 @@
       <c r="AB32" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="AC32" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -10368,25 +10575,25 @@
         <v>10</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="L33" s="7" t="n">
@@ -10440,6 +10647,9 @@
       <c r="AB33" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="AC33" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -10466,16 +10676,16 @@
         <v>10</v>
       </c>
       <c r="F34" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G34" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="H34" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H34" s="3" t="n">
-        <v>14</v>
-      </c>
       <c r="I34" s="3" t="n">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -10540,6 +10750,9 @@
       <c r="AB34" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="AC34" s="8" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -10566,16 +10779,16 @@
         <v>10</v>
       </c>
       <c r="F35" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G35" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="G35" s="3" t="n">
-        <v>15</v>
-      </c>
       <c r="H35" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -10640,6 +10853,9 @@
       <c r="AB35" s="8" t="n">
         <v>31</v>
       </c>
+      <c r="AC35" s="8" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -10666,16 +10882,16 @@
         <v>10</v>
       </c>
       <c r="F36" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G36" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G36" s="3" t="n">
-        <v>16</v>
-      </c>
       <c r="H36" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>654</v>
+        <v>691</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -10738,6 +10954,9 @@
       <c r="AB36" s="8" t="n">
         <v>13</v>
       </c>
+      <c r="AC36" s="8" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -10764,16 +10983,16 @@
         <v>10</v>
       </c>
       <c r="F37" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G37" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G37" s="3" t="n">
-        <v>16</v>
-      </c>
       <c r="H37" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>371</v>
+        <v>407</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -10836,6 +11055,9 @@
       <c r="AB37" s="8" t="n">
         <v>24</v>
       </c>
+      <c r="AC37" s="8" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -10862,16 +11084,16 @@
         <v>10</v>
       </c>
       <c r="F38" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G38" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G38" s="3" t="n">
-        <v>16</v>
-      </c>
       <c r="H38" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -10934,6 +11156,9 @@
       <c r="AB38" s="8" t="n">
         <v>12</v>
       </c>
+      <c r="AC38" s="8" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -10960,16 +11185,16 @@
         <v>50</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>11</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1696</v>
+        <v>1708</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -10978,7 +11203,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="L39" s="8" t="n">
@@ -11034,21 +11259,24 @@
       <c r="AB39" s="8" t="n">
         <v>266</v>
       </c>
+      <c r="AC39" s="10" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>889665664809402368</t>
+          <t>0a83933al1l9u8y6b894j6jxgvg9a7ye</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>高新-高校-金科南门C-全周-全天-20</t>
+          <t>锦文大道辅路龙湖·水晶郦城站点C</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -11057,19 +11285,19 @@
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>13</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>1153</v>
+        <v>738</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -11078,77 +11306,80 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="L40" s="8" t="n">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="M40" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="N40" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="O40" s="8" t="n">
+        <v>88</v>
+      </c>
+      <c r="P40" s="8" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q40" s="8" t="n">
         <v>44</v>
       </c>
-      <c r="N40" s="8" t="n">
-        <v>57</v>
-      </c>
-      <c r="O40" s="8" t="n">
-        <v>78</v>
-      </c>
-      <c r="P40" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q40" s="10" t="n">
-        <v>12</v>
-      </c>
       <c r="R40" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="S40" s="10" t="n">
-        <v>8</v>
+        <v>77</v>
+      </c>
+      <c r="S40" s="8" t="n">
+        <v>74</v>
       </c>
       <c r="T40" s="8" t="n">
-        <v>123</v>
+        <v>33</v>
       </c>
       <c r="U40" s="8" t="n">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="V40" s="8" t="n">
-        <v>113</v>
+        <v>52</v>
       </c>
       <c r="W40" s="8" t="n">
-        <v>173</v>
+        <v>56</v>
       </c>
       <c r="X40" s="9" t="inlineStr">
         <is>
-          <t>0☂</t>
+          <t>42☂</t>
         </is>
       </c>
       <c r="Y40" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z40" s="8" t="n">
-        <v>115</v>
-      </c>
-      <c r="AA40" s="8" t="n">
-        <v>63</v>
-      </c>
-      <c r="AB40" s="8" t="n">
-        <v>109</v>
+        <v>33</v>
+      </c>
+      <c r="Z40" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA40" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB40" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC40" s="10" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>0a83933al1l9u8y6b894j6jxgvg9a7ye</t>
+          <t>889665664809402368</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>锦文大道辅路龙湖·水晶郦城站点C</t>
+          <t>高新-高校-金科南门C-全周-全天-20</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -11157,19 +11388,19 @@
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>727</v>
+        <v>1191</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -11178,61 +11409,64 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="L41" s="8" t="n">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="M41" s="8" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="N41" s="8" t="n">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="O41" s="8" t="n">
-        <v>88</v>
-      </c>
-      <c r="P41" s="8" t="n">
+        <v>78</v>
+      </c>
+      <c r="P41" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q41" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="R41" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="S41" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v>123</v>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v>83</v>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v>113</v>
+      </c>
+      <c r="W41" s="8" t="n">
+        <v>173</v>
+      </c>
+      <c r="X41" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y41" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="Z41" s="8" t="n">
+        <v>115</v>
+      </c>
+      <c r="AA41" s="8" t="n">
         <v>63</v>
       </c>
-      <c r="Q41" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="R41" s="8" t="n">
-        <v>77</v>
-      </c>
-      <c r="S41" s="8" t="n">
-        <v>74</v>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="W41" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="X41" s="9" t="inlineStr">
-        <is>
-          <t>42☂</t>
-        </is>
-      </c>
-      <c r="Y41" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="Z41" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA41" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB41" s="10" t="n">
-        <v>16</v>
+      <c r="AB41" s="8" t="n">
+        <v>109</v>
+      </c>
+      <c r="AC41" s="8" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="42">
@@ -11260,16 +11494,16 @@
         <v>10</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>657</v>
+        <v>693</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -11336,6 +11570,9 @@
       <c r="AB42" s="8" t="n">
         <v>44</v>
       </c>
+      <c r="AC42" s="8" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -11362,16 +11599,16 @@
         <v>11</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>409</v>
+        <v>459</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -11438,6 +11675,9 @@
       <c r="AB43" s="8" t="n">
         <v>31</v>
       </c>
+      <c r="AC43" s="8" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -11464,16 +11704,16 @@
         <v>20</v>
       </c>
       <c r="F44" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="H44" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="G44" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>15</v>
-      </c>
       <c r="I44" s="3" t="n">
-        <v>2307</v>
+        <v>2347</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -11538,6 +11778,9 @@
       <c r="AB44" s="8" t="n">
         <v>71</v>
       </c>
+      <c r="AC44" s="8" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -11564,16 +11807,16 @@
         <v>30</v>
       </c>
       <c r="F45" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="H45" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="G45" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>15</v>
-      </c>
       <c r="I45" s="3" t="n">
-        <v>3474</v>
+        <v>3514</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -11638,6 +11881,9 @@
       <c r="AB45" s="8" t="n">
         <v>182</v>
       </c>
+      <c r="AC45" s="8" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -11664,16 +11910,16 @@
         <v>20</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>855</v>
+        <v>903</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -11738,6 +11984,9 @@
       <c r="AB46" s="8" t="n">
         <v>22</v>
       </c>
+      <c r="AC46" s="8" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -11764,16 +12013,16 @@
         <v>10</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>331</v>
+        <v>370</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -11838,6 +12087,9 @@
       <c r="AB47" s="8" t="n">
         <v>22</v>
       </c>
+      <c r="AC47" s="8" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -11864,16 +12116,16 @@
         <v>40</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1924</v>
+        <v>2017</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -11938,6 +12190,9 @@
       <c r="AB48" s="8" t="n">
         <v>84</v>
       </c>
+      <c r="AC48" s="8" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -11964,16 +12219,16 @@
         <v>10</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>296</v>
+        <v>321</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -12038,6 +12293,9 @@
       <c r="AB49" s="8" t="n">
         <v>12</v>
       </c>
+      <c r="AC49" s="8" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -12064,16 +12322,16 @@
         <v>10</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>921</v>
+        <v>971</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -12138,6 +12396,9 @@
       <c r="AB50" s="8" t="n">
         <v>30</v>
       </c>
+      <c r="AC50" s="8" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -12164,16 +12425,16 @@
         <v>60</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>5330</v>
+        <v>5671</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -12238,6 +12499,9 @@
       <c r="AB51" s="8" t="n">
         <v>250</v>
       </c>
+      <c r="AC51" s="8" t="n">
+        <v>341</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -12264,16 +12528,16 @@
         <v>10</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>953</v>
+        <v>1043</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -12338,6 +12602,9 @@
       <c r="AB52" s="8" t="n">
         <v>70</v>
       </c>
+      <c r="AC52" s="8" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -12364,16 +12631,16 @@
         <v>10</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>2714</v>
+        <v>2754</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -12438,6 +12705,9 @@
       <c r="AB53" s="8" t="n">
         <v>40</v>
       </c>
+      <c r="AC53" s="8" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -12464,16 +12734,16 @@
         <v>10</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>444</v>
+        <v>488</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -12537,6 +12807,9 @@
       </c>
       <c r="AB54" s="8" t="n">
         <v>28</v>
+      </c>
+      <c r="AC54" s="8" t="n">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -16263,25 +16536,25 @@
         <v>4</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>86.9%</t>
+          <t>87.7%</t>
         </is>
       </c>
     </row>
@@ -16298,25 +16571,25 @@
         <v>5</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>84.9%</t>
         </is>
       </c>
     </row>
@@ -16333,25 +16606,25 @@
         <v>11</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>88.2%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -16368,25 +16641,25 @@
         <v>2</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>79.4%</t>
         </is>
       </c>
     </row>
@@ -16403,25 +16676,25 @@
         <v>1</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>47.1%</t>
         </is>
       </c>
     </row>
@@ -16438,25 +16711,25 @@
         <v>2</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F8" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="G8" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="G8" s="3" t="n">
-        <v>25</v>
-      </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>87.9%</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -16473,25 +16746,25 @@
         <v>6</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>87.6%</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>82.5%</t>
         </is>
       </c>
     </row>
@@ -16911,25 +17184,25 @@
         <v>10</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>95.9%</t>
         </is>
       </c>
     </row>
@@ -16946,25 +17219,25 @@
         <v>12</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>79.7%</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>62.8%</t>
         </is>
       </c>
     </row>
@@ -16981,25 +17254,25 @@
         <v>10</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>73.8%</t>
         </is>
       </c>
     </row>
@@ -17016,25 +17289,25 @@
         <v>11</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>89.8%</t>
         </is>
       </c>
     </row>
@@ -17051,25 +17324,25 @@
         <v>9</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>80.1%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>68.4%</t>
         </is>
       </c>
     </row>

--- a/coverage.xlsx
+++ b/coverage.xlsx
@@ -583,12 +583,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>88.2%</t>
+          <t>88.4%</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>84.4%</t>
+          <t>84.8%</t>
         </is>
       </c>
     </row>
@@ -639,12 +639,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -680,14 +680,14 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>数据范围: 20261001 ~ 20261026</t>
+          <t>数据范围: 20261001 ~ 20261027</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>工作日: 18天, 周末: 8天</t>
+          <t>工作日: 19天, 周末: 8天</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AD37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -762,6 +762,7 @@
     <col width="11" customWidth="1" min="27" max="27"/>
     <col width="11" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -917,6 +918,11 @@
           <t>10-26(一)</t>
         </is>
       </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>10-27(二)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -943,7 +949,7 @@
         <v>10</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>8</v>
@@ -956,12 +962,12 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="L3" s="7" t="n">
@@ -1020,6 +1026,9 @@
       <c r="AC3" s="8" t="n">
         <v>65</v>
       </c>
+      <c r="AD3" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -1046,25 +1055,25 @@
         <v>15</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>365</v>
+        <v>385</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L4" s="8" t="n">
@@ -1123,6 +1132,9 @@
       <c r="AC4" s="8" t="n">
         <v>29</v>
       </c>
+      <c r="AD4" s="8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -1149,25 +1161,25 @@
         <v>20</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L5" s="8" t="n">
@@ -1226,6 +1238,9 @@
       <c r="AC5" s="8" t="n">
         <v>25</v>
       </c>
+      <c r="AD5" s="8" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1252,25 +1267,25 @@
         <v>19</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G6" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="I6" s="3" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="L6" s="8" t="n">
@@ -1327,30 +1342,33 @@
       <c r="AC6" s="8" t="n">
         <v>20</v>
       </c>
+      <c r="AD6" s="8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>1130000746265899008</t>
+          <t>684038567596433408</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>城北万象汇</t>
+          <t>25-晚峰-地铁站-柳州东路公交站台</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>午峰+晚峰</t>
+          <t>早峰+晚峰</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>17</v>
@@ -1359,10 +1377,10 @@
         <v>13</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>734</v>
+        <v>1799</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1371,89 +1389,94 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>76%</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="8" t="n">
+          <t>未配置</t>
+        </is>
+      </c>
+      <c r="L7" s="11" t="n">
+        <v>139</v>
+      </c>
+      <c r="M7" s="11" t="n">
+        <v>161</v>
+      </c>
+      <c r="N7" s="11" t="n">
+        <v>106</v>
+      </c>
+      <c r="O7" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="P7" s="11" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="11" t="n">
+        <v>241</v>
+      </c>
+      <c r="S7" s="11" t="n">
+        <v>233</v>
+      </c>
+      <c r="T7" s="11" t="n">
+        <v>253</v>
+      </c>
+      <c r="U7" s="11" t="n">
+        <v>167</v>
+      </c>
+      <c r="V7" s="11" t="n">
+        <v>141</v>
+      </c>
+      <c r="W7" s="11" t="n">
+        <v>165</v>
+      </c>
+      <c r="X7" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y7" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Z7" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="O7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="8" t="n">
+      <c r="AA7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="Q7" s="8" t="n">
-        <v>37</v>
-      </c>
-      <c r="R7" s="8" t="n">
-        <v>38</v>
-      </c>
-      <c r="S7" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v>57</v>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="W7" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="X7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Z7" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA7" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB7" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC7" s="8" t="n">
-        <v>77</v>
+      <c r="AD7" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>973769778869174272</t>
+          <t>1130000746265899008</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>长江后街小区渗透</t>
+          <t>城北万象汇</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>午峰</t>
+          <t>午峰+晚峰</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>18</v>
@@ -1462,10 +1485,10 @@
         <v>14</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1640</v>
+        <v>809</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -1474,73 +1497,78 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>未配置</t>
-        </is>
-      </c>
-      <c r="L8" s="11" t="n">
-        <v>265</v>
-      </c>
-      <c r="M8" s="11" t="n">
-        <v>264</v>
-      </c>
-      <c r="N8" s="11" t="n">
-        <v>298</v>
-      </c>
-      <c r="O8" s="11" t="n">
-        <v>278</v>
-      </c>
-      <c r="P8" s="11" t="n">
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="O8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q8" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="R8" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="S8" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="W8" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="X8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Z8" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="Q8" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="R8" s="11" t="n">
-        <v>39</v>
-      </c>
-      <c r="S8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="11" t="n">
-        <v>21</v>
-      </c>
-      <c r="U8" s="11" t="n">
-        <v>42</v>
-      </c>
-      <c r="V8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" s="11" t="n">
-        <v>150</v>
-      </c>
-      <c r="X8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="11" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z8" s="11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA8" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB8" s="11" t="n">
-        <v>74</v>
-      </c>
-      <c r="AC8" s="7" t="n">
-        <v>0</v>
+      <c r="AA8" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB8" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC8" s="8" t="n">
+        <v>77</v>
+      </c>
+      <c r="AD8" s="8" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>1176722757207629824</t>
+          <t>973769778869174272</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>规划建设展览馆渗透</t>
+          <t>长江后街小区渗透</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1554,289 +1582,294 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G9" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>14</v>
-      </c>
       <c r="H9" s="3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1628</v>
+        <v>1678</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>78%</t>
-        </is>
-      </c>
-      <c r="L9" s="8" t="n">
-        <v>174</v>
-      </c>
-      <c r="M9" s="8" t="n">
-        <v>292</v>
-      </c>
-      <c r="N9" s="8" t="n">
-        <v>241</v>
-      </c>
-      <c r="O9" s="8" t="n">
+          <t>未配置</t>
+        </is>
+      </c>
+      <c r="L9" s="11" t="n">
+        <v>265</v>
+      </c>
+      <c r="M9" s="11" t="n">
+        <v>264</v>
+      </c>
+      <c r="N9" s="11" t="n">
+        <v>298</v>
+      </c>
+      <c r="O9" s="11" t="n">
+        <v>278</v>
+      </c>
+      <c r="P9" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="P9" s="8" t="n">
-        <v>197</v>
-      </c>
-      <c r="Q9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="S9" s="8" t="n">
+      <c r="Q9" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="R9" s="11" t="n">
         <v>39</v>
       </c>
-      <c r="T9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="W9" s="8" t="n">
-        <v>54</v>
+      <c r="S9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="U9" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="V9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="11" t="n">
+        <v>150</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="Y9" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="Z9" s="8" t="n">
-        <v>96</v>
-      </c>
-      <c r="AA9" s="8" t="n">
-        <v>89</v>
-      </c>
-      <c r="AB9" s="8" t="n">
-        <v>51</v>
-      </c>
-      <c r="AC9" s="8" t="n">
-        <v>135</v>
+      <c r="Y9" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z9" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA9" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB9" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="AC9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="11" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>0a832068l1lrine348sx5fpj3daxcqc9</t>
+          <t>1176722757207629824</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>剪子巷51号华静家园西区投放点</t>
+          <t>规划建设展览馆渗透</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>午峰+夜间</t>
+          <t>午峰</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1365</v>
+        <v>1809</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>155</v>
-      </c>
-      <c r="M10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="7" t="n">
-        <v>0</v>
+        <v>174</v>
+      </c>
+      <c r="M10" s="8" t="n">
+        <v>292</v>
+      </c>
+      <c r="N10" s="8" t="n">
+        <v>241</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>104</v>
-      </c>
-      <c r="Q10" s="8" t="n">
-        <v>80</v>
+        <v>197</v>
+      </c>
+      <c r="Q10" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="R10" s="8" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>157</v>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v>138</v>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v>115</v>
+        <v>39</v>
+      </c>
+      <c r="T10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="V10" s="8" t="n">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="X10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="Y10" s="7" t="n">
-        <v>0</v>
+      <c r="Y10" s="8" t="n">
+        <v>75</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="AA10" s="8" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AB10" s="8" t="n">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="AC10" s="8" t="n">
-        <v>80</v>
+        <v>135</v>
+      </c>
+      <c r="AD10" s="8" t="n">
+        <v>181</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>684038567596433408</t>
+          <t>0a832068l1lrine348sx5fpj3daxcqc9</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路公交站台</t>
+          <t>剪子巷51号华静家园西区投放点</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>早峰+晚峰</t>
+          <t>午峰+夜间</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1799</v>
+        <v>1445</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>未配置</t>
-        </is>
-      </c>
-      <c r="L11" s="11" t="n">
-        <v>139</v>
-      </c>
-      <c r="M11" s="11" t="n">
-        <v>161</v>
-      </c>
-      <c r="N11" s="11" t="n">
-        <v>106</v>
-      </c>
-      <c r="O11" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="P11" s="11" t="n">
-        <v>111</v>
-      </c>
-      <c r="Q11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="11" t="n">
-        <v>241</v>
-      </c>
-      <c r="S11" s="11" t="n">
-        <v>233</v>
-      </c>
-      <c r="T11" s="11" t="n">
-        <v>253</v>
-      </c>
-      <c r="U11" s="11" t="n">
-        <v>167</v>
-      </c>
-      <c r="V11" s="11" t="n">
-        <v>141</v>
-      </c>
-      <c r="W11" s="11" t="n">
-        <v>165</v>
-      </c>
-      <c r="X11" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Y11" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Z11" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="11" t="n">
-        <v>25</v>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>155</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>83</v>
+      </c>
+      <c r="P11" s="8" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q11" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="R11" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="S11" s="8" t="n">
+        <v>157</v>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v>138</v>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v>115</v>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v>77</v>
+      </c>
+      <c r="W11" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="X11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA11" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB11" s="8" t="n">
+        <v>105</v>
+      </c>
+      <c r="AC11" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AD11" s="8" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="12">
@@ -1864,25 +1897,25 @@
         <v>20</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>8</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>658</v>
+        <v>671</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="L12" s="8" t="n">
@@ -1941,6 +1974,9 @@
       <c r="AC12" s="10" t="n">
         <v>16</v>
       </c>
+      <c r="AD12" s="10" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -1967,25 +2003,25 @@
         <v>15</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1224</v>
+        <v>1336</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="L13" s="7" t="n">
@@ -2044,26 +2080,29 @@
       <c r="AC13" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="AD13" s="8" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>8d319562e65849c3a6e08eb73472a032</t>
+          <t>0a836a6al1l268p7ak2p5yn7sfzs2tsg</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>25-全天-居民区-鸡公煲门口</t>
+          <t>中山东路228号新世纪广场A幢投放点</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
@@ -2076,10 +2115,10 @@
         <v>15</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>402</v>
+        <v>1101</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -2088,178 +2127,182 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="L14" s="8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="N14" s="8" t="n">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="O14" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="P14" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q14" s="7" t="n">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="P14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="8" t="n">
+        <v>72</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="S14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="10" t="n">
-        <v>1</v>
+        <v>40</v>
+      </c>
+      <c r="S14" s="8" t="n">
+        <v>113</v>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v>40</v>
       </c>
       <c r="U14" s="8" t="n">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="V14" s="8" t="n">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="W14" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="X14" s="7" t="n">
-        <v>0</v>
+        <v>77</v>
+      </c>
+      <c r="X14" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
       <c r="Y14" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z14" s="8" t="n">
-        <v>25</v>
+        <v>79</v>
+      </c>
+      <c r="Z14" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="AA14" s="8" t="n">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="AB14" s="8" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="AC14" s="8" t="n">
-        <v>25</v>
+        <v>136</v>
+      </c>
+      <c r="AD14" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>732955980949151744</t>
+          <t>8d319562e65849c3a6e08eb73472a032</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-天润城地铁站1号口</t>
+          <t>25-全天-居民区-鸡公煲门口</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>早峰+晚峰+夜间</t>
+          <t>午峰</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F15" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G15" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="G15" s="3" t="n">
-        <v>14</v>
-      </c>
       <c r="H15" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>741</v>
+        <v>427</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>81%</t>
-        </is>
-      </c>
-      <c r="L15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="7" t="n">
-        <v>0</v>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="L15" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="M15" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="N15" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="O15" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="P15" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="O15" s="8" t="n">
+      <c r="Q15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="P15" s="8" t="n">
-        <v>59</v>
-      </c>
-      <c r="Q15" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="R15" s="8" t="n">
-        <v>53</v>
-      </c>
-      <c r="S15" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v>110</v>
+      <c r="S15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U15" s="8" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="V15" s="8" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="W15" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="X15" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Y15" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="X15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="8" t="n">
+        <v>25</v>
       </c>
       <c r="Z15" s="8" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AA15" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="AB15" s="10" t="n">
-        <v>16</v>
+        <v>25</v>
+      </c>
+      <c r="AB15" s="8" t="n">
+        <v>25</v>
       </c>
       <c r="AC15" s="8" t="n">
-        <v>53</v>
+        <v>25</v>
+      </c>
+      <c r="AD15" s="8" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>843996095354019840</t>
+          <t>732955980949151744</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路2号口</t>
+          <t>25-晚峰-地铁站-天润城地铁站1号口</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -2269,7 +2312,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>午峰+晚峰</t>
+          <t>早峰+晚峰+夜间</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -2285,7 +2328,7 @@
         <v>14</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1880</v>
+        <v>871</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -2300,41 +2343,43 @@
       <c r="L16" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="10" t="n">
-        <v>7</v>
+      <c r="M16" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N16" s="8" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="O16" s="8" t="n">
         <v>25</v>
       </c>
       <c r="P16" s="8" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q16" s="8" t="n">
-        <v>185</v>
+        <v>120</v>
       </c>
       <c r="R16" s="8" t="n">
-        <v>142</v>
+        <v>53</v>
       </c>
       <c r="S16" s="8" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="T16" s="8" t="n">
-        <v>219</v>
+        <v>110</v>
       </c>
       <c r="U16" s="8" t="n">
-        <v>195</v>
+        <v>39</v>
       </c>
       <c r="V16" s="8" t="n">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>128</v>
-      </c>
-      <c r="X16" s="7" t="n">
-        <v>0</v>
+        <v>42</v>
+      </c>
+      <c r="X16" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
       <c r="Y16" s="9" t="inlineStr">
         <is>
@@ -2342,119 +2387,125 @@
         </is>
       </c>
       <c r="Z16" s="8" t="n">
-        <v>175</v>
+        <v>42</v>
       </c>
       <c r="AA16" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB16" s="8" t="n">
-        <v>144</v>
+        <v>52</v>
+      </c>
+      <c r="AB16" s="10" t="n">
+        <v>16</v>
       </c>
       <c r="AC16" s="8" t="n">
-        <v>271</v>
+        <v>53</v>
+      </c>
+      <c r="AD16" s="8" t="n">
+        <v>130</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>0a836a6al1l268p7ak2p5yn7sfzs2tsg</t>
+          <t>843996095354019840</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>中山东路228号新世纪广场A幢投放点</t>
+          <t>25-晚峰-地铁站-柳州东路2号口</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>午峰+晚峰</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>15</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1101</v>
+        <v>2155</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="L17" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="M17" s="8" t="n">
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N17" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="N17" s="8" t="n">
-        <v>107</v>
-      </c>
       <c r="O17" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="P17" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="P17" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="Q17" s="8" t="n">
-        <v>72</v>
+        <v>185</v>
       </c>
       <c r="R17" s="8" t="n">
-        <v>40</v>
+        <v>142</v>
       </c>
       <c r="S17" s="8" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="T17" s="8" t="n">
-        <v>40</v>
+        <v>219</v>
       </c>
       <c r="U17" s="8" t="n">
-        <v>76</v>
+        <v>195</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="W17" s="8" t="n">
-        <v>77</v>
-      </c>
-      <c r="X17" s="9" t="inlineStr">
+        <v>128</v>
+      </c>
+      <c r="X17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
       </c>
-      <c r="Y17" s="8" t="n">
-        <v>79</v>
-      </c>
-      <c r="Z17" s="7" t="n">
-        <v>0</v>
+      <c r="Z17" s="8" t="n">
+        <v>175</v>
       </c>
       <c r="AA17" s="8" t="n">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="AB17" s="8" t="n">
-        <v>41</v>
+        <v>144</v>
       </c>
       <c r="AC17" s="8" t="n">
-        <v>136</v>
+        <v>271</v>
+      </c>
+      <c r="AD17" s="8" t="n">
+        <v>275</v>
       </c>
     </row>
     <row r="18">
@@ -2482,25 +2533,25 @@
         <v>19</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>757</v>
+        <v>824</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="L18" s="8" t="n">
@@ -2559,6 +2610,9 @@
       <c r="AC18" s="8" t="n">
         <v>22</v>
       </c>
+      <c r="AD18" s="8" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -2585,25 +2639,25 @@
         <v>19</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1181</v>
+        <v>1255</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="L19" s="8" t="n">
@@ -2662,6 +2716,9 @@
       <c r="AC19" s="8" t="n">
         <v>37</v>
       </c>
+      <c r="AD19" s="8" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -2688,16 +2745,16 @@
         <v>20</v>
       </c>
       <c r="F20" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G20" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="G20" s="3" t="n">
-        <v>15</v>
-      </c>
       <c r="H20" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1234</v>
+        <v>1328</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -2767,6 +2824,9 @@
       <c r="AC20" s="8" t="n">
         <v>122</v>
       </c>
+      <c r="AD20" s="8" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -2793,16 +2853,16 @@
         <v>20</v>
       </c>
       <c r="F21" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G21" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="G21" s="3" t="n">
-        <v>15</v>
-      </c>
       <c r="H21" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1763</v>
+        <v>1888</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -2872,6 +2932,9 @@
       <c r="AC21" s="8" t="n">
         <v>149</v>
       </c>
+      <c r="AD21" s="8" t="n">
+        <v>125</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -2898,16 +2961,16 @@
         <v>19</v>
       </c>
       <c r="F22" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G22" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>16</v>
-      </c>
       <c r="H22" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>1116</v>
+        <v>1195</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2916,7 +2979,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="L22" s="8" t="n">
@@ -2975,6 +3038,9 @@
       <c r="AC22" s="8" t="n">
         <v>32</v>
       </c>
+      <c r="AD22" s="8" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -3001,16 +3067,16 @@
         <v>15</v>
       </c>
       <c r="F23" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G23" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G23" s="3" t="n">
+      <c r="H23" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H23" s="3" t="n">
-        <v>15</v>
-      </c>
       <c r="I23" s="3" t="n">
-        <v>1878</v>
+        <v>1935</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -3019,7 +3085,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="L23" s="8" t="n">
@@ -3078,6 +3144,9 @@
       <c r="AC23" s="10" t="n">
         <v>14</v>
       </c>
+      <c r="AD23" s="8" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -3104,16 +3173,16 @@
         <v>19</v>
       </c>
       <c r="F24" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G24" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G24" s="3" t="n">
+      <c r="H24" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H24" s="3" t="n">
-        <v>15</v>
-      </c>
       <c r="I24" s="3" t="n">
-        <v>443</v>
+        <v>463</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -3122,7 +3191,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="L24" s="8" t="n">
@@ -3181,6 +3250,9 @@
       <c r="AC24" s="8" t="n">
         <v>20</v>
       </c>
+      <c r="AD24" s="8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -3207,16 +3279,16 @@
         <v>15</v>
       </c>
       <c r="F25" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G25" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G25" s="3" t="n">
-        <v>16</v>
-      </c>
       <c r="H25" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1739</v>
+        <v>1831</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -3284,6 +3356,9 @@
       <c r="AC25" s="8" t="n">
         <v>64</v>
       </c>
+      <c r="AD25" s="8" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -3310,20 +3385,20 @@
         <v>0</v>
       </c>
       <c r="F26" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G26" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="G26" s="3" t="n">
-        <v>17</v>
-      </c>
       <c r="H26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>981</v>
+        <v>1006</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
@@ -3385,6 +3460,9 @@
       <c r="AC26" s="11" t="n">
         <v>25</v>
       </c>
+      <c r="AD26" s="11" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -3411,16 +3489,16 @@
         <v>0</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>2235</v>
+        <v>2603</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -3490,6 +3568,9 @@
       <c r="AC27" s="11" t="n">
         <v>243</v>
       </c>
+      <c r="AD27" s="11" t="n">
+        <v>368</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -3516,16 +3597,16 @@
         <v>15</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2543</v>
+        <v>2758</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -3595,6 +3676,9 @@
       <c r="AC28" s="8" t="n">
         <v>148</v>
       </c>
+      <c r="AD28" s="8" t="n">
+        <v>215</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -3621,16 +3705,16 @@
         <v>20</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1908</v>
+        <v>2066</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -3698,6 +3782,9 @@
       <c r="AC29" s="8" t="n">
         <v>116</v>
       </c>
+      <c r="AD29" s="8" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -3724,16 +3811,16 @@
         <v>15</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>1088</v>
+        <v>1109</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -3801,6 +3888,9 @@
       <c r="AC30" s="8" t="n">
         <v>47</v>
       </c>
+      <c r="AD30" s="8" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -3827,16 +3917,16 @@
         <v>20</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>3030</v>
+        <v>3272</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -3904,6 +3994,9 @@
       <c r="AC31" s="8" t="n">
         <v>175</v>
       </c>
+      <c r="AD31" s="8" t="n">
+        <v>242</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -3930,16 +4023,16 @@
         <v>19</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1430</v>
+        <v>1450</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -4007,6 +4100,9 @@
       <c r="AC32" s="8" t="n">
         <v>90</v>
       </c>
+      <c r="AD32" s="8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -4033,16 +4129,16 @@
         <v>19</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1957</v>
+        <v>2034</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -4110,6 +4206,9 @@
       <c r="AC33" s="8" t="n">
         <v>167</v>
       </c>
+      <c r="AD33" s="8" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -4136,16 +4235,16 @@
         <v>19</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>1450</v>
+        <v>1470</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -4213,6 +4312,9 @@
       <c r="AC34" s="8" t="n">
         <v>122</v>
       </c>
+      <c r="AD34" s="8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -4239,16 +4341,16 @@
         <v>19</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1791</v>
+        <v>1963</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -4316,6 +4418,9 @@
       <c r="AC35" s="8" t="n">
         <v>83</v>
       </c>
+      <c r="AD35" s="8" t="n">
+        <v>172</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -4342,16 +4447,16 @@
         <v>20</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>4273</v>
+        <v>4573</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -4419,6 +4524,9 @@
       <c r="AC36" s="8" t="n">
         <v>325</v>
       </c>
+      <c r="AD36" s="8" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -4445,16 +4553,16 @@
         <v>20</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>2688</v>
+        <v>2957</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -4521,6 +4629,9 @@
       </c>
       <c r="AC37" s="8" t="n">
         <v>218</v>
+      </c>
+      <c r="AD37" s="8" t="n">
+        <v>269</v>
       </c>
     </row>
   </sheetData>
@@ -7280,7 +7391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AD54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7312,6 +7423,7 @@
     <col width="11" customWidth="1" min="27" max="27"/>
     <col width="11" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7467,6 +7579,11 @@
           <t>10-26(一)</t>
         </is>
       </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>10-27(二)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -7493,7 +7610,7 @@
         <v>20</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>7</v>
@@ -7506,12 +7623,12 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="L3" s="7" t="n">
@@ -7570,6 +7687,9 @@
       <c r="AC3" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="AD3" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -7596,25 +7716,25 @@
         <v>10</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L4" s="7" t="n">
@@ -7673,6 +7793,9 @@
       <c r="AC4" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="AD4" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -7699,25 +7822,25 @@
         <v>20</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G5" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>8</v>
-      </c>
       <c r="I5" s="3" t="n">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L5" s="7" t="n">
@@ -7776,6 +7899,9 @@
       <c r="AC5" s="8" t="n">
         <v>55</v>
       </c>
+      <c r="AD5" s="8" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -7802,25 +7928,25 @@
         <v>10</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>8</v>
-      </c>
       <c r="I6" s="3" t="n">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L6" s="7" t="n">
@@ -7879,6 +8005,9 @@
       <c r="AC6" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="AD6" s="8" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -7905,25 +8034,25 @@
         <v>10</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="L7" s="7" t="n">
@@ -7982,6 +8111,9 @@
       <c r="AC7" s="8" t="n">
         <v>12</v>
       </c>
+      <c r="AD7" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -8008,25 +8140,25 @@
         <v>10</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="L8" s="7" t="n">
@@ -8085,85 +8217,88 @@
       <c r="AC8" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="AD8" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>0a83f096l1l8jjun6xxt9t7uxyibq9b9</t>
+          <t>0a8320ecl1lvbzz3tyzcnk28dt6w9vz4</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>弘利路龙湖·水晶郦城站点B</t>
+          <t>逸夫医院门口左手</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
         <v>10</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>142</v>
+        <v>273</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="L9" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="M9" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="M9" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="N9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="8" t="n">
-        <v>11</v>
+      <c r="O9" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="P9" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="Q9" s="8" t="n">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="R9" s="8" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="S9" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="U9" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="T9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="V9" s="8" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="W9" s="7" t="n">
         <v>0</v>
@@ -8173,48 +8308,51 @@
           <t>0☂</t>
         </is>
       </c>
-      <c r="Y9" s="8" t="n">
-        <v>11</v>
+      <c r="Y9" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="Z9" s="8" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AA9" s="8" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="AB9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AC9" s="7" t="n">
+      <c r="AC9" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AD9" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>0a8320ecl1lvbzz3tyzcnk28dt6w9vz4</t>
+          <t>0a83f096l1l8jjun6xxt9t7uxyibq9b9</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>逸夫医院门口左手</t>
+          <t>弘利路龙湖·水晶郦城站点B</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
         <v>10</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>11</v>
@@ -8223,50 +8361,50 @@
         <v>11</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>273</v>
+        <v>153</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="L10" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="M10" s="8" t="n">
-        <v>12</v>
+        <v>32</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O10" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="P10" s="7" t="n">
-        <v>0</v>
+      <c r="O10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="8" t="n">
+        <v>11</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="R10" s="8" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="T10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="U10" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="V10" s="8" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="W10" s="7" t="n">
         <v>0</v>
@@ -8276,20 +8414,23 @@
           <t>0☂</t>
         </is>
       </c>
-      <c r="Y10" s="7" t="n">
-        <v>0</v>
+      <c r="Y10" s="8" t="n">
+        <v>11</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AA10" s="8" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="AB10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AC10" s="8" t="n">
-        <v>36</v>
+      <c r="AC10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="8" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -8317,7 +8458,7 @@
         <v>20</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>13</v>
@@ -8330,12 +8471,12 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="L11" s="10" t="n">
@@ -8394,16 +8535,19 @@
       <c r="AC11" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="AD11" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>889717813217533952</t>
+          <t>0a8302d5l1lir2dxfqaeqgk2ktn2mjev</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>高新-高校-交院东门-全周-全天-50</t>
+          <t>高新-高校-金科北门2-全周-全天-30</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -8413,142 +8557,143 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>午峰</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>425</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="M12" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="I12" s="3" t="n">
-        <v>881</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>76%</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>65%</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="n">
-        <v>43</v>
-      </c>
-      <c r="M12" s="8" t="n">
-        <v>33</v>
-      </c>
       <c r="N12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="7" t="n">
-        <v>0</v>
+      <c r="O12" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="P12" s="8" t="n">
+        <v>25</v>
       </c>
       <c r="Q12" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="R12" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="S12" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v>86</v>
+      <c r="R12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="T12" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="U12" s="8" t="n">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="V12" s="8" t="n">
-        <v>101</v>
+        <v>22</v>
       </c>
       <c r="W12" s="8" t="n">
-        <v>155</v>
-      </c>
-      <c r="X12" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+        <v>35</v>
+      </c>
+      <c r="X12" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="Y12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Z12" s="8" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="AA12" s="8" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AB12" s="8" t="n">
-        <v>138</v>
-      </c>
-      <c r="AC12" s="10" t="n">
-        <v>9</v>
+        <v>89</v>
+      </c>
+      <c r="AC12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>0a83d695l1lz6m3vbn8zbatt525u6cbu</t>
+          <t>889717813217533952</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>景明北大街站点B</t>
+          <t>高新-高校-交院东门-全周-全天-50</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>12</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>473</v>
+        <v>914</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>71%</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="7" t="n">
-        <v>0</v>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="M13" s="8" t="n">
+        <v>33</v>
       </c>
       <c r="N13" s="7" t="n">
         <v>0</v>
@@ -8556,65 +8701,68 @@
       <c r="O13" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P13" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q13" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="R13" s="10" t="n">
-        <v>6</v>
+      <c r="P13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="R13" s="8" t="n">
+        <v>40</v>
       </c>
       <c r="S13" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v>86</v>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v>95</v>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v>101</v>
+      </c>
+      <c r="W13" s="8" t="n">
+        <v>155</v>
+      </c>
+      <c r="X13" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA13" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="T13" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v>49</v>
-      </c>
-      <c r="W13" s="8" t="n">
-        <v>38</v>
-      </c>
-      <c r="X13" s="9" t="inlineStr">
-        <is>
-          <t>34☂</t>
-        </is>
-      </c>
-      <c r="Y13" s="8" t="n">
+      <c r="AB13" s="8" t="n">
+        <v>138</v>
+      </c>
+      <c r="AC13" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD13" s="8" t="n">
         <v>33</v>
-      </c>
-      <c r="Z13" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="AA13" s="8" t="n">
-        <v>49</v>
-      </c>
-      <c r="AB13" s="8" t="n">
-        <v>49</v>
-      </c>
-      <c r="AC13" s="8" t="n">
-        <v>51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>0a837fbbl1lcvvfvrrb6nbtsxdr5xk2w</t>
+          <t>0a83d695l1lz6m3vbn8zbatt525u6cbu</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>天元东路辅路南京义乌小商品城站点H</t>
+          <t>景明北大街站点B</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -8623,96 +8771,99 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G14" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="H14" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="I14" s="3" t="n">
-        <v>278</v>
+        <v>539</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>71%</t>
-        </is>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>12</v>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="M14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N14" s="8" t="n">
+      <c r="N14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="O14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="8" t="n">
-        <v>24</v>
-      </c>
       <c r="Q14" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="R14" s="8" t="n">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="R14" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="S14" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="T14" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="U14" s="7" t="n">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v>22</v>
       </c>
       <c r="V14" s="8" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="W14" s="8" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="X14" s="9" t="inlineStr">
         <is>
-          <t>24☂</t>
+          <t>34☂</t>
         </is>
       </c>
       <c r="Y14" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z14" s="7" t="n">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="Z14" s="8" t="n">
+        <v>33</v>
       </c>
       <c r="AA14" s="8" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="AB14" s="8" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="AC14" s="8" t="n">
-        <v>36</v>
+        <v>51</v>
+      </c>
+      <c r="AD14" s="8" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>889935238642700288</t>
+          <t>0a837fbbl1lcvvfvrrb6nbtsxdr5xk2w</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>南京市江宁区淳化街道博观路保利·梧桐语</t>
+          <t>天元东路辅路南京义乌小商品城站点H</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -8729,98 +8880,101 @@
         <v>10</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>13</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>242</v>
+        <v>290</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>76%</t>
-        </is>
-      </c>
-      <c r="L15" s="7" t="n">
-        <v>0</v>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="L15" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="M15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="O15" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="P15" s="7" t="n">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="O15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="Q15" s="8" t="n">
         <v>12</v>
       </c>
       <c r="R15" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="S15" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="T15" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="S15" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v>21</v>
-      </c>
       <c r="W15" s="8" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="X15" s="9" t="inlineStr">
         <is>
-          <t>0☂</t>
+          <t>24☂</t>
         </is>
       </c>
       <c r="Y15" s="8" t="n">
-        <v>38</v>
-      </c>
-      <c r="Z15" s="8" t="n">
-        <v>25</v>
+        <v>12</v>
+      </c>
+      <c r="Z15" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="AA15" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AB15" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="AB15" s="8" t="n">
+        <v>36</v>
       </c>
       <c r="AC15" s="8" t="n">
         <v>36</v>
       </c>
+      <c r="AD15" s="8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>0a838d77l1lhvwurirt76tdpsj4f7z4m</t>
+          <t>889935238642700288</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>龙昌路中南·上悦城站点A</t>
+          <t>南京市江宁区淳化街道博观路保利·梧桐语</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>李小凯</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -8832,93 +8986,96 @@
         <v>10</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G16" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>254</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="O16" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="P16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="R16" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="S16" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="T16" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="I16" s="3" t="n">
-        <v>144</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>76%</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>76%</t>
-        </is>
-      </c>
-      <c r="L16" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="M16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="P16" s="8" t="n">
+      <c r="U16" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="W16" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="X16" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y16" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z16" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA16" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AD16" s="8" t="n">
         <v>12</v>
-      </c>
-      <c r="Q16" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="R16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="W16" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="X16" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Y16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA16" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB16" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC16" s="8" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>1084739124625276928</t>
+          <t>0a838d77l1lhvwurirt76tdpsj4f7z4m</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>骆村路骆村新寓A区站点A</t>
+          <t>龙昌路中南·上悦城站点A</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -8935,25 +9092,25 @@
         <v>10</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="L17" s="8" t="n">
@@ -8962,14 +9119,14 @@
       <c r="M17" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N17" s="8" t="n">
-        <v>23</v>
+      <c r="N17" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="O17" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="P17" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="P17" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="Q17" s="8" t="n">
         <v>10</v>
@@ -8978,16 +9135,16 @@
         <v>0</v>
       </c>
       <c r="S17" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T17" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U17" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W17" s="8" t="n">
         <v>11</v>
@@ -9001,41 +9158,44 @@
         <v>0</v>
       </c>
       <c r="Z17" s="8" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AA17" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB17" s="8" t="n">
         <v>11</v>
-      </c>
-      <c r="AB17" s="8" t="n">
-        <v>12</v>
       </c>
       <c r="AC17" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="AD17" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>0a8302d5l1lir2dxfqaeqgk2ktn2mjev</t>
+          <t>1084739124625276928</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>高新-高校-金科北门2-全周-全天-30</t>
+          <t>骆村路骆村新寓A区站点A</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>李小凯</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>18</v>
@@ -9044,10 +9204,10 @@
         <v>14</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>425</v>
+        <v>180</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -9056,62 +9216,67 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="L18" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="M18" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="10" t="n">
+      <c r="M18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="O18" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="P18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="R18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="P18" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q18" s="10" t="n">
+      <c r="T18" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="W18" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="R18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="10" t="n">
+      <c r="X18" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA18" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="T18" s="10" t="n">
+      <c r="AB18" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC18" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="U18" s="8" t="n">
-        <v>66</v>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="W18" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="X18" s="10" t="n">
+      <c r="AD18" s="8" t="n">
         <v>11</v>
-      </c>
-      <c r="Y18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA18" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB18" s="8" t="n">
-        <v>89</v>
-      </c>
-      <c r="AC18" s="7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -9139,25 +9304,25 @@
         <v>10</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G19" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="H19" s="3" t="n">
-        <v>13</v>
-      </c>
       <c r="I19" s="3" t="n">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="L19" s="8" t="n">
@@ -9216,6 +9381,9 @@
       <c r="AC19" s="8" t="n">
         <v>21</v>
       </c>
+      <c r="AD19" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -9242,25 +9410,25 @@
         <v>10</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="L20" s="8" t="n">
@@ -9319,6 +9487,9 @@
       <c r="AC20" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="AD20" s="8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -9345,25 +9516,25 @@
         <v>30</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>684</v>
+        <v>727</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="L21" s="7" t="n">
@@ -9420,6 +9591,9 @@
       <c r="AC21" s="10" t="n">
         <v>11</v>
       </c>
+      <c r="AD21" s="8" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -9446,25 +9620,25 @@
         <v>20</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>448</v>
+        <v>480</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="L22" s="10" t="n">
@@ -9521,6 +9695,9 @@
       <c r="AC22" s="8" t="n">
         <v>47</v>
       </c>
+      <c r="AD22" s="8" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -9547,25 +9724,25 @@
         <v>20</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>514</v>
+        <v>558</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="L23" s="8" t="n">
@@ -9624,6 +9801,9 @@
       <c r="AC23" s="8" t="n">
         <v>34</v>
       </c>
+      <c r="AD23" s="8" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -9650,25 +9830,25 @@
         <v>20</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>565</v>
+        <v>586</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="L24" s="7" t="n">
@@ -9727,6 +9907,9 @@
       <c r="AC24" s="8" t="n">
         <v>38</v>
       </c>
+      <c r="AD24" s="8" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -9753,25 +9936,25 @@
         <v>20</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>594</v>
+        <v>638</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="L25" s="10" t="n">
@@ -9830,6 +10013,9 @@
       <c r="AC25" s="8" t="n">
         <v>44</v>
       </c>
+      <c r="AD25" s="8" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -9856,25 +10042,25 @@
         <v>50</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>1067</v>
+        <v>1131</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="L26" s="7" t="n">
@@ -9933,6 +10119,9 @@
       <c r="AC26" s="8" t="n">
         <v>56</v>
       </c>
+      <c r="AD26" s="8" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -9959,25 +10148,25 @@
         <v>20</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1086</v>
+        <v>1185</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="L27" s="7" t="n">
@@ -10036,6 +10225,9 @@
       <c r="AC27" s="8" t="n">
         <v>110</v>
       </c>
+      <c r="AD27" s="8" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -10062,25 +10254,25 @@
         <v>10</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="L28" s="7" t="n">
@@ -10139,6 +10331,9 @@
       <c r="AC28" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="AD28" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -10165,25 +10360,25 @@
         <v>10</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="L29" s="8" t="n">
@@ -10242,6 +10437,9 @@
       <c r="AC29" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="AD29" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -10268,25 +10466,25 @@
         <v>10</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>491</v>
+        <v>511</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="L30" s="7" t="n">
@@ -10345,6 +10543,9 @@
       <c r="AC30" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="AD30" s="8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -10371,25 +10572,25 @@
         <v>10</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>515</v>
+        <v>535</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="L31" s="8" t="n">
@@ -10448,6 +10649,9 @@
       <c r="AC31" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="AD31" s="8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -10474,16 +10678,16 @@
         <v>10</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -10549,6 +10753,9 @@
       <c r="AC32" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="AD32" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -10575,16 +10782,16 @@
         <v>10</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>373</v>
+        <v>395</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -10650,6 +10857,9 @@
       <c r="AC33" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="AD33" s="8" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -10676,16 +10886,16 @@
         <v>10</v>
       </c>
       <c r="F34" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G34" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="H34" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H34" s="3" t="n">
-        <v>15</v>
-      </c>
       <c r="I34" s="3" t="n">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -10694,7 +10904,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="L34" s="8" t="n">
@@ -10753,6 +10963,9 @@
       <c r="AC34" s="8" t="n">
         <v>16</v>
       </c>
+      <c r="AD34" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -10779,16 +10992,16 @@
         <v>10</v>
       </c>
       <c r="F35" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G35" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G35" s="3" t="n">
-        <v>16</v>
-      </c>
       <c r="H35" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -10856,6 +11069,9 @@
       <c r="AC35" s="8" t="n">
         <v>22</v>
       </c>
+      <c r="AD35" s="8" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -10882,25 +11098,25 @@
         <v>10</v>
       </c>
       <c r="F36" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G36" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="G36" s="3" t="n">
-        <v>17</v>
-      </c>
       <c r="H36" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>691</v>
+        <v>728</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="L36" s="8" t="n">
@@ -10957,6 +11173,9 @@
       <c r="AC36" s="8" t="n">
         <v>37</v>
       </c>
+      <c r="AD36" s="8" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -10983,25 +11202,25 @@
         <v>10</v>
       </c>
       <c r="F37" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G37" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="G37" s="3" t="n">
-        <v>17</v>
-      </c>
       <c r="H37" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>407</v>
+        <v>445</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="L37" s="8" t="n">
@@ -11058,6 +11277,9 @@
       <c r="AC37" s="8" t="n">
         <v>36</v>
       </c>
+      <c r="AD37" s="8" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -11084,25 +11306,25 @@
         <v>10</v>
       </c>
       <c r="F38" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G38" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="G38" s="3" t="n">
-        <v>17</v>
-      </c>
       <c r="H38" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="L38" s="8" t="n">
@@ -11159,6 +11381,9 @@
       <c r="AC38" s="8" t="n">
         <v>19</v>
       </c>
+      <c r="AD38" s="8" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -11185,16 +11410,16 @@
         <v>50</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>11</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1708</v>
+        <v>1721</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -11203,7 +11428,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="L39" s="8" t="n">
@@ -11262,6 +11487,9 @@
       <c r="AC39" s="10" t="n">
         <v>12</v>
       </c>
+      <c r="AD39" s="10" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -11288,16 +11516,16 @@
         <v>20</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>738</v>
+        <v>771</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -11306,7 +11534,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="L40" s="8" t="n">
@@ -11365,6 +11593,9 @@
       <c r="AC40" s="10" t="n">
         <v>11</v>
       </c>
+      <c r="AD40" s="8" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -11391,16 +11622,16 @@
         <v>30</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>1191</v>
+        <v>1251</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -11409,7 +11640,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="L41" s="8" t="n">
@@ -11468,6 +11699,9 @@
       <c r="AC41" s="8" t="n">
         <v>38</v>
       </c>
+      <c r="AD41" s="8" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -11494,16 +11728,16 @@
         <v>10</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>693</v>
+        <v>751</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -11573,6 +11807,9 @@
       <c r="AC42" s="8" t="n">
         <v>36</v>
       </c>
+      <c r="AD42" s="8" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -11599,16 +11836,16 @@
         <v>11</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -11678,6 +11915,9 @@
       <c r="AC43" s="8" t="n">
         <v>50</v>
       </c>
+      <c r="AD43" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -11704,16 +11944,16 @@
         <v>20</v>
       </c>
       <c r="F44" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H44" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G44" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>16</v>
-      </c>
       <c r="I44" s="3" t="n">
-        <v>2347</v>
+        <v>2378</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -11781,6 +12021,9 @@
       <c r="AC44" s="8" t="n">
         <v>40</v>
       </c>
+      <c r="AD44" s="8" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -11807,16 +12050,16 @@
         <v>30</v>
       </c>
       <c r="F45" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H45" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G45" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>16</v>
-      </c>
       <c r="I45" s="3" t="n">
-        <v>3514</v>
+        <v>3614</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -11884,6 +12127,9 @@
       <c r="AC45" s="8" t="n">
         <v>40</v>
       </c>
+      <c r="AD45" s="8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -11910,16 +12156,16 @@
         <v>20</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>903</v>
+        <v>945</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -11987,6 +12233,9 @@
       <c r="AC46" s="8" t="n">
         <v>48</v>
       </c>
+      <c r="AD46" s="8" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -12013,16 +12262,16 @@
         <v>10</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -12090,6 +12339,9 @@
       <c r="AC47" s="8" t="n">
         <v>39</v>
       </c>
+      <c r="AD47" s="8" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -12116,16 +12368,16 @@
         <v>40</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2017</v>
+        <v>2158</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -12193,6 +12445,9 @@
       <c r="AC48" s="8" t="n">
         <v>93</v>
       </c>
+      <c r="AD48" s="8" t="n">
+        <v>141</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -12219,16 +12474,16 @@
         <v>10</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -12296,6 +12551,9 @@
       <c r="AC49" s="8" t="n">
         <v>25</v>
       </c>
+      <c r="AD49" s="8" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -12322,16 +12580,16 @@
         <v>10</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>971</v>
+        <v>1044</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -12399,6 +12657,9 @@
       <c r="AC50" s="8" t="n">
         <v>50</v>
       </c>
+      <c r="AD50" s="8" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -12425,16 +12686,16 @@
         <v>60</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>5671</v>
+        <v>5971</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -12502,6 +12763,9 @@
       <c r="AC51" s="8" t="n">
         <v>341</v>
       </c>
+      <c r="AD51" s="8" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -12528,16 +12792,16 @@
         <v>10</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>1043</v>
+        <v>1113</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -12605,6 +12869,9 @@
       <c r="AC52" s="8" t="n">
         <v>90</v>
       </c>
+      <c r="AD52" s="8" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -12631,16 +12898,16 @@
         <v>10</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>2754</v>
+        <v>2794</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -12708,6 +12975,9 @@
       <c r="AC53" s="8" t="n">
         <v>40</v>
       </c>
+      <c r="AD53" s="8" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -12734,16 +13004,16 @@
         <v>10</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>488</v>
+        <v>532</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -12809,6 +13079,9 @@
         <v>28</v>
       </c>
       <c r="AC54" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AD54" s="8" t="n">
         <v>44</v>
       </c>
     </row>
@@ -16536,25 +16809,25 @@
         <v>4</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>88.4%</t>
         </is>
       </c>
     </row>
@@ -16571,25 +16844,25 @@
         <v>5</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -16606,16 +16879,16 @@
         <v>11</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -16624,7 +16897,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>89.0%</t>
         </is>
       </c>
     </row>
@@ -16641,25 +16914,25 @@
         <v>2</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>80.6%</t>
         </is>
       </c>
     </row>
@@ -16676,10 +16949,10 @@
         <v>1</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>8</v>
@@ -16689,12 +16962,12 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -16711,25 +16984,25 @@
         <v>2</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F8" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="G8" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="G8" s="3" t="n">
-        <v>27</v>
-      </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>87.9%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>82.9%</t>
         </is>
       </c>
     </row>
@@ -16746,25 +17019,25 @@
         <v>6</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>87.6%</t>
+          <t>88.3%</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>82.6%</t>
         </is>
       </c>
     </row>
@@ -17184,25 +17457,25 @@
         <v>10</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>96.1%</t>
         </is>
       </c>
     </row>
@@ -17219,25 +17492,25 @@
         <v>12</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>79.0%</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.6%</t>
         </is>
       </c>
     </row>
@@ -17254,25 +17527,25 @@
         <v>10</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>75.3%</t>
         </is>
       </c>
     </row>
@@ -17289,25 +17562,25 @@
         <v>11</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>90.4%</t>
         </is>
       </c>
     </row>
@@ -17324,25 +17597,25 @@
         <v>9</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>70.1%</t>
         </is>
       </c>
     </row>

--- a/coverage.xlsx
+++ b/coverage.xlsx
@@ -99,12 +99,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BDD7EE"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -583,12 +583,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>88.4%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>85.6%</t>
         </is>
       </c>
     </row>
@@ -639,12 +639,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>86.0%</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>79.7%</t>
         </is>
       </c>
     </row>
@@ -680,14 +680,14 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>数据范围: 20261001 ~ 20261027</t>
+          <t>数据范围: 20261001 ~ 20261028</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>工作日: 19天, 周末: 8天</t>
+          <t>工作日: 20天, 周末: 8天</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD37"/>
+  <dimension ref="A1:AE37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -763,6 +763,7 @@
     <col width="11" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -923,6 +924,11 @@
           <t>10-27(二)</t>
         </is>
       </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>10-28(三)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -949,25 +955,25 @@
         <v>10</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>365</v>
+        <v>407</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="L3" s="7" t="n">
@@ -1029,6 +1035,9 @@
       <c r="AD3" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="AE3" s="8" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -1055,25 +1064,25 @@
         <v>15</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>385</v>
+        <v>408</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="L4" s="8" t="n">
@@ -1135,30 +1144,33 @@
       <c r="AD4" s="8" t="n">
         <v>20</v>
       </c>
+      <c r="AE4" s="8" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>778851422965239808</t>
+          <t>684038567596433408</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-仙林新村</t>
+          <t>25-晚峰-地铁站-柳州东路公交站台</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+晚峰</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>18</v>
@@ -1167,10 +1179,10 @@
         <v>13</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>261</v>
+        <v>1799</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -1179,92 +1191,97 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="L5" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="M5" s="7" t="n">
-        <v>0</v>
+          <t>未配置</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="n">
+        <v>139</v>
+      </c>
+      <c r="M5" s="10" t="n">
+        <v>161</v>
       </c>
       <c r="N5" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="O5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="7" t="n">
-        <v>0</v>
+        <v>106</v>
+      </c>
+      <c r="O5" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="P5" s="10" t="n">
+        <v>111</v>
       </c>
       <c r="Q5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="R5" s="8" t="n">
+      <c r="R5" s="10" t="n">
+        <v>241</v>
+      </c>
+      <c r="S5" s="10" t="n">
+        <v>233</v>
+      </c>
+      <c r="T5" s="10" t="n">
+        <v>253</v>
+      </c>
+      <c r="U5" s="10" t="n">
+        <v>167</v>
+      </c>
+      <c r="V5" s="10" t="n">
+        <v>141</v>
+      </c>
+      <c r="W5" s="10" t="n">
+        <v>165</v>
+      </c>
+      <c r="X5" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y5" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Z5" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="S5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" s="8" t="n">
+      <c r="AA5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="V5" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="W5" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="X5" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Y5" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z5" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA5" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB5" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AC5" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AD5" s="8" t="n">
-        <v>25</v>
+      <c r="AD5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>1174627346911133696</t>
+          <t>778851422965239808</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>南京市秦淮区洪武路街道户部街长发银座</t>
+          <t>25-早峰-居民区-仙林新村</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>19</v>
@@ -1273,10 +1290,10 @@
         <v>14</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -1285,17 +1302,17 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="M6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="7" t="n">
-        <v>0</v>
+      <c r="N6" s="11" t="n">
+        <v>5</v>
       </c>
       <c r="O6" s="7" t="n">
         <v>0</v>
@@ -1303,155 +1320,159 @@
       <c r="P6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="10" t="n">
-        <v>10</v>
+      <c r="Q6" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="S6" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v>20</v>
+        <v>25</v>
+      </c>
+      <c r="S6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="V6" s="8" t="n">
         <v>25</v>
+      </c>
+      <c r="V6" s="11" t="n">
+        <v>15</v>
       </c>
       <c r="W6" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="X6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="8" t="n">
-        <v>20</v>
+      <c r="X6" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y6" s="11" t="n">
+        <v>11</v>
       </c>
       <c r="Z6" s="8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AA6" s="8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AB6" s="8" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AC6" s="8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AD6" s="8" t="n">
-        <v>20</v>
+        <v>25</v>
+      </c>
+      <c r="AE6" s="8" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>684038567596433408</t>
+          <t>1174627346911133696</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路公交站台</t>
+          <t>南京市秦淮区洪武路街道户部街长发银座</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>早峰+晚峰</t>
+          <t>午峰</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1799</v>
+        <v>320</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>未配置</t>
-        </is>
-      </c>
-      <c r="L7" s="11" t="n">
-        <v>139</v>
-      </c>
-      <c r="M7" s="11" t="n">
-        <v>161</v>
-      </c>
-      <c r="N7" s="11" t="n">
-        <v>106</v>
-      </c>
-      <c r="O7" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="P7" s="11" t="n">
-        <v>111</v>
-      </c>
-      <c r="Q7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="11" t="n">
-        <v>241</v>
-      </c>
-      <c r="S7" s="11" t="n">
-        <v>233</v>
-      </c>
-      <c r="T7" s="11" t="n">
-        <v>253</v>
-      </c>
-      <c r="U7" s="11" t="n">
-        <v>167</v>
-      </c>
-      <c r="V7" s="11" t="n">
-        <v>141</v>
-      </c>
-      <c r="W7" s="11" t="n">
-        <v>165</v>
-      </c>
-      <c r="X7" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Y7" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Z7" s="11" t="n">
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="R7" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="V7" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="AA7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="11" t="n">
+      <c r="W7" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="AD7" s="7" t="n">
-        <v>0</v>
+      <c r="X7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z7" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA7" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB7" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC7" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD7" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE7" s="8" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -1479,25 +1500,25 @@
         <v>15</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>809</v>
+        <v>884</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="L8" s="7" t="n">
@@ -1559,6 +1580,9 @@
       <c r="AD8" s="8" t="n">
         <v>75</v>
       </c>
+      <c r="AE8" s="8" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -1585,20 +1609,20 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1678</v>
+        <v>1749</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -1606,62 +1630,65 @@
           <t>未配置</t>
         </is>
       </c>
-      <c r="L9" s="11" t="n">
+      <c r="L9" s="10" t="n">
         <v>265</v>
       </c>
-      <c r="M9" s="11" t="n">
+      <c r="M9" s="10" t="n">
         <v>264</v>
       </c>
-      <c r="N9" s="11" t="n">
+      <c r="N9" s="10" t="n">
         <v>298</v>
       </c>
-      <c r="O9" s="11" t="n">
+      <c r="O9" s="10" t="n">
         <v>278</v>
       </c>
-      <c r="P9" s="11" t="n">
+      <c r="P9" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="Q9" s="11" t="n">
+      <c r="Q9" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="R9" s="11" t="n">
+      <c r="R9" s="10" t="n">
         <v>39</v>
       </c>
       <c r="S9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T9" s="11" t="n">
+      <c r="T9" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="U9" s="11" t="n">
+      <c r="U9" s="10" t="n">
         <v>42</v>
       </c>
       <c r="V9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="W9" s="11" t="n">
+      <c r="W9" s="10" t="n">
         <v>150</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="Y9" s="11" t="n">
+      <c r="Y9" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="Z9" s="11" t="n">
+      <c r="Z9" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="AA9" s="11" t="n">
+      <c r="AA9" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="AB9" s="11" t="n">
+      <c r="AB9" s="10" t="n">
         <v>74</v>
       </c>
       <c r="AC9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AD9" s="11" t="n">
+      <c r="AD9" s="10" t="n">
         <v>38</v>
+      </c>
+      <c r="AE9" s="10" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -1689,25 +1716,25 @@
         <v>15</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1809</v>
+        <v>1988</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="L10" s="8" t="n">
@@ -1767,6 +1794,9 @@
       <c r="AD10" s="8" t="n">
         <v>181</v>
       </c>
+      <c r="AE10" s="8" t="n">
+        <v>179</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -1793,25 +1823,25 @@
         <v>15</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1445</v>
+        <v>1548</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="L11" s="8" t="n">
@@ -1871,6 +1901,9 @@
       <c r="AD11" s="8" t="n">
         <v>80</v>
       </c>
+      <c r="AE11" s="8" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -1897,25 +1930,25 @@
         <v>20</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>671</v>
+        <v>726</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="L12" s="8" t="n">
@@ -1948,10 +1981,10 @@
       <c r="U12" s="8" t="n">
         <v>58</v>
       </c>
-      <c r="V12" s="10" t="n">
+      <c r="V12" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="W12" s="10" t="n">
+      <c r="W12" s="11" t="n">
         <v>7</v>
       </c>
       <c r="X12" s="9" t="inlineStr">
@@ -1962,20 +1995,23 @@
       <c r="Y12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" s="10" t="n">
+      <c r="Z12" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="AA12" s="10" t="n">
+      <c r="AA12" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="AB12" s="10" t="n">
+      <c r="AB12" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="AC12" s="10" t="n">
+      <c r="AC12" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="AD12" s="10" t="n">
+      <c r="AD12" s="11" t="n">
         <v>13</v>
+      </c>
+      <c r="AE12" s="8" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="13">
@@ -2003,25 +2039,25 @@
         <v>15</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1336</v>
+        <v>1358</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="L13" s="7" t="n">
@@ -2083,6 +2119,9 @@
       <c r="AD13" s="8" t="n">
         <v>112</v>
       </c>
+      <c r="AE13" s="8" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -2109,25 +2148,25 @@
         <v>20</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1101</v>
+        <v>1140</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="L14" s="8" t="n">
@@ -2189,6 +2228,9 @@
       <c r="AD14" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="AE14" s="8" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -2215,25 +2257,25 @@
         <v>20</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G15" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="H15" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H15" s="3" t="n">
-        <v>15</v>
-      </c>
       <c r="I15" s="3" t="n">
-        <v>427</v>
+        <v>452</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="L15" s="8" t="n">
@@ -2260,7 +2302,7 @@
       <c r="S15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="T15" s="10" t="n">
+      <c r="T15" s="11" t="n">
         <v>1</v>
       </c>
       <c r="U15" s="8" t="n">
@@ -2293,6 +2335,9 @@
       <c r="AD15" s="8" t="n">
         <v>25</v>
       </c>
+      <c r="AE15" s="8" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -2319,25 +2364,25 @@
         <v>20</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G16" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H16" s="3" t="n">
-        <v>14</v>
-      </c>
       <c r="I16" s="3" t="n">
-        <v>871</v>
+        <v>975</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="L16" s="7" t="n">
@@ -2392,7 +2437,7 @@
       <c r="AA16" s="8" t="n">
         <v>52</v>
       </c>
-      <c r="AB16" s="10" t="n">
+      <c r="AB16" s="11" t="n">
         <v>16</v>
       </c>
       <c r="AC16" s="8" t="n">
@@ -2401,6 +2446,9 @@
       <c r="AD16" s="8" t="n">
         <v>130</v>
       </c>
+      <c r="AE16" s="8" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -2427,16 +2475,16 @@
         <v>20</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G17" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="H17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H17" s="3" t="n">
-        <v>15</v>
-      </c>
       <c r="I17" s="3" t="n">
-        <v>2155</v>
+        <v>2330</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -2445,13 +2493,13 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="L17" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M17" s="10" t="n">
+      <c r="M17" s="11" t="n">
         <v>7</v>
       </c>
       <c r="N17" s="8" t="n">
@@ -2507,6 +2555,9 @@
       <c r="AD17" s="8" t="n">
         <v>275</v>
       </c>
+      <c r="AE17" s="8" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -2533,16 +2584,16 @@
         <v>19</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>824</v>
+        <v>904</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -2613,6 +2664,9 @@
       <c r="AD18" s="8" t="n">
         <v>67</v>
       </c>
+      <c r="AE18" s="8" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -2639,16 +2693,16 @@
         <v>19</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1255</v>
+        <v>1338</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -2719,6 +2773,9 @@
       <c r="AD19" s="8" t="n">
         <v>74</v>
       </c>
+      <c r="AE19" s="8" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -2745,16 +2802,16 @@
         <v>20</v>
       </c>
       <c r="F20" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G20" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G20" s="3" t="n">
-        <v>16</v>
-      </c>
       <c r="H20" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1328</v>
+        <v>1392</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -2827,6 +2884,9 @@
       <c r="AD20" s="8" t="n">
         <v>94</v>
       </c>
+      <c r="AE20" s="8" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -2853,16 +2913,16 @@
         <v>20</v>
       </c>
       <c r="F21" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G21" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="G21" s="3" t="n">
-        <v>16</v>
-      </c>
       <c r="H21" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1888</v>
+        <v>2036</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -2935,6 +2995,9 @@
       <c r="AD21" s="8" t="n">
         <v>125</v>
       </c>
+      <c r="AE21" s="8" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -2961,31 +3024,31 @@
         <v>19</v>
       </c>
       <c r="F22" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G22" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>17</v>
-      </c>
       <c r="H22" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>1195</v>
+        <v>1257</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="L22" s="8" t="n">
         <v>53</v>
       </c>
-      <c r="M22" s="10" t="n">
+      <c r="M22" s="11" t="n">
         <v>4</v>
       </c>
       <c r="N22" s="8" t="n">
@@ -3003,7 +3066,7 @@
       <c r="R22" s="8" t="n">
         <v>72</v>
       </c>
-      <c r="S22" s="10" t="n">
+      <c r="S22" s="11" t="n">
         <v>6</v>
       </c>
       <c r="T22" s="8" t="n">
@@ -3041,6 +3104,9 @@
       <c r="AD22" s="8" t="n">
         <v>79</v>
       </c>
+      <c r="AE22" s="8" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -3067,20 +3133,20 @@
         <v>15</v>
       </c>
       <c r="F23" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G23" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="G23" s="3" t="n">
+      <c r="H23" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="H23" s="3" t="n">
-        <v>16</v>
-      </c>
       <c r="I23" s="3" t="n">
-        <v>1935</v>
+        <v>2071</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -3141,12 +3207,15 @@
       <c r="AB23" s="8" t="n">
         <v>126</v>
       </c>
-      <c r="AC23" s="10" t="n">
+      <c r="AC23" s="11" t="n">
         <v>14</v>
       </c>
       <c r="AD23" s="8" t="n">
         <v>57</v>
       </c>
+      <c r="AE23" s="8" t="n">
+        <v>136</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -3173,20 +3242,20 @@
         <v>19</v>
       </c>
       <c r="F24" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G24" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="G24" s="3" t="n">
+      <c r="H24" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="H24" s="3" t="n">
-        <v>16</v>
-      </c>
       <c r="I24" s="3" t="n">
-        <v>463</v>
+        <v>483</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
@@ -3203,7 +3272,7 @@
       <c r="N24" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="O24" s="10" t="n">
+      <c r="O24" s="11" t="n">
         <v>11</v>
       </c>
       <c r="P24" s="8" t="n">
@@ -3253,6 +3322,9 @@
       <c r="AD24" s="8" t="n">
         <v>20</v>
       </c>
+      <c r="AE24" s="8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -3279,25 +3351,25 @@
         <v>15</v>
       </c>
       <c r="F25" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G25" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="G25" s="3" t="n">
-        <v>17</v>
-      </c>
       <c r="H25" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1831</v>
+        <v>1926</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="L25" s="8" t="n">
@@ -3359,6 +3431,9 @@
       <c r="AD25" s="8" t="n">
         <v>92</v>
       </c>
+      <c r="AE25" s="8" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -3385,16 +3460,16 @@
         <v>0</v>
       </c>
       <c r="F26" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G26" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G26" s="3" t="n">
-        <v>18</v>
-      </c>
       <c r="H26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>1006</v>
+        <v>1031</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -3406,61 +3481,64 @@
           <t>未配置</t>
         </is>
       </c>
-      <c r="L26" s="11" t="n">
+      <c r="L26" s="10" t="n">
         <v>175</v>
       </c>
-      <c r="M26" s="11" t="n">
+      <c r="M26" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="N26" s="11" t="n">
+      <c r="N26" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="O26" s="11" t="n">
+      <c r="O26" s="10" t="n">
         <v>197</v>
       </c>
-      <c r="P26" s="11" t="n">
+      <c r="P26" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="Q26" s="11" t="n">
+      <c r="Q26" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="R26" s="11" t="n">
+      <c r="R26" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="S26" s="11" t="n">
+      <c r="S26" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="T26" s="11" t="n">
+      <c r="T26" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="U26" s="11" t="n">
+      <c r="U26" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="V26" s="11" t="n">
+      <c r="V26" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="W26" s="11" t="n">
+      <c r="W26" s="10" t="n">
         <v>119</v>
       </c>
-      <c r="X26" s="11" t="n">
+      <c r="X26" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="Y26" s="11" t="n">
+      <c r="Y26" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="Z26" s="11" t="n">
+      <c r="Z26" s="10" t="n">
         <v>25</v>
       </c>
       <c r="AA26" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AB26" s="11" t="n">
+      <c r="AB26" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="AC26" s="11" t="n">
+      <c r="AC26" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="AD26" s="11" t="n">
+      <c r="AD26" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE26" s="10" t="n">
         <v>25</v>
       </c>
     </row>
@@ -3489,16 +3567,16 @@
         <v>0</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>2603</v>
+        <v>2931</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -3510,40 +3588,40 @@
           <t>未配置</t>
         </is>
       </c>
-      <c r="L27" s="11" t="n">
+      <c r="L27" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="M27" s="11" t="n">
+      <c r="M27" s="10" t="n">
         <v>56</v>
       </c>
-      <c r="N27" s="11" t="n">
+      <c r="N27" s="10" t="n">
         <v>53</v>
       </c>
-      <c r="O27" s="11" t="n">
+      <c r="O27" s="10" t="n">
         <v>123</v>
       </c>
-      <c r="P27" s="11" t="n">
+      <c r="P27" s="10" t="n">
         <v>62</v>
       </c>
-      <c r="Q27" s="11" t="n">
+      <c r="Q27" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="R27" s="11" t="n">
+      <c r="R27" s="10" t="n">
         <v>68</v>
       </c>
-      <c r="S27" s="11" t="n">
+      <c r="S27" s="10" t="n">
         <v>78</v>
       </c>
-      <c r="T27" s="11" t="n">
+      <c r="T27" s="10" t="n">
         <v>74</v>
       </c>
-      <c r="U27" s="11" t="n">
+      <c r="U27" s="10" t="n">
         <v>126</v>
       </c>
-      <c r="V27" s="11" t="n">
+      <c r="V27" s="10" t="n">
         <v>231</v>
       </c>
-      <c r="W27" s="11" t="n">
+      <c r="W27" s="10" t="n">
         <v>240</v>
       </c>
       <c r="X27" s="9" t="inlineStr">
@@ -3556,20 +3634,23 @@
           <t>35☂</t>
         </is>
       </c>
-      <c r="Z27" s="11" t="n">
+      <c r="Z27" s="10" t="n">
         <v>188</v>
       </c>
-      <c r="AA27" s="11" t="n">
+      <c r="AA27" s="10" t="n">
         <v>228</v>
       </c>
-      <c r="AB27" s="11" t="n">
+      <c r="AB27" s="10" t="n">
         <v>308</v>
       </c>
-      <c r="AC27" s="11" t="n">
+      <c r="AC27" s="10" t="n">
         <v>243</v>
       </c>
-      <c r="AD27" s="11" t="n">
+      <c r="AD27" s="10" t="n">
         <v>368</v>
+      </c>
+      <c r="AE27" s="10" t="n">
+        <v>328</v>
       </c>
     </row>
     <row r="28">
@@ -3597,16 +3678,16 @@
         <v>15</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2758</v>
+        <v>2995</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -3615,13 +3696,13 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="L28" s="10" t="n">
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="L28" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="M28" s="10" t="n">
+      <c r="M28" s="11" t="n">
         <v>2</v>
       </c>
       <c r="N28" s="8" t="n">
@@ -3679,6 +3760,9 @@
       <c r="AD28" s="8" t="n">
         <v>215</v>
       </c>
+      <c r="AE28" s="8" t="n">
+        <v>237</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -3705,16 +3789,16 @@
         <v>20</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2066</v>
+        <v>2183</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -3785,6 +3869,9 @@
       <c r="AD29" s="8" t="n">
         <v>158</v>
       </c>
+      <c r="AE29" s="8" t="n">
+        <v>117</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -3811,16 +3898,16 @@
         <v>15</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>1109</v>
+        <v>1130</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -3891,6 +3978,9 @@
       <c r="AD30" s="8" t="n">
         <v>21</v>
       </c>
+      <c r="AE30" s="8" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -3917,16 +4007,16 @@
         <v>20</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>3272</v>
+        <v>3479</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -3997,6 +4087,9 @@
       <c r="AD31" s="8" t="n">
         <v>242</v>
       </c>
+      <c r="AE31" s="8" t="n">
+        <v>207</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -4023,16 +4116,16 @@
         <v>19</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1450</v>
+        <v>1549</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -4103,6 +4196,9 @@
       <c r="AD32" s="8" t="n">
         <v>20</v>
       </c>
+      <c r="AE32" s="8" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -4129,16 +4225,16 @@
         <v>19</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>2034</v>
+        <v>2153</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -4209,6 +4305,9 @@
       <c r="AD33" s="8" t="n">
         <v>77</v>
       </c>
+      <c r="AE33" s="8" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -4235,16 +4334,16 @@
         <v>19</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>1470</v>
+        <v>1598</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -4315,6 +4414,9 @@
       <c r="AD34" s="8" t="n">
         <v>20</v>
       </c>
+      <c r="AE34" s="8" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -4341,16 +4443,16 @@
         <v>19</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1963</v>
+        <v>2146</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -4421,6 +4523,9 @@
       <c r="AD35" s="8" t="n">
         <v>172</v>
       </c>
+      <c r="AE35" s="8" t="n">
+        <v>183</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -4447,16 +4552,16 @@
         <v>20</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>4573</v>
+        <v>4773</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -4527,6 +4632,9 @@
       <c r="AD36" s="8" t="n">
         <v>300</v>
       </c>
+      <c r="AE36" s="8" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -4553,16 +4661,16 @@
         <v>20</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>2957</v>
+        <v>3240</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -4632,6 +4740,9 @@
       </c>
       <c r="AD37" s="8" t="n">
         <v>269</v>
+      </c>
+      <c r="AE37" s="8" t="n">
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -5050,13 +5161,13 @@
       <c r="M6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="11" t="n">
+      <c r="N6" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="O6" s="11" t="n">
+      <c r="O6" s="10" t="n">
         <v>66</v>
       </c>
-      <c r="P6" s="11" t="n">
+      <c r="P6" s="10" t="n">
         <v>55</v>
       </c>
       <c r="Q6" s="7" t="n">
@@ -5268,13 +5379,13 @@
           <t>94☂</t>
         </is>
       </c>
-      <c r="M9" s="11" t="n">
+      <c r="M9" s="10" t="n">
         <v>146</v>
       </c>
-      <c r="N9" s="11" t="n">
+      <c r="N9" s="10" t="n">
         <v>236</v>
       </c>
-      <c r="O9" s="11" t="n">
+      <c r="O9" s="10" t="n">
         <v>26</v>
       </c>
       <c r="P9" s="7" t="n">
@@ -5340,10 +5451,10 @@
           <t>38%</t>
         </is>
       </c>
-      <c r="L10" s="10" t="n">
+      <c r="L10" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="M10" s="10" t="n">
+      <c r="M10" s="11" t="n">
         <v>13</v>
       </c>
       <c r="N10" s="8" t="n">
@@ -5499,7 +5610,7 @@
       <c r="P12" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="Q12" s="10" t="n">
+      <c r="Q12" s="11" t="n">
         <v>14</v>
       </c>
       <c r="R12" s="8" t="n">
@@ -5714,7 +5825,7 @@
       <c r="N15" s="8" t="n">
         <v>80</v>
       </c>
-      <c r="O15" s="10" t="n">
+      <c r="O15" s="11" t="n">
         <v>14</v>
       </c>
       <c r="P15" s="7" t="n">
@@ -5785,7 +5896,7 @@
           <t>0☂</t>
         </is>
       </c>
-      <c r="M16" s="10" t="n">
+      <c r="M16" s="11" t="n">
         <v>10</v>
       </c>
       <c r="N16" s="8" t="n">
@@ -5872,7 +5983,7 @@
       <c r="P17" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="Q17" s="10" t="n">
+      <c r="Q17" s="11" t="n">
         <v>3</v>
       </c>
       <c r="R17" s="7" t="n">
@@ -6310,16 +6421,16 @@
           <t>17☂</t>
         </is>
       </c>
-      <c r="M23" s="11" t="n">
+      <c r="M23" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="N23" s="11" t="n">
+      <c r="N23" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="O23" s="11" t="n">
+      <c r="O23" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="P23" s="11" t="n">
+      <c r="P23" s="10" t="n">
         <v>125</v>
       </c>
       <c r="Q23" s="9" t="inlineStr">
@@ -6327,7 +6438,7 @@
           <t>100☂</t>
         </is>
       </c>
-      <c r="R23" s="11" t="n">
+      <c r="R23" s="10" t="n">
         <v>12</v>
       </c>
       <c r="S23" s="9" t="inlineStr">
@@ -6382,28 +6493,28 @@
           <t>未配置</t>
         </is>
       </c>
-      <c r="L24" s="11" t="n">
+      <c r="L24" s="10" t="n">
         <v>94</v>
       </c>
-      <c r="M24" s="11" t="n">
+      <c r="M24" s="10" t="n">
         <v>147</v>
       </c>
-      <c r="N24" s="11" t="n">
+      <c r="N24" s="10" t="n">
         <v>167</v>
       </c>
-      <c r="O24" s="11" t="n">
+      <c r="O24" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="P24" s="11" t="n">
+      <c r="P24" s="10" t="n">
         <v>225</v>
       </c>
-      <c r="Q24" s="11" t="n">
+      <c r="Q24" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="R24" s="11" t="n">
+      <c r="R24" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="S24" s="11" t="n">
+      <c r="S24" s="10" t="n">
         <v>50</v>
       </c>
     </row>
@@ -6453,28 +6564,28 @@
           <t>未配置</t>
         </is>
       </c>
-      <c r="L25" s="11" t="n">
+      <c r="L25" s="10" t="n">
         <v>252</v>
       </c>
-      <c r="M25" s="11" t="n">
+      <c r="M25" s="10" t="n">
         <v>208</v>
       </c>
-      <c r="N25" s="11" t="n">
+      <c r="N25" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="O25" s="11" t="n">
+      <c r="O25" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="P25" s="11" t="n">
+      <c r="P25" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="Q25" s="11" t="n">
+      <c r="Q25" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="11" t="n">
+      <c r="R25" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="S25" s="11" t="n">
+      <c r="S25" s="10" t="n">
         <v>45</v>
       </c>
     </row>
@@ -6763,7 +6874,7 @@
       <c r="M29" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="N29" s="10" t="n">
+      <c r="N29" s="11" t="n">
         <v>5</v>
       </c>
       <c r="O29" s="8" t="n">
@@ -7391,7 +7502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD54"/>
+  <dimension ref="A1:AE54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7424,6 +7535,7 @@
     <col width="11" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7584,6 +7696,11 @@
           <t>10-27(二)</t>
         </is>
       </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>10-28(三)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -7610,25 +7727,25 @@
         <v>20</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="L3" s="7" t="n">
@@ -7658,7 +7775,7 @@
       <c r="T3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U3" s="10" t="n">
+      <c r="U3" s="11" t="n">
         <v>12</v>
       </c>
       <c r="V3" s="8" t="n">
@@ -7675,10 +7792,10 @@
       <c r="Y3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" s="10" t="n">
+      <c r="Z3" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="AA3" s="10" t="n">
+      <c r="AA3" s="11" t="n">
         <v>12</v>
       </c>
       <c r="AB3" s="8" t="n">
@@ -7690,6 +7807,9 @@
       <c r="AD3" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="AE3" s="8" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -7716,25 +7836,25 @@
         <v>10</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="L4" s="7" t="n">
@@ -7796,6 +7916,9 @@
       <c r="AD4" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="AE4" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -7822,31 +7945,31 @@
         <v>20</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H5" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="I5" s="3" t="n">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="L5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="10" t="n">
+      <c r="M5" s="11" t="n">
         <v>11</v>
       </c>
       <c r="N5" s="7" t="n">
@@ -7902,6 +8025,9 @@
       <c r="AD5" s="8" t="n">
         <v>22</v>
       </c>
+      <c r="AE5" s="8" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -7928,25 +8054,25 @@
         <v>10</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G6" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="I6" s="3" t="n">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="L6" s="7" t="n">
@@ -7961,7 +8087,7 @@
       <c r="O6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="10" t="n">
+      <c r="P6" s="11" t="n">
         <v>2</v>
       </c>
       <c r="Q6" s="7" t="n">
@@ -8008,6 +8134,9 @@
       <c r="AD6" s="8" t="n">
         <v>21</v>
       </c>
+      <c r="AE6" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -8034,25 +8163,25 @@
         <v>10</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="L7" s="7" t="n">
@@ -8114,6 +8243,9 @@
       <c r="AD7" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="AE7" s="8" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -8140,25 +8272,25 @@
         <v>10</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="L8" s="7" t="n">
@@ -8220,6 +8352,9 @@
       <c r="AD8" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="AE8" s="8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -8246,25 +8381,25 @@
         <v>10</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="L9" s="8" t="n">
@@ -8326,6 +8461,9 @@
       <c r="AD9" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="AE9" s="8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -8352,25 +8490,25 @@
         <v>10</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="L10" s="8" t="n">
@@ -8432,6 +8570,9 @@
       <c r="AD10" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="AE10" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -8458,49 +8599,49 @@
         <v>20</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G11" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>274</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="L11" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="M11" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="P11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="H11" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>238</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>72%</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="L11" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="M11" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="N11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="P11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="S11" s="10" t="n">
+      <c r="S11" s="11" t="n">
         <v>12</v>
       </c>
       <c r="T11" s="8" t="n">
@@ -8520,16 +8661,16 @@
           <t>0☂</t>
         </is>
       </c>
-      <c r="Y11" s="10" t="n">
+      <c r="Y11" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="Z11" s="10" t="n">
+      <c r="Z11" s="11" t="n">
         <v>12</v>
       </c>
       <c r="AA11" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="AB11" s="10" t="n">
+      <c r="AB11" s="11" t="n">
         <v>12</v>
       </c>
       <c r="AC11" s="7" t="n">
@@ -8537,6 +8678,9 @@
       </c>
       <c r="AD11" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="AE11" s="8" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="12">
@@ -8564,52 +8708,52 @@
         <v>20</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="L12" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="M12" s="10" t="n">
+      <c r="M12" s="11" t="n">
         <v>11</v>
       </c>
       <c r="N12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="10" t="n">
+      <c r="O12" s="11" t="n">
         <v>12</v>
       </c>
       <c r="P12" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="Q12" s="10" t="n">
+      <c r="Q12" s="11" t="n">
         <v>11</v>
       </c>
       <c r="R12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S12" s="10" t="n">
+      <c r="S12" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="T12" s="10" t="n">
+      <c r="T12" s="11" t="n">
         <v>11</v>
       </c>
       <c r="U12" s="8" t="n">
@@ -8621,7 +8765,7 @@
       <c r="W12" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="X12" s="10" t="n">
+      <c r="X12" s="11" t="n">
         <v>11</v>
       </c>
       <c r="Y12" s="7" t="n">
@@ -8642,6 +8786,9 @@
       <c r="AD12" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="AE12" s="8" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -8668,25 +8815,25 @@
         <v>20</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>914</v>
+        <v>946</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="L13" s="8" t="n">
@@ -8704,7 +8851,7 @@
       <c r="P13" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" s="10" t="n">
+      <c r="Q13" s="11" t="n">
         <v>11</v>
       </c>
       <c r="R13" s="8" t="n">
@@ -8742,12 +8889,15 @@
       <c r="AB13" s="8" t="n">
         <v>138</v>
       </c>
-      <c r="AC13" s="10" t="n">
+      <c r="AC13" s="11" t="n">
         <v>9</v>
       </c>
       <c r="AD13" s="8" t="n">
         <v>33</v>
       </c>
+      <c r="AE13" s="8" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -8774,25 +8924,25 @@
         <v>20</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G14" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="H14" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="H14" s="3" t="n">
-        <v>13</v>
-      </c>
       <c r="I14" s="3" t="n">
-        <v>539</v>
+        <v>581</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="L14" s="7" t="n">
@@ -8813,7 +8963,7 @@
       <c r="Q14" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="R14" s="10" t="n">
+      <c r="R14" s="11" t="n">
         <v>6</v>
       </c>
       <c r="S14" s="8" t="n">
@@ -8854,6 +9004,9 @@
       <c r="AD14" s="8" t="n">
         <v>66</v>
       </c>
+      <c r="AE14" s="8" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -8880,25 +9033,25 @@
         <v>10</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G15" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="H15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="H15" s="3" t="n">
-        <v>13</v>
-      </c>
       <c r="I15" s="3" t="n">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="L15" s="8" t="n">
@@ -8925,7 +9078,7 @@
       <c r="S15" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="T15" s="10" t="n">
+      <c r="T15" s="11" t="n">
         <v>6</v>
       </c>
       <c r="U15" s="7" t="n">
@@ -8960,6 +9113,9 @@
       <c r="AD15" s="8" t="n">
         <v>12</v>
       </c>
+      <c r="AE15" s="8" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -8986,25 +9142,25 @@
         <v>10</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="L16" s="7" t="n">
@@ -9066,6 +9222,9 @@
       <c r="AD16" s="8" t="n">
         <v>12</v>
       </c>
+      <c r="AE16" s="8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -9092,25 +9251,25 @@
         <v>10</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="L17" s="8" t="n">
@@ -9172,6 +9331,9 @@
       <c r="AD17" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="AE17" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -9198,25 +9360,25 @@
         <v>10</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="L18" s="8" t="n">
@@ -9278,6 +9440,9 @@
       <c r="AD18" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="AE18" s="8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -9304,25 +9469,25 @@
         <v>10</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G19" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H19" s="3" t="n">
-        <v>14</v>
-      </c>
       <c r="I19" s="3" t="n">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="L19" s="8" t="n">
@@ -9334,7 +9499,7 @@
       <c r="N19" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="O19" s="10" t="n">
+      <c r="O19" s="11" t="n">
         <v>5</v>
       </c>
       <c r="P19" s="7" t="n">
@@ -9384,6 +9549,9 @@
       <c r="AD19" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="AE19" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -9410,25 +9578,25 @@
         <v>10</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="L20" s="8" t="n">
@@ -9490,6 +9658,9 @@
       <c r="AD20" s="8" t="n">
         <v>20</v>
       </c>
+      <c r="AE20" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -9516,25 +9687,25 @@
         <v>30</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>727</v>
+        <v>796</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="L21" s="7" t="n">
@@ -9543,22 +9714,22 @@
       <c r="M21" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N21" s="10" t="n">
+      <c r="N21" s="11" t="n">
         <v>11</v>
       </c>
       <c r="O21" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P21" s="10" t="n">
+      <c r="P21" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="Q21" s="10" t="n">
+      <c r="Q21" s="11" t="n">
         <v>22</v>
       </c>
       <c r="R21" s="8" t="n">
         <v>54</v>
       </c>
-      <c r="S21" s="10" t="n">
+      <c r="S21" s="11" t="n">
         <v>21</v>
       </c>
       <c r="T21" s="8" t="n">
@@ -9576,7 +9747,7 @@
       <c r="X21" s="8" t="n">
         <v>66</v>
       </c>
-      <c r="Y21" s="10" t="n">
+      <c r="Y21" s="11" t="n">
         <v>23</v>
       </c>
       <c r="Z21" s="8" t="n">
@@ -9588,12 +9759,15 @@
       <c r="AB21" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="AC21" s="10" t="n">
+      <c r="AC21" s="11" t="n">
         <v>11</v>
       </c>
       <c r="AD21" s="8" t="n">
         <v>43</v>
       </c>
+      <c r="AE21" s="8" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -9620,31 +9794,31 @@
         <v>20</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>480</v>
+        <v>523</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>68%</t>
-        </is>
-      </c>
-      <c r="L22" s="10" t="n">
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="L22" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="M22" s="10" t="n">
+      <c r="M22" s="11" t="n">
         <v>11</v>
       </c>
       <c r="N22" s="7" t="n">
@@ -9653,7 +9827,7 @@
       <c r="O22" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P22" s="10" t="n">
+      <c r="P22" s="11" t="n">
         <v>11</v>
       </c>
       <c r="Q22" s="8" t="n">
@@ -9698,6 +9872,9 @@
       <c r="AD22" s="8" t="n">
         <v>32</v>
       </c>
+      <c r="AE22" s="8" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -9724,16 +9901,16 @@
         <v>20</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>558</v>
+        <v>581</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -9742,7 +9919,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="L23" s="8" t="n">
@@ -9769,10 +9946,10 @@
       <c r="S23" s="8" t="n">
         <v>78</v>
       </c>
-      <c r="T23" s="10" t="n">
+      <c r="T23" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="U23" s="10" t="n">
+      <c r="U23" s="11" t="n">
         <v>11</v>
       </c>
       <c r="V23" s="8" t="n">
@@ -9786,7 +9963,7 @@
           <t>19☂</t>
         </is>
       </c>
-      <c r="Y23" s="10" t="n">
+      <c r="Y23" s="11" t="n">
         <v>11</v>
       </c>
       <c r="Z23" s="8" t="n">
@@ -9804,6 +9981,9 @@
       <c r="AD23" s="8" t="n">
         <v>44</v>
       </c>
+      <c r="AE23" s="8" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -9830,16 +10010,16 @@
         <v>20</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>586</v>
+        <v>625</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -9848,22 +10028,22 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="L24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M24" s="10" t="n">
+      <c r="M24" s="11" t="n">
         <v>19</v>
       </c>
       <c r="N24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O24" s="10" t="n">
+      <c r="O24" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="P24" s="10" t="n">
+      <c r="P24" s="11" t="n">
         <v>11</v>
       </c>
       <c r="Q24" s="8" t="n">
@@ -9910,6 +10090,9 @@
       <c r="AD24" s="8" t="n">
         <v>21</v>
       </c>
+      <c r="AE24" s="8" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -9936,16 +10119,16 @@
         <v>20</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>638</v>
+        <v>693</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -9954,10 +10137,10 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>72%</t>
-        </is>
-      </c>
-      <c r="L25" s="10" t="n">
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="L25" s="11" t="n">
         <v>11</v>
       </c>
       <c r="M25" s="7" t="n">
@@ -9972,10 +10155,10 @@
       <c r="P25" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="Q25" s="10" t="n">
+      <c r="Q25" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="R25" s="10" t="n">
+      <c r="R25" s="11" t="n">
         <v>11</v>
       </c>
       <c r="S25" s="8" t="n">
@@ -10016,6 +10199,9 @@
       <c r="AD25" s="8" t="n">
         <v>44</v>
       </c>
+      <c r="AE25" s="8" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -10042,16 +10228,16 @@
         <v>50</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>1131</v>
+        <v>1219</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -10060,7 +10246,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="L26" s="7" t="n">
@@ -10081,7 +10267,7 @@
       <c r="Q26" s="8" t="n">
         <v>66</v>
       </c>
-      <c r="R26" s="10" t="n">
+      <c r="R26" s="11" t="n">
         <v>38</v>
       </c>
       <c r="S26" s="8" t="n">
@@ -10107,7 +10293,7 @@
       <c r="Y26" s="8" t="n">
         <v>53</v>
       </c>
-      <c r="Z26" s="10" t="n">
+      <c r="Z26" s="11" t="n">
         <v>48</v>
       </c>
       <c r="AA26" s="8" t="n">
@@ -10122,6 +10308,9 @@
       <c r="AD26" s="8" t="n">
         <v>64</v>
       </c>
+      <c r="AE26" s="8" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -10148,16 +10337,16 @@
         <v>20</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1185</v>
+        <v>1261</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -10166,7 +10355,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="L27" s="7" t="n">
@@ -10175,13 +10364,13 @@
       <c r="M27" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N27" s="10" t="n">
+      <c r="N27" s="11" t="n">
         <v>11</v>
       </c>
       <c r="O27" s="8" t="n">
         <v>49</v>
       </c>
-      <c r="P27" s="10" t="n">
+      <c r="P27" s="11" t="n">
         <v>11</v>
       </c>
       <c r="Q27" s="8" t="n">
@@ -10228,6 +10417,9 @@
       <c r="AD27" s="8" t="n">
         <v>99</v>
       </c>
+      <c r="AE27" s="8" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -10254,16 +10446,16 @@
         <v>10</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -10334,6 +10526,9 @@
       <c r="AD28" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="AE28" s="8" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -10360,16 +10555,16 @@
         <v>10</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -10440,6 +10635,9 @@
       <c r="AD29" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="AE29" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -10466,16 +10664,16 @@
         <v>10</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -10546,6 +10744,9 @@
       <c r="AD30" s="8" t="n">
         <v>20</v>
       </c>
+      <c r="AE30" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -10572,16 +10773,16 @@
         <v>10</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>535</v>
+        <v>545</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -10652,6 +10853,9 @@
       <c r="AD31" s="8" t="n">
         <v>20</v>
       </c>
+      <c r="AE31" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -10678,25 +10882,25 @@
         <v>10</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="L32" s="8" t="n">
@@ -10756,6 +10960,9 @@
       <c r="AD32" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="AE32" s="8" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -10782,25 +10989,25 @@
         <v>10</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="L33" s="7" t="n">
@@ -10860,6 +11067,9 @@
       <c r="AD33" s="8" t="n">
         <v>22</v>
       </c>
+      <c r="AE33" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -10886,20 +11096,20 @@
         <v>10</v>
       </c>
       <c r="F34" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G34" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="H34" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="H34" s="3" t="n">
-        <v>16</v>
-      </c>
       <c r="I34" s="3" t="n">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
@@ -10925,7 +11135,7 @@
       <c r="Q34" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="R34" s="10" t="n">
+      <c r="R34" s="11" t="n">
         <v>3</v>
       </c>
       <c r="S34" s="8" t="n">
@@ -10966,6 +11176,9 @@
       <c r="AD34" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="AE34" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -10992,25 +11205,25 @@
         <v>10</v>
       </c>
       <c r="F35" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G35" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="G35" s="3" t="n">
-        <v>17</v>
-      </c>
       <c r="H35" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="L35" s="8" t="n">
@@ -11072,6 +11285,9 @@
       <c r="AD35" s="8" t="n">
         <v>21</v>
       </c>
+      <c r="AE35" s="8" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -11098,16 +11314,16 @@
         <v>10</v>
       </c>
       <c r="F36" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G36" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G36" s="3" t="n">
-        <v>18</v>
-      </c>
       <c r="H36" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>728</v>
+        <v>777</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -11176,6 +11392,9 @@
       <c r="AD36" s="8" t="n">
         <v>37</v>
       </c>
+      <c r="AE36" s="8" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -11202,16 +11421,16 @@
         <v>10</v>
       </c>
       <c r="F37" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G37" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G37" s="3" t="n">
-        <v>18</v>
-      </c>
       <c r="H37" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>445</v>
+        <v>509</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -11280,6 +11499,9 @@
       <c r="AD37" s="8" t="n">
         <v>38</v>
       </c>
+      <c r="AE37" s="8" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -11306,16 +11528,16 @@
         <v>10</v>
       </c>
       <c r="F38" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G38" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G38" s="3" t="n">
-        <v>18</v>
-      </c>
       <c r="H38" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>258</v>
+        <v>283</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -11384,6 +11606,9 @@
       <c r="AD38" s="8" t="n">
         <v>22</v>
       </c>
+      <c r="AE38" s="8" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -11410,16 +11635,16 @@
         <v>50</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1721</v>
+        <v>1891</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -11428,31 +11653,31 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="L39" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="M39" s="10" t="n">
+      <c r="M39" s="11" t="n">
         <v>36</v>
       </c>
       <c r="N39" s="8" t="n">
         <v>53</v>
       </c>
-      <c r="O39" s="10" t="n">
+      <c r="O39" s="11" t="n">
         <v>42</v>
       </c>
       <c r="P39" s="8" t="n">
         <v>53</v>
       </c>
-      <c r="Q39" s="10" t="n">
+      <c r="Q39" s="11" t="n">
         <v>34</v>
       </c>
       <c r="R39" s="8" t="n">
         <v>73</v>
       </c>
-      <c r="S39" s="10" t="n">
+      <c r="S39" s="11" t="n">
         <v>42</v>
       </c>
       <c r="T39" s="8" t="n">
@@ -11472,7 +11697,7 @@
           <t>0☂</t>
         </is>
       </c>
-      <c r="Y39" s="10" t="n">
+      <c r="Y39" s="11" t="n">
         <v>37</v>
       </c>
       <c r="Z39" s="8" t="n">
@@ -11484,11 +11709,14 @@
       <c r="AB39" s="8" t="n">
         <v>266</v>
       </c>
-      <c r="AC39" s="10" t="n">
+      <c r="AC39" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="AD39" s="10" t="n">
+      <c r="AD39" s="11" t="n">
         <v>13</v>
+      </c>
+      <c r="AE39" s="8" t="n">
+        <v>170</v>
       </c>
     </row>
     <row r="40">
@@ -11516,16 +11744,16 @@
         <v>20</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>771</v>
+        <v>793</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -11534,7 +11762,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="L40" s="8" t="n">
@@ -11581,21 +11809,24 @@
       <c r="Y40" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="Z40" s="10" t="n">
+      <c r="Z40" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="AA40" s="10" t="n">
+      <c r="AA40" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="AB40" s="10" t="n">
+      <c r="AB40" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="AC40" s="10" t="n">
+      <c r="AC40" s="11" t="n">
         <v>11</v>
       </c>
       <c r="AD40" s="8" t="n">
         <v>33</v>
       </c>
+      <c r="AE40" s="8" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -11622,16 +11853,16 @@
         <v>30</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>1251</v>
+        <v>1374</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -11640,7 +11871,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="L41" s="8" t="n">
@@ -11655,16 +11886,16 @@
       <c r="O41" s="8" t="n">
         <v>78</v>
       </c>
-      <c r="P41" s="10" t="n">
+      <c r="P41" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="Q41" s="10" t="n">
+      <c r="Q41" s="11" t="n">
         <v>12</v>
       </c>
       <c r="R41" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="S41" s="10" t="n">
+      <c r="S41" s="11" t="n">
         <v>8</v>
       </c>
       <c r="T41" s="8" t="n">
@@ -11702,6 +11933,9 @@
       <c r="AD41" s="8" t="n">
         <v>60</v>
       </c>
+      <c r="AE41" s="8" t="n">
+        <v>123</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -11728,16 +11962,16 @@
         <v>10</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>751</v>
+        <v>786</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -11810,6 +12044,9 @@
       <c r="AD42" s="8" t="n">
         <v>58</v>
       </c>
+      <c r="AE42" s="8" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -11836,16 +12073,16 @@
         <v>11</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>470</v>
+        <v>492</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -11918,6 +12155,9 @@
       <c r="AD43" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="AE43" s="8" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -11944,16 +12184,16 @@
         <v>20</v>
       </c>
       <c r="F44" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="H44" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="G44" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>17</v>
-      </c>
       <c r="I44" s="3" t="n">
-        <v>2378</v>
+        <v>2438</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -11962,7 +12202,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="L44" s="8" t="n">
@@ -12006,7 +12246,7 @@
           <t>0☂</t>
         </is>
       </c>
-      <c r="Y44" s="10" t="n">
+      <c r="Y44" s="11" t="n">
         <v>10</v>
       </c>
       <c r="Z44" s="8" t="n">
@@ -12024,6 +12264,9 @@
       <c r="AD44" s="8" t="n">
         <v>31</v>
       </c>
+      <c r="AE44" s="8" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -12050,16 +12293,16 @@
         <v>30</v>
       </c>
       <c r="F45" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="H45" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="G45" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>17</v>
-      </c>
       <c r="I45" s="3" t="n">
-        <v>3614</v>
+        <v>3784</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -12068,7 +12311,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="L45" s="8" t="n">
@@ -12092,7 +12335,7 @@
       <c r="R45" s="8" t="n">
         <v>104</v>
       </c>
-      <c r="S45" s="10" t="n">
+      <c r="S45" s="11" t="n">
         <v>20</v>
       </c>
       <c r="T45" s="8" t="n">
@@ -12130,6 +12373,9 @@
       <c r="AD45" s="8" t="n">
         <v>100</v>
       </c>
+      <c r="AE45" s="8" t="n">
+        <v>170</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -12156,16 +12402,16 @@
         <v>20</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>945</v>
+        <v>1013</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -12236,6 +12482,9 @@
       <c r="AD46" s="8" t="n">
         <v>42</v>
       </c>
+      <c r="AE46" s="8" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -12262,16 +12511,16 @@
         <v>10</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>397</v>
+        <v>420</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -12342,6 +12591,9 @@
       <c r="AD47" s="8" t="n">
         <v>27</v>
       </c>
+      <c r="AE47" s="8" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -12368,16 +12620,16 @@
         <v>40</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2158</v>
+        <v>2271</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -12448,6 +12700,9 @@
       <c r="AD48" s="8" t="n">
         <v>141</v>
       </c>
+      <c r="AE48" s="8" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -12474,16 +12729,16 @@
         <v>10</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>334</v>
+        <v>370</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -12554,6 +12809,9 @@
       <c r="AD49" s="8" t="n">
         <v>13</v>
       </c>
+      <c r="AE49" s="8" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -12580,16 +12838,16 @@
         <v>10</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>1044</v>
+        <v>1084</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -12660,6 +12918,9 @@
       <c r="AD50" s="8" t="n">
         <v>73</v>
       </c>
+      <c r="AE50" s="8" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -12686,16 +12947,16 @@
         <v>60</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>5971</v>
+        <v>6211</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -12766,6 +13027,9 @@
       <c r="AD51" s="8" t="n">
         <v>300</v>
       </c>
+      <c r="AE51" s="8" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -12792,16 +13056,16 @@
         <v>10</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>1113</v>
+        <v>1164</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -12872,6 +13136,9 @@
       <c r="AD52" s="8" t="n">
         <v>70</v>
       </c>
+      <c r="AE52" s="8" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -12898,16 +13165,16 @@
         <v>10</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>2794</v>
+        <v>2844</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -12978,6 +13245,9 @@
       <c r="AD53" s="8" t="n">
         <v>40</v>
       </c>
+      <c r="AE53" s="8" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -13004,16 +13274,16 @@
         <v>10</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>532</v>
+        <v>582</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -13083,6 +13353,9 @@
       </c>
       <c r="AD54" s="8" t="n">
         <v>44</v>
+      </c>
+      <c r="AE54" s="8" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -13284,7 +13557,7 @@
       <c r="O3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P3" s="10" t="n">
+      <c r="P3" s="11" t="n">
         <v>4</v>
       </c>
       <c r="Q3" s="7" t="n">
@@ -13437,7 +13710,7 @@
       <c r="P5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" s="10" t="n">
+      <c r="Q5" s="11" t="n">
         <v>11</v>
       </c>
       <c r="R5" s="7" t="n">
@@ -13584,10 +13857,10 @@
       <c r="O7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P7" s="10" t="n">
+      <c r="P7" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="Q7" s="10" t="n">
+      <c r="Q7" s="11" t="n">
         <v>12</v>
       </c>
       <c r="R7" s="7" t="n">
@@ -13665,7 +13938,7 @@
       <c r="Q8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="R8" s="10" t="n">
+      <c r="R8" s="11" t="n">
         <v>11</v>
       </c>
       <c r="S8" s="9" t="inlineStr">
@@ -13725,7 +13998,7 @@
           <t>11☂</t>
         </is>
       </c>
-      <c r="M9" s="10" t="n">
+      <c r="M9" s="11" t="n">
         <v>8</v>
       </c>
       <c r="N9" s="7" t="n">
@@ -13885,10 +14158,10 @@
       <c r="P11" s="8" t="n">
         <v>77</v>
       </c>
-      <c r="Q11" s="10" t="n">
+      <c r="Q11" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="R11" s="10" t="n">
+      <c r="R11" s="11" t="n">
         <v>11</v>
       </c>
       <c r="S11" s="7" t="n">
@@ -13949,10 +14222,10 @@
       <c r="M12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N12" s="10" t="n">
+      <c r="N12" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="O12" s="10" t="n">
+      <c r="O12" s="11" t="n">
         <v>4</v>
       </c>
       <c r="P12" s="8" t="n">
@@ -14027,7 +14300,7 @@
       <c r="N13" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="O13" s="10" t="n">
+      <c r="O13" s="11" t="n">
         <v>11</v>
       </c>
       <c r="P13" s="8" t="n">
@@ -14096,7 +14369,7 @@
           <t>10☂</t>
         </is>
       </c>
-      <c r="M14" s="10" t="n">
+      <c r="M14" s="11" t="n">
         <v>11</v>
       </c>
       <c r="N14" s="8" t="n">
@@ -14771,7 +15044,7 @@
       <c r="P23" s="8" t="n">
         <v>217</v>
       </c>
-      <c r="Q23" s="10" t="n">
+      <c r="Q23" s="11" t="n">
         <v>49</v>
       </c>
       <c r="R23" s="8" t="n">
@@ -14846,7 +15119,7 @@
       <c r="P24" s="8" t="n">
         <v>61</v>
       </c>
-      <c r="Q24" s="10" t="n">
+      <c r="Q24" s="11" t="n">
         <v>13</v>
       </c>
       <c r="R24" s="8" t="n">
@@ -15129,7 +15402,7 @@
           <t>62%</t>
         </is>
       </c>
-      <c r="L28" s="10" t="n">
+      <c r="L28" s="11" t="n">
         <v>11</v>
       </c>
       <c r="M28" s="7" t="n">
@@ -15144,7 +15417,7 @@
       <c r="P28" s="8" t="n">
         <v>86</v>
       </c>
-      <c r="Q28" s="10" t="n">
+      <c r="Q28" s="11" t="n">
         <v>10</v>
       </c>
       <c r="R28" s="8" t="n">
@@ -15200,7 +15473,7 @@
           <t>62%</t>
         </is>
       </c>
-      <c r="L29" s="10" t="n">
+      <c r="L29" s="11" t="n">
         <v>11</v>
       </c>
       <c r="M29" s="7" t="n">
@@ -15209,7 +15482,7 @@
       <c r="N29" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="O29" s="10" t="n">
+      <c r="O29" s="11" t="n">
         <v>17</v>
       </c>
       <c r="P29" s="8" t="n">
@@ -15276,7 +15549,7 @@
           <t>51☂</t>
         </is>
       </c>
-      <c r="M30" s="10" t="n">
+      <c r="M30" s="11" t="n">
         <v>33</v>
       </c>
       <c r="N30" s="8" t="n">
@@ -15291,7 +15564,7 @@
       <c r="Q30" s="8" t="n">
         <v>66</v>
       </c>
-      <c r="R30" s="10" t="n">
+      <c r="R30" s="11" t="n">
         <v>44</v>
       </c>
       <c r="S30" s="9" t="inlineStr">
@@ -15357,7 +15630,7 @@
       <c r="N31" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="O31" s="10" t="n">
+      <c r="O31" s="11" t="n">
         <v>11</v>
       </c>
       <c r="P31" s="8" t="n">
@@ -15438,7 +15711,7 @@
       <c r="P32" s="8" t="n">
         <v>43</v>
       </c>
-      <c r="Q32" s="10" t="n">
+      <c r="Q32" s="11" t="n">
         <v>9</v>
       </c>
       <c r="R32" s="8" t="n">
@@ -16809,25 +17082,25 @@
         <v>4</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>88.4%</t>
+          <t>89.0%</t>
         </is>
       </c>
     </row>
@@ -16844,25 +17117,25 @@
         <v>5</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>86.5%</t>
         </is>
       </c>
     </row>
@@ -16879,25 +17152,25 @@
         <v>11</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>89.6%</t>
         </is>
       </c>
     </row>
@@ -16914,25 +17187,25 @@
         <v>2</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>81.6%</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>81.6%</t>
         </is>
       </c>
     </row>
@@ -16949,25 +17222,25 @@
         <v>1</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>47.4%</t>
         </is>
       </c>
     </row>
@@ -16984,25 +17257,25 @@
         <v>2</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F8" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="G8" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="G8" s="3" t="n">
-        <v>29</v>
-      </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>82.9%</t>
+          <t>83.8%</t>
         </is>
       </c>
     </row>
@@ -17019,25 +17292,25 @@
         <v>6</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>88.3%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>83.5%</t>
         </is>
       </c>
     </row>
@@ -17457,25 +17730,25 @@
         <v>10</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>96.3%</t>
         </is>
       </c>
     </row>
@@ -17492,25 +17765,25 @@
         <v>12</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>80.1%</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>64.5%</t>
         </is>
       </c>
     </row>
@@ -17527,25 +17800,25 @@
         <v>10</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>76.6%</t>
         </is>
       </c>
     </row>
@@ -17562,25 +17835,25 @@
         <v>11</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.9%</t>
         </is>
       </c>
     </row>
@@ -17597,25 +17870,25 @@
         <v>9</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>82.7%</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>71.7%</t>
         </is>
       </c>
     </row>

--- a/coverage.xlsx
+++ b/coverage.xlsx
@@ -583,12 +583,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>88.7%</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>85.6%</t>
+          <t>85.5%</t>
         </is>
       </c>
     </row>
@@ -639,12 +639,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>86.5%</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>80.4%</t>
         </is>
       </c>
     </row>
@@ -680,14 +680,14 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>数据范围: 20261001 ~ 20261028</t>
+          <t>数据范围: 20261001 ~ 20261029</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>工作日: 20天, 周末: 8天</t>
+          <t>工作日: 21天, 周末: 8天</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE37"/>
+  <dimension ref="A1:AF37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -764,6 +764,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="11" customWidth="1" min="30" max="30"/>
     <col width="11" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -929,6 +930,11 @@
           <t>10-28(三)</t>
         </is>
       </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>10-29(四)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -955,7 +961,7 @@
         <v>10</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>9</v>
@@ -968,12 +974,12 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="L3" s="7" t="n">
@@ -1038,30 +1044,33 @@
       <c r="AE3" s="8" t="n">
         <v>42</v>
       </c>
+      <c r="AF3" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>0a8331d4l1lrsht99jr5si9gwy5xrc6x</t>
+          <t>684038567596433408</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>钟灵街2A</t>
+          <t>25-晚峰-地铁站-柳州东路公交站台</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>耿明</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+晚峰</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>19</v>
@@ -1070,10 +1079,10 @@
         <v>13</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>408</v>
+        <v>1799</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -1082,197 +1091,203 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>68%</t>
-        </is>
-      </c>
-      <c r="L4" s="8" t="n">
+          <t>未配置</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="n">
+        <v>139</v>
+      </c>
+      <c r="M4" s="10" t="n">
+        <v>161</v>
+      </c>
+      <c r="N4" s="10" t="n">
+        <v>106</v>
+      </c>
+      <c r="O4" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="P4" s="10" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="10" t="n">
+        <v>241</v>
+      </c>
+      <c r="S4" s="10" t="n">
+        <v>233</v>
+      </c>
+      <c r="T4" s="10" t="n">
+        <v>253</v>
+      </c>
+      <c r="U4" s="10" t="n">
+        <v>167</v>
+      </c>
+      <c r="V4" s="10" t="n">
+        <v>141</v>
+      </c>
+      <c r="W4" s="10" t="n">
+        <v>165</v>
+      </c>
+      <c r="X4" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y4" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Z4" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="M4" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="N4" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="O4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v>43</v>
-      </c>
-      <c r="W4" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="X4" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Y4" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z4" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="AA4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AB4" s="8" t="n">
+      <c r="AB4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="AC4" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="AD4" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE4" s="8" t="n">
-        <v>23</v>
+      <c r="AD4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>684038567596433408</t>
+          <t>778851422965239808</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路公交站台</t>
+          <t>25-早峰-居民区-仙林新村</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>早峰+晚峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1799</v>
+        <v>286</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>未配置</t>
-        </is>
-      </c>
-      <c r="L5" s="10" t="n">
-        <v>139</v>
-      </c>
-      <c r="M5" s="10" t="n">
-        <v>161</v>
-      </c>
-      <c r="N5" s="10" t="n">
-        <v>106</v>
-      </c>
-      <c r="O5" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="P5" s="10" t="n">
-        <v>111</v>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="O5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="Q5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="R5" s="10" t="n">
-        <v>241</v>
-      </c>
-      <c r="S5" s="10" t="n">
-        <v>233</v>
-      </c>
-      <c r="T5" s="10" t="n">
-        <v>253</v>
-      </c>
-      <c r="U5" s="10" t="n">
-        <v>167</v>
-      </c>
-      <c r="V5" s="10" t="n">
-        <v>141</v>
-      </c>
-      <c r="W5" s="10" t="n">
-        <v>165</v>
+      <c r="R5" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="S5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="V5" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="W5" s="8" t="n">
+        <v>25</v>
       </c>
       <c r="X5" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
       </c>
-      <c r="Y5" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Z5" s="10" t="n">
+      <c r="Y5" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z5" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="AA5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="10" t="n">
+      <c r="AA5" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="AD5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="7" t="n">
+      <c r="AB5" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC5" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD5" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE5" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF5" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>778851422965239808</t>
+          <t>0a8331d4l1lrsht99jr5si9gwy5xrc6x</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>25-早峰-居民区-仙林新村</t>
+          <t>钟灵街2A</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>耿明</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1281,91 +1296,94 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>14</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>286</v>
+        <v>428</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="L6" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="M6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="11" t="n">
-        <v>5</v>
+        <v>25</v>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="N6" s="8" t="n">
+        <v>65</v>
       </c>
       <c r="O6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="7" t="n">
-        <v>0</v>
+      <c r="P6" s="8" t="n">
+        <v>44</v>
       </c>
       <c r="Q6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="R6" s="8" t="n">
+      <c r="R6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="W6" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="X6" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y6" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="S6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="V6" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="W6" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="X6" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Y6" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z6" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA6" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB6" s="8" t="n">
-        <v>26</v>
-      </c>
       <c r="AC6" s="8" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AD6" s="8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AE6" s="8" t="n">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="AF6" s="8" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -1393,25 +1411,25 @@
         <v>19</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G7" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H7" s="3" t="n">
-        <v>14</v>
-      </c>
       <c r="I7" s="3" t="n">
-        <v>320</v>
+        <v>349</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="L7" s="8" t="n">
@@ -1474,139 +1492,145 @@
       <c r="AE7" s="8" t="n">
         <v>20</v>
       </c>
+      <c r="AF7" s="8" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>1130000746265899008</t>
+          <t>0a836a6al1l268p7ak2p5yn7sfzs2tsg</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>城北万象汇</t>
+          <t>中山东路228号新世纪广场A幢投放点</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>郭富荣</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>午峰+晚峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>884</v>
+        <v>1140</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>0</v>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>40</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="O8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="8" t="n">
-        <v>25</v>
+        <v>107</v>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="P8" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="R8" s="8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="T8" s="8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="U8" s="8" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="V8" s="8" t="n">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="W8" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="X8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="9" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="X8" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
       </c>
-      <c r="Z8" s="8" t="n">
-        <v>100</v>
+      <c r="Y8" s="8" t="n">
+        <v>79</v>
+      </c>
+      <c r="Z8" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="AA8" s="8" t="n">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="AB8" s="8" t="n">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="AC8" s="8" t="n">
-        <v>77</v>
-      </c>
-      <c r="AD8" s="8" t="n">
-        <v>75</v>
+        <v>136</v>
+      </c>
+      <c r="AD8" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="AE8" s="8" t="n">
-        <v>75</v>
+        <v>39</v>
+      </c>
+      <c r="AF8" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>973769778869174272</t>
+          <t>1130000746265899008</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>长江后街小区渗透</t>
+          <t>城北万象汇</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>郭富荣</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>午峰</t>
+          <t>午峰+晚峰</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>20</v>
@@ -1615,10 +1639,10 @@
         <v>16</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1749</v>
+        <v>984</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1627,79 +1651,84 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>未配置</t>
-        </is>
-      </c>
-      <c r="L9" s="10" t="n">
-        <v>265</v>
-      </c>
-      <c r="M9" s="10" t="n">
-        <v>264</v>
-      </c>
-      <c r="N9" s="10" t="n">
-        <v>298</v>
-      </c>
-      <c r="O9" s="10" t="n">
-        <v>278</v>
-      </c>
-      <c r="P9" s="10" t="n">
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="O9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q9" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="R9" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="S9" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="W9" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="X9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Z9" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="Q9" s="10" t="n">
-        <v>26</v>
-      </c>
-      <c r="R9" s="10" t="n">
-        <v>39</v>
-      </c>
-      <c r="S9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="U9" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="V9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" s="10" t="n">
-        <v>150</v>
-      </c>
-      <c r="X9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z9" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA9" s="10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB9" s="10" t="n">
-        <v>74</v>
-      </c>
-      <c r="AC9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AE9" s="10" t="n">
-        <v>71</v>
+      <c r="AA9" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB9" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC9" s="8" t="n">
+        <v>77</v>
+      </c>
+      <c r="AD9" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AE9" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF9" s="8" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>1176722757207629824</t>
+          <t>973769778869174272</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>规划建设展览馆渗透</t>
+          <t>长江后街小区渗透</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1713,316 +1742,323 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1988</v>
+        <v>1770</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="L10" s="8" t="n">
-        <v>174</v>
-      </c>
-      <c r="M10" s="8" t="n">
-        <v>292</v>
-      </c>
-      <c r="N10" s="8" t="n">
-        <v>241</v>
-      </c>
-      <c r="O10" s="8" t="n">
+          <t>未配置</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>265</v>
+      </c>
+      <c r="M10" s="10" t="n">
+        <v>264</v>
+      </c>
+      <c r="N10" s="10" t="n">
+        <v>298</v>
+      </c>
+      <c r="O10" s="10" t="n">
+        <v>278</v>
+      </c>
+      <c r="P10" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="P10" s="8" t="n">
-        <v>197</v>
-      </c>
-      <c r="Q10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="S10" s="8" t="n">
+      <c r="Q10" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="R10" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="T10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="W10" s="8" t="n">
-        <v>54</v>
+      <c r="S10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="U10" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="V10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="10" t="n">
+        <v>150</v>
       </c>
       <c r="X10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="Y10" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="Z10" s="8" t="n">
-        <v>96</v>
-      </c>
-      <c r="AA10" s="8" t="n">
-        <v>89</v>
-      </c>
-      <c r="AB10" s="8" t="n">
-        <v>51</v>
-      </c>
-      <c r="AC10" s="8" t="n">
-        <v>135</v>
-      </c>
-      <c r="AD10" s="8" t="n">
-        <v>181</v>
-      </c>
-      <c r="AE10" s="8" t="n">
-        <v>179</v>
+      <c r="Y10" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z10" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA10" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB10" s="10" t="n">
+        <v>74</v>
+      </c>
+      <c r="AC10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE10" s="10" t="n">
+        <v>71</v>
+      </c>
+      <c r="AF10" s="10" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>0a832068l1lrine348sx5fpj3daxcqc9</t>
+          <t>1176722757207629824</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>剪子巷51号华静家园西区投放点</t>
+          <t>规划建设展览馆渗透</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>午峰+夜间</t>
+          <t>午峰</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v>15</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1548</v>
+        <v>2123</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="L11" s="8" t="n">
-        <v>155</v>
-      </c>
-      <c r="M11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="7" t="n">
-        <v>0</v>
+        <v>174</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>292</v>
+      </c>
+      <c r="N11" s="8" t="n">
+        <v>241</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="P11" s="8" t="n">
-        <v>104</v>
-      </c>
-      <c r="Q11" s="8" t="n">
-        <v>80</v>
+        <v>197</v>
+      </c>
+      <c r="Q11" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="S11" s="8" t="n">
-        <v>157</v>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v>138</v>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v>115</v>
+        <v>39</v>
+      </c>
+      <c r="T11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="W11" s="8" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="X11" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="Y11" s="7" t="n">
-        <v>0</v>
+      <c r="Y11" s="8" t="n">
+        <v>75</v>
       </c>
       <c r="Z11" s="8" t="n">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="AA11" s="8" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AB11" s="8" t="n">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="AC11" s="8" t="n">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="AD11" s="8" t="n">
-        <v>80</v>
+        <v>181</v>
       </c>
       <c r="AE11" s="8" t="n">
-        <v>103</v>
+        <v>179</v>
+      </c>
+      <c r="AF11" s="8" t="n">
+        <v>135</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>948393128847777792</t>
+          <t>0a832068l1lrine348sx5fpj3daxcqc9</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>30-工作日-全天-地铁-明故宫2渗透</t>
+          <t>剪子巷51号华静家园西区投放点</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>顾星宇</t>
+          <t>林杜鹏</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>午峰+夜间</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>726</v>
+        <v>1659</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="L12" s="8" t="n">
+        <v>155</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>83</v>
+      </c>
+      <c r="P12" s="8" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q12" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="R12" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="S12" s="8" t="n">
+        <v>157</v>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v>138</v>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v>115</v>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v>77</v>
+      </c>
+      <c r="W12" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="X12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA12" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="M12" s="8" t="n">
-        <v>68</v>
-      </c>
-      <c r="N12" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="O12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="8" t="n">
-        <v>31</v>
-      </c>
-      <c r="R12" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="S12" s="8" t="n">
-        <v>91</v>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="V12" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="W12" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="X12" s="9" t="inlineStr">
-        <is>
-          <t>20☂</t>
-        </is>
-      </c>
-      <c r="Y12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA12" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB12" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC12" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD12" s="11" t="n">
-        <v>13</v>
+      <c r="AB12" s="8" t="n">
+        <v>105</v>
+      </c>
+      <c r="AC12" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AD12" s="8" t="n">
+        <v>80</v>
       </c>
       <c r="AE12" s="8" t="n">
-        <v>55</v>
+        <v>103</v>
+      </c>
+      <c r="AF12" s="8" t="n">
+        <v>111</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>1090491857237020672</t>
+          <t>948393128847777792</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>太平北路华海大厦(太平北路)投放点A</t>
+          <t>30-工作日-全天-地铁-明故宫2渗透</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -2032,229 +2068,235 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G13" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>736</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="M13" s="8" t="n">
+        <v>68</v>
+      </c>
+      <c r="N13" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="O13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="R13" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="S13" s="8" t="n">
+        <v>91</v>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="V13" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="W13" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="X13" s="9" t="inlineStr">
+        <is>
+          <t>20☂</t>
+        </is>
+      </c>
+      <c r="Y13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA13" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="AB13" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC13" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="I13" s="3" t="n">
-        <v>1358</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>84%</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>84%</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="O13" s="8" t="n">
-        <v>90</v>
-      </c>
-      <c r="P13" s="8" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q13" s="8" t="n">
-        <v>66</v>
-      </c>
-      <c r="R13" s="8" t="n">
-        <v>87</v>
-      </c>
-      <c r="S13" s="8" t="n">
-        <v>139</v>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v>87</v>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v>110</v>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v>87</v>
-      </c>
-      <c r="W13" s="8" t="n">
-        <v>130</v>
-      </c>
-      <c r="X13" s="9" t="inlineStr">
-        <is>
-          <t>56☂</t>
-        </is>
-      </c>
-      <c r="Y13" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="Z13" s="8" t="n">
-        <v>158</v>
-      </c>
-      <c r="AA13" s="8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB13" s="8" t="n">
-        <v>66</v>
-      </c>
-      <c r="AC13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="8" t="n">
-        <v>112</v>
+      <c r="AD13" s="11" t="n">
+        <v>13</v>
       </c>
       <c r="AE13" s="8" t="n">
-        <v>22</v>
+        <v>55</v>
+      </c>
+      <c r="AF13" s="11" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>0a836a6al1l268p7ak2p5yn7sfzs2tsg</t>
+          <t>843996095354019840</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>中山东路228号新世纪广场A幢投放点</t>
+          <t>25-晚峰-地铁站-柳州东路2号口</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>林杜鹏</t>
+          <t>张书军</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>午峰+晚峰</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>16</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1140</v>
+        <v>2330</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>84%</t>
-        </is>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="M14" s="8" t="n">
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="N14" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="N14" s="8" t="n">
-        <v>107</v>
-      </c>
       <c r="O14" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="P14" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="P14" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>72</v>
+        <v>185</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>40</v>
+        <v>142</v>
       </c>
       <c r="S14" s="8" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="T14" s="8" t="n">
-        <v>40</v>
+        <v>219</v>
       </c>
       <c r="U14" s="8" t="n">
-        <v>76</v>
+        <v>195</v>
       </c>
       <c r="V14" s="8" t="n">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="W14" s="8" t="n">
-        <v>77</v>
-      </c>
-      <c r="X14" s="9" t="inlineStr">
+        <v>128</v>
+      </c>
+      <c r="X14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="9" t="inlineStr">
         <is>
           <t>0☂</t>
         </is>
       </c>
-      <c r="Y14" s="8" t="n">
-        <v>79</v>
-      </c>
-      <c r="Z14" s="7" t="n">
-        <v>0</v>
+      <c r="Z14" s="8" t="n">
+        <v>175</v>
       </c>
       <c r="AA14" s="8" t="n">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="AB14" s="8" t="n">
-        <v>41</v>
+        <v>144</v>
       </c>
       <c r="AC14" s="8" t="n">
-        <v>136</v>
-      </c>
-      <c r="AD14" s="7" t="n">
-        <v>0</v>
+        <v>271</v>
+      </c>
+      <c r="AD14" s="8" t="n">
+        <v>275</v>
       </c>
       <c r="AE14" s="8" t="n">
-        <v>39</v>
+        <v>175</v>
+      </c>
+      <c r="AF14" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>8d319562e65849c3a6e08eb73472a032</t>
+          <t>1090491857237020672</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>25-全天-居民区-鸡公煲门口</t>
+          <t>太平北路华海大厦(太平北路)投放点A</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>杨志伟</t>
+          <t>顾星宇</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>20</v>
@@ -2263,10 +2305,10 @@
         <v>17</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>452</v>
+        <v>1402</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -2275,190 +2317,194 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="M15" s="8" t="n">
-        <v>50</v>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N15" s="8" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="O15" s="8" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="P15" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q15" s="7" t="n">
-        <v>0</v>
+        <v>39</v>
+      </c>
+      <c r="Q15" s="8" t="n">
+        <v>66</v>
       </c>
       <c r="R15" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="S15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="11" t="n">
-        <v>1</v>
+        <v>87</v>
+      </c>
+      <c r="S15" s="8" t="n">
+        <v>139</v>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v>87</v>
       </c>
       <c r="U15" s="8" t="n">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="V15" s="8" t="n">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="W15" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="X15" s="7" t="n">
-        <v>0</v>
+        <v>130</v>
+      </c>
+      <c r="X15" s="9" t="inlineStr">
+        <is>
+          <t>56☂</t>
+        </is>
       </c>
       <c r="Y15" s="8" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="Z15" s="8" t="n">
-        <v>25</v>
+        <v>158</v>
       </c>
       <c r="AA15" s="8" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="AB15" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC15" s="8" t="n">
-        <v>25</v>
+        <v>66</v>
+      </c>
+      <c r="AC15" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="AD15" s="8" t="n">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="AE15" s="8" t="n">
-        <v>25</v>
+        <v>22</v>
+      </c>
+      <c r="AF15" s="8" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>732955980949151744</t>
+          <t>8d319562e65849c3a6e08eb73472a032</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-天润城地铁站1号口</t>
+          <t>25-全天-居民区-鸡公煲门口</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>张书军</t>
+          <t>杨志伟</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>早峰+晚峰+夜间</t>
+          <t>午峰</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F16" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="G16" s="3" t="n">
-        <v>16</v>
-      </c>
       <c r="H16" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>975</v>
+        <v>477</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="7" t="n">
-        <v>0</v>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="M16" s="8" t="n">
+        <v>50</v>
       </c>
       <c r="N16" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="O16" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="P16" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="O16" s="8" t="n">
+      <c r="Q16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="P16" s="8" t="n">
-        <v>59</v>
-      </c>
-      <c r="Q16" s="8" t="n">
-        <v>120</v>
-      </c>
-      <c r="R16" s="8" t="n">
-        <v>53</v>
-      </c>
-      <c r="S16" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v>110</v>
+      <c r="S16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="U16" s="8" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="V16" s="8" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="X16" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Y16" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="X16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="8" t="n">
+        <v>25</v>
       </c>
       <c r="Z16" s="8" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AA16" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="AB16" s="11" t="n">
-        <v>16</v>
+        <v>25</v>
+      </c>
+      <c r="AB16" s="8" t="n">
+        <v>25</v>
       </c>
       <c r="AC16" s="8" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="AD16" s="8" t="n">
-        <v>130</v>
+        <v>25</v>
       </c>
       <c r="AE16" s="8" t="n">
-        <v>104</v>
+        <v>25</v>
+      </c>
+      <c r="AF16" s="8" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>843996095354019840</t>
+          <t>732955980949151744</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>25-晚峰-地铁站-柳州东路2号口</t>
+          <t>25-晚峰-地铁站-天润城地铁站1号口</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -2468,7 +2514,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>午峰+晚峰</t>
+          <t>早峰+晚峰+夜间</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
@@ -2484,7 +2530,7 @@
         <v>16</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>2330</v>
+        <v>1076</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -2499,41 +2545,43 @@
       <c r="L17" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M17" s="11" t="n">
-        <v>7</v>
+      <c r="M17" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="N17" s="8" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="O17" s="8" t="n">
         <v>25</v>
       </c>
       <c r="P17" s="8" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q17" s="8" t="n">
-        <v>185</v>
+        <v>120</v>
       </c>
       <c r="R17" s="8" t="n">
-        <v>142</v>
+        <v>53</v>
       </c>
       <c r="S17" s="8" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="T17" s="8" t="n">
-        <v>219</v>
+        <v>110</v>
       </c>
       <c r="U17" s="8" t="n">
-        <v>195</v>
+        <v>39</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="W17" s="8" t="n">
-        <v>128</v>
-      </c>
-      <c r="X17" s="7" t="n">
-        <v>0</v>
+        <v>42</v>
+      </c>
+      <c r="X17" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
       </c>
       <c r="Y17" s="9" t="inlineStr">
         <is>
@@ -2541,22 +2589,25 @@
         </is>
       </c>
       <c r="Z17" s="8" t="n">
-        <v>175</v>
+        <v>42</v>
       </c>
       <c r="AA17" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB17" s="8" t="n">
-        <v>144</v>
+        <v>52</v>
+      </c>
+      <c r="AB17" s="11" t="n">
+        <v>16</v>
       </c>
       <c r="AC17" s="8" t="n">
-        <v>271</v>
+        <v>53</v>
       </c>
       <c r="AD17" s="8" t="n">
-        <v>275</v>
+        <v>130</v>
       </c>
       <c r="AE17" s="8" t="n">
-        <v>175</v>
+        <v>104</v>
+      </c>
+      <c r="AF17" s="8" t="n">
+        <v>101</v>
       </c>
     </row>
     <row r="18">
@@ -2584,25 +2635,25 @@
         <v>19</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>904</v>
+        <v>946</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="L18" s="8" t="n">
@@ -2667,6 +2718,9 @@
       <c r="AE18" s="8" t="n">
         <v>80</v>
       </c>
+      <c r="AF18" s="8" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -2693,25 +2747,25 @@
         <v>19</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1338</v>
+        <v>1420</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="L19" s="8" t="n">
@@ -2776,6 +2830,9 @@
       <c r="AE19" s="8" t="n">
         <v>83</v>
       </c>
+      <c r="AF19" s="8" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -2802,25 +2859,25 @@
         <v>20</v>
       </c>
       <c r="F20" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G20" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="G20" s="3" t="n">
-        <v>17</v>
-      </c>
       <c r="H20" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1392</v>
+        <v>1509</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="L20" s="8" t="n">
@@ -2887,6 +2944,9 @@
       <c r="AE20" s="8" t="n">
         <v>64</v>
       </c>
+      <c r="AF20" s="8" t="n">
+        <v>117</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -2913,25 +2973,25 @@
         <v>20</v>
       </c>
       <c r="F21" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G21" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="G21" s="3" t="n">
-        <v>17</v>
-      </c>
       <c r="H21" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>2036</v>
+        <v>2186</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="L21" s="8" t="n">
@@ -2998,6 +3058,9 @@
       <c r="AE21" s="8" t="n">
         <v>148</v>
       </c>
+      <c r="AF21" s="8" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -3024,16 +3087,16 @@
         <v>19</v>
       </c>
       <c r="F22" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G22" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>18</v>
-      </c>
       <c r="H22" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>1257</v>
+        <v>1284</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -3042,7 +3105,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="L22" s="8" t="n">
@@ -3107,6 +3170,9 @@
       <c r="AE22" s="8" t="n">
         <v>62</v>
       </c>
+      <c r="AF22" s="8" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -3133,16 +3199,16 @@
         <v>15</v>
       </c>
       <c r="F23" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G23" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G23" s="3" t="n">
+      <c r="H23" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H23" s="3" t="n">
-        <v>17</v>
-      </c>
       <c r="I23" s="3" t="n">
-        <v>2071</v>
+        <v>2174</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -3151,7 +3217,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="L23" s="8" t="n">
@@ -3216,6 +3282,9 @@
       <c r="AE23" s="8" t="n">
         <v>136</v>
       </c>
+      <c r="AF23" s="8" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -3242,16 +3311,16 @@
         <v>19</v>
       </c>
       <c r="F24" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G24" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G24" s="3" t="n">
+      <c r="H24" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H24" s="3" t="n">
-        <v>17</v>
-      </c>
       <c r="I24" s="3" t="n">
-        <v>483</v>
+        <v>503</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -3260,7 +3329,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="L24" s="8" t="n">
@@ -3325,6 +3394,9 @@
       <c r="AE24" s="8" t="n">
         <v>20</v>
       </c>
+      <c r="AF24" s="8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -3351,16 +3423,16 @@
         <v>15</v>
       </c>
       <c r="F25" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G25" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G25" s="3" t="n">
-        <v>18</v>
-      </c>
       <c r="H25" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1926</v>
+        <v>2020</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -3434,6 +3506,9 @@
       <c r="AE25" s="8" t="n">
         <v>95</v>
       </c>
+      <c r="AF25" s="8" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -3460,16 +3535,16 @@
         <v>0</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>1031</v>
+        <v>1056</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -3541,6 +3616,9 @@
       <c r="AE26" s="10" t="n">
         <v>25</v>
       </c>
+      <c r="AF26" s="10" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -3567,16 +3645,16 @@
         <v>0</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>2931</v>
+        <v>3149</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -3652,6 +3730,9 @@
       <c r="AE27" s="10" t="n">
         <v>328</v>
       </c>
+      <c r="AF27" s="10" t="n">
+        <v>218</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -3678,16 +3759,16 @@
         <v>15</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2995</v>
+        <v>3214</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -3763,6 +3844,9 @@
       <c r="AE28" s="8" t="n">
         <v>237</v>
       </c>
+      <c r="AF28" s="8" t="n">
+        <v>219</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -3789,16 +3873,16 @@
         <v>20</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2183</v>
+        <v>2318</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -3872,6 +3956,9 @@
       <c r="AE29" s="8" t="n">
         <v>117</v>
       </c>
+      <c r="AF29" s="8" t="n">
+        <v>135</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -3898,16 +3985,16 @@
         <v>15</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>1130</v>
+        <v>1197</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -3981,6 +4068,9 @@
       <c r="AE30" s="8" t="n">
         <v>21</v>
       </c>
+      <c r="AF30" s="8" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -4007,16 +4097,16 @@
         <v>20</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>3479</v>
+        <v>3709</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -4090,6 +4180,9 @@
       <c r="AE31" s="8" t="n">
         <v>207</v>
       </c>
+      <c r="AF31" s="8" t="n">
+        <v>230</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -4116,16 +4209,16 @@
         <v>19</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1549</v>
+        <v>1662</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -4199,6 +4292,9 @@
       <c r="AE32" s="8" t="n">
         <v>99</v>
       </c>
+      <c r="AF32" s="8" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -4225,16 +4321,16 @@
         <v>19</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>2153</v>
+        <v>2329</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -4308,6 +4404,9 @@
       <c r="AE33" s="8" t="n">
         <v>119</v>
       </c>
+      <c r="AF33" s="8" t="n">
+        <v>176</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -4334,16 +4433,16 @@
         <v>19</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>1598</v>
+        <v>1668</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -4417,6 +4516,9 @@
       <c r="AE34" s="8" t="n">
         <v>128</v>
       </c>
+      <c r="AF34" s="8" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -4443,16 +4545,16 @@
         <v>19</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>2146</v>
+        <v>2228</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -4526,6 +4628,9 @@
       <c r="AE35" s="8" t="n">
         <v>183</v>
       </c>
+      <c r="AF35" s="8" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -4552,16 +4657,16 @@
         <v>20</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>4773</v>
+        <v>5073</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -4635,6 +4740,9 @@
       <c r="AE36" s="8" t="n">
         <v>200</v>
       </c>
+      <c r="AF36" s="8" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -4661,16 +4769,16 @@
         <v>20</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>3240</v>
+        <v>3490</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -4743,6 +4851,9 @@
       </c>
       <c r="AE37" s="8" t="n">
         <v>283</v>
+      </c>
+      <c r="AF37" s="8" t="n">
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -7502,7 +7613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE54"/>
+  <dimension ref="A1:AF54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7536,6 +7647,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="11" customWidth="1" min="30" max="30"/>
     <col width="11" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7701,6 +7813,11 @@
           <t>10-28(三)</t>
         </is>
       </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>10-29(四)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -7727,25 +7844,25 @@
         <v>20</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>231</v>
+        <v>269</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="L3" s="7" t="n">
@@ -7810,6 +7927,9 @@
       <c r="AE3" s="8" t="n">
         <v>25</v>
       </c>
+      <c r="AF3" s="8" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -7836,25 +7956,25 @@
         <v>10</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="L4" s="7" t="n">
@@ -7919,21 +8039,24 @@
       <c r="AE4" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="AF4" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>0a8321fcl1ljahethcjq9qq42q3axjr8</t>
+          <t>0a83e824l1lbnte698jzx9rudh6mt9tj</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>锦文大道鲁能硅谷公馆站点A</t>
+          <t>南京市玄武区孝陵卫街道梅花谷路梅花谷公园</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>王兴星</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -7942,107 +8065,110 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>11</v>
       </c>
       <c r="H5" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="I5" s="3" t="n">
-        <v>355</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>58%</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>53%</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="N5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="U5" s="7" t="n">
-        <v>0</v>
+      <c r="T5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="V5" s="8" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="W5" s="8" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="X5" s="9" t="inlineStr">
         <is>
-          <t>44☂</t>
+          <t>0☂</t>
         </is>
       </c>
       <c r="Y5" s="8" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="Z5" s="8" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="AA5" s="8" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="AB5" s="8" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="AC5" s="8" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="AD5" s="8" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="AE5" s="8" t="n">
-        <v>22</v>
+        <v>20</v>
+      </c>
+      <c r="AF5" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>893732199694139392</t>
+          <t>0a8321fcl1ljahethcjq9qq42q3axjr8</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>东新南路瓯江大厦站点</t>
+          <t>锦文大道鲁能硅谷公馆站点A</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>李小凯</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -8051,35 +8177,35 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G6" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="I6" s="3" t="n">
-        <v>130</v>
+        <v>377</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="L6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M6" s="7" t="n">
-        <v>0</v>
+      <c r="M6" s="11" t="n">
+        <v>11</v>
       </c>
       <c r="N6" s="7" t="n">
         <v>0</v>
@@ -8087,8 +8213,8 @@
       <c r="O6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="11" t="n">
-        <v>2</v>
+      <c r="P6" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="Q6" s="7" t="n">
         <v>0</v>
@@ -8100,53 +8226,56 @@
         <v>0</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v>11</v>
+        <v>22</v>
+      </c>
+      <c r="U6" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="W6" s="8" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="X6" s="9" t="inlineStr">
         <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Y6" s="7" t="n">
-        <v>0</v>
+          <t>44☂</t>
+        </is>
+      </c>
+      <c r="Y6" s="8" t="n">
+        <v>22</v>
       </c>
       <c r="Z6" s="8" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="AA6" s="8" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="AB6" s="8" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="AC6" s="8" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="AD6" s="8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE6" s="8" t="n">
-        <v>11</v>
+        <v>22</v>
+      </c>
+      <c r="AF6" s="8" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>893715809572151296</t>
+          <t>893732199694139392</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>土山路华意泰富花苑站点A</t>
+          <t>东新南路瓯江大厦站点</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -8163,25 +8292,25 @@
         <v>10</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>11</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="L7" s="7" t="n">
@@ -8196,8 +8325,8 @@
       <c r="O7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P7" s="7" t="n">
-        <v>0</v>
+      <c r="P7" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="Q7" s="7" t="n">
         <v>0</v>
@@ -8205,14 +8334,14 @@
       <c r="R7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" s="8" t="n">
-        <v>12</v>
+      <c r="S7" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T7" s="8" t="n">
         <v>10</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V7" s="8" t="n">
         <v>12</v>
@@ -8222,45 +8351,48 @@
       </c>
       <c r="X7" s="9" t="inlineStr">
         <is>
-          <t>12☂</t>
+          <t>0☂</t>
         </is>
       </c>
       <c r="Y7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" s="8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AA7" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB7" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC7" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD7" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE7" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF7" s="8" t="n">
         <v>13</v>
-      </c>
-      <c r="AB7" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC7" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD7" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE7" s="8" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>0a83e824l1lbnte698jzx9rudh6mt9tj</t>
+          <t>893715809572151296</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>南京市玄武区孝陵卫街道梅花谷路梅花谷公园</t>
+          <t>土山路华意泰富花苑站点A</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>王兴星</t>
+          <t>李小凯</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -8272,25 +8404,25 @@
         <v>10</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="L8" s="7" t="n">
@@ -8315,45 +8447,48 @@
         <v>0</v>
       </c>
       <c r="S8" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="T8" s="8" t="n">
         <v>10</v>
-      </c>
-      <c r="T8" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="U8" s="8" t="n">
         <v>12</v>
       </c>
       <c r="V8" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W8" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X8" s="9" t="inlineStr">
         <is>
-          <t>0☂</t>
-        </is>
-      </c>
-      <c r="Y8" s="8" t="n">
-        <v>10</v>
+          <t>12☂</t>
+        </is>
+      </c>
+      <c r="Y8" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="Z8" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA8" s="8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AB8" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AC8" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AD8" s="8" t="n">
         <v>10</v>
       </c>
       <c r="AE8" s="8" t="n">
-        <v>20</v>
+        <v>14</v>
+      </c>
+      <c r="AF8" s="8" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -8381,25 +8516,25 @@
         <v>10</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>285</v>
+        <v>321</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="L9" s="8" t="n">
@@ -8464,6 +8599,9 @@
       <c r="AE9" s="8" t="n">
         <v>12</v>
       </c>
+      <c r="AF9" s="8" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -8490,25 +8628,25 @@
         <v>10</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="L10" s="8" t="n">
@@ -8573,6 +8711,9 @@
       <c r="AE10" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="AF10" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -8599,25 +8740,25 @@
         <v>20</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>274</v>
+        <v>310</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="L11" s="11" t="n">
@@ -8682,16 +8823,19 @@
       <c r="AE11" s="8" t="n">
         <v>36</v>
       </c>
+      <c r="AF11" s="8" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>0a8302d5l1lir2dxfqaeqgk2ktn2mjev</t>
+          <t>889935238642700288</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>高新-高校-金科北门2-全周-全天-30</t>
+          <t>南京市江宁区淳化街道博观路保利·梧桐语</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -8701,11 +8845,11 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>午峰</t>
+          <t>早峰</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>20</v>
@@ -8714,10 +8858,10 @@
         <v>15</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>446</v>
+        <v>266</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -8726,79 +8870,84 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>45%</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="M12" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="N12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="11" t="n">
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="O12" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="P12" s="8" t="n">
+      <c r="P12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="R12" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="S12" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="W12" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="X12" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y12" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z12" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="Q12" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="R12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="T12" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v>66</v>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="W12" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="X12" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="8" t="n">
-        <v>34</v>
-      </c>
       <c r="AA12" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB12" s="8" t="n">
-        <v>89</v>
-      </c>
-      <c r="AC12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="7" t="n">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="AB12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AD12" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="AE12" s="8" t="n">
-        <v>21</v>
+        <v>12</v>
+      </c>
+      <c r="AF12" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>889717813217533952</t>
+          <t>0a8302d5l1lir2dxfqaeqgk2ktn2mjev</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>高新-高校-交院东门-全周-全天-50</t>
+          <t>高新-高校-金科北门2-全周-全天-30</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -8808,148 +8957,149 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>早峰+午峰</t>
+          <t>午峰</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>946</v>
+        <v>467</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="L13" s="8" t="n">
-        <v>43</v>
-      </c>
-      <c r="M13" s="8" t="n">
-        <v>33</v>
+        <v>55</v>
+      </c>
+      <c r="M13" s="11" t="n">
+        <v>11</v>
       </c>
       <c r="N13" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="7" t="n">
-        <v>0</v>
+      <c r="O13" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="P13" s="8" t="n">
+        <v>25</v>
       </c>
       <c r="Q13" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="R13" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="S13" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v>86</v>
+      <c r="R13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="T13" s="11" t="n">
+        <v>11</v>
       </c>
       <c r="U13" s="8" t="n">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="V13" s="8" t="n">
-        <v>101</v>
+        <v>22</v>
       </c>
       <c r="W13" s="8" t="n">
-        <v>155</v>
-      </c>
-      <c r="X13" s="9" t="inlineStr">
-        <is>
-          <t>0☂</t>
-        </is>
+        <v>35</v>
+      </c>
+      <c r="X13" s="11" t="n">
+        <v>11</v>
       </c>
       <c r="Y13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Z13" s="8" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="AA13" s="8" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AB13" s="8" t="n">
-        <v>138</v>
-      </c>
-      <c r="AC13" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD13" s="8" t="n">
-        <v>33</v>
+        <v>89</v>
+      </c>
+      <c r="AC13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="AE13" s="8" t="n">
-        <v>32</v>
+        <v>21</v>
+      </c>
+      <c r="AF13" s="8" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>0a83d695l1lz6m3vbn8zbatt525u6cbu</t>
+          <t>889717813217533952</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>景明北大街站点B</t>
+          <t>高新-高校-交院东门-全周-全天-50</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>赵龙浩</t>
+          <t>李嘉烨</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>早峰</t>
+          <t>早峰+午峰</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
         <v>20</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>14</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>581</v>
+        <v>989</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>74%</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="7" t="n">
-        <v>0</v>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>33</v>
       </c>
       <c r="N14" s="7" t="n">
         <v>0</v>
@@ -8957,71 +9107,74 @@
       <c r="O14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P14" s="8" t="n">
+      <c r="P14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="R14" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="S14" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v>86</v>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v>95</v>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v>101</v>
+      </c>
+      <c r="W14" s="8" t="n">
+        <v>155</v>
+      </c>
+      <c r="X14" s="9" t="inlineStr">
+        <is>
+          <t>0☂</t>
+        </is>
+      </c>
+      <c r="Y14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA14" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="AB14" s="8" t="n">
+        <v>138</v>
+      </c>
+      <c r="AC14" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD14" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="AE14" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="Q14" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="R14" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="S14" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v>49</v>
-      </c>
-      <c r="W14" s="8" t="n">
-        <v>38</v>
-      </c>
-      <c r="X14" s="9" t="inlineStr">
-        <is>
-          <t>34☂</t>
-        </is>
-      </c>
-      <c r="Y14" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="Z14" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="AA14" s="8" t="n">
-        <v>49</v>
-      </c>
-      <c r="AB14" s="8" t="n">
-        <v>49</v>
-      </c>
-      <c r="AC14" s="8" t="n">
-        <v>51</v>
-      </c>
-      <c r="AD14" s="8" t="n">
-        <v>66</v>
-      </c>
-      <c r="AE14" s="8" t="n">
-        <v>42</v>
+      <c r="AF14" s="8" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>0a837fbbl1lcvvfvrrb6nbtsxdr5xk2w</t>
+          <t>0a83d695l1lz6m3vbn8zbatt525u6cbu</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>天元东路辅路南京义乌小商品城站点H</t>
+          <t>景明北大街站点B</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>李嘉烨</t>
+          <t>赵龙浩</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -9030,102 +9183,105 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G15" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H15" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H15" s="3" t="n">
-        <v>14</v>
-      </c>
       <c r="I15" s="3" t="n">
-        <v>316</v>
+        <v>625</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>74%</t>
-        </is>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>12</v>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="M15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N15" s="8" t="n">
+      <c r="N15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="O15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="8" t="n">
-        <v>24</v>
-      </c>
       <c r="Q15" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="R15" s="8" t="n">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="R15" s="11" t="n">
+        <v>6</v>
       </c>
       <c r="S15" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="T15" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="U15" s="7" t="n">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v>22</v>
       </c>
       <c r="V15" s="8" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="W15" s="8" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="X15" s="9" t="inlineStr">
         <is>
-          <t>24☂</t>
+          <t>34☂</t>
         </is>
       </c>
       <c r="Y15" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z15" s="7" t="n">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="Z15" s="8" t="n">
+        <v>33</v>
       </c>
       <c r="AA15" s="8" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="AB15" s="8" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="AC15" s="8" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="AD15" s="8" t="n">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="AE15" s="8" t="n">
-        <v>26</v>
+        <v>42</v>
+      </c>
+      <c r="AF15" s="8" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>889935238642700288</t>
+          <t>0a837fbbl1lcvvfvrrb6nbtsxdr5xk2w</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>南京市江宁区淳化街道博观路保利·梧桐语</t>
+          <t>天元东路辅路南京义乌小商品城站点H</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -9142,79 +9298,79 @@
         <v>10</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>15</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>266</v>
+        <v>328</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="n">
-        <v>0</v>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="M16" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="O16" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="P16" s="7" t="n">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="O16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="Q16" s="8" t="n">
         <v>12</v>
       </c>
       <c r="R16" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="S16" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="T16" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="S16" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v>21</v>
-      </c>
       <c r="W16" s="8" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="X16" s="9" t="inlineStr">
         <is>
-          <t>0☂</t>
+          <t>24☂</t>
         </is>
       </c>
       <c r="Y16" s="8" t="n">
-        <v>38</v>
-      </c>
-      <c r="Z16" s="8" t="n">
-        <v>25</v>
+        <v>12</v>
+      </c>
+      <c r="Z16" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="AA16" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AB16" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="AB16" s="8" t="n">
+        <v>36</v>
       </c>
       <c r="AC16" s="8" t="n">
         <v>36</v>
@@ -9223,6 +9379,9 @@
         <v>12</v>
       </c>
       <c r="AE16" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF16" s="8" t="n">
         <v>12</v>
       </c>
     </row>
@@ -9251,25 +9410,25 @@
         <v>10</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="L17" s="8" t="n">
@@ -9334,6 +9493,9 @@
       <c r="AE17" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="AF17" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -9360,25 +9522,25 @@
         <v>10</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="L18" s="8" t="n">
@@ -9443,6 +9605,9 @@
       <c r="AE18" s="8" t="n">
         <v>12</v>
       </c>
+      <c r="AF18" s="8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -9469,25 +9634,25 @@
         <v>10</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G19" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H19" s="3" t="n">
-        <v>15</v>
-      </c>
       <c r="I19" s="3" t="n">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="L19" s="8" t="n">
@@ -9552,6 +9717,9 @@
       <c r="AE19" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="AF19" s="8" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -9578,25 +9746,25 @@
         <v>10</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="L20" s="8" t="n">
@@ -9661,6 +9829,9 @@
       <c r="AE20" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="AF20" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -9687,25 +9858,25 @@
         <v>30</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>796</v>
+        <v>851</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="L21" s="7" t="n">
@@ -9768,6 +9939,9 @@
       <c r="AE21" s="8" t="n">
         <v>69</v>
       </c>
+      <c r="AF21" s="8" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -9794,25 +9968,25 @@
         <v>20</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>523</v>
+        <v>556</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="L22" s="11" t="n">
@@ -9875,6 +10049,9 @@
       <c r="AE22" s="8" t="n">
         <v>43</v>
       </c>
+      <c r="AF22" s="8" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -9901,25 +10078,25 @@
         <v>20</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>14</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>581</v>
+        <v>592</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="L23" s="8" t="n">
@@ -9984,6 +10161,9 @@
       <c r="AE23" s="8" t="n">
         <v>23</v>
       </c>
+      <c r="AF23" s="11" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -10010,25 +10190,25 @@
         <v>20</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>625</v>
+        <v>658</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L24" s="7" t="n">
@@ -10093,6 +10273,9 @@
       <c r="AE24" s="8" t="n">
         <v>39</v>
       </c>
+      <c r="AF24" s="8" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -10119,25 +10302,25 @@
         <v>20</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>693</v>
+        <v>726</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L25" s="11" t="n">
@@ -10202,6 +10385,9 @@
       <c r="AE25" s="8" t="n">
         <v>55</v>
       </c>
+      <c r="AF25" s="8" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -10228,25 +10414,25 @@
         <v>50</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>1219</v>
+        <v>1323</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="L26" s="7" t="n">
@@ -10311,6 +10497,9 @@
       <c r="AE26" s="8" t="n">
         <v>88</v>
       </c>
+      <c r="AF26" s="8" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -10337,25 +10526,25 @@
         <v>20</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1261</v>
+        <v>1359</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="L27" s="7" t="n">
@@ -10420,6 +10609,9 @@
       <c r="AE27" s="8" t="n">
         <v>76</v>
       </c>
+      <c r="AF27" s="8" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -10446,25 +10638,25 @@
         <v>10</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="L28" s="7" t="n">
@@ -10529,6 +10721,9 @@
       <c r="AE28" s="8" t="n">
         <v>13</v>
       </c>
+      <c r="AF28" s="8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -10555,25 +10750,25 @@
         <v>10</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="L29" s="8" t="n">
@@ -10638,6 +10833,9 @@
       <c r="AE29" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="AF29" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -10664,25 +10862,25 @@
         <v>10</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>521</v>
+        <v>531</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="L30" s="7" t="n">
@@ -10747,6 +10945,9 @@
       <c r="AE30" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="AF30" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -10773,25 +10974,25 @@
         <v>10</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>545</v>
+        <v>555</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="L31" s="8" t="n">
@@ -10856,6 +11057,9 @@
       <c r="AE31" s="8" t="n">
         <v>10</v>
       </c>
+      <c r="AF31" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -10882,16 +11086,16 @@
         <v>10</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -10963,6 +11167,9 @@
       <c r="AE32" s="8" t="n">
         <v>13</v>
       </c>
+      <c r="AF32" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -10989,16 +11196,16 @@
         <v>10</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -11070,6 +11277,9 @@
       <c r="AE33" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="AF33" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -11096,16 +11306,16 @@
         <v>10</v>
       </c>
       <c r="F34" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G34" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="H34" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H34" s="3" t="n">
-        <v>17</v>
-      </c>
       <c r="I34" s="3" t="n">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -11114,7 +11324,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="L34" s="8" t="n">
@@ -11179,6 +11389,9 @@
       <c r="AE34" s="8" t="n">
         <v>11</v>
       </c>
+      <c r="AF34" s="8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -11205,16 +11418,16 @@
         <v>10</v>
       </c>
       <c r="F35" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G35" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G35" s="3" t="n">
-        <v>18</v>
-      </c>
       <c r="H35" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>356</v>
+        <v>376</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -11288,6 +11501,9 @@
       <c r="AE35" s="8" t="n">
         <v>22</v>
       </c>
+      <c r="AF35" s="8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -11314,16 +11530,16 @@
         <v>10</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>777</v>
+        <v>799</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -11395,6 +11611,9 @@
       <c r="AE36" s="8" t="n">
         <v>49</v>
       </c>
+      <c r="AF36" s="8" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -11421,16 +11640,16 @@
         <v>10</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>509</v>
+        <v>546</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -11502,6 +11721,9 @@
       <c r="AE37" s="8" t="n">
         <v>64</v>
       </c>
+      <c r="AF37" s="8" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -11528,16 +11750,16 @@
         <v>10</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -11609,6 +11831,9 @@
       <c r="AE38" s="8" t="n">
         <v>25</v>
       </c>
+      <c r="AF38" s="8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -11635,16 +11860,16 @@
         <v>50</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1891</v>
+        <v>1989</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -11653,7 +11878,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="L39" s="8" t="n">
@@ -11718,6 +11943,9 @@
       <c r="AE39" s="8" t="n">
         <v>170</v>
       </c>
+      <c r="AF39" s="8" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -11744,16 +11972,16 @@
         <v>20</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>793</v>
+        <v>815</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -11762,7 +11990,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="L40" s="8" t="n">
@@ -11827,6 +12055,9 @@
       <c r="AE40" s="8" t="n">
         <v>22</v>
       </c>
+      <c r="AF40" s="8" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -11853,16 +12084,16 @@
         <v>30</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>1374</v>
+        <v>1418</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -11871,7 +12102,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="L41" s="8" t="n">
@@ -11936,6 +12167,9 @@
       <c r="AE41" s="8" t="n">
         <v>123</v>
       </c>
+      <c r="AF41" s="8" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -11962,16 +12196,16 @@
         <v>10</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>786</v>
+        <v>830</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -12047,6 +12281,9 @@
       <c r="AE42" s="8" t="n">
         <v>35</v>
       </c>
+      <c r="AF42" s="8" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -12073,16 +12310,16 @@
         <v>11</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>492</v>
+        <v>514</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -12158,6 +12395,9 @@
       <c r="AE43" s="8" t="n">
         <v>22</v>
       </c>
+      <c r="AF43" s="8" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -12184,16 +12424,16 @@
         <v>20</v>
       </c>
       <c r="F44" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H44" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G44" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>18</v>
-      </c>
       <c r="I44" s="3" t="n">
-        <v>2438</v>
+        <v>2468</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -12267,6 +12507,9 @@
       <c r="AE44" s="8" t="n">
         <v>60</v>
       </c>
+      <c r="AF44" s="8" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -12293,16 +12536,16 @@
         <v>30</v>
       </c>
       <c r="F45" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H45" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G45" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>18</v>
-      </c>
       <c r="I45" s="3" t="n">
-        <v>3784</v>
+        <v>3834</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -12376,6 +12619,9 @@
       <c r="AE45" s="8" t="n">
         <v>170</v>
       </c>
+      <c r="AF45" s="8" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -12402,16 +12648,16 @@
         <v>20</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>1013</v>
+        <v>1064</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -12485,6 +12731,9 @@
       <c r="AE46" s="8" t="n">
         <v>68</v>
       </c>
+      <c r="AF46" s="8" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -12511,16 +12760,16 @@
         <v>10</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>420</v>
+        <v>444</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -12594,6 +12843,9 @@
       <c r="AE47" s="8" t="n">
         <v>23</v>
       </c>
+      <c r="AF47" s="8" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -12620,16 +12872,16 @@
         <v>40</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2271</v>
+        <v>2414</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -12703,6 +12955,9 @@
       <c r="AE48" s="8" t="n">
         <v>113</v>
       </c>
+      <c r="AF48" s="8" t="n">
+        <v>143</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -12729,16 +12984,16 @@
         <v>10</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -12812,6 +13067,9 @@
       <c r="AE49" s="8" t="n">
         <v>36</v>
       </c>
+      <c r="AF49" s="8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -12838,16 +13096,16 @@
         <v>10</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>1084</v>
+        <v>1124</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -12921,6 +13179,9 @@
       <c r="AE50" s="8" t="n">
         <v>40</v>
       </c>
+      <c r="AF50" s="8" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -12947,16 +13208,16 @@
         <v>60</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>6211</v>
+        <v>6531</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -13030,6 +13291,9 @@
       <c r="AE51" s="8" t="n">
         <v>240</v>
       </c>
+      <c r="AF51" s="8" t="n">
+        <v>320</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -13056,16 +13320,16 @@
         <v>10</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>1164</v>
+        <v>1224</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -13139,6 +13403,9 @@
       <c r="AE52" s="8" t="n">
         <v>51</v>
       </c>
+      <c r="AF52" s="8" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -13165,16 +13432,16 @@
         <v>10</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>2844</v>
+        <v>2874</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -13248,6 +13515,9 @@
       <c r="AE53" s="8" t="n">
         <v>50</v>
       </c>
+      <c r="AF53" s="8" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -13274,16 +13544,16 @@
         <v>10</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>582</v>
+        <v>625</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -13356,6 +13626,9 @@
       </c>
       <c r="AE54" s="8" t="n">
         <v>50</v>
+      </c>
+      <c r="AF54" s="8" t="n">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -17082,25 +17355,25 @@
         <v>4</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>88.7%</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>88.3%</t>
         </is>
       </c>
     </row>
@@ -17117,25 +17390,25 @@
         <v>5</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>86.5%</t>
+          <t>86.1%</t>
         </is>
       </c>
     </row>
@@ -17152,20 +17425,20 @@
         <v>11</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -17187,25 +17460,25 @@
         <v>2</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>82.5%</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>82.5%</t>
         </is>
       </c>
     </row>
@@ -17222,10 +17495,10 @@
         <v>1</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>9</v>
@@ -17235,12 +17508,12 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>45.0%</t>
         </is>
       </c>
     </row>
@@ -17257,25 +17530,25 @@
         <v>2</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F8" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G8" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="G8" s="3" t="n">
-        <v>31</v>
-      </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>83.8%</t>
+          <t>84.6%</t>
         </is>
       </c>
     </row>
@@ -17292,20 +17565,20 @@
         <v>6</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -17730,25 +18003,25 @@
         <v>10</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>96.5%</t>
         </is>
       </c>
     </row>
@@ -17765,25 +18038,25 @@
         <v>12</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>80.1%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>65.4%</t>
         </is>
       </c>
     </row>
@@ -17800,25 +18073,25 @@
         <v>10</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>79.2%</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>77.7%</t>
         </is>
       </c>
     </row>
@@ -17835,20 +18108,20 @@
         <v>11</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -17870,25 +18143,25 @@
         <v>9</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>83.5%</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>73.1%</t>
         </is>
       </c>
     </row>
